--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -601,12 +601,14 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.995</v>
+        <v>0.708</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>0.29</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
@@ -626,7 +628,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -635,20 +637,17 @@
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>0.005</v>
-      </c>
       <c r="E3" s="4" t="n">
-        <v>0.991</v>
+        <v>0.019</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.004</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -658,20 +657,20 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.711</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="3" t="n">
-        <v>0.283</v>
+        <v>0.778</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
+        <v>0.216</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
@@ -687,7 +686,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -696,23 +695,23 @@
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0.001</v>
-      </c>
       <c r="G5" s="4" t="n">
-        <v>0.024</v>
+        <v>0.222</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.974</v>
+        <v>0.731</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.001</v>
+        <v>0.043</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -725,23 +724,29 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="H6" s="3" t="n">
+        <v>0.042</v>
+      </c>
       <c r="I6" s="3" t="n">
-        <v>0.457</v>
+        <v>0.575</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.248</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.042</v>
+        <v>0.108</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M6" s="2" t="n"/>
+        <v>0.024</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="P6" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -751,7 +756,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -761,34 +766,37 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.468</v>
+        <v>0.18</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.315</v>
+        <v>0.336</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.151</v>
+        <v>0.367</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.047</v>
+        <v>0.083</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0.002</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -801,46 +809,38 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="H8" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>0.037</v>
+        <v>0.194</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.095</v>
+        <v>0.347</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.321</v>
+        <v>0.329</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.226</v>
+        <v>0.081</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.137</v>
+        <v>0.027</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.094</v>
+        <v>0.008</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.039</v>
+        <v>0.007</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -855,74 +855,76 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.053</v>
+        <v>0.04</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.215</v>
+        <v>0.108</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.242</v>
+        <v>0.296</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0.18</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.114</v>
+        <v>0.122</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.053</v>
+        <v>0.091</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.024</v>
+        <v>0.039</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="3" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0.023</v>
-      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
@@ -931,175 +933,154 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9970000000000001</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0.013</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.131</v>
+        <v>0.037</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.18</v>
+        <v>0.153</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.162</v>
+        <v>0.14</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.103</v>
+        <v>0.211</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.076</v>
+        <v>0.171</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.056</v>
+        <v>0.12</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.093</v>
+        <v>0.136</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.131</v>
+        <v>0.16</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.145</v>
+        <v>0.149</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.158</v>
+        <v>0.182</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.105</v>
+        <v>0.125</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>0.014</v>
-      </c>
+        <v>0.004</v>
+      </c>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.01</v>
-      </c>
       <c r="K13" s="4" t="n">
-        <v>0.062</v>
+        <v>0.015</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.106</v>
+        <v>0.066</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.123</v>
+        <v>0.079</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.149</v>
+        <v>0.113</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.147</v>
+        <v>0.192</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.123</v>
+        <v>0.237</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.091</v>
+        <v>0.214</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.9590000000000001</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
@@ -1111,99 +1092,70 @@
         <v>0.001</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.061</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.121</v>
+        <v>0.15</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.128</v>
+        <v>0.231</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.163</v>
+        <v>0.305</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.123</v>
+        <v>0.108</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.1</v>
+        <v>0.014</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0.059</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9570000000000001</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="R15" s="4" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="S15" s="4" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="T15" s="4" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>0.054</v>
+        <v>0.9999999999999999</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.017</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9369999999999999</v>
+        <v>0.9930000000000001</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
@@ -1212,79 +1164,83 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
-      <c r="K16" s="3" t="n">
-        <v>0.008999999999999999</v>
-      </c>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>0.027</v>
+        <v>0.001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.063</v>
+        <v>0.007</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.081</v>
+        <v>0.022</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.103</v>
+        <v>0.06</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.143</v>
+        <v>0.168</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.173</v>
+        <v>0.532</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.907</v>
+        <v>0.877</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0.001</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>0.014</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.053</v>
+        <v>0.102</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.208</v>
+        <v>0.368</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.272</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.899</v>
+        <v>0.6619999999999999</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1293,51 +1249,39 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="3" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0.109</v>
-      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
       <c r="Q18" s="3" t="n">
-        <v>0.111</v>
+        <v>0.005</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.127</v>
+        <v>0.051</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.144</v>
+        <v>0.193</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.114</v>
+        <v>0.217</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.104</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.8440000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -1346,51 +1290,39 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="6" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0.075</v>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="6" t="n">
-        <v>0.093</v>
+        <v>0.002</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.147</v>
+        <v>0.023</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.127</v>
+        <v>0.229</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.165</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.214</v>
+        <v>0.593</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1400,82 +1332,63 @@
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
       <c r="Q20" s="3" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.029</v>
+        <v>0.139</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.047</v>
+        <v>0.201</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0.013</v>
+        <v>0.149</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.032</v>
+        <v>0.045</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.09899999999999999</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1488,70 +1401,48 @@
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
-      <c r="O22" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>0.012</v>
-      </c>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.035</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>0.008</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1568,42 +1459,45 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
-      <c r="S24" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
         <v>0.002</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0.001</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="2" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
@@ -1620,13 +1514,15 @@
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="n"/>
+      <c r="T26" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="U26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>averagemorningstarenjoyer</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1636,7 +1532,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>nnnekk</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1665,7 +1561,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SPQR</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1675,7 +1571,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1704,7 +1600,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1714,7 +1610,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1743,7 +1639,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ArutunyanArsen</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1753,7 +1649,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1782,7 +1678,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1792,7 +1688,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1821,7 +1717,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1831,7 +1727,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FISHer</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1860,7 +1756,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1870,7 +1766,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Акоп</t>
+          <t>nnnekk</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1899,7 +1795,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>бандэрос</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1909,7 +1805,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1938,7 +1834,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>averagemorningstarenjoyer</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1948,7 +1844,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Андрюха Пират</t>
+          <t>SPQR</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -1977,7 +1873,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1987,7 +1883,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2016,7 +1912,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Чейз</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2026,7 +1922,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2055,7 +1951,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2065,7 +1961,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>dialse</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2094,7 +1990,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jieb</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2104,7 +2000,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2133,7 +2029,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2143,7 +2039,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>ArutunyanArsen</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2172,7 +2068,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2182,7 +2078,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2211,7 +2107,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>FISHer</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2221,7 +2117,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>lavr</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2250,7 +2146,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2260,7 +2156,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2289,7 +2185,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Акоп</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2299,7 +2195,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Чейз</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2328,7 +2224,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>xairullah</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2338,7 +2234,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ЭтоМойНик</t>
+          <t>Андрюха Пират</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2367,7 +2263,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>бандэрос</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2377,7 +2273,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>jieb</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2406,7 +2302,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2416,7 +2312,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Отец Дмитрий</t>
+          <t>egoist</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -2445,7 +2341,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hachatur</t>
+          <t>aisel_gizatova</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2455,7 +2351,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>ЭтоМойНик</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -2484,7 +2380,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lilyokge</t>
+          <t>Afteromanov</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2494,7 +2390,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>desssai</t>
+          <t>Aronio</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -2523,7 +2419,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DmitryParf</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2562,7 +2458,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kykywka</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2572,7 +2468,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -2601,7 +2497,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>stimylenok</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2611,7 +2507,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>депаю_квартиру</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -2640,7 +2536,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mkrnnv</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2650,7 +2546,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -2679,7 +2575,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Danila158</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2689,7 +2585,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -2718,7 +2614,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>lilyokge</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2728,7 +2624,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>sushk0v_aa</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -2757,7 +2653,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2767,7 +2663,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -2796,7 +2692,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Me1man77</t>
+          <t>hachatur</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2806,7 +2702,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>maksim</t>
+          <t>kykywka</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -2835,7 +2731,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2874,7 +2770,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Korney</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2884,7 +2780,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -2913,7 +2809,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Влад MaJor Несмашный</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2923,7 +2819,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Отец Дмитрий</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -2952,7 +2848,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ташкент</t>
+          <t>maksim</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2962,7 +2858,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>DmitryParf</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -2991,7 +2887,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>lavr</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3001,7 +2897,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>desssai</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -3030,7 +2926,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Moпс</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3040,7 +2936,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Babken_barber</t>
+          <t>mkrnnv</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -3069,7 +2965,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>stimylenok</t>
         </is>
       </c>
       <c r="B101" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -601,10 +601,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.708</v>
+        <v>0.72</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.29</v>
+        <v>0.278</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0.002</v>
@@ -628,7 +628,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Я ненавижу покер v.2</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -637,17 +637,20 @@
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="D3" s="4" t="n">
+        <v>0.28</v>
+      </c>
       <c r="E3" s="4" t="n">
-        <v>0.019</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.981</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Я ненавижу покер v.2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -657,20 +660,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="3" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
@@ -686,7 +685,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -696,22 +695,19 @@
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.222</v>
+        <v>0.752</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.731</v>
+        <v>0.242</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -723,30 +719,24 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="3" t="n">
+        <v>0.244</v>
+      </c>
       <c r="H6" s="3" t="n">
-        <v>0.042</v>
+        <v>0.72</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.575</v>
+        <v>0.033</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
-      <c r="P6" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -756,7 +746,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -765,38 +755,35 @@
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="G7" s="4" t="n">
+        <v>0.003</v>
+      </c>
       <c r="H7" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.18</v>
+        <v>0.516</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.336</v>
+        <v>0.283</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.367</v>
+        <v>0.145</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.083</v>
+        <v>0.025</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -810,32 +797,30 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="3" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.194</v>
+        <v>0.218</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.347</v>
+        <v>0.343</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.027</v>
+        <v>0.015</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.005</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -845,7 +830,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -854,41 +839,41 @@
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="G9" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.007</v>
+      </c>
       <c r="I9" s="4" t="n">
-        <v>0.003</v>
+        <v>0.217</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.04</v>
+        <v>0.309</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.108</v>
+        <v>0.337</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.296</v>
+        <v>0.082</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.18</v>
+        <v>0.029</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.122</v>
+        <v>0.011</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.107</v>
+        <v>0.005</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -902,30 +887,36 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
+      <c r="I10" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.039</v>
+      </c>
       <c r="K10" s="3" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="R10" s="3" t="n">
         <v>0.005</v>
       </c>
-      <c r="L10" s="3" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n"/>
@@ -933,7 +924,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -942,37 +933,25 @@
       <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>0.01</v>
-      </c>
       <c r="K11" s="4" t="n">
-        <v>0.037</v>
+        <v>0.003</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.153</v>
+        <v>0.159</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.125</v>
+        <v>0.376</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.14</v>
+        <v>0.333</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.211</v>
+        <v>0.102</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.171</v>
+        <v>0.026</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T11" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -993,33 +972,35 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.024</v>
+        <v>0.034</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.136</v>
+        <v>0.149</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.16</v>
+        <v>0.145</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.174</v>
+        <v>0.189</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.182</v>
+        <v>0.173</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0.004</v>
@@ -1030,7 +1011,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1039,41 +1020,47 @@
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J13" s="4" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.066</v>
+        <v>0.118</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.079</v>
+        <v>0.122</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.113</v>
+        <v>0.147</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.192</v>
+        <v>0.204</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.237</v>
+        <v>0.189</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.214</v>
+        <v>0.137</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.074</v>
+        <v>0.038</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1087,62 +1074,93 @@
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J14" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T14" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="T14" s="3" t="n">
+      <c r="U14" s="3" t="n">
         <v>0.002</v>
       </c>
-      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9999999999999999</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.017</v>
+        <v>1</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="16">
@@ -1155,7 +1173,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9930000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
@@ -1169,31 +1187,31 @@
         <v>0.001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>0.007</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.06</v>
+        <v>0.049</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.168</v>
+        <v>0.147</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.532</v>
+        <v>0.454</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.126</v>
+        <v>0.195</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.049</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="17">
@@ -1206,41 +1224,44 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.877</v>
+        <v>0.7950000000000002</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.001</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.014</v>
+        <v>0.026</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.368</v>
+        <v>0.272</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.24</v>
+        <v>0.197</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.151</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.6619999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1253,35 +1274,37 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
+      <c r="O18" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="3" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.051</v>
+        <v>0.076</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.193</v>
+        <v>0.18</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.217</v>
+        <v>0.253</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.196</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.605</v>
+        <v>0.524</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -1297,32 +1320,32 @@
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="6" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.023</v>
+        <v>0.04</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.132</v>
+        <v>0.105</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.229</v>
+        <v>0.191</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.219</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.593</v>
+        <v>0.457</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1338,57 +1361,60 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="3" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.139</v>
+        <v>0.112</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.201</v>
+        <v>0.126</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.222</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.149</v>
+        <v>0.426</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0.003</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.004</v>
+        <v>0.027</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.016</v>
+        <v>0.096</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.045</v>
+        <v>0.13</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.09899999999999999</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1404,13 +1430,17 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
-      <c r="R22" s="2" t="n"/>
-      <c r="S22" s="2" t="n"/>
+      <c r="R22" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>0.006</v>
+      </c>
       <c r="T22" s="3" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.089</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="23">
@@ -1423,26 +1453,26 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1460,30 +1490,25 @@
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
-      <c r="T24" s="3" t="n">
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="3" t="n">
         <v>0.002</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>0.005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T25" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="26">
@@ -1495,9 +1520,7 @@
       <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
@@ -1514,9 +1537,7 @@
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T26" s="2" t="n"/>
       <c r="U26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -1639,7 +1660,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1649,7 +1670,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1756,7 +1777,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>nnnekk</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1766,7 +1787,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>nnnekk</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1883,7 +1904,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -1912,7 +1933,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1951,7 +1972,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1961,7 +1982,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>dialse</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -1990,7 +2011,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>dialse</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2000,7 +2021,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2029,7 +2050,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2068,7 +2089,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2078,7 +2099,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2146,7 +2167,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2156,7 +2177,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2234,7 +2255,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Андрюха Пират</t>
+          <t>бандэрос</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2263,7 +2284,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>бандэрос</t>
+          <t>Андрюха Пират</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2497,7 +2518,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2507,7 +2528,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -2585,7 +2606,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>lilyokge</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -2614,7 +2635,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lilyokge</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2624,7 +2645,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>sushk0v_aa</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -2663,7 +2684,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>sushk0v_aa</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -2731,7 +2752,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2741,7 +2762,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>vovaa_25</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -2770,7 +2791,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2780,7 +2801,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -2809,7 +2830,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Отец Дмитрий</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2819,7 +2840,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Отец Дмитрий</t>
+          <t>vovaa_25</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -2858,7 +2879,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>DmitryParf</t>
+          <t>desssai</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -2887,7 +2908,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>mkrnnv</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2897,7 +2918,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>desssai</t>
+          <t>xairullah</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -2926,7 +2947,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2936,7 +2957,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>mkrnnv</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -2965,7 +2986,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>stimylenok</t>
+          <t>DmitryParf</t>
         </is>
       </c>
       <c r="B101" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -601,13 +601,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.72</v>
+        <v>0.752</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.278</v>
+        <v>0.243</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
@@ -638,13 +638,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.28</v>
+        <v>0.246</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.726</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="4">
@@ -659,12 +659,14 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="E4" s="3" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.971</v>
+        <v>0.967</v>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
@@ -695,13 +697,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.752</v>
+        <v>0.782</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.242</v>
+        <v>0.215</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="6">
@@ -720,18 +722,20 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="3" t="n">
-        <v>0.244</v>
+        <v>0.216</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.72</v>
+        <v>0.748</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K6" s="2" t="n"/>
+        <v>0.001</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
@@ -756,34 +760,34 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>0.003</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="O7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -797,30 +801,32 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="3" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.218</v>
+        <v>0.193</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.343</v>
+        <v>0.328</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.078</v>
+        <v>0.103</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P8" s="2" t="n"/>
+        <v>0.005</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -830,7 +836,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -839,41 +845,44 @@
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="I9" s="4" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S9" s="4" t="n">
         <v>0.001</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0.002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -887,36 +896,28 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.039</v>
-      </c>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
       <c r="K10" s="3" t="n">
-        <v>0.103</v>
+        <v>0.003</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.287</v>
+        <v>0.134</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.167</v>
+        <v>0.352</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.138</v>
+        <v>0.326</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.129</v>
+        <v>0.155</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.005</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n"/>
@@ -924,7 +925,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -933,32 +934,47 @@
       <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="I11" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="K11" s="4" t="n">
-        <v>0.003</v>
+        <v>0.047</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.159</v>
+        <v>0.128</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.376</v>
+        <v>0.156</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.333</v>
+        <v>0.163</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.102</v>
+        <v>0.179</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.026</v>
+        <v>0.165</v>
       </c>
       <c r="Q11" s="4" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="T11" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -972,32 +988,30 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.149</v>
+        <v>0.117</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.145</v>
+        <v>0.148</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.148</v>
+        <v>0.157</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.189</v>
+        <v>0.174</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.173</v>
+        <v>0.178</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.111</v>
+        <v>0.146</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0.039</v>
@@ -1011,7 +1025,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1020,38 +1034,38 @@
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.011</v>
-      </c>
       <c r="K13" s="4" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.118</v>
+        <v>0.051</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.122</v>
+        <v>0.066</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.147</v>
+        <v>0.083</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.204</v>
+        <v>0.177</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.189</v>
+        <v>0.219</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.137</v>
+        <v>0.292</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.038</v>
+        <v>0.073</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.007</v>
+        <v>0.023</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0.002</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0.001</v>
@@ -1060,106 +1074,98 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="H14" s="3" t="n">
+        <v>0.003</v>
+      </c>
       <c r="I14" s="3" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O14" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>0.179</v>
-      </c>
       <c r="P14" s="3" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="T14" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1</v>
+        <v>0.999</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.001</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.035</v>
+        <v>0.067</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.057</v>
+        <v>0.077</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.08</v>
+        <v>0.118</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.163</v>
+        <v>0.166</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.244</v>
+        <v>0.251</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.294</v>
+        <v>0.24</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.102</v>
+        <v>0.053</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="U15" s="4" t="n">
         <v>0.002</v>
       </c>
     </row>
@@ -1173,7 +1179,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.981</v>
+        <v>0.9760000000000001</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
@@ -1183,35 +1189,33 @@
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="L16" s="2" t="n"/>
       <c r="M16" s="3" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.147</v>
+        <v>0.119</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.195</v>
+        <v>0.2</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.029</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="17">
@@ -1224,31 +1228,31 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7950000000000002</v>
+        <v>0.7889999999999999</v>
       </c>
       <c r="N17" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="O17" s="4" t="n">
-        <v>0.002</v>
-      </c>
       <c r="P17" s="4" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.026</v>
+        <v>0.018</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.132</v>
+        <v>0.129</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.272</v>
+        <v>0.235</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.197</v>
+        <v>0.222</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.159</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="18">
@@ -1261,7 +1265,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1274,24 +1278,24 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="3" t="n">
+        <v>0.006</v>
+      </c>
       <c r="Q18" s="3" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.076</v>
+        <v>0.09</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.18</v>
+        <v>0.205</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.253</v>
+        <v>0.213</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.212</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="19">
@@ -1304,7 +1308,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.524</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -1318,21 +1322,23 @@
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
+      <c r="P19" s="6" t="n">
+        <v>0.001</v>
+      </c>
       <c r="Q19" s="6" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.04</v>
+        <v>0.055</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.105</v>
+        <v>0.134</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.191</v>
+        <v>0.161</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.187</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="20">
@@ -1345,7 +1351,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.457</v>
+        <v>0.468</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1361,19 +1367,19 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="3" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.026</v>
+        <v>0.035</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.112</v>
+        <v>0.097</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.126</v>
+        <v>0.142</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.189</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="21">
@@ -1386,22 +1392,28 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.426</v>
+        <v>0.415</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0.001</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.096</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.13</v>
+        <v>0.138</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.17</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="22">
@@ -1414,7 +1426,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1434,38 +1446,38 @@
         <v>0.002</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>0.025</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>Mihmbox</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1498,29 +1510,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Mihmbox</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="2" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
@@ -1538,7 +1552,9 @@
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n"/>
-      <c r="U26" s="2" t="n"/>
+      <c r="U26" s="3" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1660,7 +1676,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1670,7 +1686,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1787,7 +1803,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>@TryFraiz</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1816,7 +1832,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>@TryFraiz</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1865,7 +1881,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SPQR</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -1894,7 +1910,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>SPQR</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1904,7 +1920,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -1933,7 +1949,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1972,7 +1988,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1982,7 +1998,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>dialse</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2011,7 +2027,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dialse</t>
+          <t>ArutunyanArsen</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2021,7 +2037,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2050,7 +2066,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2060,7 +2076,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ArutunyanArsen</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2099,7 +2115,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>FISHer</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2128,7 +2144,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FISHer</t>
+          <t>lavr</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2138,7 +2154,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>lavr</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2167,7 +2183,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2177,7 +2193,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>Акоп</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2206,7 +2222,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Акоп</t>
+          <t>Чейз</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2216,7 +2232,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Чейз</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2245,7 +2261,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Андрюха Пират</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2284,7 +2300,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Андрюха Пират</t>
+          <t>jieb</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2294,7 +2310,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>jieb</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2323,7 +2339,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>aisel_gizatova</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2333,7 +2349,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>egoist</t>
+          <t>ЭтоМойНик</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -2362,7 +2378,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>aisel_gizatova</t>
+          <t>egoist</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2372,7 +2388,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ЭтоМойНик</t>
+          <t>Afteromanov</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -2401,7 +2417,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Afteromanov</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2440,7 +2456,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2450,7 +2466,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -2489,7 +2505,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -2528,7 +2544,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -2557,7 +2573,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2567,7 +2583,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>Danila158</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -2596,7 +2612,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Danila158</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2635,7 +2651,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2674,7 +2690,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>sushk0v_aa</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2684,7 +2700,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>sushk0v_aa</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -2762,7 +2778,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -2791,7 +2807,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2801,7 +2817,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -2879,7 +2895,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>desssai</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -2908,7 +2924,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mkrnnv</t>
+          <t>desssai</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2918,7 +2934,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>xairullah</t>
+          <t>DmitryParf</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -2947,7 +2963,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>xairullah</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2957,7 +2973,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -2986,7 +3002,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DmitryParf</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="B101" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -601,14 +601,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.005</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
@@ -637,14 +633,8 @@
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>0.246</v>
-      </c>
       <c r="E3" s="4" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.028</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -659,14 +649,10 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.031</v>
-      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n">
-        <v>0.967</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
@@ -697,19 +683,19 @@
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.782</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.215</v>
+        <v>0.06</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -722,16 +708,16 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="3" t="n">
-        <v>0.216</v>
+        <v>0.059</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.748</v>
+        <v>0.715</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.034</v>
+        <v>0.189</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.001</v>
+        <v>0.036</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.001</v>
@@ -750,7 +736,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -763,31 +749,25 @@
         <v>0.002</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.032</v>
+        <v>0.165</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.556</v>
+        <v>0.435</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.259</v>
+        <v>0.323</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.125</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="M7" s="4" t="n">
         <v>0.003</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -801,32 +781,22 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="3" t="n">
-        <v>0.002</v>
+        <v>0.056</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.193</v>
+        <v>0.329</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.328</v>
+        <v>0.542</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.073</v>
+      </c>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -836,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -845,44 +815,35 @@
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="H9" s="4" t="n">
+        <v>0.004</v>
+      </c>
       <c r="I9" s="4" t="n">
-        <v>0.008</v>
+        <v>0.044</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.034</v>
+        <v>0.093</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.116</v>
+        <v>0.647</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.287</v>
+        <v>0.136</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.154</v>
+        <v>0.059</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.13</v>
+        <v>0.014</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -896,26 +857,28 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
+      <c r="I10" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.004</v>
+      </c>
       <c r="K10" s="3" t="n">
-        <v>0.003</v>
+        <v>0.091</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.134</v>
+        <v>0.447</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.352</v>
+        <v>0.359</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.326</v>
+        <v>0.092</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.006</v>
+      </c>
+      <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
@@ -925,7 +888,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -937,44 +900,35 @@
       <c r="I11" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0.118</v>
-      </c>
       <c r="R11" s="4" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -990,34 +944,34 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.032</v>
+        <v>0.042</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.117</v>
+        <v>0.157</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.148</v>
+        <v>0.235</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.157</v>
+        <v>0.325</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.174</v>
+        <v>0.155</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.178</v>
+        <v>0.061</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.146</v>
+        <v>0.016</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.039</v>
+        <v>0.006</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="T12" s="2" t="n"/>
       <c r="U12" s="2" t="n"/>
@@ -1025,7 +979,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1034,152 +988,129 @@
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0.012</v>
-      </c>
       <c r="L13" s="4" t="n">
-        <v>0.051</v>
+        <v>0.005</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.066</v>
+        <v>0.017</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.083</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.177</v>
+        <v>0.206</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.219</v>
+        <v>0.249</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.292</v>
+        <v>0.172</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.073</v>
+        <v>0.217</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.023</v>
+        <v>0.06</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="U13" s="4" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.091</v>
-      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="3" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.005</v>
+        <v>0.03</v>
       </c>
       <c r="O14" s="3" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T14" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="P14" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="I15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0.077</v>
-      </c>
       <c r="N15" s="4" t="n">
-        <v>0.118</v>
+        <v>0.032</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.166</v>
+        <v>0.075</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.251</v>
+        <v>0.178</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.24</v>
+        <v>0.271</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.053</v>
+        <v>0.382</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="T15" s="4" t="n">
-        <v>0.002</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9760000000000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
@@ -1188,84 +1119,86 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
+      <c r="K16" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.017</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>0.002</v>
+        <v>0.064</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.004</v>
+        <v>0.185</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.021</v>
+        <v>0.316</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.045</v>
+        <v>0.187</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.119</v>
+        <v>0.109</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.452</v>
+        <v>0.08</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.034</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>yakushevass</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7889999999999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.003</v>
+        <v>0.038</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.018</v>
+        <v>0.038</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.129</v>
+        <v>0.082</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.235</v>
+        <v>0.698</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.222</v>
+        <v>0.128</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.179</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>yakushevass</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.73</v>
+        <v>0.994</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1280,35 +1213,33 @@
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>0.014</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="Q18" s="2" t="n"/>
       <c r="R18" s="3" t="n">
-        <v>0.09</v>
+        <v>0.008</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.205</v>
+        <v>0.107</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.213</v>
+        <v>0.755</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.202</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.537</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -1325,33 +1256,29 @@
       <c r="P19" s="6" t="n">
         <v>0.001</v>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0.055</v>
-      </c>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
       <c r="S19" s="6" t="n">
-        <v>0.134</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.161</v>
+        <v>0.063</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.198</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.468</v>
+        <v>0.466</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1366,54 +1293,32 @@
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>0.035</v>
-      </c>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="3" t="n">
-        <v>0.097</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.142</v>
+        <v>0.05</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.191</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>0.138</v>
+        <v>0.003</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.148</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="22">
@@ -1425,9 +1330,7 @@
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>0.062</v>
-      </c>
+      <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
@@ -1442,18 +1345,10 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
-      <c r="R22" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>0.034</v>
-      </c>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1464,28 +1359,17 @@
       <c r="B23" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Amaney</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
@@ -1503,38 +1387,28 @@
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="n"/>
-      <c r="U24" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="U24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Amaney</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
@@ -1552,14 +1426,12 @@
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n"/>
-      <c r="U26" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="U26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1598,7 +1470,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>finch79</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1608,7 +1480,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>EliasPavlov</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1637,7 +1509,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>finch79</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1647,7 +1519,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1676,7 +1548,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EliasPavlov</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1686,7 +1558,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1715,7 +1587,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1725,7 +1597,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1754,7 +1626,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1764,7 +1636,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1793,7 +1665,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nnnekk</t>
+          <t>Дядя Витя</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1803,7 +1675,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1842,7 +1714,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>dama_pica</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1871,7 +1743,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>averagemorningstarenjoyer</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1881,7 +1753,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -1910,7 +1782,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SPQR</t>
+          <t>Тихоня</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1920,7 +1792,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>dama_pica</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -1949,7 +1821,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Дядя Витя</t>
+          <t>АРАМАИСКА</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1959,7 +1831,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>АРАМАИСКА</t>
+          <t>yankkk</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -1988,7 +1860,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Тихоня</t>
+          <t>nnnekk</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1998,7 +1870,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>dialse</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2027,7 +1899,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ArutunyanArsen</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2037,7 +1909,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>Добряк</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2066,7 +1938,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2076,7 +1948,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2105,7 +1977,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yankkk</t>
+          <t>averagemorningstarenjoyer</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2115,7 +1987,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FISHer</t>
+          <t>Кесадилия</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2144,7 +2016,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>lavr</t>
+          <t>бандэрос</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2154,7 +2026,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Добряк</t>
+          <t>lavr</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2183,7 +2055,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2193,7 +2065,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Акоп</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2222,7 +2094,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Чейз</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2232,7 +2104,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2261,7 +2133,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Андрюха Пират</t>
+          <t>ЭтоМойНик</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2271,7 +2143,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>бандэрос</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2300,7 +2172,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jieb</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2310,7 +2182,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>Чейз</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2339,7 +2211,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>aisel_gizatova</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2349,7 +2221,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ЭтоМойНик</t>
+          <t>dialse</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -2378,7 +2250,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>egoist</t>
+          <t>SPQR</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2388,7 +2260,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Afteromanov</t>
+          <t>ArutunyanArsen</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -2417,7 +2289,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>jieb</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2456,7 +2328,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2466,7 +2338,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Акоп</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -2495,7 +2367,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>aisel_gizatova</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2505,7 +2377,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -2534,7 +2406,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Кесадилия</t>
+          <t>Afteromanov</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2544,7 +2416,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>Андрюха Пират</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -2573,7 +2445,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>lilyokge</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2583,7 +2455,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Danila158</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -2612,7 +2484,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>Отец Дмитрий</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2622,7 +2494,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>lilyokge</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -2651,7 +2523,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2661,7 +2533,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -2690,7 +2562,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sushk0v_aa</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2700,7 +2572,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>Danila158</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -2729,7 +2601,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hachatur</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2739,7 +2611,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>kykywka</t>
+          <t>Пупупу</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -2768,7 +2640,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>egoist</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2778,7 +2650,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>vovaa_25</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -2807,7 +2679,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>maksim</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2817,7 +2689,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>hachatur</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -2846,7 +2718,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Отец Дмитрий</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2856,7 +2728,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>vovaa_25</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -2885,7 +2757,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>maksim</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2895,7 +2767,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>ceocench23</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -2924,7 +2796,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>desssai</t>
+          <t>Кадык</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2934,7 +2806,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>DmitryParf</t>
+          <t>LateNightCraver</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -2963,7 +2835,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>xairullah</t>
+          <t>sushk0v_aa</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2973,7 +2845,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>kykywka</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -3002,7 +2874,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>xairullah</t>
         </is>
       </c>
       <c r="B101" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -598,59 +598,57 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.18</v>
+        <v>0.155</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.144</v>
+        <v>0.141</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.105</v>
+        <v>0.121</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.092</v>
+        <v>0.095</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.081</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.064</v>
+        <v>0.077</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.048</v>
+        <v>0.073</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="P2" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="Q2" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="R2" s="3" t="n">
         <v>0.007</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>0.004</v>
       </c>
-      <c r="S2" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -663,55 +661,61 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.164</v>
+        <v>0.141</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.124</v>
+        <v>0.137</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.123</v>
+        <v>0.102</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.093</v>
+        <v>0.098</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.068</v>
+        <v>0.073</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.043</v>
+        <v>0.059</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="R3" s="4" t="n">
         <v>0.007</v>
       </c>
       <c r="S3" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T3" s="4" t="n">
         <v>0.003</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
@@ -724,46 +728,46 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.126</v>
+        <v>0.134</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.106</v>
+        <v>0.097</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.098</v>
+        <v>0.081</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.094</v>
+        <v>0.102</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.066</v>
+        <v>0.081</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.053</v>
+        <v>0.063</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0.038</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.039</v>
+        <v>0.026</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0.007</v>
@@ -772,12 +776,12 @@
         <v>0.004</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.003</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -789,122 +793,122 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.097</v>
+        <v>0.094</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.097</v>
+        <v>0.118</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0.095</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0.095</v>
-      </c>
       <c r="J5" s="4" t="n">
-        <v>0.082</v>
+        <v>0.064</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.083</v>
+        <v>0.061</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.055</v>
+        <v>0.066</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>0.092</v>
-      </c>
       <c r="F6" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.078</v>
-      </c>
       <c r="J6" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.077</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.055</v>
+        <v>0.068</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.048</v>
+        <v>0.057</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.058</v>
+        <v>0.038</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="S6" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>0.003</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0.004</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0.002</v>
@@ -913,465 +917,470 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>0.065</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.068</v>
-      </c>
       <c r="N7" s="4" t="n">
-        <v>0.068</v>
+        <v>0.055</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.017</v>
+        <v>0.027</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.047</v>
+        <v>0.055</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.065</v>
+        <v>0.057</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
       <c r="G8" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>0.08</v>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="J8" s="3" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>0.077</v>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
       <c r="L8" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.076</v>
+        <v>0.063</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="T8" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>0.003</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>0.002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1</v>
+        <v>0.298</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.052</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.062</v>
+        <v>0.074</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H9" s="4" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>0.073</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>0.075</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0.09</v>
-      </c>
       <c r="M9" s="4" t="n">
-        <v>0.101</v>
+        <v>0.079</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.057</v>
+        <v>0.047</v>
       </c>
       <c r="Q9" s="4" t="n">
         <v>0.035</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.298</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.056</v>
+        <v>0.067</v>
       </c>
       <c r="G10" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>0.089</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="J10" s="3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>0.077</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0.07099999999999999</v>
-      </c>
       <c r="N10" s="3" t="n">
-        <v>0.076</v>
+        <v>0.066</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.053</v>
+        <v>0.068</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.024</v>
+        <v>0.042</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U10" s="2" t="n"/>
+        <v>0.01</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.999</v>
+        <v>0.297702</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>0.048</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.061</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.058</v>
+        <v>0.068</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="I11" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>0.082</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="N11" s="4" t="n">
-        <v>0.09</v>
+        <v>0.062</v>
       </c>
       <c r="O11" s="4" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="P11" s="4" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="P11" s="4" t="n">
-        <v>0.042</v>
-      </c>
       <c r="Q11" s="4" t="n">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.005</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.9980000000000001</v>
+        <v>0.2974040000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.044</v>
+        <v>0.041</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.061</v>
+        <v>0.046</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.068</v>
+        <v>0.064</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.08</v>
-      </c>
       <c r="N12" s="3" t="n">
-        <v>0.079</v>
+        <v>0.097</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0.075</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.075</v>
+        <v>0.048</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="R12" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>0.015</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>0.012</v>
-      </c>
       <c r="T12" s="3" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.998</v>
+        <v>0.2971060000000001</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.053</v>
+        <v>0.057</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.08</v>
+        <v>0.067</v>
       </c>
       <c r="H13" s="4" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="J13" s="4" t="n">
         <v>0.077</v>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0.079</v>
-      </c>
       <c r="K13" s="4" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="L13" s="4" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>0.08699999999999999</v>
-      </c>
       <c r="N13" s="4" t="n">
-        <v>0.063</v>
+        <v>0.093</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>0.067</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.028</v>
+        <v>0.036</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
@@ -1384,59 +1393,61 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.9159999999999999</v>
+        <v>0.272372</v>
       </c>
       <c r="D14" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>0.002</v>
       </c>
-      <c r="E14" s="2" t="n"/>
       <c r="F14" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>0.003</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.004</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.007</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.049</v>
+        <v>0.028</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.119</v>
+        <v>0.109</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.111</v>
+        <v>0.107</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.097</v>
+        <v>0.094</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.096</v>
+        <v>0.108</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.068</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1449,182 +1460,174 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.876</v>
+        <v>0.262538</v>
       </c>
       <c r="E15" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>0.001</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.004</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>0.004</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.058</v>
+        <v>0.082</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.099</v>
+        <v>0.094</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.108</v>
+        <v>0.103</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.099</v>
+        <v>0.109</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.109</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.8519999999999999</v>
+        <v>0.2577700000000001</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="3" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.004</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>0.015</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.044</v>
+        <v>0.037</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.066</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.12</v>
+        <v>0.117</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.115</v>
+        <v>0.106</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.105</v>
+        <v>0.109</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.09</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.833</v>
+        <v>0.255386</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.018</v>
+        <v>0.032</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.035</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.046</v>
+        <v>0.059</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="Q17" s="4" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="U17" s="4" t="n">
         <v>0.099</v>
-      </c>
-      <c r="R17" s="4" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="18">
@@ -1637,55 +1640,55 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.8039999999999999</v>
+        <v>0.246744</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="F18" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.004</v>
-      </c>
       <c r="J18" s="3" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.04</v>
+        <v>0.051</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.076</v>
+        <v>0.056</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.098</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.091</v>
+        <v>0.102</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.105</v>
+        <v>0.125</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.133</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="19">
@@ -1698,7 +1701,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.799</v>
+        <v>0.22648</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="6" t="n">
@@ -1707,46 +1710,46 @@
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K19" s="6" t="n">
         <v>0.002</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0.001</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>0.008</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.029</v>
+        <v>0.021</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.127</v>
+        <v>0.118</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.115</v>
+        <v>0.093</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.101</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="20">
@@ -1759,53 +1762,57 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
+        <v>0.21903</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="3" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.023</v>
+        <v>0.033</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.042</v>
+        <v>0.047</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.089</v>
+        <v>0.093</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.099</v>
+        <v>0.09</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.131</v>
+        <v>0.118</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.127</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="21">
@@ -1818,49 +1825,40 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0.002</v>
+        <v>0.1937</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.018</v>
+        <v>0.026</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.079</v>
+        <v>0.057</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.082</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.131</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="22">
@@ -1873,7 +1871,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.398</v>
+        <v>0.118902</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1881,39 +1879,37 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L22" s="2" t="n"/>
       <c r="M22" s="3" t="n">
         <v>0.003</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.044</v>
+        <v>0.051</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1926,35 +1922,35 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>0.002</v>
+        <v>0.09917080405271408</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0.005942641661835695</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.001</v>
+        <v>0.005942641661835695</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.005</v>
+        <v>0.02377056664734278</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.002</v>
+        <v>0.02971320830917848</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.014</v>
+        <v>0.08913962492753542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.025</v>
+        <v>0.09652633751593225</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1968,37 +1964,46 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
+      <c r="P24" s="3" t="n">
+        <v>0.01245822631852507</v>
+      </c>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S24" s="2" t="n"/>
-      <c r="T24" s="2" t="n"/>
+        <v>0.01245822631852507</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>0.01245822631852507</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>0.0373746789555752</v>
+      </c>
       <c r="U24" s="3" t="n">
-        <v>0.007</v>
+        <v>0.07474935791115041</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.023</v>
+        <v>0.09390580362346135</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.002</v>
+        <v>0.01432364301761155</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.001</v>
+        <v>0.01432364301761155</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0.01432364301761155</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.004</v>
+        <v>0.07161821508805777</v>
       </c>
     </row>
     <row r="26">
@@ -2011,7 +2016,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.007</v>
+        <v>0.09130942297598842</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
@@ -2029,36 +2034,39 @@
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="T26" s="2" t="n"/>
       <c r="U26" s="3" t="n">
-        <v>0.003</v>
+        <v>0.1021358198836559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.001</v>
+        <v>0.08873742238943043</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0.1488882925997155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="2" t="n"/>
+      <c r="C28" s="3" t="n">
+        <v>0.08619003519239145</v>
+      </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
@@ -2076,7 +2084,9 @@
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="n"/>
-      <c r="U28" s="2" t="n"/>
+      <c r="U28" s="3" t="n">
+        <v>0.1446141530073682</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2087,6 +2097,9 @@
       <c r="B29" t="n">
         <v>28</v>
       </c>
+      <c r="C29" s="4" t="n">
+        <v>0.08366750154394066</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2097,7 +2110,9 @@
       <c r="B30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="3" t="n">
+        <v>0.08117006877353256</v>
+      </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
@@ -2126,6 +2141,9 @@
       <c r="B31" t="n">
         <v>30</v>
       </c>
+      <c r="C31" s="4" t="n">
+        <v>0.07869799174509248</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2136,7 +2154,9 @@
       <c r="B32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>0.07625153324752322</v>
+      </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
@@ -2165,6 +2185,9 @@
       <c r="B33" t="n">
         <v>32</v>
       </c>
+      <c r="C33" s="4" t="n">
+        <v>0.0738309644141493</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2175,7 +2198,9 @@
       <c r="B34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>0.07143656517391686</v>
+      </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
@@ -2204,17 +2229,22 @@
       <c r="B35" t="n">
         <v>34</v>
       </c>
+      <c r="C35" s="4" t="n">
+        <v>0.06906862473750806</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>0.06672744212192308</v>
+      </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
@@ -2237,23 +2267,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
+      <c r="C37" s="4" t="n">
+        <v>0.06441332671753436</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>0.06212659890213935</v>
+      </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
@@ -2282,17 +2317,22 @@
       <c r="B39" t="n">
         <v>38</v>
       </c>
+      <c r="C39" s="4" t="n">
+        <v>0.05986759070714237</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="C40" s="2" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>0.05763664654169758</v>
+      </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
@@ -2315,23 +2355,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
+      <c r="C41" s="4" t="n">
+        <v>0.05543412398146273</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="2" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>0.05326039462957088</v>
+      </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
@@ -2360,6 +2405,9 @@
       <c r="B43" t="n">
         <v>42</v>
       </c>
+      <c r="C43" s="4" t="n">
+        <v>0.0511158450585511</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2370,7 +2418,9 @@
       <c r="B44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>0.04900087784325523</v>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -2399,6 +2449,9 @@
       <c r="B45" t="n">
         <v>44</v>
       </c>
+      <c r="C45" s="4" t="n">
+        <v>0.04691591269641866</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2409,7 +2462,9 @@
       <c r="B46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="2" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>0.04486138772035221</v>
+      </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
@@ -2438,6 +2493,9 @@
       <c r="B47" t="n">
         <v>46</v>
       </c>
+      <c r="C47" s="4" t="n">
+        <v>0.04283776079049762</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2448,7 +2506,9 @@
       <c r="B48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="C48" s="2" t="n"/>
+      <c r="C48" s="3" t="n">
+        <v>0.04084551108926481</v>
+      </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
@@ -2477,6 +2537,9 @@
       <c r="B49" t="n">
         <v>48</v>
       </c>
+      <c r="C49" s="4" t="n">
+        <v>0.03888514081181586</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2487,7 +2550,9 @@
       <c r="B50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="2" t="n"/>
+      <c r="C50" s="3" t="n">
+        <v>0.03695717706940388</v>
+      </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="n"/>
@@ -2516,6 +2581,9 @@
       <c r="B51" t="n">
         <v>50</v>
       </c>
+      <c r="C51" s="4" t="n">
+        <v>0.03506217402069824</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2526,7 +2594,9 @@
       <c r="B52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="2" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>0.03320071526746089</v>
+      </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n"/>
@@ -2549,23 +2619,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>52</v>
       </c>
+      <c r="C53" s="4" t="n">
+        <v>0.03137341655829062</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="2" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>0.02958092885332818</v>
+      </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n"/>
@@ -2594,6 +2669,9 @@
       <c r="B55" t="n">
         <v>54</v>
       </c>
+      <c r="C55" s="4" t="n">
+        <v>0.02782394181435892</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2604,7 +2682,9 @@
       <c r="B56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="2" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>0.02610318779939383</v>
+      </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
       <c r="F56" s="2" t="n"/>
@@ -2633,6 +2713,9 @@
       <c r="B57" t="n">
         <v>56</v>
       </c>
+      <c r="C57" s="4" t="n">
+        <v>0.02441944645956044</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2643,7 +2726,9 @@
       <c r="B58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="2" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>0.02277355006037658</v>
+      </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="n"/>
@@ -2672,6 +2757,9 @@
       <c r="B59" t="n">
         <v>58</v>
       </c>
+      <c r="C59" s="4" t="n">
+        <v>0.02116638968116055</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2682,7 +2770,9 @@
       <c r="B60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="C60" s="2" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>0.01959892248821406</v>
+      </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n"/>
@@ -2711,6 +2801,9 @@
       <c r="B61" t="n">
         <v>60</v>
       </c>
+      <c r="C61" s="4" t="n">
+        <v>0.01807218033349118</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2721,7 +2814,9 @@
       <c r="B62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="2" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v>0.01658728000659684</v>
+      </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n"/>
@@ -2750,6 +2845,9 @@
       <c r="B63" t="n">
         <v>62</v>
       </c>
+      <c r="C63" s="4" t="n">
+        <v>0.01514543557290403</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2760,7 +2858,9 @@
       <c r="B64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="2" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v>0.01374797337771438</v>
+      </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n"/>
@@ -2789,6 +2889,9 @@
       <c r="B65" t="n">
         <v>64</v>
       </c>
+      <c r="C65" s="4" t="n">
+        <v>0.01239635050658926</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2799,7 +2902,9 @@
       <c r="B66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="2" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>0.0110921777986788</v>
+      </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
@@ -2828,17 +2933,22 @@
       <c r="B67" t="n">
         <v>66</v>
       </c>
+      <c r="C67" s="4" t="n">
+        <v>0.00983724896813656</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="2" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>0.008633578092188508</v>
+      </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n"/>
@@ -2861,23 +2971,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>68</v>
       </c>
+      <c r="C69" s="4" t="n">
+        <v>0.007483448838392796</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="2" t="n"/>
+      <c r="C70" s="3" t="n">
+        <v>0.006389480632318888</v>
+      </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n"/>
@@ -2900,23 +3015,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>70</v>
       </c>
+      <c r="C71" s="4" t="n">
+        <v>0.005354720098812203</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="C72" s="2" t="n"/>
+      <c r="C72" s="3" t="n">
+        <v>0.00438277175258728</v>
+      </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n"/>
@@ -2939,23 +3059,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>72</v>
       </c>
+      <c r="C73" s="4" t="n">
+        <v>0.003477992726794865</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="2" t="n"/>
+      <c r="C74" s="3" t="n">
+        <v>0.002645798710145069</v>
+      </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="n"/>
@@ -2978,23 +3103,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>74</v>
       </c>
+      <c r="C75" s="4" t="n">
+        <v>0.001893179446613004</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="C76" s="2" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>0.00122965612101707</v>
+      </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="n"/>
@@ -3017,17 +3147,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>76</v>
       </c>
+      <c r="C77" s="4" t="n">
+        <v>0.0006693400123515253</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -601,54 +601,56 @@
         <v>0.298</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.155</v>
+        <v>0.04708400000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.141</v>
+        <v>0.03963400000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.121</v>
+        <v>0.033376</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.095</v>
+        <v>0.03129000000000001</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.081</v>
+        <v>0.02801200000000001</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.081</v>
+        <v>0.02473400000000001</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.077</v>
+        <v>0.021754</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.073</v>
+        <v>0.016986</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.057</v>
+        <v>0.012218</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.037</v>
+        <v>0.015496</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.03</v>
+        <v>0.009834000000000002</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.017</v>
+        <v>0.007450000000000002</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.014</v>
+        <v>0.003874</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.01</v>
+        <v>0.004172</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.007</v>
+        <v>0.00149</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T2" s="2" t="n"/>
+        <v>0.000298</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0.000298</v>
+      </c>
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -664,58 +666,55 @@
         <v>0.298</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.141</v>
+        <v>0.045594</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.137</v>
+        <v>0.038144</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.102</v>
+        <v>0.03278</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.098</v>
+        <v>0.029204</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.097</v>
+        <v>0.026224</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.021754</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.073</v>
+        <v>0.019966</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.063</v>
+        <v>0.021456</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.058</v>
+        <v>0.018774</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.059</v>
+        <v>0.013112</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.037</v>
+        <v>0.013708</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.029</v>
+        <v>0.007450000000000002</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.02</v>
+        <v>0.004470000000000001</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.004</v>
+        <v>0.002086</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.007</v>
+        <v>0.002384</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.001</v>
+        <v>0.000298</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0005960000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -731,57 +730,57 @@
         <v>0.298</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.134</v>
+        <v>0.04678600000000001</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.113</v>
+        <v>0.03456800000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.097</v>
+        <v>0.029502</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.091</v>
+        <v>0.02503200000000001</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.081</v>
+        <v>0.021158</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.102</v>
+        <v>0.027118</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.027118</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.081</v>
+        <v>0.021456</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.018774</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.063</v>
+        <v>0.015496</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.038</v>
+        <v>0.011622</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.026</v>
+        <v>0.007152000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.017</v>
+        <v>0.004172</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.007</v>
+        <v>0.002682</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.004</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U4" s="2" t="n"/>
+        <v>0.0005960000000000001</v>
+      </c>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="3" t="n">
+        <v>0.001192</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -796,61 +795,64 @@
         <v>0.298</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.094</v>
+        <v>0.03009800000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.118</v>
+        <v>0.03009800000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.095</v>
+        <v>0.03278</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.096</v>
+        <v>0.027416</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.026522</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.022648</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.064</v>
+        <v>0.02235</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.061</v>
+        <v>0.016688</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.022946</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.066</v>
+        <v>0.017582</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.057</v>
+        <v>0.01639</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.037</v>
+        <v>0.012516</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.027</v>
+        <v>0.010132</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.017</v>
+        <v>0.003278</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.014</v>
+        <v>0.003278</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.002</v>
+        <v>0.002086</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.008</v>
+        <v>0.0005960000000000001</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0.000298</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -860,64 +862,64 @@
         <v>0.298</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.099</v>
+        <v>0.02235</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.075</v>
+        <v>0.023542</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1</v>
+        <v>0.029502</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.073</v>
+        <v>0.02384</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.09</v>
+        <v>0.029204</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.02831000000000001</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.082</v>
+        <v>0.021158</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.075</v>
+        <v>0.018774</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.019966</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.068</v>
+        <v>0.021158</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.057</v>
+        <v>0.020562</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.038</v>
+        <v>0.016986</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.039</v>
+        <v>0.009238000000000001</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.023</v>
+        <v>0.006556</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.011</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.006</v>
+        <v>0.00149</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.003</v>
+        <v>0.0005960000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.002</v>
+        <v>0.001192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -927,58 +929,58 @@
         <v>0.298</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.077</v>
+        <v>0.01341</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.073</v>
+        <v>0.015794</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.083</v>
+        <v>0.019966</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.096</v>
+        <v>0.02086</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.079</v>
+        <v>0.02682</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.08</v>
+        <v>0.022648</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.08</v>
+        <v>0.022946</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.098</v>
+        <v>0.022648</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.068</v>
+        <v>0.026522</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.065</v>
+        <v>0.023244</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.055</v>
+        <v>0.01788</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.058</v>
+        <v>0.022052</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.035</v>
+        <v>0.016986</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.027</v>
+        <v>0.011622</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.014</v>
+        <v>0.005066000000000001</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.005</v>
+        <v>0.004172</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.005</v>
+        <v>0.00298</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.002</v>
+        <v>0.002086</v>
       </c>
     </row>
     <row r="8">
@@ -991,268 +993,268 @@
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.298</v>
+        <v>0.2977020000000001</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.055</v>
+        <v>0.018774</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.057</v>
+        <v>0.020264</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.074</v>
+        <v>0.020264</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.027118</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.02235</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.08</v>
+        <v>0.023542</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.021456</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.077</v>
+        <v>0.022946</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.02682</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.022946</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.063</v>
+        <v>0.022052</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.014006</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.039</v>
+        <v>0.0149</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.025</v>
+        <v>0.008046000000000001</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.02</v>
+        <v>0.004172</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.012</v>
+        <v>0.003278</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.006</v>
+        <v>0.002682</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.003</v>
+        <v>0.002086</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.298</v>
+        <v>0.2977020000000001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.046</v>
+        <v>0.013708</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.019966</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.074</v>
+        <v>0.01937</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.083</v>
+        <v>0.021754</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.079</v>
+        <v>0.022946</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.074</v>
+        <v>0.021158</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.023244</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.073</v>
+        <v>0.021158</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.075</v>
+        <v>0.02473400000000001</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.079</v>
+        <v>0.027118</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.021158</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.055</v>
+        <v>0.025628</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.047</v>
+        <v>0.014602</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.035</v>
+        <v>0.007152000000000001</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.017</v>
+        <v>0.006854000000000001</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.01</v>
+        <v>0.004470000000000001</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.007</v>
+        <v>0.001788</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.002</v>
+        <v>0.0005960000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.298</v>
+        <v>0.297702</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.051</v>
+        <v>0.011324</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.057</v>
+        <v>0.016688</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.067</v>
+        <v>0.019072</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.075</v>
+        <v>0.021754</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.083</v>
+        <v>0.024138</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.089</v>
+        <v>0.022052</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.081</v>
+        <v>0.02473400000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.076</v>
+        <v>0.023244</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.073</v>
+        <v>0.027714</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.077</v>
+        <v>0.02384</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.066</v>
+        <v>0.027118</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.068</v>
+        <v>0.019668</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.044</v>
+        <v>0.014304</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.042</v>
+        <v>0.011622</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.019</v>
+        <v>0.004172</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.018</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0.01</v>
+        <v>0.00149</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.002</v>
+        <v>0.0008940000000000002</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.297702</v>
+        <v>0.2974040000000001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.048</v>
+        <v>0.02235</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.055</v>
+        <v>0.02384</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.025926</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.068</v>
+        <v>0.02384</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.075</v>
+        <v>0.022052</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.08</v>
+        <v>0.028608</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.073</v>
+        <v>0.024436</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.081</v>
+        <v>0.031886</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.021158</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.082</v>
+        <v>0.01937</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.062</v>
+        <v>0.016092</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.056</v>
+        <v>0.014304</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.010132</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.038</v>
+        <v>0.005662</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.02</v>
+        <v>0.004172</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.02</v>
+        <v>0.002682</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.005</v>
+        <v>0.000298</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.008</v>
+        <v>0.000298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1262,58 +1264,58 @@
         <v>0.2974040000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.041</v>
+        <v>0.013708</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.046</v>
+        <v>0.019966</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.054</v>
+        <v>0.01788</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.064</v>
+        <v>0.02473400000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02086</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.021456</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.092</v>
+        <v>0.028608</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.081</v>
+        <v>0.031588</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.097</v>
+        <v>0.02235</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.083</v>
+        <v>0.023542</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.097</v>
+        <v>0.021158</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.075</v>
+        <v>0.019966</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.048</v>
+        <v>0.01341</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.031</v>
+        <v>0.005662</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.014</v>
+        <v>0.005662</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.015</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0.01</v>
+        <v>0.002086</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.007</v>
+        <v>0.0008940000000000002</v>
       </c>
     </row>
     <row r="13">
@@ -1326,61 +1328,61 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2971060000000001</v>
+        <v>0.2968080000000001</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.057</v>
+        <v>0.012516</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.051</v>
+        <v>0.014006</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.058</v>
+        <v>0.015198</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.067</v>
+        <v>0.018178</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.020264</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.076</v>
+        <v>0.025926</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.077</v>
+        <v>0.024138</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.083</v>
+        <v>0.02831000000000001</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.078</v>
+        <v>0.02473400000000001</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.026522</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.093</v>
+        <v>0.02533000000000001</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.067</v>
+        <v>0.021456</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.05</v>
+        <v>0.013112</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.036</v>
+        <v>0.009536000000000001</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.021</v>
+        <v>0.006854000000000001</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.013</v>
+        <v>0.004470000000000001</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.01</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0008940000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -1393,180 +1395,188 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.272372</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.2708820000000001</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="3" t="n">
-        <v>0.002</v>
+        <v>0.000298</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.001</v>
+        <v>0.001192</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.003</v>
+        <v>0.00149</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.007</v>
+        <v>0.00149</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.01</v>
+        <v>0.002384</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.018</v>
+        <v>0.005066000000000001</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.018</v>
+        <v>0.004470000000000001</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.028</v>
+        <v>0.006556</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.028</v>
+        <v>0.010728</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.055</v>
+        <v>0.017284</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.077</v>
+        <v>0.018476</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.098</v>
+        <v>0.033376</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.109</v>
+        <v>0.031886</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.107</v>
+        <v>0.03576000000000001</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.094</v>
+        <v>0.03605800000000001</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.108</v>
+        <v>0.027118</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.01937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.262538</v>
+        <v>0.256876</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.002</v>
+        <v>0.000298</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.000298</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.000298</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00149</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.004</v>
+        <v>0.0005960000000000001</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.007</v>
+        <v>0.002086</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.02</v>
+        <v>0.003278</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.02</v>
+        <v>0.002086</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.025</v>
+        <v>0.007152000000000001</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.047</v>
+        <v>0.010728</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.082</v>
+        <v>0.014304</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.08</v>
+        <v>0.02235</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.094</v>
+        <v>0.02801200000000001</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.103</v>
+        <v>0.029502</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.104</v>
+        <v>0.03963400000000001</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.109</v>
+        <v>0.029502</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.094</v>
+        <v>0.035462</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2577700000000001</v>
+        <v>0.25628</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>0.000298</v>
+      </c>
       <c r="F16" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G16" s="2" t="n"/>
+        <v>0.0005960000000000001</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.0005960000000000001</v>
+      </c>
       <c r="H16" s="3" t="n">
-        <v>0.002</v>
+        <v>0.00149</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.004</v>
+        <v>0.002086</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.008</v>
+        <v>0.002682</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.013</v>
+        <v>0.004470000000000001</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.015</v>
+        <v>0.004172</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.018</v>
+        <v>0.009536000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.034</v>
+        <v>0.01341</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.037</v>
+        <v>0.021456</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.022946</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.107</v>
+        <v>0.033674</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.117</v>
+        <v>0.032184</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.106</v>
+        <v>0.028608</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.109</v>
+        <v>0.028906</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.111</v>
+        <v>0.027714</v>
       </c>
     </row>
     <row r="17">
@@ -1579,55 +1589,49 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.255386</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0.004</v>
+        <v>0.25628</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.000298</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.003</v>
+        <v>0.00149</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.008</v>
+        <v>0.001192</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.006</v>
+        <v>0.002681999999999999</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.01</v>
+        <v>0.00596</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.032</v>
+        <v>0.006854</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.035</v>
+        <v>0.007152</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.059</v>
+        <v>0.014304</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.077</v>
+        <v>0.022946</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.102</v>
+        <v>0.031886</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.114</v>
+        <v>0.033674</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.109</v>
+        <v>0.03129</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.114</v>
+        <v>0.03576</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.099</v>
+        <v>0.03129</v>
       </c>
     </row>
     <row r="18">
@@ -1640,55 +1644,53 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.246744</v>
+        <v>0.239294</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="3" t="n">
+        <v>0.000298</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.0005960000000000001</v>
+      </c>
+      <c r="I18" s="2" t="n"/>
       <c r="J18" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.00149</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0008940000000000002</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.015</v>
+        <v>0.005364000000000001</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.022</v>
+        <v>0.005364000000000001</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.026</v>
+        <v>0.008046000000000001</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.051</v>
+        <v>0.013112</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.056</v>
+        <v>0.018774</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.024138</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.102</v>
+        <v>0.030396</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.125</v>
+        <v>0.029204</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.107</v>
+        <v>0.03427000000000001</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.112</v>
+        <v>0.03456800000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1701,55 +1703,55 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.22648</v>
-      </c>
-      <c r="D19" s="5" t="n"/>
+        <v>0.234228</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.000298</v>
+      </c>
       <c r="E19" s="6" t="n">
-        <v>0.001</v>
+        <v>0.000298</v>
       </c>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="6" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.001192</v>
+      </c>
+      <c r="I19" s="5" t="n"/>
       <c r="J19" s="6" t="n">
-        <v>0.003</v>
+        <v>0.001788</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.002</v>
+        <v>0.002086</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.008</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.014</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.021</v>
+        <v>0.008940000000000002</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.031</v>
+        <v>0.010728</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.062</v>
+        <v>0.016688</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.074</v>
+        <v>0.022946</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.103</v>
+        <v>0.028906</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.118</v>
+        <v>0.031588</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.093</v>
+        <v>0.033674</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.125</v>
+        <v>0.035164</v>
       </c>
     </row>
     <row r="20">
@@ -1762,57 +1764,55 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.21903</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.229758</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H20" s="2" t="n"/>
+        <v>0.000298</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.0008940000000000002</v>
+      </c>
       <c r="I20" s="3" t="n">
-        <v>0.001</v>
+        <v>0.000298</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.005</v>
+        <v>0.00149</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.004</v>
+        <v>0.00149</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.01</v>
+        <v>0.002086</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.011</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.02</v>
+        <v>0.006258000000000001</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.033</v>
+        <v>0.009536000000000001</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.047</v>
+        <v>0.017284</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.06</v>
+        <v>0.021754</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.093</v>
+        <v>0.028608</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.09</v>
+        <v>0.02831000000000001</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.118</v>
+        <v>0.037548</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.103</v>
+        <v>0.03695200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1825,40 +1825,49 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1937</v>
+        <v>0.19817</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.000298</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.000298</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.001192</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.004</v>
+        <v>0.00149</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.004</v>
+        <v>0.00149</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.011</v>
+        <v>0.00149</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.019</v>
+        <v>0.002682</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.026</v>
+        <v>0.006258000000000001</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.032</v>
+        <v>0.01043</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.057</v>
+        <v>0.019072</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.057</v>
+        <v>0.019966</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.028608</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.111</v>
+        <v>0.027714</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.121</v>
+        <v>0.03427000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1871,7 +1880,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.118902</v>
+        <v>0.118306</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1879,37 +1888,37 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.000298</v>
+      </c>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="3" t="n">
-        <v>0.003</v>
+        <v>0.000298</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.004</v>
+        <v>0.0005960000000000001</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001192</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003576000000000001</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.018</v>
+        <v>0.006258000000000001</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.033</v>
+        <v>0.006556</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.051</v>
+        <v>0.012218</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.052</v>
+        <v>0.02235</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.027118</v>
       </c>
     </row>
     <row r="23">
@@ -1925,19 +1934,22 @@
         <v>0.09917080405271408</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.005942641661835695</v>
+        <v>0.002023893960259471</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0.002023893960259471</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.005942641661835695</v>
+        <v>0.006071681880778414</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.02377056664734278</v>
+        <v>0.006071681880778414</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.02971320830917848</v>
+        <v>0.01214336376155683</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.08913962492753542</v>
+        <v>0.01821504564233524</v>
       </c>
     </row>
     <row r="24">
@@ -1964,21 +1976,19 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
-      <c r="P24" s="3" t="n">
-        <v>0.01245822631852507</v>
-      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>0.01245822631852507</v>
+        <v>0.005362574306440681</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.01245822631852507</v>
+        <v>0.005362574306440681</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.0373746789555752</v>
+        <v>0.01072514861288136</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.07474935791115041</v>
+        <v>0.0268128715322034</v>
       </c>
     </row>
     <row r="25">
@@ -1993,17 +2003,14 @@
       <c r="C25" s="4" t="n">
         <v>0.09390580362346135</v>
       </c>
-      <c r="R25" s="4" t="n">
-        <v>0.01432364301761155</v>
-      </c>
       <c r="S25" s="4" t="n">
-        <v>0.01432364301761155</v>
+        <v>0.003756232144938454</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.01432364301761155</v>
+        <v>0.01126869643481536</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.07161821508805777</v>
+        <v>0.01126869643481536</v>
       </c>
     </row>
     <row r="26">
@@ -2034,10 +2041,10 @@
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="n"/>
-      <c r="U26" s="3" t="n">
-        <v>0.1021358198836559</v>
-      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.09130942297598842</v>
+      </c>
+      <c r="U26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2052,7 +2059,7 @@
         <v>0.08873742238943043</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.1488882925997155</v>
+        <v>0.05915828159295362</v>
       </c>
     </row>
     <row r="28">
@@ -2084,9 +2091,7 @@
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="n"/>
-      <c r="U28" s="3" t="n">
-        <v>0.1446141530073682</v>
-      </c>
+      <c r="U28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2236,7 +2241,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2280,7 +2285,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2311,7 +2316,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2324,7 +2329,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2355,7 +2360,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2368,7 +2373,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2487,7 +2492,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2500,7 +2505,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2619,7 +2624,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2632,7 +2637,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2764,7 +2769,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2795,7 +2800,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>elli</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2839,7 +2844,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>repe_kate</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2852,7 +2857,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>Mar_u_shka</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2940,7 +2945,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -2971,7 +2976,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2984,7 +2989,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3015,7 +3020,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3028,7 +3033,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3072,7 +3077,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3103,7 +3108,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3116,7 +3121,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3147,7 +3152,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B77" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -591,597 +591,600 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.298</v>
+        <v>0.25</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.04708400000000001</v>
+        <v>0.039</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.03963400000000001</v>
+        <v>0.034</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.033376</v>
+        <v>0.02475</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.03129000000000001</v>
+        <v>0.0235</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.02801200000000001</v>
+        <v>0.0245</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.02473400000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.021754</v>
+        <v>0.0155</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.016986</v>
+        <v>0.01475</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.012218</v>
+        <v>0.01725</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.015496</v>
+        <v>0.01325</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.009834000000000002</v>
+        <v>0.00775</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.007450000000000002</v>
+        <v>0.0065</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.003874</v>
+        <v>0.0055</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.004172</v>
+        <v>0.00175</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.001</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.000298</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>0.000298</v>
-      </c>
+        <v>0.0015</v>
+      </c>
+      <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.298</v>
+        <v>0.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.045594</v>
+        <v>0.03225</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.038144</v>
+        <v>0.03275</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.03278</v>
+        <v>0.02375</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.029204</v>
+        <v>0.02775</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.026224</v>
+        <v>0.01925</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.021754</v>
+        <v>0.02325</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.019966</v>
+        <v>0.01725</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.021456</v>
+        <v>0.0155</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.018774</v>
+        <v>0.013</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.013112</v>
+        <v>0.01425</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.013708</v>
+        <v>0.011</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.007450000000000002</v>
+        <v>0.01</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.004470000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.002086</v>
+        <v>0.0025</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.002384</v>
+        <v>0.00175</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.00025</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.00025</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.00025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.298</v>
+        <v>0.25</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.04678600000000001</v>
+        <v>0.00775</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.03456800000000001</v>
+        <v>0.0125</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.029502</v>
+        <v>0.0185</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.02503200000000001</v>
+        <v>0.0165</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.021158</v>
+        <v>0.02325</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.027118</v>
+        <v>0.01775</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.027118</v>
+        <v>0.02275</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.021456</v>
+        <v>0.021</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.018774</v>
+        <v>0.02</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.015496</v>
+        <v>0.0215</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.011622</v>
+        <v>0.019</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.007152000000000001</v>
+        <v>0.01975</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.004172</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.002682</v>
+        <v>0.00975</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.0005960000000000001</v>
-      </c>
-      <c r="T4" s="2" t="n"/>
+        <v>0.00125</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>0.00225</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>0.001192</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.298</v>
+        <v>0.24975</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.03009800000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.03009800000000001</v>
+        <v>0.0195</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.03278</v>
+        <v>0.0245</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.027416</v>
+        <v>0.01875</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.026522</v>
+        <v>0.022</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.022648</v>
+        <v>0.0195</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02235</v>
+        <v>0.019</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.016688</v>
+        <v>0.02425</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.022946</v>
+        <v>0.0215</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.017582</v>
+        <v>0.01725</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.01639</v>
+        <v>0.0145</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.012516</v>
+        <v>0.0105</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.010132</v>
+        <v>0.00975</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.003278</v>
+        <v>0.0045</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.003278</v>
+        <v>0.0035</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.002086</v>
+        <v>0.00075</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.00025</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.298</v>
+        <v>0.24975</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.02235</v>
+        <v>0.0165</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.023542</v>
+        <v>0.016</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.029502</v>
+        <v>0.01625</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.02384</v>
+        <v>0.01925</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.029204</v>
+        <v>0.02025</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.02831000000000001</v>
+        <v>0.01825</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.021158</v>
+        <v>0.02075</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.018774</v>
+        <v>0.02025</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.019966</v>
+        <v>0.01825</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.021158</v>
+        <v>0.018</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.020562</v>
+        <v>0.01725</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.016986</v>
+        <v>0.01775</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.009238000000000001</v>
+        <v>0.01325</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.006556</v>
+        <v>0.01075</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.002</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.0015</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.001192</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.298</v>
+        <v>0.24975</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.01341</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.015794</v>
+        <v>0.0095</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.019966</v>
+        <v>0.01425</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02086</v>
+        <v>0.019</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02682</v>
+        <v>0.02075</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.022648</v>
+        <v>0.025</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.022946</v>
+        <v>0.0175</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.022648</v>
+        <v>0.021</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.026522</v>
+        <v>0.022</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.023244</v>
+        <v>0.02425</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.01788</v>
+        <v>0.0245</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.022052</v>
+        <v>0.0145</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.016986</v>
+        <v>0.01</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.011622</v>
+        <v>0.006</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.005066000000000001</v>
+        <v>0.0045</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.004172</v>
+        <v>0.004</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.00298</v>
+        <v>0.0025</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.002086</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.2977020000000001</v>
+        <v>0.24975</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.018774</v>
+        <v>0.04575</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.020264</v>
+        <v>0.0275</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.020264</v>
+        <v>0.0305</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.027118</v>
+        <v>0.02425</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.02235</v>
+        <v>0.01975</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.023542</v>
+        <v>0.01875</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.021456</v>
+        <v>0.0195</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.022946</v>
+        <v>0.01475</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02682</v>
+        <v>0.0135</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.022946</v>
+        <v>0.012</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.022052</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.014006</v>
+        <v>0.00525</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.0149</v>
+        <v>0.0045</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.008046000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.004172</v>
+        <v>0.0015</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.003278</v>
+        <v>0.00025</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.002682</v>
+        <v>0.0005</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.002086</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2977020000000001</v>
+        <v>0.24975</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.013708</v>
+        <v>0.01825</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.019966</v>
+        <v>0.0275</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.01937</v>
+        <v>0.02325</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.021754</v>
+        <v>0.01875</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.022946</v>
+        <v>0.0195</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.021158</v>
+        <v>0.018</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.023244</v>
+        <v>0.0225</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.021158</v>
+        <v>0.024</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.02473400000000001</v>
+        <v>0.019</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.027118</v>
+        <v>0.01875</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.021158</v>
+        <v>0.012</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.025628</v>
+        <v>0.00975</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.014602</v>
+        <v>0.008</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.007152000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.006854000000000001</v>
+        <v>0.00175</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.004470000000000001</v>
+        <v>0.00075</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.001788</v>
+        <v>0.00125</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.297702</v>
+        <v>0.24975</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.011324</v>
+        <v>0.01375</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.016688</v>
+        <v>0.01425</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.019072</v>
+        <v>0.01525</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.021754</v>
+        <v>0.01825</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.024138</v>
+        <v>0.01675</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.022052</v>
+        <v>0.019</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.02473400000000001</v>
+        <v>0.01975</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.023244</v>
+        <v>0.01875</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.027714</v>
+        <v>0.02075</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.02384</v>
+        <v>0.02125</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.027118</v>
+        <v>0.02075</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.019668</v>
+        <v>0.017</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.014304</v>
+        <v>0.0145</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.011622</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.004172</v>
+        <v>0.0055</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.0008940000000000002</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="11">
@@ -1194,61 +1197,61 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2974040000000001</v>
+        <v>0.2495</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02235</v>
+        <v>0.02</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.02384</v>
+        <v>0.025</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.025926</v>
+        <v>0.02025</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.02384</v>
+        <v>0.023</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.022052</v>
+        <v>0.02225</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.028608</v>
+        <v>0.0235</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.024436</v>
+        <v>0.0195</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.031886</v>
+        <v>0.0195</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.021158</v>
+        <v>0.018</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.01937</v>
+        <v>0.013</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.016092</v>
+        <v>0.0155</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.014304</v>
+        <v>0.01175</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.010132</v>
+        <v>0.00775</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.005662</v>
+        <v>0.004</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.004172</v>
+        <v>0.00225</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.002682</v>
+        <v>0.002</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.00175</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="12">
@@ -1261,128 +1264,128 @@
         <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.2974040000000001</v>
+        <v>0.24925</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.013708</v>
+        <v>0.01375</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.019966</v>
+        <v>0.01675</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.01788</v>
+        <v>0.019</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.02473400000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.02086</v>
+        <v>0.02025</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.021456</v>
+        <v>0.021</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.028608</v>
+        <v>0.022</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.031588</v>
+        <v>0.0165</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.02235</v>
+        <v>0.01925</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.023542</v>
+        <v>0.017</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.021158</v>
+        <v>0.01925</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.019966</v>
+        <v>0.01625</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.01341</v>
+        <v>0.01225</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.005662</v>
+        <v>0.00625</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.005662</v>
+        <v>0.00475</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0.002086</v>
+        <v>0.00125</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.0008940000000000002</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2968080000000001</v>
+        <v>0.24925</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.012516</v>
+        <v>0.01425</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.014006</v>
+        <v>0.0135</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.015198</v>
+        <v>0.01825</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.018178</v>
+        <v>0.0175</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.020264</v>
+        <v>0.01825</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.025926</v>
+        <v>0.01925</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.024138</v>
+        <v>0.02425</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.02831000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.02473400000000001</v>
+        <v>0.02175</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.026522</v>
+        <v>0.02025</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.02533000000000001</v>
+        <v>0.01625</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.021456</v>
+        <v>0.013</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.013112</v>
+        <v>0.01225</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.009536000000000001</v>
+        <v>0.00675</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.006854000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.004470000000000001</v>
+        <v>0.0035</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.0008940000000000002</v>
+        <v>0.00225</v>
       </c>
     </row>
     <row r="14">
@@ -1395,243 +1398,242 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2708820000000001</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+        <v>0.23125</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="E14" s="3" t="n">
-        <v>0.000298</v>
+        <v>0.00075</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.001192</v>
+        <v>0.0005</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.002384</v>
+        <v>0.00325</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.005066000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.004470000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.006556</v>
+        <v>0.00575</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.010728</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.017284</v>
+        <v>0.014</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.018476</v>
+        <v>0.021</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.033376</v>
+        <v>0.03075</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.031886</v>
+        <v>0.02925</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.03576000000000001</v>
+        <v>0.02625</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.03605800000000001</v>
+        <v>0.023</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.027118</v>
+        <v>0.023</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.01937</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.256876</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.22275</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.00025</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.0005</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.00149</v>
+        <v>0.001</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.002086</v>
+        <v>0.00125</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.003278</v>
+        <v>0.00325</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.002086</v>
+        <v>0.0065</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.007152000000000001</v>
+        <v>0.00725</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.010728</v>
+        <v>0.01175</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.014304</v>
+        <v>0.014</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.02235</v>
+        <v>0.01975</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.02801200000000001</v>
+        <v>0.0295</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.029502</v>
+        <v>0.031</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03963400000000001</v>
+        <v>0.0275</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.029502</v>
+        <v>0.0255</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.035462</v>
+        <v>0.02075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.25628</v>
+        <v>0.21575</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="3" t="n">
-        <v>0.000298</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="3" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.00025</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.0005960000000000001</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0.00149</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.002086</v>
-      </c>
+        <v>0.00075</v>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="3" t="n">
-        <v>0.002682</v>
+        <v>0.00175</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.004470000000000001</v>
+        <v>0.0015</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.004172</v>
+        <v>0.00325</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.009536000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.01341</v>
+        <v>0.011</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.021456</v>
+        <v>0.0115</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.022946</v>
+        <v>0.0215</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.033674</v>
+        <v>0.02075</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.032184</v>
+        <v>0.0275</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.028608</v>
+        <v>0.029</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.028906</v>
+        <v>0.031</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.027714</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.25628</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.21375</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.0005</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.001192</v>
+        <v>0.0005</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.002681999999999999</v>
+        <v>0.00475</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.00596</v>
+        <v>0.00375</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.006854</v>
+        <v>0.0065</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.007152</v>
+        <v>0.00475</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.014304</v>
+        <v>0.0135</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.022946</v>
+        <v>0.02</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.031886</v>
+        <v>0.0245</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.033674</v>
+        <v>0.02575</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.03129</v>
+        <v>0.033</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.03576</v>
+        <v>0.0325</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.03129</v>
+        <v>0.02175</v>
       </c>
     </row>
     <row r="18">
@@ -1644,53 +1646,55 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.239294</v>
+        <v>0.19975</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="3" t="n">
-        <v>0.000298</v>
+        <v>0.00025</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.0005960000000000001</v>
-      </c>
-      <c r="I18" s="2" t="n"/>
+        <v>0.0005</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="J18" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.0008940000000000002</v>
+        <v>0.00125</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.005364000000000001</v>
+        <v>0.00225</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.005364000000000001</v>
+        <v>0.0055</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.008046000000000001</v>
+        <v>0.00775</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.013112</v>
+        <v>0.013</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.018774</v>
+        <v>0.014</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.024138</v>
+        <v>0.02275</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.030396</v>
+        <v>0.02425</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.029204</v>
+        <v>0.027</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.03427000000000001</v>
+        <v>0.0235</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.03456800000000001</v>
+        <v>0.03325</v>
       </c>
     </row>
     <row r="19">
@@ -1703,55 +1707,55 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.234228</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>0.000298</v>
-      </c>
+        <v>0.1945</v>
+      </c>
+      <c r="D19" s="5" t="n"/>
       <c r="E19" s="6" t="n">
-        <v>0.000298</v>
-      </c>
-      <c r="F19" s="5" t="n"/>
+        <v>0.0005</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="6" t="n">
-        <v>0.001192</v>
-      </c>
-      <c r="I19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="6" t="n">
+        <v>0.001</v>
+      </c>
       <c r="J19" s="6" t="n">
-        <v>0.001788</v>
+        <v>0.00075</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.002086</v>
+        <v>0.0015</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.00125</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.00275</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.008940000000000002</v>
+        <v>0.0055</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.010728</v>
+        <v>0.00775</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.016688</v>
+        <v>0.012</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.022946</v>
+        <v>0.01875</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.028906</v>
+        <v>0.02325</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.031588</v>
+        <v>0.029</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.033674</v>
+        <v>0.0315</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.035164</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="20">
@@ -1764,55 +1768,51 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.229758</v>
+        <v>0.18775</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="3" t="n">
-        <v>0.000298</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0.0008940000000000002</v>
-      </c>
+        <v>0.00025</v>
+      </c>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="3" t="n">
-        <v>0.000298</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.00149</v>
-      </c>
+        <v>0.00025</v>
+      </c>
+      <c r="J20" s="2" t="n"/>
       <c r="K20" s="3" t="n">
-        <v>0.00149</v>
+        <v>0.00175</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.002086</v>
+        <v>0.00175</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.00275</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.006258000000000001</v>
+        <v>0.00475</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.009536000000000001</v>
+        <v>0.00925</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.017284</v>
+        <v>0.01025</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.021754</v>
+        <v>0.01625</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.028608</v>
+        <v>0.02175</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.02831000000000001</v>
+        <v>0.02875</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.037548</v>
+        <v>0.02375</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.03695200000000001</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="21">
@@ -1825,49 +1825,46 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.19817</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.000298</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0.000298</v>
+        <v>0.171</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.001192</v>
+        <v>0.00025</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.0005</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.00149</v>
+        <v>0.00125</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.00149</v>
+        <v>0.00175</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.002682</v>
+        <v>0.0035</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.006258000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.01043</v>
+        <v>0.00775</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.019072</v>
+        <v>0.01375</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.019966</v>
+        <v>0.02125</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.028608</v>
+        <v>0.0205</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.027714</v>
+        <v>0.0275</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.03427000000000001</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="22">
@@ -1880,7 +1877,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.118306</v>
+        <v>0.0925</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1888,37 +1885,35 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="3" t="n">
-        <v>0.000298</v>
-      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="3" t="n">
-        <v>0.000298</v>
+        <v>0.00025</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.0005960000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.001192</v>
+        <v>0.001</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.003576000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.006258000000000001</v>
+        <v>0.0055</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.006556</v>
+        <v>0.00825</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.012218</v>
+        <v>0.0095</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.02235</v>
+        <v>0.01575</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.027118</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="23">
@@ -1931,38 +1926,35 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.09917080405271408</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>0.002023893960259471</v>
+        <v>0.0850229801549332</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.002023893960259471</v>
+        <v>0.001604207172734589</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.006071681880778414</v>
+        <v>0.003208414345469178</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.006071681880778414</v>
+        <v>0.004812621518203767</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.01214336376155683</v>
+        <v>0.01283365738187671</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.01821504564233524</v>
+        <v>0.02085469324554965</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.09652633751593225</v>
+        <v>0.08275577633396113</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1979,38 +1971,35 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>0.005362574306440681</v>
+        <v>0.004355567175471638</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.005362574306440681</v>
+        <v>0.004355567175471638</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.01072514861288136</v>
+        <v>0.004355567175471638</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.0268128715322034</v>
+        <v>0.02613340305282983</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.09390580362346135</v>
+        <v>0.08050909089802928</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.003756232144938454</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>0.01126869643481536</v>
+        <v>0.008945454544225476</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.01126869643481536</v>
+        <v>0.01341818181633821</v>
       </c>
     </row>
     <row r="26">
@@ -2023,7 +2012,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.09130942297598842</v>
+        <v>0.07828311297667045</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
@@ -2041,10 +2030,10 @@
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
-      <c r="T26" s="3" t="n">
-        <v>0.09130942297598842</v>
-      </c>
-      <c r="U26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="3" t="n">
+        <v>0.03914155648833523</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2056,10 +2045,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.08873742238943043</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>0.05915828159295362</v>
+        <v>0.07607803702797535</v>
       </c>
     </row>
     <row r="28">
@@ -2072,7 +2058,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.08619003519239145</v>
+        <v>0.07389406309361407</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
@@ -2103,7 +2089,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.08366750154394066</v>
+        <v>0.07173139707127972</v>
       </c>
     </row>
     <row r="30">
@@ -2116,7 +2102,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.08117006877353256</v>
+        <v>0.06959025100611502</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
@@ -2147,20 +2133,20 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.07869799174509248</v>
+        <v>0.06747084340285707</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.07625153324752322</v>
+        <v>0.06537339956063376</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
@@ -2184,14 +2170,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.0738309644141493</v>
+        <v>0.06329815193256971</v>
       </c>
     </row>
     <row r="34">
@@ -2204,7 +2190,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.07143656517391686</v>
+        <v>0.06124534051261734</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
@@ -2235,7 +2221,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.06906862473750806</v>
+        <v>0.05921521325232173</v>
       </c>
     </row>
     <row r="36">
@@ -2248,7 +2234,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.06672744212192308</v>
+        <v>0.05720802651056506</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
@@ -2272,27 +2258,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.06441332671753436</v>
+        <v>0.05522404553972425</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.06212659890213935</v>
+        <v>0.05326354501212222</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
@@ -2323,7 +2309,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.05986759070714237</v>
+        <v>0.05132680959117145</v>
       </c>
     </row>
     <row r="40">
@@ -2336,7 +2322,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.05763664654169758</v>
+        <v>0.04941413455220986</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -2360,27 +2346,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.05543412398146273</v>
+        <v>0.04752582645873005</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.05326039462957088</v>
+        <v>0.04566220390052374</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -2404,27 +2390,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>42</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.0511158450585511</v>
+        <v>0.04382359830122694</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.04900087784325523</v>
+        <v>0.04201035480388823</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -2455,7 +2441,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.04691591269641866</v>
+        <v>0.04022283324452903</v>
       </c>
     </row>
     <row r="46">
@@ -2468,7 +2454,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.04486138772035221</v>
+        <v>0.03846140922526767</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
@@ -2492,27 +2478,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.04283776079049762</v>
+        <v>0.03672647530049522</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.04084551108926481</v>
+        <v>0.03501844229189371</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
@@ -2543,7 +2529,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.03888514081181586</v>
+        <v>0.03333774075087094</v>
       </c>
     </row>
     <row r="50">
@@ -2556,7 +2542,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.03695717706940388</v>
+        <v>0.03168482259036684</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
@@ -2587,7 +2573,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.03506217402069824</v>
+        <v>0.03006016291212127</v>
       </c>
     </row>
     <row r="52">
@@ -2600,7 +2586,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.03320071526746089</v>
+        <v>0.02846426206058033</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
@@ -2631,7 +2617,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.03137341655829062</v>
+        <v>0.02689764794092131</v>
       </c>
     </row>
     <row r="54">
@@ -2644,7 +2630,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.02958092885332818</v>
+        <v>0.02536087864654337</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
@@ -2675,7 +2661,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.02782394181435892</v>
+        <v>0.02385454545126794</v>
       </c>
     </row>
     <row r="56">
@@ -2688,7 +2674,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.02610318779939383</v>
+        <v>0.0223792762340482</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
@@ -2719,7 +2705,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.02441944645956044</v>
+        <v>0.02093573942006211</v>
       </c>
     </row>
     <row r="58">
@@ -2732,7 +2718,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.02277355006037658</v>
+        <v>0.01952464854284687</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
@@ -2763,20 +2749,20 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.02116638968116055</v>
+        <v>0.01814676755929403</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>elli</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.01959892248821406</v>
+        <v>0.01680291708523153</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
@@ -2800,14 +2786,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.01807218033349118</v>
+        <v>0.01549398176739642</v>
       </c>
     </row>
     <row r="62">
@@ -2820,7 +2806,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.01658728000659684</v>
+        <v>0.01422091907287109</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
@@ -2844,27 +2830,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>Mar_u_shka</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>62</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.01514543557290403</v>
+        <v>0.01298476986703021</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>repe_kate</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.01374797337771438</v>
+        <v>0.01178667127718997</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
@@ -2895,7 +2881,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.01239635050658926</v>
+        <v>0.01062787251936665</v>
       </c>
     </row>
     <row r="66">
@@ -2908,7 +2894,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.0110921777986788</v>
+        <v>0.009509754628496918</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
@@ -2932,27 +2918,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tim19</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.00983724896813656</v>
+        <v>0.008433855425357134</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>Tim19</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.008633578092188508</v>
+        <v>0.007401901656540216</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
@@ -2976,14 +2962,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>68</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.007483448838392796</v>
+        <v>0.006415851198896431</v>
       </c>
     </row>
     <row r="70">
@@ -2996,7 +2982,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.006389480632318888</v>
+        <v>0.005477949787653368</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
@@ -3020,27 +3006,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>70</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.005354720098812203</v>
+        <v>0.004590809412561903</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.00438277175258728</v>
+        <v>0.003757520364015158</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
@@ -3064,27 +3050,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.003477992726794865</v>
+        <v>0.002981818181408492</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.002645798710145069</v>
+        <v>0.002268345944911754</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
@@ -3115,20 +3101,20 @@
         <v>74</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.001893179446613004</v>
+        <v>0.001623096233378776</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.00122965612101707</v>
+        <v>0.001054231928169642</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
@@ -3159,13 +3145,13 @@
         <v>76</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.0006693400123515253</v>
+        <v>0.0005738511765702378</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -601,60 +601,62 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.039</v>
+        <v>0.04175</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.034</v>
+        <v>0.0335</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02475</v>
+        <v>0.024</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>0.0235</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0.0245</v>
-      </c>
       <c r="I2" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.0215</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.016</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.01475</v>
+        <v>0.01425</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.01725</v>
+        <v>0.01675</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.01325</v>
+        <v>0.00975</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.00775</v>
+        <v>0.00725</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.00375</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.002</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="T2" s="2" t="n"/>
+        <v>0.00075</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -664,64 +666,58 @@
         <v>0.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.03225</v>
+        <v>0.03825</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.03275</v>
+        <v>0.027</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.02375</v>
+        <v>0.03025</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.02775</v>
+        <v>0.0235</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.01925</v>
+        <v>0.02425</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.02325</v>
+        <v>0.02</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.01725</v>
+        <v>0.01875</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.01475</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.01425</v>
+        <v>0.01175</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.011</v>
+        <v>0.0115</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0075</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>0.005</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.00325</v>
       </c>
       <c r="R3" s="4" t="n">
         <v>0.00175</v>
       </c>
-      <c r="S3" s="4" t="n">
-        <v>0.00025</v>
-      </c>
       <c r="T3" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -731,131 +727,131 @@
         <v>0.25</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.00775</v>
+        <v>0.01975</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.0205</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.02325</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.018</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.02325</v>
+        <v>0.02175</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.01775</v>
+        <v>0.022</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.02275</v>
+        <v>0.02175</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.02</v>
+        <v>0.02175</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.0215</v>
+        <v>0.0175</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.019</v>
+        <v>0.01475</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.01975</v>
+        <v>0.011</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00725</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.00975</v>
+        <v>0.00475</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>0.00125</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.00225</v>
+        <v>0.0005</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.24975</v>
+        <v>0.25</v>
       </c>
       <c r="D5" s="4" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.0195</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.0245</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0.01875</v>
-      </c>
       <c r="H5" s="4" t="n">
-        <v>0.022</v>
+        <v>0.01975</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.0225</v>
       </c>
       <c r="J5" s="4" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>0.019</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v>0.02425</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.0215</v>
-      </c>
       <c r="M5" s="4" t="n">
-        <v>0.01725</v>
+        <v>0.01975</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.01825</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.0105</v>
+        <v>0.016</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.00975</v>
+        <v>0.01225</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.0045</v>
+        <v>0.0065</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.0035</v>
+        <v>0.00325</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.00125</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.0005</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -865,122 +861,122 @@
         <v>0.24975</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.01125</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.01625</v>
+        <v>0.0175</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.01925</v>
+        <v>0.01525</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0.02025</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.01975</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.02075</v>
+        <v>0.01975</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.02025</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.02</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.01725</v>
+        <v>0.01925</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.01775</v>
+        <v>0.016</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.01325</v>
+        <v>0.015</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.01075</v>
+        <v>0.008</v>
       </c>
       <c r="R6" s="3" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>0.0025</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>0.002</v>
-      </c>
       <c r="T6" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>0.0015</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.24975</v>
+        <v>0.2495</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01325</v>
       </c>
       <c r="E7" s="4" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>0.0095</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.01425</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.02075</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.02425</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0.0245</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0.006</v>
-      </c>
       <c r="R7" s="4" t="n">
-        <v>0.0045</v>
+        <v>0.0055</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.004</v>
+        <v>0.00225</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.00325</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>0.001</v>
@@ -989,69 +985,67 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.24975</v>
+        <v>0.2495</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.04575</v>
+        <v>0.03175</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.0305</v>
+        <v>0.021</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.02425</v>
+        <v>0.02875</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.01975</v>
+        <v>0.02275</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.02175</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.0175</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.01475</v>
+        <v>0.0175</v>
       </c>
       <c r="L8" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>0.0135</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>0.012</v>
-      </c>
       <c r="N8" s="3" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.00525</v>
+        <v>0.00475</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.00575</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.00275</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0.0015</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T8" s="3" t="n">
         <v>0.00025</v>
       </c>
-      <c r="T8" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="U8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1063,134 +1057,134 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.24975</v>
+        <v>0.2495</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.01825</v>
+        <v>0.02275</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.02875</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.02325</v>
+        <v>0.02375</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.01875</v>
+        <v>0.0235</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.02075</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.018</v>
+        <v>0.02025</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0225</v>
+        <v>0.022</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.024</v>
+        <v>0.01775</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.019</v>
+        <v>0.0165</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.01875</v>
+        <v>0.01675</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0.012</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.00975</v>
+        <v>0.0095</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.008</v>
+        <v>0.0065</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.005</v>
+        <v>0.00425</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.00175</v>
+        <v>0.0025</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.0015</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.00125</v>
+        <v>0.00025</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.24975</v>
+        <v>0.2495</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01375</v>
+        <v>0.01825</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.01425</v>
+        <v>0.01875</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.01525</v>
+        <v>0.02225</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.02375</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.01675</v>
+        <v>0.022</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.019</v>
+        <v>0.0225</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.01975</v>
+        <v>0.0215</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.02175</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.02075</v>
+        <v>0.01725</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.02125</v>
+        <v>0.0155</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.02075</v>
+        <v>0.016</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.017</v>
+        <v>0.0125</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.0145</v>
+        <v>0.00775</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0045</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0015</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.00175</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1200,58 +1194,58 @@
         <v>0.2495</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0115</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0155</v>
       </c>
       <c r="F11" s="4" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.01425</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>0.02025</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>0.02225</v>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.0195</v>
-      </c>
       <c r="K11" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.021</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.018</v>
+        <v>0.0215</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0205</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.017</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.01175</v>
+        <v>0.01675</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.00775</v>
+        <v>0.01325</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.004</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.00225</v>
+        <v>0.00625</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.002</v>
+        <v>0.00375</v>
       </c>
       <c r="T11" s="4" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>0.00175</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0.00025</v>
       </c>
     </row>
     <row r="12">
@@ -1264,128 +1258,128 @@
         <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.24925</v>
+        <v>0.249</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.01375</v>
+        <v>0.01325</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.01675</v>
+        <v>0.01475</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="H12" s="3" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>0.02025</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.01925</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.017</v>
-      </c>
       <c r="N12" s="3" t="n">
-        <v>0.01925</v>
+        <v>0.01775</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.01625</v>
+        <v>0.01775</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.01225</v>
+        <v>0.00775</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.00625</v>
+        <v>0.00475</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.00475</v>
+        <v>0.006</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0.0025</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.001</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.24925</v>
+        <v>0.2485</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.01425</v>
+        <v>0.0145</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0135</v>
+        <v>0.01325</v>
       </c>
       <c r="F13" s="4" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.01725</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.02225</v>
+      </c>
+      <c r="M13" s="4" t="n">
         <v>0.01825</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0.01825</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0.01925</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0.02425</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.02175</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.02025</v>
-      </c>
       <c r="N13" s="4" t="n">
-        <v>0.01625</v>
+        <v>0.0215</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0165</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.01225</v>
+        <v>0.015</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.00675</v>
+        <v>0.00625</v>
       </c>
       <c r="R13" s="4" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="S13" s="4" t="n">
         <v>0.004</v>
       </c>
-      <c r="S13" s="4" t="n">
-        <v>0.0035</v>
-      </c>
       <c r="T13" s="4" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>0.001</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0.00225</v>
       </c>
     </row>
     <row r="14">
@@ -1398,61 +1392,61 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.23125</v>
+        <v>0.21525</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0.00025</v>
       </c>
       <c r="E14" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>0.00075</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.00125</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.00125</v>
       </c>
       <c r="I14" s="3" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>0.00325</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.0025</v>
-      </c>
       <c r="L14" s="3" t="n">
-        <v>0.00575</v>
+        <v>0.00675</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00925</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.014</v>
+        <v>0.0115</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>0.021</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.03075</v>
+        <v>0.028</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0.02925</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.02625</v>
+        <v>0.0295</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.021</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="15">
@@ -1465,7 +1459,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.22275</v>
+        <v>0.19825</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0.00025</v>
@@ -1474,59 +1468,59 @@
         <v>0.0005</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00075</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.00125</v>
+        <v>0.00225</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.00325</v>
+        <v>0.00475</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.00725</v>
+        <v>0.0075</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.01175</v>
+        <v>0.014</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.014</v>
+        <v>0.01375</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.01975</v>
+        <v>0.01475</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.02975</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.031</v>
+        <v>0.03325</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.02525</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.0255</v>
+        <v>0.02525</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.02075</v>
+        <v>0.02125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.21575</v>
+        <v>0.19025</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
@@ -1534,58 +1528,65 @@
         <v>0.00025</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>0.00075</v>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="3" t="n">
+        <v>0.00175</v>
+      </c>
       <c r="J16" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.0005</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.00225</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.00325</v>
+        <v>0.002</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.00375</v>
+        <v>0.0055</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.011</v>
+        <v>0.0105</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.013</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.0215</v>
+        <v>0.019</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.02075</v>
+        <v>0.024</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.02625</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.029</v>
+        <v>0.02775</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.031</v>
+        <v>0.02975</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.026</v>
+        <v>0.02675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.21375</v>
+        <v>0.18975</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.0005</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0.00025</v>
@@ -1594,46 +1595,46 @@
         <v>0.0005</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.00025</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.00125</v>
+        <v>0.00025</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.00075</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.00475</v>
+        <v>0.00325</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.00375</v>
+        <v>0.00425</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.00675</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.00475</v>
+        <v>0.00675</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0135</v>
+        <v>0.0145</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01925</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.0245</v>
+        <v>0.02725</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>0.02575</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.033</v>
+        <v>0.02625</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.0275</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.02175</v>
+        <v>0.02575</v>
       </c>
     </row>
     <row r="18">
@@ -1646,55 +1647,57 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.19975</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+        <v>0.178</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.00025</v>
       </c>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.00025</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.00075</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0.00125</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.00275</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0.00225</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0035</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.00775</v>
+        <v>0.008</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.014</v>
+        <v>0.0165</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.02275</v>
+        <v>0.021</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.02425</v>
+        <v>0.02925</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.027</v>
+        <v>0.02725</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.0235</v>
+        <v>0.02875</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.03325</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="19">
@@ -1707,19 +1710,19 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.1945</v>
+        <v>0.1685</v>
       </c>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="6" t="n">
         <v>0.0005</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>0.00025</v>
       </c>
-      <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="6" t="n">
-        <v>0.001</v>
+        <v>0.00075</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>0.00075</v>
@@ -1728,34 +1731,34 @@
         <v>0.0015</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.00125</v>
+        <v>0.00175</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.00275</v>
+        <v>0.0055</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0055</v>
+        <v>0.00525</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.00775</v>
+        <v>0.01</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.01875</v>
+        <v>0.01925</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.02325</v>
+        <v>0.01775</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.029</v>
+        <v>0.0285</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.0315</v>
+        <v>0.02875</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.0285</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="20">
@@ -1768,51 +1771,51 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.18775</v>
+        <v>0.1495</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="3" t="n">
         <v>0.00025</v>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="3" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.0015</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.00225</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.002</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.00475</v>
+        <v>0.00425</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.00925</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.01025</v>
+        <v>0.012</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.01625</v>
+        <v>0.017</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.02175</v>
+        <v>0.02</v>
       </c>
       <c r="S20" s="3" t="n">
+        <v>0.02475</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>0.02875</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0.02375</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>0.034</v>
       </c>
     </row>
     <row r="21">
@@ -1825,7 +1828,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.171</v>
+        <v>0.134</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.00025</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>0.00025</v>
@@ -1833,38 +1839,35 @@
       <c r="J21" s="4" t="n">
         <v>0.0005</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>0.00125</v>
-      </c>
       <c r="L21" s="4" t="n">
-        <v>0.00125</v>
+        <v>0.001</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.00175</v>
+        <v>0.00225</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.0035</v>
+        <v>0.00275</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.00775</v>
+        <v>0.01</v>
       </c>
       <c r="Q21" s="4" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>0.01375</v>
       </c>
-      <c r="R21" s="4" t="n">
-        <v>0.02125</v>
-      </c>
       <c r="S21" s="4" t="n">
-        <v>0.0205</v>
+        <v>0.02175</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.0325</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0285</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="22">
@@ -1877,7 +1880,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.0925</v>
+        <v>0.08271522788301899</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1885,35 +1888,35 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="3" t="n">
+        <v>0.0003121329354076188</v>
+      </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.001248531741630475</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.001</v>
+        <v>0.001872797612445713</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.002809196418668569</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.00530625990192952</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.00825</v>
+        <v>0.0115489186100819</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.0095</v>
+        <v>0.01591877970578856</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.01575</v>
+        <v>0.01841584318904951</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.0215</v>
+        <v>0.02528276776801713</v>
       </c>
     </row>
     <row r="23">
@@ -1926,22 +1929,25 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.0850229801549332</v>
+        <v>0.08054808646256829</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0.002301373898930523</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.001604207172734589</v>
+        <v>0.002301373898930523</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.003208414345469178</v>
+        <v>0.009205495595722091</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.004812621518203767</v>
+        <v>0.01380824339358314</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.01283365738187671</v>
+        <v>0.01380824339358314</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.02085469324554965</v>
+        <v>0.03912335628181889</v>
       </c>
     </row>
     <row r="24">
@@ -1954,7 +1960,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.08275577633396113</v>
+        <v>0.07840020915848948</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1970,17 +1976,15 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="3" t="n">
-        <v>0.004355567175471638</v>
-      </c>
+      <c r="R24" s="2" t="n"/>
       <c r="S24" s="3" t="n">
-        <v>0.004355567175471638</v>
+        <v>0.0156800418316979</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.004355567175471638</v>
+        <v>0.02352006274754685</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.02613340305282983</v>
+        <v>0.03920010457924474</v>
       </c>
     </row>
     <row r="25">
@@ -1993,13 +1997,19 @@
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.08050909089802928</v>
+        <v>0.07627177032444879</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>0.005867059255726829</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.008945454544225476</v>
+        <v>0.005867059255726829</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0.02346823702290732</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.01341818181633821</v>
+        <v>0.04106941479008781</v>
       </c>
     </row>
     <row r="26">
@@ -2012,7 +2022,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.07828311297667045</v>
+        <v>0.07416294913579306</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
@@ -2032,7 +2042,7 @@
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n"/>
       <c r="U26" s="3" t="n">
-        <v>0.03914155648833523</v>
+        <v>0.07416294913579306</v>
       </c>
     </row>
     <row r="27">
@@ -2045,7 +2055,10 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.07607803702797535</v>
+        <v>0.07207392981597664</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0.07207392981597664</v>
       </c>
     </row>
     <row r="28">
@@ -2058,7 +2071,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.07389406309361407</v>
+        <v>0.07000490187816071</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
@@ -2077,7 +2090,9 @@
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="n"/>
-      <c r="U28" s="2" t="n"/>
+      <c r="U28" s="3" t="n">
+        <v>0.07000490187816071</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2089,7 +2104,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.07173139707127972</v>
+        <v>0.06795606038331763</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>0.06795606038331763</v>
       </c>
     </row>
     <row r="30">
@@ -2102,7 +2120,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.06959025100611502</v>
+        <v>0.06592760621631949</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
@@ -2121,7 +2139,9 @@
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="n"/>
-      <c r="U30" s="2" t="n"/>
+      <c r="U30" s="3" t="n">
+        <v>0.06592760621631949</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2133,20 +2153,23 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.06747084340285707</v>
+        <v>0.06391974638165407</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>0.06391974638165407</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.06537339956063376</v>
+        <v>0.06193269432060041</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
@@ -2165,19 +2188,24 @@
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="n"/>
-      <c r="U32" s="2" t="n"/>
+      <c r="U32" s="3" t="n">
+        <v>0.06193269432060041</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.06329815193256971</v>
+        <v>0.05996667025190814</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>0.05996667025190814</v>
       </c>
     </row>
     <row r="34">
@@ -2190,7 +2218,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.06124534051261734</v>
+        <v>0.05802190153826906</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
@@ -2209,7 +2237,9 @@
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="n"/>
+      <c r="U34" s="3" t="n">
+        <v>0.05802190153826906</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2221,20 +2251,23 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.05921521325232173</v>
+        <v>0.05609862308114691</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>0.05609862308114691</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.05720802651056506</v>
+        <v>0.05419707774685112</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
@@ -2253,32 +2286,37 @@
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n"/>
-      <c r="U36" s="2" t="n"/>
+      <c r="U36" s="3" t="n">
+        <v>0.05419707774685112</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.05522404553972425</v>
+        <v>0.05231751682710718</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>0.05231751682710718</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.05326354501212222</v>
+        <v>0.0504602005378</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
@@ -2297,32 +2335,37 @@
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n"/>
+      <c r="U38" s="3" t="n">
+        <v>0.0504602005378</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.05132680959117145</v>
+        <v>0.04862539856005715</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>0.04862539856005715</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.04941413455220986</v>
+        <v>0.04681339062840933</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -2341,32 +2384,37 @@
       <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n"/>
-      <c r="U40" s="2" t="n"/>
+      <c r="U40" s="3" t="n">
+        <v>0.04681339062840933</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.04752582645873005</v>
+        <v>0.04502446717142847</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>0.04502446717142847</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.04566220390052374</v>
+        <v>0.04325893001102249</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -2385,32 +2433,37 @@
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="n"/>
+      <c r="U42" s="3" t="n">
+        <v>0.04325893001102249</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>42</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.04382359830122694</v>
+        <v>0.04151709312747816</v>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>0.04151709312747816</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.04201035480388823</v>
+        <v>0.03979928349842043</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -2429,7 +2482,9 @@
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n"/>
-      <c r="U44" s="2" t="n"/>
+      <c r="U44" s="3" t="n">
+        <v>0.03979928349842043</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2441,7 +2496,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.04022283324452903</v>
+        <v>0.03810584202113276</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>0.03810584202113276</v>
       </c>
     </row>
     <row r="46">
@@ -2454,7 +2512,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.03846140922526767</v>
+        <v>0.03643712452920096</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
@@ -2473,7 +2531,9 @@
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
+      <c r="U46" s="3" t="n">
+        <v>0.03643712452920096</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2485,7 +2545,10 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.03672647530049522</v>
+        <v>0.03479350291625863</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>0.03479350291625863</v>
       </c>
     </row>
     <row r="48">
@@ -2498,7 +2561,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.03501844229189371</v>
+        <v>0.03317536638179404</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
@@ -2517,7 +2580,9 @@
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="n"/>
-      <c r="U48" s="2" t="n"/>
+      <c r="U48" s="3" t="n">
+        <v>0.03317536638179404</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2529,7 +2594,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.03333774075087094</v>
+        <v>0.03158312281661457</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>0.03158312281661457</v>
       </c>
     </row>
     <row r="50">
@@ -2542,7 +2610,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.03168482259036684</v>
+        <v>0.03001720034876858</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
@@ -2561,32 +2629,37 @@
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="n"/>
-      <c r="U50" s="2" t="n"/>
+      <c r="U50" s="3" t="n">
+        <v>0.03001720034876858</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>OlgaaGeorgieva</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.03006016291212127</v>
+        <v>0.0284780490746412</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>0.0284780490746412</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>OlgaaGeorgieva</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.02846426206058033</v>
+        <v>0.02696614300476031</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
@@ -2605,7 +2678,9 @@
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="n"/>
-      <c r="U52" s="2" t="n"/>
+      <c r="U52" s="3" t="n">
+        <v>0.02696614300476031</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2617,7 +2692,10 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.02689764794092131</v>
+        <v>0.02548198225982019</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>0.02548198225982019</v>
       </c>
     </row>
     <row r="54">
@@ -2630,7 +2708,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.02536087864654337</v>
+        <v>0.02402609555988319</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
@@ -2649,7 +2727,9 @@
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="n"/>
-      <c r="U54" s="2" t="n"/>
+      <c r="U54" s="3" t="n">
+        <v>0.02402609555988319</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2661,7 +2741,10 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.02385454545126794</v>
+        <v>0.02259904305909594</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>0.02259904305909594</v>
       </c>
     </row>
     <row r="56">
@@ -2674,7 +2757,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.0223792762340482</v>
+        <v>0.02120141959015093</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
@@ -2693,7 +2776,9 @@
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="2" t="n"/>
-      <c r="U56" s="2" t="n"/>
+      <c r="U56" s="3" t="n">
+        <v>0.02120141959015093</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2705,7 +2790,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.02093573942006211</v>
+        <v>0.01983385839795358</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>0.01983385839795358</v>
       </c>
     </row>
     <row r="58">
@@ -2718,7 +2806,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.01952464854284687</v>
+        <v>0.0184970354616444</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
@@ -2737,7 +2825,9 @@
       <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="2" t="n"/>
-      <c r="U58" s="2" t="n"/>
+      <c r="U58" s="3" t="n">
+        <v>0.0184970354616444</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2749,7 +2839,10 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.01814676755929403</v>
+        <v>0.0171916745298575</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>0.0171916745298575</v>
       </c>
     </row>
     <row r="60">
@@ -2762,7 +2855,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.01680291708523153</v>
+        <v>0.01591855302811408</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
@@ -2781,7 +2874,9 @@
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="2" t="n"/>
-      <c r="U60" s="2" t="n"/>
+      <c r="U60" s="3" t="n">
+        <v>0.01591855302811408</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2793,7 +2888,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.01549398176739642</v>
+        <v>0.01467850904279661</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>0.01467850904279661</v>
       </c>
     </row>
     <row r="62">
@@ -2806,7 +2904,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.01422091907287109</v>
+        <v>0.01347244964798314</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
@@ -2825,7 +2923,9 @@
       <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="n"/>
-      <c r="U62" s="2" t="n"/>
+      <c r="U62" s="3" t="n">
+        <v>0.01347244964798314</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2837,7 +2937,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.01298476986703021</v>
+        <v>0.0123013609266602</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>0.0123013609266602</v>
       </c>
     </row>
     <row r="64">
@@ -2850,7 +2953,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.01178667127718997</v>
+        <v>0.01116632015733787</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
@@ -2869,7 +2972,9 @@
       <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="n"/>
-      <c r="U64" s="2" t="n"/>
+      <c r="U64" s="3" t="n">
+        <v>0.01116632015733787</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2881,7 +2986,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.01062787251936665</v>
+        <v>0.01006851080782104</v>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>0.01006851080782104</v>
       </c>
     </row>
     <row r="66">
@@ -2894,7 +3002,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.009509754628496918</v>
+        <v>0.00900924122699708</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
@@ -2913,32 +3021,37 @@
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="2" t="n"/>
-      <c r="U66" s="2" t="n"/>
+      <c r="U66" s="3" t="n">
+        <v>0.00900924122699708</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>Tim19</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.008433855425357134</v>
+        <v>0.007989968297706759</v>
+      </c>
+      <c r="U67" s="4" t="n">
+        <v>0.007989968297706759</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Tim19</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.007401901656540216</v>
+        <v>0.007012327885143364</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
@@ -2957,32 +3070,37 @@
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="2" t="n"/>
-      <c r="U68" s="2" t="n"/>
+      <c r="U68" s="3" t="n">
+        <v>0.007012327885143364</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>68</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.006415851198896431</v>
+        <v>0.006078174820007144</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>0.006078174820007144</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.005477949787653368</v>
+        <v>0.00518963664093477</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
@@ -3001,32 +3119,37 @@
       <c r="R70" s="2" t="n"/>
       <c r="S70" s="2" t="n"/>
       <c r="T70" s="2" t="n"/>
-      <c r="U70" s="2" t="n"/>
+      <c r="U70" s="3" t="n">
+        <v>0.00518963664093477</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>70</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.004590809412561903</v>
+        <v>0.004349187864532329</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>0.004349187864532329</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.003757520364015158</v>
+        <v>0.00355975613433015</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
@@ -3045,32 +3168,37 @@
       <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="n"/>
-      <c r="U72" s="2" t="n"/>
+      <c r="U72" s="3" t="n">
+        <v>0.00355975613433015</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.002981818181408492</v>
+        <v>0.002824880382386993</v>
+      </c>
+      <c r="U73" s="4" t="n">
+        <v>0.002824880382386993</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.002268345944911754</v>
+        <v>0.002148959316232187</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
@@ -3089,32 +3217,37 @@
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="n"/>
-      <c r="U74" s="2" t="n"/>
+      <c r="U74" s="3" t="n">
+        <v>0.002148959316232187</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>74</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.001623096233378776</v>
+        <v>0.001537670115832525</v>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>0.001537670115832525</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.001054231928169642</v>
+        <v>0.0009987460372133448</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
@@ -3133,25 +3266,30 @@
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="2" t="n"/>
-      <c r="U76" s="2" t="n"/>
+      <c r="U76" s="3" t="n">
+        <v>0.0009987460372133448</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>76</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.0005738511765702378</v>
+        <v>0.0005436484830665411</v>
+      </c>
+      <c r="U77" s="4" t="n">
+        <v>0.0005436484830665411</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -601,49 +601,49 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.04175</v>
+        <v>0.03325</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0335</v>
+        <v>0.02625</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.024</v>
+        <v>0.02725</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02525</v>
+        <v>0.02325</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.0235</v>
+        <v>0.02225</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.0215</v>
+        <v>0.02225</v>
       </c>
       <c r="J2" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0.016</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>0.01425</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.01675</v>
-      </c>
       <c r="M2" s="3" t="n">
-        <v>0.00975</v>
+        <v>0.01225</v>
       </c>
       <c r="N2" s="3" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>0.00725</v>
       </c>
-      <c r="O2" s="3" t="n">
-        <v>0.008500000000000001</v>
-      </c>
       <c r="P2" s="3" t="n">
-        <v>0.00375</v>
+        <v>0.0035</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.002</v>
+        <v>0.00225</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.001</v>
+        <v>0.00225</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>0.00075</v>
@@ -656,7 +656,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -666,58 +666,64 @@
         <v>0.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.03825</v>
+        <v>0.02525</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.03025</v>
+        <v>0.0205</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0.0235</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.02425</v>
+        <v>0.0245</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0225</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.01875</v>
+        <v>0.017</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.01475</v>
+        <v>0.02625</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.012</v>
+        <v>0.01725</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.01175</v>
+        <v>0.015</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.0115</v>
+        <v>0.01375</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.0075</v>
+        <v>0.01</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.005</v>
+        <v>0.00775</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.00325</v>
+        <v>0.004</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.00175</v>
+        <v>0.00075</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.0015</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.00025</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.00025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -727,55 +733,55 @@
         <v>0.25</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.01975</v>
+        <v>0.01875</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.0205</v>
+        <v>0.0245</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.02325</v>
+        <v>0.0225</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0.02175</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>0.02075</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0.022</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>0.02175</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.02</v>
-      </c>
       <c r="L4" s="3" t="n">
-        <v>0.02175</v>
+        <v>0.01975</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.016</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.01475</v>
+        <v>0.016</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.011</v>
+        <v>0.0095</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.00725</v>
+        <v>0.00775</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.00475</v>
+        <v>0.00325</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.00075</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.00025</v>
@@ -784,7 +790,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -794,13 +800,13 @@
         <v>0.25</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.01325</v>
+        <v>0.017</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.018</v>
+        <v>0.0165</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.02025</v>
+        <v>0.01775</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0.0195</v>
@@ -809,43 +815,43 @@
         <v>0.01975</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>0.0225</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.01975</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0.01825</v>
-      </c>
       <c r="O5" s="4" t="n">
-        <v>0.016</v>
+        <v>0.01525</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.01225</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.005</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>0.00325</v>
       </c>
       <c r="S5" s="4" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="T5" s="4" t="n">
         <v>0.00125</v>
       </c>
-      <c r="T5" s="4" t="n">
-        <v>0.0005</v>
-      </c>
       <c r="U5" s="4" t="n">
-        <v>0.001</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="6">
@@ -861,131 +867,128 @@
         <v>0.24975</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01125</v>
+        <v>0.01275</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>0.0175</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.01525</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.02025</v>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>0.01975</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>0.01975</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.02025</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.02</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>0.024</v>
+        <v>0.02275</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.01925</v>
+        <v>0.02125</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.016</v>
+        <v>0.0165</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.015</v>
+        <v>0.01375</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0065</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.00325</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0.0025</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.001</v>
+        <v>0.00125</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2495</v>
+        <v>0.24975</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.01325</v>
+        <v>0.0355</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.01375</v>
+        <v>0.03225</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.02075</v>
+        <v>0.0295</v>
       </c>
       <c r="G7" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>0.018</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>0.01675</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>0.02075</v>
-      </c>
       <c r="K7" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.015</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.01875</v>
+        <v>0.017</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.02025</v>
+        <v>0.01475</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.02025</v>
+        <v>0.0105</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.01575</v>
+        <v>0.0075</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.01375</v>
+        <v>0.003</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.0095</v>
+        <v>0.00375</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.0055</v>
+        <v>0.0015</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.00225</v>
+        <v>0.0005</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -995,62 +998,64 @@
         <v>0.2495</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.03175</v>
+        <v>0.01025</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0325</v>
+        <v>0.01375</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.021</v>
+        <v>0.0155</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.017</v>
       </c>
       <c r="H8" s="3" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>0.02275</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>0.02175</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.0175</v>
-      </c>
       <c r="L8" s="3" t="n">
-        <v>0.016</v>
+        <v>0.01875</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.0135</v>
+        <v>0.023</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.0105</v>
+        <v>0.0255</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.00475</v>
+        <v>0.01775</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.00575</v>
+        <v>0.01175</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.00825</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.00175</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.001</v>
+        <v>0.00175</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="U8" s="2" t="n"/>
+        <v>0.00325</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0.0005</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1060,122 +1065,116 @@
         <v>0.2495</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.02275</v>
+        <v>0.0405</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.02875</v>
+        <v>0.0335</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.02375</v>
+        <v>0.023</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.0275</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02075</v>
+        <v>0.01825</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.02025</v>
+        <v>0.02</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01775</v>
+        <v>0.01475</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.0165</v>
+        <v>0.017</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.01675</v>
+        <v>0.012</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.0095</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.0045</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.00425</v>
+        <v>0.00175</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.00025</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.2495</v>
+        <v>0.24925</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>0.01175</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0.01825</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="G10" s="3" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.02225</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>0.01875</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.02375</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.02175</v>
-      </c>
       <c r="L10" s="3" t="n">
-        <v>0.01725</v>
+        <v>0.02325</v>
       </c>
       <c r="M10" s="3" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="N10" s="3" t="n">
         <v>0.0155</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>0.016</v>
-      </c>
       <c r="O10" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.01925</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.00775</v>
+        <v>0.01275</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.006</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.00375</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0.00175</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0.001</v>
+        <v>0.0015</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>0.001</v>
@@ -1184,74 +1183,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2495</v>
+        <v>0.24925</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.0115</v>
+        <v>0.02225</v>
       </c>
       <c r="E11" s="4" t="n">
+        <v>0.02225</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.02375</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>0.0155</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.01425</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0.01825</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0.02025</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.0205</v>
-      </c>
       <c r="N11" s="4" t="n">
-        <v>0.017</v>
+        <v>0.01625</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.01675</v>
+        <v>0.011</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.01325</v>
+        <v>0.00625</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00275</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.00625</v>
+        <v>0.002</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.00375</v>
+        <v>0.001</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.00075</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.00175</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1261,58 +1260,58 @@
         <v>0.249</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.01325</v>
+        <v>0.01175</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.01475</v>
+        <v>0.0145</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.014</v>
+        <v>0.01775</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.0205</v>
+        <v>0.01725</v>
       </c>
       <c r="H12" s="3" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>0.0215</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>0.02075</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.02075</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.02075</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.02025</v>
-      </c>
       <c r="N12" s="3" t="n">
-        <v>0.01775</v>
+        <v>0.01575</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.01775</v>
+        <v>0.0185</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.00775</v>
+        <v>0.01175</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.00475</v>
+        <v>0.00675</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.006</v>
+        <v>0.0055</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0.001</v>
+        <v>0.00075</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="13">
@@ -1325,61 +1324,61 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2485</v>
+        <v>0.24825</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.011</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.01325</v>
+        <v>0.01425</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01675</v>
+        <v>0.01575</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01725</v>
+        <v>0.0185</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0.01575</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.01875</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.02275</v>
+        <v>0.022</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.02225</v>
+        <v>0.0195</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.01825</v>
+        <v>0.023</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.01925</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.0165</v>
+        <v>0.01725</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.00625</v>
+        <v>0.008</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.00525</v>
+        <v>0.00575</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>0.00175</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="14">
@@ -1392,61 +1391,57 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.21525</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+        <v>0.20925</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.00075</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.0005</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.0015</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.00175</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.00225</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.00325</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.00675</v>
+        <v>0.00425</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.00925</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.01</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.021</v>
+        <v>0.01825</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.028</v>
+        <v>0.02825</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.02925</v>
+        <v>0.0285</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.0295</v>
+        <v>0.03225</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.031</v>
+        <v>0.0265</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.019</v>
+        <v>0.02125</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.02075</v>
       </c>
     </row>
     <row r="15">
@@ -1459,55 +1454,55 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.19825</v>
-      </c>
-      <c r="F15" s="4" t="n">
+        <v>0.20075</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>0.00025</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>0.0005</v>
-      </c>
       <c r="H15" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.00125</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.003</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.00225</v>
+        <v>0.0015</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.00475</v>
+        <v>0.0015</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0045</v>
+        <v>0.00275</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>0.0075</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.014</v>
+        <v>0.0095</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.01375</v>
+        <v>0.0135</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.01475</v>
+        <v>0.0225</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.02975</v>
+        <v>0.0235</v>
       </c>
       <c r="R15" s="4" t="n">
         <v>0.03325</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.02525</v>
+        <v>0.031</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.02525</v>
+        <v>0.02575</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.02125</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="16">
@@ -1520,121 +1515,114 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.19025</v>
+        <v>0.18925</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="F16" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.0005</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.0005</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.001</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.0005</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.00225</v>
+        <v>0.00325</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.002</v>
+        <v>0.00375</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0045</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.0105</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.019</v>
+        <v>0.0205</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.02625</v>
+        <v>0.0285</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.02775</v>
+        <v>0.02525</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.02975</v>
+        <v>0.0255</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.02675</v>
+        <v>0.02725</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.18975</v>
-      </c>
-      <c r="E17" s="4" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>0.0005</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0.00025</v>
-      </c>
       <c r="I17" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="J17" s="4" t="n">
         <v>0.00075</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.00325</v>
+        <v>0.00075</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.00425</v>
+        <v>0.002</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.00675</v>
+        <v>0.00225</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.00675</v>
+        <v>0.0055</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.00925</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.01925</v>
+        <v>0.014</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.02725</v>
+        <v>0.02225</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.02575</v>
+        <v>0.027</v>
       </c>
       <c r="S17" s="4" t="n">
         <v>0.02625</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.03175</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.02575</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="18">
@@ -1647,188 +1635,176 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+        <v>0.1705</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="3" t="n">
         <v>0.00025</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.0005</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.0005</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.0015</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.00225</v>
+        <v>0.00175</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.004</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.008</v>
+        <v>0.00525</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.01</v>
+        <v>0.01325</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.019</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.02925</v>
+        <v>0.02425</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.02725</v>
+        <v>0.028</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.0275</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.026</v>
+        <v>0.02475</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.1685</v>
+        <v>0.16175</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
-      <c r="F19" s="6" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="6" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.00075</v>
-      </c>
+        <v>0.00025</v>
+      </c>
+      <c r="J19" s="5" t="n"/>
       <c r="K19" s="6" t="n">
         <v>0.0015</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.00175</v>
+        <v>0.00225</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0055</v>
+        <v>0.00325</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.00525</v>
+        <v>0.005</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.01</v>
+        <v>0.008750000000000001</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.015</v>
+        <v>0.0155</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.01925</v>
+        <v>0.02475</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.01775</v>
+        <v>0.022</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.0285</v>
+        <v>0.0245</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.02875</v>
+        <v>0.02675</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.033</v>
+        <v>0.02725</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1495</v>
+        <v>0.1485</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="3" t="n">
         <v>0.0005</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.0005</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.00225</v>
+        <v>0.001</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0.002</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.00425</v>
+        <v>0.00225</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.012</v>
+        <v>0.01075</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01725</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.02475</v>
+        <v>0.0295</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.02625</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.134</v>
+        <v>0.147</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>0.00025</v>
@@ -1839,35 +1815,38 @@
       <c r="J21" s="4" t="n">
         <v>0.0005</v>
       </c>
+      <c r="K21" s="4" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L21" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00075</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.00225</v>
+        <v>0.002</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.00425</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.01</v>
+        <v>0.01175</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.01275</v>
+        <v>0.021</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.01375</v>
+        <v>0.01825</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.02175</v>
+        <v>0.02525</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.0325</v>
+        <v>0.03</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.03125</v>
+        <v>0.02375</v>
       </c>
     </row>
     <row r="22">
@@ -1880,43 +1859,49 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.08271522788301899</v>
+        <v>0.09399999999999999</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="H22" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>0.0003121329354076188</v>
+        <v>0.00025</v>
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
+      <c r="M22" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="N22" s="3" t="n">
-        <v>0.001248531741630475</v>
+        <v>0.00125</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.001872797612445713</v>
+        <v>0.00375</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.002809196418668569</v>
+        <v>0.00575</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.00530625990192952</v>
+        <v>0.00725</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.0115489186100819</v>
+        <v>0.01375</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.01591877970578856</v>
+        <v>0.0155</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.01841584318904951</v>
+        <v>0.01875</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.02528276776801713</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="23">
@@ -1932,28 +1917,28 @@
         <v>0.08054808646256829</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.002301373898930523</v>
+        <v>0.002684936215418943</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.002301373898930523</v>
+        <v>0.005369872430837886</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.009205495595722091</v>
+        <v>0.002684936215418943</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01380824339358314</v>
+        <v>0.008054808646256828</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.01380824339358314</v>
+        <v>0.02147948972335154</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.03912335628181889</v>
+        <v>0.04027404323128414</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1978,19 +1963,19 @@
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="3" t="n">
-        <v>0.0156800418316979</v>
+        <v>0.007840020915848948</v>
       </c>
       <c r="T24" s="3" t="n">
+        <v>0.04704012549509369</v>
+      </c>
+      <c r="U24" s="3" t="n">
         <v>0.02352006274754685</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>0.03920010457924474</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2000,16 +1985,16 @@
         <v>0.07627177032444879</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.005867059255726829</v>
+        <v>0.01271196172074147</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.005867059255726829</v>
+        <v>0.01271196172074147</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.02346823702290732</v>
+        <v>0.02542392344148293</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.04106941479008781</v>
+        <v>0.02542392344148293</v>
       </c>
     </row>
     <row r="26">
@@ -2260,7 +2245,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2293,7 +2278,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2309,7 +2294,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2342,7 +2327,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2358,7 +2343,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2391,7 +2376,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2407,7 +2392,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2440,7 +2425,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2456,7 +2441,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2636,7 +2621,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OlgaaGeorgieva</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2652,7 +2637,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>OlgaaGeorgieva</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2701,7 +2686,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2734,7 +2719,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2848,7 +2833,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2881,7 +2866,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>elli</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2930,7 +2915,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>repe_kate</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2946,7 +2931,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>Mar_u_shka</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -3044,7 +3029,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -3077,7 +3062,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3093,7 +3078,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3126,7 +3111,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3142,7 +3127,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3175,7 +3160,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3191,7 +3176,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3224,7 +3209,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3240,7 +3225,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3273,7 +3258,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3289,7 +3274,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -601,62 +601,36 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.03325</v>
+        <v>0.17025</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.02625</v>
+        <v>0.065</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.02725</v>
+        <v>0.01425</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02325</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0.01225</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>0.01275</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0.00725</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.00225</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.00225</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="T2" s="3" t="n">
         <v>0.0005</v>
       </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -666,64 +640,25 @@
         <v>0.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.02525</v>
+        <v>0.008</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.02</v>
+        <v>0.04425</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.0205</v>
+        <v>0.18675</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.01075</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.0245</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.02625</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0.01725</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="U3" s="4" t="n">
         <v>0.00025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -732,65 +667,37 @@
       <c r="C4" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0245</v>
-      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.01225</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.021</v>
+        <v>0.20375</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.02175</v>
+        <v>0.03025</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.02075</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.01975</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+        <v>0.00375</v>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -799,391 +706,232 @@
       <c r="C5" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.01775</v>
-      </c>
       <c r="G5" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.0315</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.01975</v>
+        <v>0.17625</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.0185</v>
+        <v>0.042</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.02325</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0.01525</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.0015</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.24975</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.01275</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.01825</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="3" t="n">
-        <v>0.01775</v>
+        <v>0.003</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.043</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.196</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.007</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.01775</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.01975</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0.02275</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0.02125</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+        <v>0.001</v>
+      </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.24975</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.03225</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.25</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.01675</v>
+        <v>0.15375</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.015</v>
+        <v>0.066</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.017</v>
+        <v>0.0175</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.01475</v>
+        <v>0.00475</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.0105</v>
+        <v>0.00075</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="T7" s="4" t="n">
         <v>0.00025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.2495</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0.01025</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0.01875</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="3" t="n">
-        <v>0.0205</v>
+        <v>0.00125</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.07124999999999999</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.02275</v>
+        <v>0.11275</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.04275</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.0255</v>
+        <v>0.0035</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.01775</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.01175</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>0.00825</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="U8" s="3" t="n">
         <v>0.0005</v>
       </c>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.2495</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.0405</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.01825</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.018</v>
+        <v>0.0145</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01475</v>
+        <v>0.044</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.017</v>
+        <v>0.08925</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.012</v>
+        <v>0.05525</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0215</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.01375</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0045</v>
+        <v>0.00575</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.00175</v>
+        <v>0.003</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.00125</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>0.001</v>
       </c>
+      <c r="T9" s="4" t="n">
+        <v>0.00075</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.24925</v>
+        <v>0.25</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01175</v>
+        <v>0.07174999999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.14075</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.03675</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.01925</v>
+        <v>0.0005</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.01875</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.02325</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0.02125</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>0.01925</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.01275</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.00025</v>
+      </c>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1192,59 +940,41 @@
       <c r="C11" s="4" t="n">
         <v>0.24925</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.02275</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.02125</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0.02375</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0.0195</v>
-      </c>
       <c r="J11" s="4" t="n">
-        <v>0.022</v>
+        <v>0.00275</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02125</v>
+        <v>0.017</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.0185</v>
+        <v>0.047</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.067</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.01625</v>
+        <v>0.04575</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.011</v>
+        <v>0.02825</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.00625</v>
+        <v>0.0165</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.01225</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="S11" s="4" t="n">
+        <v>0.00425</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>0.001</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0.00025</v>
       </c>
     </row>
     <row r="12">
@@ -1257,431 +987,347 @@
         <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0.01175</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0.01775</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0.01725</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0.02025</v>
-      </c>
+        <v>0.2445</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>0.02175</v>
+        <v>0.00025</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.02125</v>
+        <v>0.0055</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.02275</v>
+        <v>0.0225</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.0215</v>
+        <v>0.03</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.01575</v>
+        <v>0.049</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.0185</v>
+        <v>0.0355</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.01175</v>
+        <v>0.03575</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.00675</v>
+        <v>0.02675</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.01625</v>
       </c>
       <c r="S12" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>0.002</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>0.00075</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.24825</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.01425</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.01575</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0.01575</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0.01875</v>
+        <v>0.241</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.025</v>
+        <v>0.00025</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.022</v>
+        <v>0.00125</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.00975</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0205</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.01925</v>
+        <v>0.03275</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.01725</v>
+        <v>0.03575</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.01</v>
+        <v>0.037</v>
       </c>
       <c r="Q13" s="4" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>0.008</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0.00575</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0.00075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.20925</v>
+        <v>0.2355</v>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="3" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.00225</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
       <c r="K14" s="3" t="n">
-        <v>0.00325</v>
+        <v>0.001</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.00425</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.00925</v>
+        <v>0.01825</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02875</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.0365</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.02825</v>
+        <v>0.03725</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.0285</v>
+        <v>0.03275</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.03225</v>
+        <v>0.02925</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.0265</v>
+        <v>0.02025</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.02125</v>
+        <v>0.01325</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.02075</v>
+        <v>0.00975</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.20075</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0.0015</v>
+        <v>0.235</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0015</v>
+        <v>0.00075</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.00675</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.0075</v>
+        <v>0.01625</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.0095</v>
+        <v>0.03325</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.0135</v>
+        <v>0.036</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.0225</v>
+        <v>0.034</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.033</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.03325</v>
+        <v>0.02925</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.031</v>
+        <v>0.02075</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.02575</v>
+        <v>0.0145</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.18925</v>
+        <v>0.22</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="F16" s="3" t="n">
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="3" t="n">
         <v>0.0005</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0.00325</v>
-      </c>
       <c r="L16" s="3" t="n">
-        <v>0.00375</v>
+        <v>0.003</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.011</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0155</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.012</v>
+        <v>0.02575</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.0205</v>
+        <v>0.0235</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.026</v>
+        <v>0.03325</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.0285</v>
+        <v>0.0365</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.02525</v>
+        <v>0.028</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>0.0255</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>0.02725</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1725</v>
-      </c>
-      <c r="G17" s="4" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>0.00025</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0.00075</v>
-      </c>
       <c r="L17" s="4" t="n">
-        <v>0.002</v>
+        <v>0.00275</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.00225</v>
+        <v>0.00725</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.0055</v>
+        <v>0.011</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.00925</v>
+        <v>0.02175</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.014</v>
+        <v>0.0285</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.02225</v>
+        <v>0.0305</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.027</v>
+        <v>0.03075</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.02625</v>
+        <v>0.033</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.03175</v>
+        <v>0.0285</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1705</v>
+        <v>0.16175</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="3" t="n">
         <v>0.00025</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.00175</v>
-      </c>
       <c r="M18" s="3" t="n">
-        <v>0.004</v>
+        <v>0.00225</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.00525</v>
+        <v>0.00375</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.01325</v>
+        <v>0.00675</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.019</v>
+        <v>0.0145</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.02</v>
+        <v>0.0155</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.02425</v>
+        <v>0.02575</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.028</v>
+        <v>0.0305</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.03125</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.02475</v>
+        <v>0.03125</v>
       </c>
     </row>
     <row r="19">
@@ -1694,49 +1340,43 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.16175</v>
+        <v>0.12</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
-      <c r="I19" s="6" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
-      <c r="K19" s="6" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="L19" s="6" t="n">
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="6" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="N19" s="6" t="n">
         <v>0.00225</v>
       </c>
-      <c r="M19" s="6" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.005</v>
-      </c>
       <c r="O19" s="6" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.006</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.02475</v>
+        <v>0.00975</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.022</v>
+        <v>0.01375</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.0245</v>
+        <v>0.0185</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.02675</v>
+        <v>0.03325</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.02725</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="20">
@@ -1749,7 +1389,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1485</v>
+        <v>0.11375</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1757,41 +1397,35 @@
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
-      <c r="J20" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.001</v>
-      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
       <c r="M20" s="3" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="O20" s="3" t="n">
         <v>0.002</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>0.00225</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>0.006</v>
-      </c>
       <c r="P20" s="3" t="n">
-        <v>0.01075</v>
+        <v>0.0065</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.018</v>
+        <v>0.0095</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.01725</v>
+        <v>0.01525</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.0295</v>
+        <v>0.02225</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.02625</v>
+        <v>0.02775</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="21">
@@ -1804,110 +1438,85 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.08490146367539786</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.002</v>
+        <v>0.0002858635140585786</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.00425</v>
+        <v>0.001715181084351472</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.007</v>
+        <v>0.002572771626527207</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.01175</v>
+        <v>0.001715181084351472</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.021</v>
+        <v>0.005145543253054415</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.01825</v>
+        <v>0.007718314879581623</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.02525</v>
+        <v>0.01658008381539756</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02029630949815908</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.02375</v>
+        <v>0.02887221491991644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>AlexBluff</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.09399999999999999</v>
+        <v>0.08271522788301899</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>0.00125</v>
-      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="3" t="n">
-        <v>0.00375</v>
+        <v>0.001434368113578364</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.00575</v>
+        <v>0.002390613522630607</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.00725</v>
+        <v>0.004303104340735092</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.01375</v>
+        <v>0.008128085976944064</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.01434368113578364</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.01673429465841425</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.027</v>
+        <v>0.03538108013493298</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AlexBluff</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1917,28 +1526,28 @@
         <v>0.08054808646256829</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.002684936215418943</v>
+        <v>0.001776796024909595</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.005369872430837886</v>
+        <v>0.004145857391455722</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.002684936215418943</v>
+        <v>0.00355359204981919</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.008054808646256828</v>
+        <v>0.01184530683273063</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.02147948972335154</v>
+        <v>0.02369061366546127</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.04027404323128414</v>
+        <v>0.0355359204981919</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1959,23 +1568,29 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="n"/>
+      <c r="P24" s="3" t="n">
+        <v>0.002657634208762355</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>0.003986451313143533</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>0.005315268417524711</v>
+      </c>
       <c r="S24" s="3" t="n">
-        <v>0.007840020915848948</v>
+        <v>0.01661021380476472</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.04704012549509369</v>
+        <v>0.01594580525257413</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.02352006274754685</v>
+        <v>0.03388483616172003</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1984,23 +1599,26 @@
       <c r="C25" s="4" t="n">
         <v>0.07627177032444879</v>
       </c>
+      <c r="Q25" s="4" t="n">
+        <v>0.003720574162168234</v>
+      </c>
       <c r="R25" s="4" t="n">
-        <v>0.01271196172074147</v>
+        <v>0.0111617224865047</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.01271196172074147</v>
+        <v>0.007441148324336468</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.02542392344148293</v>
+        <v>0.01674258372975705</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.02542392344148293</v>
+        <v>0.03720574162168234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2020,20 +1638,26 @@
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
+      <c r="O26" s="3" t="n">
+        <v>0.00200440403069711</v>
+      </c>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="n"/>
+      <c r="S26" s="3" t="n">
+        <v>0.008017616122788439</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.02405284836836532</v>
+      </c>
       <c r="U26" s="3" t="n">
-        <v>0.07416294913579306</v>
+        <v>0.04008808061394219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2042,8 +1666,23 @@
       <c r="C27" s="4" t="n">
         <v>0.07207392981597664</v>
       </c>
+      <c r="P27" s="4" t="n">
+        <v>0.002059255137599333</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0.002059255137599333</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0.004118510275198666</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0.006177765412797998</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0.01647404110079466</v>
+      </c>
       <c r="U27" s="4" t="n">
-        <v>0.07207392981597664</v>
+        <v>0.04118510275198665</v>
       </c>
     </row>
     <row r="28">
@@ -2071,12 +1710,20 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
-      <c r="T28" s="2" t="n"/>
+      <c r="Q28" s="3" t="n">
+        <v>0.005384992452166209</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>0.01076998490433242</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>0.01615497735649863</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>0.005384992452166209</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>0.07000490187816071</v>
+        <v>0.03230995471299725</v>
       </c>
     </row>
     <row r="29">
@@ -2091,8 +1738,20 @@
       <c r="C29" s="4" t="n">
         <v>0.06795606038331763</v>
       </c>
+      <c r="Q29" s="4" t="n">
+        <v>0.004530404025554508</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0.004530404025554508</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>0.009060808051109016</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>0.009060808051109016</v>
+      </c>
       <c r="U29" s="4" t="n">
-        <v>0.06795606038331763</v>
+        <v>0.04077363622999057</v>
       </c>
     </row>
     <row r="30">
@@ -2122,16 +1781,20 @@
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n"/>
+      <c r="S30" s="3" t="n">
+        <v>0.02197586873877316</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>0.03296380310815974</v>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>0.06592760621631949</v>
+        <v>0.01098793436938658</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2147,7 +1810,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -2180,7 +1843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2196,7 +1859,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -2229,7 +1892,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2238,14 +1901,14 @@
       <c r="C35" s="4" t="n">
         <v>0.05609862308114691</v>
       </c>
-      <c r="U35" s="4" t="n">
-        <v>0.05609862308114691</v>
+      <c r="S35" s="4" t="n">
+        <v>0.05609862308114692</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2278,7 +1941,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2294,7 +1957,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -2343,7 +2006,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2376,7 +2039,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2425,7 +2088,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>mflameee</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2441,7 +2104,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2474,7 +2137,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2490,7 +2153,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2523,7 +2186,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2539,7 +2202,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2572,7 +2235,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Адольф</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2588,7 +2251,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2621,7 +2284,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Адольф</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2637,7 +2300,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>OlgaaGeorgieva</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2670,7 +2333,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>OlgaaGeorgieva</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2686,7 +2349,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>STG</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2719,7 +2382,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2735,7 +2398,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>STG</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2784,7 +2447,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>dance_with_vlad</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2817,7 +2480,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ташкент</t>
+          <t>elli</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2833,7 +2496,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>dance_with_vlad</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2866,7 +2529,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>imt360_ATDK</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2882,7 +2545,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>imt360_ATDK</t>
+          <t>Ташкент</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3062,7 +2725,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3078,7 +2741,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -3111,7 +2774,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3160,7 +2823,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3176,7 +2839,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3209,7 +2872,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3225,7 +2888,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3258,7 +2921,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3274,7 +2937,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -601,583 +601,929 @@
         <v>0.25</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.17025</v>
+        <v>0.02875</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.065</v>
+        <v>0.03075</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.01425</v>
+        <v>0.0255</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.01525</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
+      <c r="T2" s="3" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.00075</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Гризли</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.25</v>
+        <v>0.24975</v>
       </c>
       <c r="D3" s="4" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.02775</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.02525</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.01725</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>0.008</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>0.04425</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.18675</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.01075</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.00025</v>
+      <c r="Q3" s="4" t="n">
+        <v>0.00425</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.00075</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
+        <v>0.24975</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.0285</v>
+      </c>
       <c r="F4" s="3" t="n">
-        <v>0.01225</v>
+        <v>0.03075</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.20375</v>
+        <v>0.0205</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.03025</v>
+        <v>0.0185</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
+        <v>0.0165</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.01125</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.008750000000000001</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>кинчоч</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.25</v>
+        <v>0.24925</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.02375</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.0315</v>
+        <v>0.01875</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.17625</v>
+        <v>0.022</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.042</v>
+        <v>0.0175</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.019</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0.0015</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+        <v>0.24825</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.017</v>
+      </c>
       <c r="G6" s="3" t="n">
-        <v>0.003</v>
+        <v>0.01575</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.043</v>
+        <v>0.01375</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.196</v>
+        <v>0.0145</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.007</v>
+        <v>0.0175</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="n"/>
+        <v>0.01725</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0.0025</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.25</v>
+        <v>0.248</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.02125</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.007</v>
+        <v>0.01875</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.15375</v>
+        <v>0.01825</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.066</v>
+        <v>0.0195</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.0175</v>
+        <v>0.014</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.00475</v>
+        <v>0.01425</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.01375</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.0165</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0.00175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+        <v>0.248</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.0145</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.0185</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.07124999999999999</v>
+        <v>0.01775</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.11275</v>
+        <v>0.01825</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.04275</v>
+        <v>0.02225</v>
       </c>
       <c r="M8" s="3" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0.01775</v>
+      </c>
+      <c r="P8" s="3" t="n">
         <v>0.016</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
+        <v>0.01225</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.00475</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0.00275</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>кинчоч</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.25</v>
+        <v>0.24775</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.01925</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.01675</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.044</v>
+        <v>0.01825</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.08925</v>
+        <v>0.0195</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.05525</v>
+        <v>0.01575</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.0215</v>
+        <v>0.014</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.01375</v>
+        <v>0.01075</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.00575</v>
+        <v>0.01075</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.003</v>
+        <v>0.00775</v>
       </c>
       <c r="R9" s="4" t="n">
+        <v>0.00475</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="T9" s="4" t="n">
         <v>0.00125</v>
       </c>
-      <c r="S9" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0.00075</v>
+      <c r="U9" s="4" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Гризли</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24775</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.07174999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.14075</v>
+        <v>0.014</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.03675</v>
+        <v>0.0125</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.017</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
+        <v>0.01725</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.01725</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.01725</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.00725</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.00075</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.24925</v>
+        <v>0.24725</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.02025</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.018</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.019</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.017</v>
+        <v>0.0165</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.047</v>
+        <v>0.021</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.067</v>
+        <v>0.01575</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.04575</v>
+        <v>0.02025</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.02825</v>
+        <v>0.0165</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.0165</v>
+        <v>0.01525</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.01225</v>
+        <v>0.01</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.006</v>
+        <v>0.0065</v>
       </c>
       <c r="S11" s="4" t="n">
         <v>0.00425</v>
       </c>
       <c r="T11" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>0.0015</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.2445</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+        <v>0.24725</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.02075</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.01775</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.01775</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.01675</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.03</v>
+        <v>0.0165</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.049</v>
+        <v>0.01625</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.0355</v>
+        <v>0.01475</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.03575</v>
+        <v>0.01225</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0.02675</v>
+        <v>0.01325</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0.01625</v>
+        <v>0.00975</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0.008</v>
+        <v>0.00425</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.002</v>
+        <v>0.00175</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.241</v>
+        <v>0.24725</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.01625</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.02325</v>
       </c>
       <c r="K13" s="4" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0.01075</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>0.00125</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.00975</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0.03275</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0.03575</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0.02875</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0.008</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2355</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
+        <v>0.245</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.01425</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.016</v>
+      </c>
       <c r="K14" s="3" t="n">
-        <v>0.001</v>
+        <v>0.01875</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.01825</v>
+        <v>0.02125</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.016</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.016</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.03725</v>
+        <v>0.01925</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.03275</v>
+        <v>0.0115</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.02925</v>
+        <v>0.01125</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.02025</v>
+        <v>0.0065</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.01325</v>
+        <v>0.00425</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.00975</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.235</v>
+        <v>0.23775</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.01175</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.01075</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.0135</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.00675</v>
+        <v>0.016</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.01625</v>
+        <v>0.017</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.03325</v>
+        <v>0.0195</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.036</v>
+        <v>0.0205</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.02925</v>
+        <v>0.0165</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.02075</v>
+        <v>0.01325</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.0105</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.0105</v>
+        <v>0.00825</v>
       </c>
     </row>
     <row r="16">
@@ -1190,282 +1536,342 @@
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.22</v>
+        <v>0.17125</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.0015</v>
+      </c>
       <c r="K16" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.00275</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.003</v>
+        <v>0.00375</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.011</v>
+        <v>0.00475</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.00625</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="U16" s="3" t="n">
         <v>0.02575</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0.03325</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>0.0255</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>0.0175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.211</v>
+        <v>0.153</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.00125</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.002</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.0015</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.00725</v>
+        <v>0.00425</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.011</v>
+        <v>0.0065</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.02175</v>
+        <v>0.008</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.0285</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="Q17" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0.02425</v>
+      </c>
+      <c r="S17" s="4" t="n">
         <v>0.0305</v>
       </c>
-      <c r="R17" s="4" t="n">
-        <v>0.03075</v>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>0.033</v>
-      </c>
       <c r="T17" s="4" t="n">
-        <v>0.0285</v>
+        <v>0.02675</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.01675</v>
+        <v>0.02375</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.16175</v>
+        <v>0.1315</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="H18" s="3" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.00075</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.002</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.00225</v>
+        <v>0.00275</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.00375</v>
+        <v>0.00175</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.00675</v>
+        <v>0.00825</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.0145</v>
+        <v>0.00725</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.0155</v>
+        <v>0.011</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.02575</v>
+        <v>0.0185</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.0305</v>
+        <v>0.02175</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.03125</v>
+        <v>0.027</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.03125</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.12</v>
+        <v>0.1175</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.00075</v>
+      </c>
       <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="M19" s="6" t="n">
-        <v>0.0005</v>
+        <v>0.00275</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.00225</v>
+        <v>0.003</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.0025</v>
+        <v>0.0035</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.006</v>
+        <v>0.00625</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.00975</v>
+        <v>0.0095</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.01375</v>
+        <v>0.01775</v>
       </c>
       <c r="S19" s="6" t="n">
         <v>0.0185</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.03325</v>
+        <v>0.02425</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.0335</v>
+        <v>0.02925</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.11375</v>
+        <v>0.115</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
+      <c r="I20" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.00125</v>
+      </c>
       <c r="M20" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.00175</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.0025</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.002</v>
+        <v>0.0045</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.00725</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.0095</v>
+        <v>0.012</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.01525</v>
+        <v>0.0145</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.02225</v>
+        <v>0.02125</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.02775</v>
+        <v>0.02175</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.08490146367539786</v>
+        <v>0.1145</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.00075</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.0002858635140585786</v>
+        <v>0.0015</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.001715181084351472</v>
+        <v>0.00225</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.002572771626527207</v>
+        <v>0.00425</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.001715181084351472</v>
+        <v>0.005</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.005145543253054415</v>
+        <v>0.01275</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.007718314879581623</v>
+        <v>0.016</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.01658008381539756</v>
+        <v>0.0195</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.02029630949815908</v>
+        <v>0.0245</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.02887221491991644</v>
+        <v>0.02625</v>
       </c>
     </row>
     <row r="22">
@@ -1478,76 +1884,107 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.08271522788301899</v>
+        <v>0.104</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+      <c r="I22" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.00075</v>
+      </c>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
+      <c r="M22" s="3" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0.00125</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>0.001434368113578364</v>
+        <v>0.00525</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.002390613522630607</v>
+        <v>0.00475</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.004303104340735092</v>
+        <v>0.0105</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.008128085976944064</v>
+        <v>0.013</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.01434368113578364</v>
+        <v>0.01975</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.01673429465841425</v>
+        <v>0.02275</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.03538108013493298</v>
+        <v>0.02375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.08054808646256829</v>
+        <v>0.08875</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.00125</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0.00225</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.001776796024909595</v>
+        <v>0.00575</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.004145857391455722</v>
+        <v>0.00625</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.00355359204981919</v>
+        <v>0.012</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01184530683273063</v>
+        <v>0.0165</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.02369061366546127</v>
+        <v>0.01725</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.0355359204981919</v>
+        <v>0.02225</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1563,28 +2000,34 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="n"/>
+      <c r="K24" s="3" t="n">
+        <v>0.0008711134350943276</v>
+      </c>
       <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="3" t="n">
+        <v>0.0008711134350943276</v>
+      </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="O24" s="3" t="n">
+        <v>0.0008711134350943276</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>0.002657634208762355</v>
+        <v>0.004355567175471638</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.003986451313143533</v>
+        <v>0.00348445374037731</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>0.005315268417524711</v>
+        <v>0.007840020915848948</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.01661021380476472</v>
+        <v>0.008711134350943277</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.01594580525257413</v>
+        <v>0.02439117618264117</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.03388483616172003</v>
+        <v>0.02700451648792416</v>
       </c>
     </row>
     <row r="25">
@@ -1599,26 +2042,32 @@
       <c r="C25" s="4" t="n">
         <v>0.07627177032444879</v>
       </c>
+      <c r="N25" s="4" t="n">
+        <v>0.002276769263416382</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>0.002276769263416382</v>
+      </c>
       <c r="Q25" s="4" t="n">
-        <v>0.003720574162168234</v>
+        <v>0.002276769263416382</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.0111617224865047</v>
+        <v>0.005691923158540954</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.007441148324336468</v>
+        <v>0.01593738484391467</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.01674258372975705</v>
+        <v>0.01593738484391467</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.03720574162168234</v>
+        <v>0.03187476968782935</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>Davit</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1638,26 +2087,20 @@
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
-      <c r="O26" s="3" t="n">
-        <v>0.00200440403069711</v>
-      </c>
+      <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
-      <c r="S26" s="3" t="n">
-        <v>0.008017616122788439</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>0.02405284836836532</v>
-      </c>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
       <c r="U26" s="3" t="n">
-        <v>0.04008808061394219</v>
+        <v>0.07416294913579306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>bogdanov</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1666,29 +2109,23 @@
       <c r="C27" s="4" t="n">
         <v>0.07207392981597664</v>
       </c>
-      <c r="P27" s="4" t="n">
-        <v>0.002059255137599333</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0.002059255137599333</v>
+      <c r="O27" s="4" t="n">
+        <v>0.01201232163599611</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.004118510275198666</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>0.006177765412797998</v>
+        <v>0.01201232163599611</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.01647404110079466</v>
+        <v>0.02402464327199222</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.04118510275198665</v>
+        <v>0.02402464327199222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1710,26 +2147,18 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="3" t="n">
-        <v>0.005384992452166209</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>0.01076998490433242</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>0.01615497735649863</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>0.005384992452166209</v>
-      </c>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
       <c r="U28" s="3" t="n">
-        <v>0.03230995471299725</v>
+        <v>0.07000490187816071</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1738,26 +2167,14 @@
       <c r="C29" s="4" t="n">
         <v>0.06795606038331763</v>
       </c>
-      <c r="Q29" s="4" t="n">
-        <v>0.004530404025554508</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0.004530404025554508</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>0.009060808051109016</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>0.009060808051109016</v>
-      </c>
       <c r="U29" s="4" t="n">
-        <v>0.04077363622999057</v>
+        <v>0.06795606038331763</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1781,20 +2198,16 @@
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
-      <c r="S30" s="3" t="n">
-        <v>0.02197586873877316</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>0.03296380310815974</v>
-      </c>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
       <c r="U30" s="3" t="n">
-        <v>0.01098793436938658</v>
+        <v>0.06592760621631949</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1810,7 +2223,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1843,7 +2256,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1859,7 +2272,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1901,14 +2314,14 @@
       <c r="C35" s="4" t="n">
         <v>0.05609862308114691</v>
       </c>
-      <c r="S35" s="4" t="n">
-        <v>0.05609862308114692</v>
+      <c r="U35" s="4" t="n">
+        <v>0.05609862308114691</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1941,7 +2354,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1957,7 +2370,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1990,7 +2403,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2006,7 +2419,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>mflameee</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -2039,7 +2452,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2055,7 +2468,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -2088,7 +2501,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2104,7 +2517,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2137,7 +2550,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2186,7 +2599,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2202,7 +2615,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2235,7 +2648,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2251,7 +2664,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2431,7 +2844,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2447,7 +2860,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>elli</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2480,7 +2893,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2496,7 +2909,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>dance_with_vlad</t>
+          <t>imt360_ATDK</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2529,7 +2942,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>imt360_ATDK</t>
+          <t>dance_with_vlad</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2692,7 +3105,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -2725,7 +3138,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2741,7 +3154,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -2774,7 +3187,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2790,7 +3203,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -2823,7 +3236,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2839,7 +3252,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -601,27 +601,29 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.594</v>
+        <v>0.71</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.235</v>
+        <v>0.203</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.112</v>
+        <v>0.053</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.034</v>
+        <v>0.022</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.002</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K2" s="2" t="n"/>
+        <v>0.001</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -646,31 +648,31 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.262</v>
+        <v>0.235</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.32</v>
+        <v>0.417</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.208</v>
+        <v>0.16</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.075</v>
+        <v>0.092</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
@@ -683,53 +685,55 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8432000000000001</v>
+        <v>0.8457500000000001</v>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="3" t="n">
+        <v>0.00595</v>
+      </c>
       <c r="H4" s="3" t="n">
-        <v>0.00255</v>
+        <v>0.0051</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.06034999999999999</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.10965</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.12835</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.10115</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.07479999999999999</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>0.0051</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.01615</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.02635</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.06204999999999999</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0.11135</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0.1207</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0.1241</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.10965</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.0595</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>0.05695</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0.017</v>
       </c>
     </row>
     <row r="5">
@@ -744,44 +748,47 @@
       <c r="C5" s="4" t="n">
         <v>0.8245</v>
       </c>
+      <c r="H5" s="4" t="n">
+        <v>0.00085</v>
+      </c>
       <c r="I5" s="4" t="n">
-        <v>0.00085</v>
+        <v>0.0034</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.00255</v>
+        <v>0.00595</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.01275</v>
+        <v>0.0102</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.017</v>
+        <v>0.03825</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.0408</v>
+        <v>0.0595</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.0663</v>
+        <v>0.0799</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.11135</v>
+        <v>0.12495</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.1003</v>
+        <v>0.13175</v>
       </c>
       <c r="Q5" s="4" t="n">
         <v>0.11815</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.10115</v>
+        <v>0.1139</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.10795</v>
+        <v>0.07905</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.04505</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.0425</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="6">
@@ -794,49 +801,51 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.8126</v>
+        <v>0.8168500000000001</v>
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="3" t="n">
+        <v>0.00085</v>
+      </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="3" t="n">
-        <v>0.00255</v>
+        <v>0.0051</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.0102</v>
+        <v>0.01275</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0255</v>
+        <v>0.02465</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.04165</v>
+        <v>0.04845</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.0765</v>
+        <v>0.08754999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.0901</v>
+        <v>0.0935</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.0901</v>
+        <v>0.12835</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.10965</v>
+        <v>0.1258</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.12495</v>
+        <v>0.12155</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.09179999999999999</v>
+        <v>0.0799</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.0765</v>
+        <v>0.0527</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.04675</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="7">
@@ -852,40 +861,40 @@
         <v>0.55</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.05885000000000001</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.08855</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.09570000000000001</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.09625</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.08745000000000001</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0.01815</v>
+      </c>
+      <c r="N7" s="4" t="n">
         <v>0.0044</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>0.02255</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.0396</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0.07754999999999999</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.08855</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>0.10395</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.0968</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0.06050000000000001</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.03465</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.009350000000000001</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0.00825</v>
-      </c>
       <c r="O7" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0033</v>
       </c>
       <c r="P7" s="4" t="n">
         <v>0.0011</v>
@@ -907,47 +916,45 @@
         <v>0.55</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0011</v>
+        <v>0.00055</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0143</v>
+        <v>0.01925</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.02365</v>
+        <v>0.05335000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.0517</v>
+        <v>0.06325000000000001</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.09295000000000002</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.09075000000000001</v>
+        <v>0.09350000000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.11</v>
+        <v>0.099</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.09405000000000001</v>
+        <v>0.06985000000000001</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.0462</v>
+        <v>0.03135</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.0198</v>
+        <v>0.01595</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.00715</v>
+        <v>0.00495</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.00165</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="Q8" s="3" t="n">
         <v>0.00055</v>
       </c>
+      <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n"/>
@@ -963,163 +970,165 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>0.00055</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.00165</v>
+        <v>0.0022</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.0033</v>
+        <v>0.003850000000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.01375</v>
+        <v>0.0143</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02035</v>
+        <v>0.0297</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04125</v>
+        <v>0.05060000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.07095000000000001</v>
+        <v>0.06050000000000001</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.10175</v>
+        <v>0.1122</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.09405000000000001</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0781</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.04565</v>
+        <v>0.0539</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.03465</v>
+        <v>0.02475</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0154</v>
+        <v>0.0143</v>
       </c>
       <c r="Q9" s="4" t="n">
         <v>0.00605</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.0033</v>
+        <v>0.0011</v>
       </c>
       <c r="S9" s="4" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="T9" s="4" t="n">
         <v>0.0011</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0.00055</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FISHer</t>
+          <t>Great Teacher Onizuka</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.3876000000000001</v>
+        <v>0.3732</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="3" t="n">
         <v>0.0004</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.002</v>
-      </c>
+      <c r="J10" s="2" t="n"/>
       <c r="K10" s="3" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0012</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.032</v>
+        <v>0.0144</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.0408</v>
+        <v>0.0296</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.0464</v>
+        <v>0.03920000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.0644</v>
+        <v>0.0444</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.0524</v>
+        <v>0.064</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.0328</v>
+        <v>0.0576</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0.0256</v>
+        <v>0.034</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0.0196</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Great Teacher Onizuka</t>
+          <t>FISHer</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3840000000000001</v>
+        <v>0.3556</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.002</v>
+        <v>0.0008</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.0036</v>
+        <v>0.0016</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.0208</v>
+        <v>0.0116</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0164</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.0344</v>
+        <v>0.0264</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.05280000000000001</v>
+        <v>0.0356</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.0576</v>
+        <v>0.052</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.05280000000000001</v>
+        <v>0.0644</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.04040000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0368</v>
+        <v>0.04680000000000001</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.0252</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="12">
@@ -1135,41 +1144,45 @@
         <v>0.25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.0065</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.04725</v>
+        <v>0.0285</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.05875</v>
+        <v>0.0565</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.05175</v>
+        <v>0.047</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.03375</v>
+        <v>0.041</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.02125</v>
+        <v>0.0295</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.01175</v>
+        <v>0.0235</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.00625</v>
+        <v>0.0105</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.00475</v>
       </c>
       <c r="M12" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N12" s="3" t="n">
         <v>0.00075</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="O12" s="3" t="n">
         <v>0.00025</v>
       </c>
-      <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
+      <c r="Q12" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="n"/>
@@ -1188,34 +1201,37 @@
         <v>0.25</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.0095</v>
+        <v>0.003</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.0255</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.044</v>
+        <v>0.0485</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.053</v>
+        <v>0.0485</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0405</v>
+        <v>0.04575</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.037</v>
+        <v>0.03425</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.02125</v>
+        <v>0.02225</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.01225</v>
+        <v>0.0145</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.004</v>
+        <v>0.00625</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="14">
@@ -1231,44 +1247,48 @@
         <v>0.25</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.00725</v>
+        <v>0.0025</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.019</v>
+        <v>0.01875</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.033</v>
+        <v>0.03625</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.046</v>
+        <v>0.04375</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.04575</v>
+        <v>0.03825</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.04475</v>
+        <v>0.04125</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.03675</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.01375</v>
+        <v>0.0145</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.00825</v>
+        <v>0.0105</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.00325</v>
+        <v>0.00425</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.001</v>
+        <v>0.00175</v>
       </c>
       <c r="O14" s="3" t="n">
+        <v>0.00075</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>0.0005</v>
       </c>
-      <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
+      <c r="R14" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="n"/>
@@ -1286,49 +1306,52 @@
         <v>0.25</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00075</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.004</v>
+        <v>0.00225</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.0035</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.01325</v>
+        <v>0.007</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.0175</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.03875</v>
+        <v>0.0295</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0585</v>
+        <v>0.04825</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>0.046</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.02625</v>
+        <v>0.03525</v>
       </c>
       <c r="N15" s="4" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>0.016</v>
       </c>
-      <c r="O15" s="4" t="n">
-        <v>0.00475</v>
-      </c>
       <c r="P15" s="4" t="n">
-        <v>0.00675</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.006</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.00125</v>
+        <v>0.00375</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.0015</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0.00025</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0.00025</v>
@@ -1347,53 +1370,55 @@
         <v>0.2495</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.0005</v>
+      </c>
       <c r="G16" s="3" t="n">
-        <v>0.0005</v>
+        <v>0.00125</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.002</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.0055</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.00725</v>
+        <v>0.01</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.0375</v>
+        <v>0.035</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.04075</v>
+        <v>0.04025</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.03825</v>
+        <v>0.04375</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.034</v>
+        <v>0.02875</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.024</v>
+        <v>0.0245</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.02</v>
+        <v>0.0155</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.01275</v>
+        <v>0.01175</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.0065</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>0.00225</v>
-      </c>
+        <v>0.00175</v>
+      </c>
+      <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1405,49 +1430,52 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.24875</v>
+        <v>0.24625</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.00025</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0.00025</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.0015</v>
+        <v>0.00075</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.00475</v>
+        <v>0.003</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0075</v>
+        <v>0.011</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.02075</v>
+        <v>0.01775</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.032</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.0375</v>
+        <v>0.035</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.03625</v>
+        <v>0.038</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.029</v>
+        <v>0.03775</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.0245</v>
+        <v>0.02825</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.018</v>
+        <v>0.0175</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.01675</v>
+        <v>0.0135</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.00925</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.00275</v>
       </c>
     </row>
     <row r="18">
@@ -1460,7 +1488,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.248</v>
+        <v>0.1836</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1470,35 +1498,31 @@
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="3" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0.0024</v>
-      </c>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
       <c r="N18" s="3" t="n">
-        <v>0.002</v>
+        <v>0.0012</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.0032</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.0104</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>0.0168</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.0296</v>
+        <v>0.0216</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.0328</v>
+        <v>0.0356</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.048</v>
+        <v>0.0492</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.04680000000000001</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="19">
@@ -1511,7 +1535,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.16825</v>
+        <v>0.11175</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -1519,41 +1543,37 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="6" t="n">
         <v>0.00025</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>0.00025</v>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0.00075</v>
-      </c>
       <c r="N19" s="6" t="n">
-        <v>0.002</v>
+        <v>0.00125</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.00375</v>
+        <v>0.00225</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.00725</v>
+        <v>0.0045</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.0115</v>
+        <v>0.008</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.01775</v>
+        <v>0.013</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.025</v>
+        <v>0.02175</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.0365</v>
+        <v>0.03025</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.0335</v>
+        <v>0.03025</v>
       </c>
     </row>
     <row r="20">
@@ -1566,7 +1586,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.14675</v>
+        <v>0.10475</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1578,31 +1598,31 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="3" t="n">
-        <v>0.00075</v>
+        <v>0.0005</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.00175</v>
+        <v>0.001</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.00225</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.00275</v>
+        <v>0.0035</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.011</v>
+        <v>0.0045</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.0145</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.02175</v>
+        <v>0.01625</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.02425</v>
+        <v>0.02875</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.0315</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="21">
@@ -1615,25 +1635,22 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0.001</v>
+        <v>0.095</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.022</v>
+        <v>0.028</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>0.041</v>
@@ -1649,7 +1666,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.0935</v>
+        <v>0.07875</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1660,79 +1677,75 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>0.00075</v>
-      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="3" t="n">
         <v>0.00075</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.00125</v>
+        <v>0.00175</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.00325</v>
+        <v>0.00375</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0.00575</v>
+        <v>0.00725</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.013</v>
+        <v>0.01075</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.01475</v>
+        <v>0.02375</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.02725</v>
+        <v>0.03075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dzhemus</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.07100000000000001</v>
+        <v>0.05610000000000001</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.00055</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.00075</v>
+        <v>0.00055</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.00175</v>
+        <v>0.00165</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.0065</v>
+        <v>0.0011</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.01155</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.01175</v>
+        <v>0.011</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.0165</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>dzhemus</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.06985000000000001</v>
+        <v>0.05225</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1744,23 +1757,29 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
+      <c r="N24" s="3" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0.00025</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>0.00165</v>
-      </c>
-      <c r="Q24" s="2" t="n"/>
+        <v>0.00025</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>0.00175</v>
+      </c>
       <c r="R24" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.00325</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.006600000000000001</v>
+        <v>0.00725</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.011</v>
+        <v>0.01625</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.01815</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="25">
@@ -1773,22 +1792,25 @@
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.04675</v>
+        <v>0.0319</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0.00055</v>
       </c>
+      <c r="Q25" s="4" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="R25" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0033</v>
       </c>
       <c r="S25" s="4" t="n">
         <v>0.00495</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.007700000000000001</v>
+        <v>0.00605</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.01155</v>
+        <v>0.01595</v>
       </c>
     </row>
     <row r="26">
@@ -1801,7 +1823,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.02110070273650771</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
@@ -1813,27 +1835,23 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
-      <c r="N26" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>0.0005</v>
-      </c>
+        <v>0.0007033567578835906</v>
+      </c>
+      <c r="Q26" s="2" t="n"/>
       <c r="R26" s="3" t="n">
-        <v>0.00025</v>
+        <v>0.002110070273650772</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.00425</v>
+        <v>0.002110070273650772</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.005275175684126929</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.01025</v>
+        <v>0.01090202974719565</v>
       </c>
     </row>
     <row r="27">
@@ -1846,19 +1864,25 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.02211176079249519</v>
+        <v>0.02094798390867965</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0.0005661617272616122</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0.0005661617272616122</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.0005264704950594091</v>
+        <v>0.001698485181784837</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.002105881980237636</v>
+        <v>0.003963132090831285</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.002105881980237636</v>
+        <v>0.006793940727139346</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.006317645940712909</v>
+        <v>0.007360102454400958</v>
       </c>
     </row>
     <row r="28">
@@ -1871,7 +1895,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.02203130567831103</v>
+        <v>0.0208717632741894</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
@@ -1886,18 +1910,18 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="3" t="n">
-        <v>0.002002845970755548</v>
-      </c>
+      <c r="Q28" s="3" t="n">
+        <v>0.001605520251860723</v>
+      </c>
+      <c r="R28" s="2" t="n"/>
       <c r="S28" s="3" t="n">
-        <v>0.001001422985377774</v>
+        <v>0.001605520251860723</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0.003004268956133323</v>
+        <v>0.004013800629651808</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0.005007114926888871</v>
+        <v>0.01364692214081615</v>
       </c>
     </row>
     <row r="29">
@@ -1910,16 +1934,19 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.02195094838195516</v>
+        <v>0.02079563530922068</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>0.00109450712153793</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.0008780379352782066</v>
+        <v>0.00109450712153793</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.00263411380583462</v>
+        <v>0.0109450712153793</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.006146265546947445</v>
+        <v>0.007661549850765513</v>
       </c>
     </row>
     <row r="30">
@@ -1932,7 +1959,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.02187068902264514</v>
+        <v>0.02071960012671645</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
@@ -1949,12 +1976,12 @@
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
-      <c r="S30" s="3" t="n">
-        <v>0.001562192073046082</v>
-      </c>
-      <c r="T30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="3" t="n">
+        <v>0.005919885750490416</v>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>0.006248768292184327</v>
+        <v>0.01479971437622604</v>
       </c>
     </row>
     <row r="31">
@@ -1967,13 +1994,16 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02179052772003551</v>
+        <v>0.02064365784003364</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.002723815965004438</v>
+        <v>0.00516091446000841</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>0.00516091446000841</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.01089526386001775</v>
+        <v>0.01032182892001682</v>
       </c>
     </row>
     <row r="32">
@@ -1986,7 +2016,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.0217104645942204</v>
+        <v>0.02056780856294565</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
@@ -2005,10 +2035,10 @@
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>0.005427616148555101</v>
+        <v>0.005141952140736412</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>0.005427616148555101</v>
+        <v>0.01542585642220924</v>
       </c>
     </row>
     <row r="33">
@@ -2021,10 +2051,10 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02163049976573634</v>
+        <v>0.02049205240964496</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.01081524988286817</v>
+        <v>0.02049205240964496</v>
       </c>
     </row>
     <row r="34">
@@ -2037,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.02155063335556488</v>
+        <v>0.02041638949474567</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
@@ -2054,39 +2084,45 @@
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="3" t="n">
-        <v>0.007183544451854958</v>
-      </c>
+      <c r="S34" s="3" t="n">
+        <v>0.02041638949474567</v>
+      </c>
+      <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.02147086548513538</v>
+        <v>0.02034081993328614</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>0.006780273311095381</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>0.006780273311095381</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.01431391032342358</v>
+        <v>0.006780273311095381</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.02139119627632777</v>
+        <v>0.02026534384073158</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
@@ -2105,35 +2141,37 @@
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n"/>
-      <c r="U36" s="2" t="n"/>
+      <c r="U36" s="3" t="n">
+        <v>0.02026534384073158</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STrelOK</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.02131162585147538</v>
+        <v>0.02018996133297668</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>0.007103875283825127</v>
+        <v>0.02018996133297668</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>STrelOK</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.02123215433336769</v>
+        <v>0.02011467252634834</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
@@ -2151,22 +2189,25 @@
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
-      <c r="T38" s="3" t="n">
-        <v>0.02123215433336769</v>
-      </c>
-      <c r="U38" s="2" t="n"/>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="3" t="n">
+        <v>0.02011467252634834</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.02115278184525321</v>
+        <v>0.0200394775376083</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>0.0200394775376083</v>
       </c>
     </row>
     <row r="40">
@@ -2179,7 +2220,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.02107350851084236</v>
+        <v>0.01996437648395592</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -2198,32 +2239,37 @@
       <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n"/>
-      <c r="U40" s="2" t="n"/>
+      <c r="U40" s="3" t="n">
+        <v>0.01996437648395592</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Комар</t>
+          <t>z9</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.02099433445431035</v>
+        <v>0.01988936948303086</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>0.01988936948303086</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Лось</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.02091525980030007</v>
+        <v>0.01981445665291585</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -2242,35 +2288,37 @@
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="n"/>
+      <c r="U42" s="3" t="n">
+        <v>0.01981445665291585</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>z9</t>
+          <t>Комар</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>42</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.02083628467392509</v>
+        <v>0.01973963811213955</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>0.02083628467392509</v>
+        <v>0.01973963811213955</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.02075740920077257</v>
+        <v>0.01966491397967927</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -2289,19 +2337,24 @@
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n"/>
-      <c r="U44" s="2" t="n"/>
+      <c r="U44" s="3" t="n">
+        <v>0.01966491397967927</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Лось</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.02067863350690629</v>
+        <v>0.01959028437496386</v>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>0.01959028437496386</v>
       </c>
     </row>
     <row r="46">
@@ -2314,7 +2367,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.02059995771886969</v>
+        <v>0.01951574941787655</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
@@ -2333,7 +2386,9 @@
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
+      <c r="U46" s="3" t="n">
+        <v>0.01951574941787655</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2345,20 +2400,23 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.02052138196368886</v>
+        <v>0.01944130922875786</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>0.01944130922875786</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Deroz</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.02044290636887566</v>
+        <v>0.01936696392840852</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
@@ -2377,32 +2435,37 @@
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="n"/>
-      <c r="U48" s="2" t="n"/>
+      <c r="U48" s="3" t="n">
+        <v>0.01936696392840852</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Deroz</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.02036453106243084</v>
+        <v>0.01929271363809237</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>0.01929271363809237</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.02028625617284711</v>
+        <v>0.01921855847953937</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
@@ -2421,19 +2484,24 @@
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="n"/>
-      <c r="U50" s="2" t="n"/>
+      <c r="U50" s="3" t="n">
+        <v>0.01921855847953937</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.02020808182911237</v>
+        <v>0.01914449857494856</v>
+      </c>
+      <c r="U51" s="4" t="n">
+        <v>0.01914449857494856</v>
       </c>
     </row>
     <row r="52">
@@ -2446,7 +2514,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.02013000816071283</v>
+        <v>0.01907053404699111</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
@@ -2465,7 +2533,9 @@
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="n"/>
-      <c r="U52" s="2" t="n"/>
+      <c r="U52" s="3" t="n">
+        <v>0.01907053404699111</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2477,20 +2547,23 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.0200520352976363</v>
+        <v>0.01899666501881334</v>
+      </c>
+      <c r="U53" s="4" t="n">
+        <v>0.01899666501881334</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>mvp</t>
+          <t>Koff1ek</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.01997416337037537</v>
+        <v>0.01892289161403983</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
@@ -2509,7 +2582,9 @@
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="n"/>
-      <c r="U54" s="2" t="n"/>
+      <c r="U54" s="3" t="n">
+        <v>0.01892289161403983</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2521,20 +2596,23 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.01989639250993073</v>
+        <v>0.01884921395677648</v>
+      </c>
+      <c r="U55" s="4" t="n">
+        <v>0.01884921395677648</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Koff1ek</t>
+          <t>mvp</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.01981872284781446</v>
+        <v>0.0187756321716137</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
@@ -2553,32 +2631,37 @@
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="2" t="n"/>
-      <c r="U56" s="2" t="n"/>
+      <c r="U56" s="3" t="n">
+        <v>0.0187756321716137</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>swapblet</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01974115451605335</v>
+        <v>0.01870214638362949</v>
+      </c>
+      <c r="U57" s="4" t="n">
+        <v>0.01870214638362949</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.01966368764719231</v>
+        <v>0.01862875671839271</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
@@ -2597,7 +2680,9 @@
       <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="2" t="n"/>
-      <c r="U58" s="2" t="n"/>
+      <c r="U58" s="3" t="n">
+        <v>0.01862875671839271</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2609,20 +2694,23 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.01958632237429771</v>
+        <v>0.01855546330196625</v>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>0.01855546330196625</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>swapblet</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.01950905883096086</v>
+        <v>0.01848226626091028</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
@@ -2641,32 +2729,37 @@
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="2" t="n"/>
-      <c r="U60" s="2" t="n"/>
+      <c r="U60" s="3" t="n">
+        <v>0.01848226626091028</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vovaa_25</t>
+          <t>dunkaeva</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.01943189715130143</v>
+        <v>0.01840916572228557</v>
+      </c>
+      <c r="U61" s="4" t="n">
+        <v>0.01840916572228557</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>dunkaeva</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.01935483746997099</v>
+        <v>0.01833616181365673</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
@@ -2685,32 +2778,37 @@
       <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="n"/>
-      <c r="U62" s="2" t="n"/>
+      <c r="U62" s="3" t="n">
+        <v>0.01833616181365673</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>vovaa_25</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>62</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.01927787992215648</v>
+        <v>0.01826325466309562</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>0.01826325466309562</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>danalanaaa</t>
+          <t>FreSko</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.01920102464358381</v>
+        <v>0.01819044439918466</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
@@ -2729,32 +2827,37 @@
       <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="n"/>
-      <c r="U64" s="2" t="n"/>
+      <c r="U64" s="3" t="n">
+        <v>0.01819044439918466</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FreSko</t>
+          <t>danalanaaa</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.01912427177052142</v>
+        <v>0.01811773115102029</v>
+      </c>
+      <c r="U65" s="4" t="n">
+        <v>0.01811773115102029</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>HellGnomik</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.01904762143978391</v>
+        <v>0.01804511504821634</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
@@ -2773,32 +2876,37 @@
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="2" t="n"/>
-      <c r="U66" s="2" t="n"/>
+      <c r="U66" s="3" t="n">
+        <v>0.01804511504821634</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lethalpresence</t>
+          <t>Dima!</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.01897107378873574</v>
+        <v>0.01797259622090755</v>
+      </c>
+      <c r="U67" s="4" t="n">
+        <v>0.01797259622090755</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Leomane</t>
+          <t>Jeereky</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.01889462895529487</v>
+        <v>0.01790017479975304</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
@@ -2817,32 +2925,37 @@
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="2" t="n"/>
-      <c r="U68" s="2" t="n"/>
+      <c r="U68" s="3" t="n">
+        <v>0.01790017479975304</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HellGnomik</t>
+          <t>bad_teacher</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>68</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.0188182870779365</v>
+        <v>0.01782785091593984</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>0.01782785091593984</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>bad_teacher</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.01874204829569683</v>
+        <v>0.01775562470118647</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
@@ -2861,32 +2974,37 @@
       <c r="R70" s="2" t="n"/>
       <c r="S70" s="2" t="n"/>
       <c r="T70" s="2" t="n"/>
-      <c r="U70" s="2" t="n"/>
+      <c r="U70" s="3" t="n">
+        <v>0.01775562470118647</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>lethalpresence</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>70</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.0186659127481769</v>
+        <v>0.01768349628774654</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>0.01768349628774654</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Leomane</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.01858988057554638</v>
+        <v>0.01761146580841236</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
@@ -2905,32 +3023,37 @@
       <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="n"/>
-      <c r="U72" s="2" t="n"/>
+      <c r="U72" s="3" t="n">
+        <v>0.01761146580841236</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dima!</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.01851395191854743</v>
+        <v>0.01753953339651862</v>
+      </c>
+      <c r="U73" s="4" t="n">
+        <v>0.01753953339651862</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Jeereky</t>
+          <t>duy27</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.01843812691849865</v>
+        <v>0.0174676991859461</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
@@ -2949,19 +3072,24 @@
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="n"/>
-      <c r="U74" s="2" t="n"/>
+      <c r="U74" s="3" t="n">
+        <v>0.0174676991859461</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>duy27</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>74</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.01836240571729901</v>
+        <v>0.01739596331112538</v>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>0.01739596331112538</v>
       </c>
     </row>
     <row r="76">
@@ -2974,7 +3102,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.01828678845743183</v>
+        <v>0.01732432590704068</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
@@ -2993,32 +3121,37 @@
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="2" t="n"/>
-      <c r="U76" s="2" t="n"/>
+      <c r="U76" s="3" t="n">
+        <v>0.01732432590704068</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>76</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.01821127528196877</v>
+        <v>0.01725278710923357</v>
+      </c>
+      <c r="U77" s="4" t="n">
+        <v>0.01725278710923357</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GodЗИЛLa</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0.01813586633457397</v>
+        <v>0.01718134705380692</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n"/>
@@ -3037,32 +3170,37 @@
       <c r="R78" s="2" t="n"/>
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="2" t="n"/>
-      <c r="U78" s="2" t="n"/>
+      <c r="U78" s="3" t="n">
+        <v>0.01718134705380692</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>Горыныч</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>78</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0.01806056175950806</v>
+        <v>0.01711000587742869</v>
+      </c>
+      <c r="U79" s="4" t="n">
+        <v>0.01711000587742869</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>GodЗИЛLa</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.01798536170163237</v>
+        <v>0.01703876371733593</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n"/>
@@ -3081,7 +3219,9 @@
       <c r="R80" s="2" t="n"/>
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="n"/>
-      <c r="U80" s="2" t="n"/>
+      <c r="U80" s="3" t="n">
+        <v>0.01703876371733593</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3093,20 +3233,23 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>0.01791026630641307</v>
+        <v>0.01696762071133869</v>
+      </c>
+      <c r="U81" s="4" t="n">
+        <v>0.01696762071133869</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.01783527571992538</v>
+        <v>0.01689657699782405</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="n"/>
@@ -3125,32 +3268,37 @@
       <c r="R82" s="2" t="n"/>
       <c r="S82" s="2" t="n"/>
       <c r="T82" s="2" t="n"/>
-      <c r="U82" s="2" t="n"/>
+      <c r="U82" s="3" t="n">
+        <v>0.01689657699782405</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MAKKSMIR</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>82</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0.01776039008885791</v>
+        <v>0.01682563271576013</v>
+      </c>
+      <c r="U83" s="4" t="n">
+        <v>0.01682563271576013</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>Николай К</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0.01768560956051686</v>
+        <v>0.01675478800470018</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n"/>
@@ -3169,19 +3317,24 @@
       <c r="R84" s="2" t="n"/>
       <c r="S84" s="2" t="n"/>
       <c r="T84" s="2" t="n"/>
-      <c r="U84" s="2" t="n"/>
+      <c r="U84" s="3" t="n">
+        <v>0.01675478800470018</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Горыныч</t>
+          <t>MAKKSMIR</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>84</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>0.01761093428283042</v>
+        <v>0.01668404300478672</v>
+      </c>
+      <c r="U85" s="4" t="n">
+        <v>0.01668404300478672</v>
       </c>
     </row>
     <row r="86">
@@ -3194,7 +3347,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.01753636440435319</v>
+        <v>0.01661339785675565</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n"/>
@@ -3213,32 +3366,37 @@
       <c r="R86" s="2" t="n"/>
       <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="n"/>
-      <c r="U86" s="2" t="n"/>
+      <c r="U86" s="3" t="n">
+        <v>0.01661339785675565</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>86</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0.01746190007427053</v>
+        <v>0.0165428527019405</v>
+      </c>
+      <c r="U87" s="4" t="n">
+        <v>0.0165428527019405</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Николай К</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.01738754144240312</v>
+        <v>0.01647240768227664</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n"/>
@@ -3257,19 +3415,24 @@
       <c r="R88" s="2" t="n"/>
       <c r="S88" s="2" t="n"/>
       <c r="T88" s="2" t="n"/>
-      <c r="U88" s="2" t="n"/>
+      <c r="U88" s="3" t="n">
+        <v>0.01647240768227664</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Лабуба</t>
+          <t>Татьяна Юрьевна Р.</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>88</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0.01731328865921142</v>
+        <v>0.01640206294030556</v>
+      </c>
+      <c r="U89" s="4" t="n">
+        <v>0.01640206294030556</v>
       </c>
     </row>
     <row r="90">
@@ -3282,7 +3445,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0.0172391418758003</v>
+        <v>0.01633181861917923</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n"/>
@@ -3301,32 +3464,37 @@
       <c r="R90" s="2" t="n"/>
       <c r="S90" s="2" t="n"/>
       <c r="T90" s="2" t="n"/>
-      <c r="U90" s="2" t="n"/>
+      <c r="U90" s="3" t="n">
+        <v>0.01633181861917923</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Holmes</t>
+          <t>Chimedaschool1</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.01716510124392357</v>
+        <v>0.01626167486266444</v>
+      </c>
+      <c r="U91" s="4" t="n">
+        <v>0.01626167486266444</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Чучел</t>
+          <t>Лабуба</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.01709116691598872</v>
+        <v>0.01619163181514721</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="n"/>
@@ -3345,7 +3513,9 @@
       <c r="R92" s="2" t="n"/>
       <c r="S92" s="2" t="n"/>
       <c r="T92" s="2" t="n"/>
-      <c r="U92" s="2" t="n"/>
+      <c r="U92" s="3" t="n">
+        <v>0.01619163181514721</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3357,20 +3527,23 @@
         <v>92</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0.01701733904506158</v>
+        <v>0.01612168962163728</v>
+      </c>
+      <c r="U93" s="4" t="n">
+        <v>0.01612168962163728</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Billie</t>
+          <t>Чучел</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.01694361778487107</v>
+        <v>0.01605184842777259</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
@@ -3389,32 +3562,37 @@
       <c r="R94" s="2" t="n"/>
       <c r="S94" s="2" t="n"/>
       <c r="T94" s="2" t="n"/>
-      <c r="U94" s="2" t="n"/>
+      <c r="U94" s="3" t="n">
+        <v>0.01605184842777259</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>94</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0.01687000328981402</v>
+        <v>0.01598210837982381</v>
+      </c>
+      <c r="U95" s="4" t="n">
+        <v>0.01598210837982381</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Татьяна Юрьевна Р.</t>
+          <t>Billie</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.01679649571496005</v>
+        <v>0.01591246962469899</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n"/>
@@ -3433,32 +3611,37 @@
       <c r="R96" s="2" t="n"/>
       <c r="S96" s="2" t="n"/>
       <c r="T96" s="2" t="n"/>
-      <c r="U96" s="2" t="n"/>
+      <c r="U96" s="3" t="n">
+        <v>0.01591246962469899</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>willy &lt;/3</t>
+          <t>srgzorge</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>96</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.01672309521605639</v>
+        <v>0.01584293230994815</v>
+      </c>
+      <c r="U97" s="4" t="n">
+        <v>0.01584293230994815</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>0.0166498019495329</v>
+        <v>0.01577349658376801</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n"/>
@@ -3477,32 +3660,37 @@
       <c r="R98" s="2" t="n"/>
       <c r="S98" s="2" t="n"/>
       <c r="T98" s="2" t="n"/>
-      <c r="U98" s="2" t="n"/>
+      <c r="U98" s="3" t="n">
+        <v>0.01577349658376801</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>srgzorge</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0.01657661607250703</v>
+        <v>0.01570416259500667</v>
+      </c>
+      <c r="U99" s="4" t="n">
+        <v>0.01570416259500667</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Chimedaschool1</t>
+          <t>willy &lt;/3</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.01650353774278892</v>
+        <v>0.01563493049316845</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n"/>
@@ -3521,19 +3709,24 @@
       <c r="R100" s="2" t="n"/>
       <c r="S100" s="2" t="n"/>
       <c r="T100" s="2" t="n"/>
-      <c r="U100" s="2" t="n"/>
+      <c r="U100" s="3" t="n">
+        <v>0.01563493049316845</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0.01643056711888645</v>
+        <v>0.01556580042841874</v>
+      </c>
+      <c r="U101" s="4" t="n">
+        <v>0.01556580042841874</v>
       </c>
     </row>
     <row r="102">
@@ -3546,7 +3739,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0.01635770436001041</v>
+        <v>0.01549677255158882</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="n"/>
@@ -3565,32 +3758,37 @@
       <c r="R102" s="2" t="n"/>
       <c r="S102" s="2" t="n"/>
       <c r="T102" s="2" t="n"/>
-      <c r="U102" s="2" t="n"/>
+      <c r="U102" s="3" t="n">
+        <v>0.01549677255158882</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>dance_with_vlad</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>102</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0.01628494962607976</v>
+        <v>0.01542784701418083</v>
+      </c>
+      <c r="U103" s="4" t="n">
+        <v>0.01542784701418083</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Пупупу</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.01621230307772682</v>
+        <v>0.01535902396837277</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="n"/>
@@ -3609,32 +3807,37 @@
       <c r="R104" s="2" t="n"/>
       <c r="S104" s="2" t="n"/>
       <c r="T104" s="2" t="n"/>
-      <c r="U104" s="2" t="n"/>
+      <c r="U104" s="3" t="n">
+        <v>0.01535902396837277</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kichatov</t>
+          <t>Dio</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0.01613976487630263</v>
+        <v>0.01529030356702354</v>
+      </c>
+      <c r="U105" s="4" t="n">
+        <v>0.01529030356702354</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>OwTlion</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.01606733518388234</v>
+        <v>0.01522168596367801</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n"/>
@@ -3653,32 +3856,37 @@
       <c r="R106" s="2" t="n"/>
       <c r="S106" s="2" t="n"/>
       <c r="T106" s="2" t="n"/>
-      <c r="U106" s="2" t="n"/>
+      <c r="U106" s="3" t="n">
+        <v>0.01522168596367801</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dance_with_vlad</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>106</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0.01599501416327062</v>
+        <v>0.01515317131257217</v>
+      </c>
+      <c r="U107" s="4" t="n">
+        <v>0.01515317131257217</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Пупупу</t>
+          <t>Kichatov</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0.01592280197800714</v>
+        <v>0.01508475976863835</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n"/>
@@ -3697,32 +3905,37 @@
       <c r="R108" s="2" t="n"/>
       <c r="S108" s="2" t="n"/>
       <c r="T108" s="2" t="n"/>
-      <c r="U108" s="2" t="n"/>
+      <c r="U108" s="3" t="n">
+        <v>0.01508475976863835</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dio</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>108</v>
       </c>
       <c r="C109" s="4" t="n">
-        <v>0.01585069879237215</v>
+        <v>0.01501645148751045</v>
+      </c>
+      <c r="U109" s="4" t="n">
+        <v>0.01501645148751045</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>OwTlion</t>
+          <t>AlexBluff</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0.01577870477139203</v>
+        <v>0.0149482466255293</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n"/>
@@ -3741,32 +3954,37 @@
       <c r="R110" s="2" t="n"/>
       <c r="S110" s="2" t="n"/>
       <c r="T110" s="2" t="n"/>
-      <c r="U110" s="2" t="n"/>
+      <c r="U110" s="3" t="n">
+        <v>0.0149482466255293</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>kapayaki</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0.01570682008084505</v>
+        <v>0.01488014533974794</v>
+      </c>
+      <c r="U111" s="4" t="n">
+        <v>0.01488014533974794</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>kapayaki</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.01563504488726698</v>
+        <v>0.01481214778793714</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n"/>
@@ -3785,32 +4003,37 @@
       <c r="R112" s="2" t="n"/>
       <c r="S112" s="2" t="n"/>
       <c r="T112" s="2" t="n"/>
-      <c r="U112" s="2" t="n"/>
+      <c r="U112" s="3" t="n">
+        <v>0.01481214778793714</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>112</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.01556337935795697</v>
+        <v>0.01474425412859081</v>
+      </c>
+      <c r="U113" s="4" t="n">
+        <v>0.01474425412859081</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Lawyer</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0.01549182366098336</v>
+        <v>0.0146764645209316</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" s="2" t="n"/>
@@ -3829,19 +4052,24 @@
       <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
       <c r="T114" s="2" t="n"/>
-      <c r="U114" s="2" t="n"/>
+      <c r="U114" s="3" t="n">
+        <v>0.0146764645209316</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AlexBluff</t>
+          <t>bogdanov</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.01542037796518959</v>
+        <v>0.01460877912491645</v>
+      </c>
+      <c r="U115" s="4" t="n">
+        <v>0.01460877912491645</v>
       </c>
     </row>
     <row r="116">
@@ -3854,7 +4082,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0.01534904244020019</v>
+        <v>0.01454119810124228</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="n"/>
@@ -3873,32 +4101,37 @@
       <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
       <c r="T116" s="2" t="n"/>
-      <c r="U116" s="2" t="n"/>
+      <c r="U116" s="3" t="n">
+        <v>0.01454119810124228</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Лука</t>
+          <t>Lawyer</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>116</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>0.01527781725642681</v>
+        <v>0.01447372161135172</v>
+      </c>
+      <c r="U117" s="4" t="n">
+        <v>0.01447372161135172</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Milana_Xam</t>
+          <t>Legi</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.01520670258507435</v>
+        <v>0.01440634981743885</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="n"/>
@@ -3917,32 +4150,37 @@
       <c r="R118" s="2" t="n"/>
       <c r="S118" s="2" t="n"/>
       <c r="T118" s="2" t="n"/>
-      <c r="U118" s="2" t="n"/>
+      <c r="U118" s="3" t="n">
+        <v>0.01440634981743885</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ташкент</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>118</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.01513569859814707</v>
+        <v>0.01433908288245512</v>
+      </c>
+      <c r="U119" s="4" t="n">
+        <v>0.01433908288245512</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Ташкент</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>119</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0.01506480546845493</v>
+        <v>0.0142719209701152</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="n"/>
@@ -3961,32 +4199,37 @@
       <c r="R120" s="2" t="n"/>
       <c r="S120" s="2" t="n"/>
       <c r="T120" s="2" t="n"/>
-      <c r="U120" s="2" t="n"/>
+      <c r="U120" s="3" t="n">
+        <v>0.0142719209701152</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>serpav_04</t>
+          <t>Лука</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>120</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.0149940233696198</v>
+        <v>0.01420486424490297</v>
+      </c>
+      <c r="U121" s="4" t="n">
+        <v>0.01420486424490297</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Катальня</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>0.01492335247608191</v>
+        <v>0.0141379128720776</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="n"/>
@@ -4005,32 +4248,37 @@
       <c r="R122" s="2" t="n"/>
       <c r="S122" s="2" t="n"/>
       <c r="T122" s="2" t="n"/>
-      <c r="U122" s="2" t="n"/>
+      <c r="U122" s="3" t="n">
+        <v>0.0141379128720776</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>Milana_Xam</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>122</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0.01485279296310625</v>
+        <v>0.01407106701767961</v>
+      </c>
+      <c r="U123" s="4" t="n">
+        <v>0.01407106701767961</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
         <v>123</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0.01478234500678913</v>
+        <v>0.01400432684853707</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="n"/>
@@ -4049,32 +4297,37 @@
       <c r="R124" s="2" t="n"/>
       <c r="S124" s="2" t="n"/>
       <c r="T124" s="2" t="n"/>
-      <c r="U124" s="2" t="n"/>
+      <c r="U124" s="3" t="n">
+        <v>0.01400432684853707</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Legi</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>124</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>0.01471200878406473</v>
+        <v>0.01393769253227185</v>
+      </c>
+      <c r="U125" s="4" t="n">
+        <v>0.01393769253227185</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Лина</t>
+          <t>Константин 1</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0.01464178447271182</v>
+        <v>0.01387116423730594</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
@@ -4093,32 +4346,37 @@
       <c r="R126" s="2" t="n"/>
       <c r="S126" s="2" t="n"/>
       <c r="T126" s="2" t="n"/>
-      <c r="U126" s="2" t="n"/>
+      <c r="U126" s="3" t="n">
+        <v>0.01387116423730594</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Константин 1</t>
+          <t>serpav_04</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>126</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>0.01457167225136044</v>
+        <v>0.01380474213286778</v>
+      </c>
+      <c r="U127" s="4" t="n">
+        <v>0.01380474213286778</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Катальня</t>
+          <t>sssx_xsss</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0.01450167229949876</v>
+        <v>0.01373842638899882</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" s="2" t="n"/>
@@ -4137,7 +4395,9 @@
       <c r="R128" s="2" t="n"/>
       <c r="S128" s="2" t="n"/>
       <c r="T128" s="2" t="n"/>
-      <c r="U128" s="2" t="n"/>
+      <c r="U128" s="3" t="n">
+        <v>0.01373842638899882</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4149,20 +4409,23 @@
         <v>128</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.01443178479747995</v>
+        <v>0.01367221717655996</v>
+      </c>
+      <c r="U129" s="4" t="n">
+        <v>0.01367221717655996</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ajolana</t>
+          <t>Лина</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.01436200992652917</v>
+        <v>0.01360611466723817</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" s="2" t="n"/>
@@ -4181,32 +4444,37 @@
       <c r="R130" s="2" t="n"/>
       <c r="S130" s="2" t="n"/>
       <c r="T130" s="2" t="n"/>
-      <c r="U130" s="2" t="n"/>
+      <c r="U130" s="3" t="n">
+        <v>0.01360611466723817</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>sssx_xsss</t>
+          <t>Xxx</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>0.0142923478687506</v>
+        <v>0.0135401190335532</v>
+      </c>
+      <c r="U131" s="4" t="n">
+        <v>0.0135401190335532</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Xxx</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.01422279880713458</v>
+        <v>0.01347423044886434</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="n"/>
@@ -4225,32 +4493,37 @@
       <c r="R132" s="2" t="n"/>
       <c r="S132" s="2" t="n"/>
       <c r="T132" s="2" t="n"/>
-      <c r="U132" s="2" t="n"/>
+      <c r="U132" s="3" t="n">
+        <v>0.01347423044886434</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>ajolana</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.01415336292556481</v>
+        <v>0.01340844908737719</v>
+      </c>
+      <c r="U133" s="4" t="n">
+        <v>0.01340844908737719</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>No1z11</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0.01408404040882566</v>
+        <v>0.01334277512415062</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" s="2" t="n"/>
@@ -4269,32 +4542,37 @@
       <c r="R134" s="2" t="n"/>
       <c r="S134" s="2" t="n"/>
       <c r="T134" s="2" t="n"/>
-      <c r="U134" s="2" t="n"/>
+      <c r="U134" s="3" t="n">
+        <v>0.01334277512415062</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Студент</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>134</v>
       </c>
       <c r="C135" s="4" t="n">
-        <v>0.01401483144260952</v>
+        <v>0.01327720873510376</v>
+      </c>
+      <c r="U135" s="4" t="n">
+        <v>0.01327720873510376</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ForceUser</t>
+          <t>ddv</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>0.0139457362135243</v>
+        <v>0.01321175009702302</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" s="2" t="n"/>
@@ -4313,32 +4591,37 @@
       <c r="R136" s="2" t="n"/>
       <c r="S136" s="2" t="n"/>
       <c r="T136" s="2" t="n"/>
-      <c r="U136" s="2" t="n"/>
+      <c r="U136" s="3" t="n">
+        <v>0.01321175009702302</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Бутербродский</t>
+          <t>Davit</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>136</v>
       </c>
       <c r="C137" s="4" t="n">
-        <v>0.01387675490910093</v>
+        <v>0.0131463993875693</v>
+      </c>
+      <c r="U137" s="4" t="n">
+        <v>0.0131463993875693</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ddv</t>
+          <t>Бутербродский</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>0.01380788771780104</v>
+        <v>0.0130811567852852</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="n"/>
@@ -4357,32 +4640,37 @@
       <c r="R138" s="2" t="n"/>
       <c r="S138" s="2" t="n"/>
       <c r="T138" s="2" t="n"/>
-      <c r="U138" s="2" t="n"/>
+      <c r="U138" s="3" t="n">
+        <v>0.0130811567852852</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Лудоданя</t>
+          <t>Анна Мария Гансалез</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0.01373913482902466</v>
+        <v>0.01301602246960231</v>
+      </c>
+      <c r="U139" s="4" t="n">
+        <v>0.01301602246960231</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Анна Мария Гансалез</t>
+          <t>Kepeeshman</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>0.01367049643311804</v>
+        <v>0.01295099662084867</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="n"/>
@@ -4401,32 +4689,37 @@
       <c r="R140" s="2" t="n"/>
       <c r="S140" s="2" t="n"/>
       <c r="T140" s="2" t="n"/>
-      <c r="U140" s="2" t="n"/>
+      <c r="U140" s="3" t="n">
+        <v>0.01295099662084867</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>sasha12039</t>
+          <t>Фиш</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>140</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>0.01360197272138152</v>
+        <v>0.01288607942025618</v>
+      </c>
+      <c r="U141" s="4" t="n">
+        <v>0.01288607942025618</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Kepeeshman</t>
+          <t>Студент</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="C142" s="3" t="n">
-        <v>0.01353356388607761</v>
+        <v>0.01282127104996827</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" s="2" t="n"/>
@@ -4445,32 +4738,37 @@
       <c r="R142" s="2" t="n"/>
       <c r="S142" s="2" t="n"/>
       <c r="T142" s="2" t="n"/>
-      <c r="U142" s="2" t="n"/>
+      <c r="U142" s="3" t="n">
+        <v>0.01282127104996827</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>No1z11</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>0.013465270120439</v>
+        <v>0.01275657169304748</v>
+      </c>
+      <c r="U143" s="4" t="n">
+        <v>0.01275657169304748</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>sasha12039</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>0.01339709161867679</v>
+        <v>0.01269198153348327</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" s="2" t="n"/>
@@ -4489,32 +4787,37 @@
       <c r="R144" s="2" t="n"/>
       <c r="S144" s="2" t="n"/>
       <c r="T144" s="2" t="n"/>
-      <c r="U144" s="2" t="n"/>
+      <c r="U144" s="3" t="n">
+        <v>0.01269198153348327</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Фиш</t>
+          <t>Margaery_ZHU</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>144</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>0.01332902857598876</v>
+        <v>0.01262750075619988</v>
+      </c>
+      <c r="U145" s="4" t="n">
+        <v>0.01262750075619988</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>ForceUser</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="C146" s="3" t="n">
-        <v>0.01326108118856774</v>
+        <v>0.01256312954706418</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="n"/>
@@ -4533,19 +4836,24 @@
       <c r="R146" s="2" t="n"/>
       <c r="S146" s="2" t="n"/>
       <c r="T146" s="2" t="n"/>
-      <c r="U146" s="2" t="n"/>
+      <c r="U146" s="3" t="n">
+        <v>0.01256312954706418</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>Лудоданя</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>146</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>0.01319324965361015</v>
+        <v>0.01249886809289382</v>
+      </c>
+      <c r="U147" s="4" t="n">
+        <v>0.01249886809289382</v>
       </c>
     </row>
     <row r="148">
@@ -4558,7 +4866,7 @@
         <v>147</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>0.01312553416932451</v>
+        <v>0.01243471658146532</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" s="2" t="n"/>
@@ -4577,32 +4885,37 @@
       <c r="R148" s="2" t="n"/>
       <c r="S148" s="2" t="n"/>
       <c r="T148" s="2" t="n"/>
-      <c r="U148" s="2" t="n"/>
+      <c r="U148" s="3" t="n">
+        <v>0.01243471658146532</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Margaery_ZHU</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>148</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.01305793493494018</v>
+        <v>0.01237067520152228</v>
+      </c>
+      <c r="U149" s="4" t="n">
+        <v>0.01237067520152228</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Dupont</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="C150" s="3" t="n">
-        <v>0.01299045215071612</v>
+        <v>0.0123067441427837</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" s="2" t="n"/>
@@ -4621,32 +4934,37 @@
       <c r="R150" s="2" t="n"/>
       <c r="S150" s="2" t="n"/>
       <c r="T150" s="2" t="n"/>
-      <c r="U150" s="2" t="n"/>
+      <c r="U150" s="3" t="n">
+        <v>0.0123067441427837</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>Бандэрос</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>0.01292308601794983</v>
+        <v>0.01224292359595247</v>
+      </c>
+      <c r="U151" s="4" t="n">
+        <v>0.01224292359595247</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Бандэрос</t>
+          <t>Dupont</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>0.01285583673898631</v>
+        <v>0.01217921375272387</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" s="2" t="n"/>
@@ -4665,7 +4983,9 @@
       <c r="R152" s="2" t="n"/>
       <c r="S152" s="2" t="n"/>
       <c r="T152" s="2" t="n"/>
-      <c r="U152" s="2" t="n"/>
+      <c r="U152" s="3" t="n">
+        <v>0.01217921375272387</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4677,20 +4997,23 @@
         <v>152</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0.0127887045172272</v>
+        <v>0.01211561480579419</v>
+      </c>
+      <c r="U153" s="4" t="n">
+        <v>0.01211561480579419</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>𝓼𝓸𝓾𝓵</t>
+          <t>Катала</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>0.01272168955714002</v>
+        <v>0.01205212694886949</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" s="2" t="n"/>
@@ -4709,7 +5032,9 @@
       <c r="R154" s="2" t="n"/>
       <c r="S154" s="2" t="n"/>
       <c r="T154" s="2" t="n"/>
-      <c r="U154" s="2" t="n"/>
+      <c r="U154" s="3" t="n">
+        <v>0.01205212694886949</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4721,20 +5046,23 @@
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>0.01265479206426748</v>
+        <v>0.01198875037667445</v>
+      </c>
+      <c r="U155" s="4" t="n">
+        <v>0.01198875037667445</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Yandi</t>
+          <t>𝓼𝓸𝓾𝓵</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>0.01258801224523697</v>
+        <v>0.01192548528496134</v>
       </c>
       <c r="D156" s="2" t="n"/>
       <c r="E156" s="2" t="n"/>
@@ -4753,32 +5081,37 @@
       <c r="R156" s="2" t="n"/>
       <c r="S156" s="2" t="n"/>
       <c r="T156" s="2" t="n"/>
-      <c r="U156" s="2" t="n"/>
+      <c r="U156" s="3" t="n">
+        <v>0.01192548528496134</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>katevertu</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>0.01252135030777012</v>
+        <v>0.01186233187051906</v>
+      </c>
+      <c r="U157" s="4" t="n">
+        <v>0.01186233187051906</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Стич</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>0.01245480646069248</v>
+        <v>0.01179929033118235</v>
       </c>
       <c r="D158" s="2" t="n"/>
       <c r="E158" s="2" t="n"/>
@@ -4797,32 +5130,37 @@
       <c r="R158" s="2" t="n"/>
       <c r="S158" s="2" t="n"/>
       <c r="T158" s="2" t="n"/>
-      <c r="U158" s="2" t="n"/>
+      <c r="U158" s="3" t="n">
+        <v>0.01179929033118235</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>katevertu</t>
+          <t>KLO</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>0.01238838091394334</v>
+        <v>0.01173636086584106</v>
+      </c>
+      <c r="U159" s="4" t="n">
+        <v>0.01173636086584106</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>0.01232207387858569</v>
+        <v>0.01167354367444961</v>
       </c>
       <c r="D160" s="2" t="n"/>
       <c r="E160" s="2" t="n"/>
@@ -4841,32 +5179,37 @@
       <c r="R160" s="2" t="n"/>
       <c r="S160" s="2" t="n"/>
       <c r="T160" s="2" t="n"/>
-      <c r="U160" s="2" t="n"/>
+      <c r="U160" s="3" t="n">
+        <v>0.01167354367444961</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Вега</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>160</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>0.01225588556681624</v>
+        <v>0.01161083895803644</v>
+      </c>
+      <c r="U161" s="4" t="n">
+        <v>0.01161083895803644</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="C162" s="3" t="n">
-        <v>0.01218981619197563</v>
+        <v>0.01154824691871376</v>
       </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="n"/>
@@ -4885,32 +5228,37 @@
       <c r="R162" s="2" t="n"/>
       <c r="S162" s="2" t="n"/>
       <c r="T162" s="2" t="n"/>
-      <c r="U162" s="2" t="n"/>
+      <c r="U162" s="3" t="n">
+        <v>0.01154824691871376</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>162</v>
       </c>
       <c r="C163" s="4" t="n">
-        <v>0.01212386596855876</v>
+        <v>0.01148576775968724</v>
+      </c>
+      <c r="U163" s="4" t="n">
+        <v>0.01148576775968724</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Катала</t>
+          <t>Вега</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>0.01205803511222517</v>
+        <v>0.01142340168526594</v>
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" s="2" t="n"/>
@@ -4929,32 +5277,37 @@
       <c r="R164" s="2" t="n"/>
       <c r="S164" s="2" t="n"/>
       <c r="T164" s="2" t="n"/>
-      <c r="U164" s="2" t="n"/>
+      <c r="U164" s="3" t="n">
+        <v>0.01142340168526594</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Стич</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>164</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>0.0119923238398097</v>
+        <v>0.01136114890087235</v>
+      </c>
+      <c r="U165" s="4" t="n">
+        <v>0.01136114890087235</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>Yandi</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>0.01192673236933317</v>
+        <v>0.01129900961305248</v>
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" s="2" t="n"/>
@@ -4973,7 +5326,9 @@
       <c r="R166" s="2" t="n"/>
       <c r="S166" s="2" t="n"/>
       <c r="T166" s="2" t="n"/>
-      <c r="U166" s="2" t="n"/>
+      <c r="U166" s="3" t="n">
+        <v>0.01129900961305248</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4985,20 +5340,23 @@
         <v>166</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>0.01186126092001322</v>
+        <v>0.01123698402948621</v>
+      </c>
+      <c r="U167" s="4" t="n">
+        <v>0.01123698402948621</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Black Crystal</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>0.0117959097122753</v>
+        <v>0.01117507235899765</v>
       </c>
       <c r="D168" s="2" t="n"/>
       <c r="E168" s="2" t="n"/>
@@ -5017,32 +5375,37 @@
       <c r="R168" s="2" t="n"/>
       <c r="S168" s="2" t="n"/>
       <c r="T168" s="2" t="n"/>
-      <c r="U168" s="2" t="n"/>
+      <c r="U168" s="3" t="n">
+        <v>0.01117507235899765</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Эди не доехал</t>
+          <t>Black Crystal</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>168</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>0.01173067896776382</v>
+        <v>0.01111327481156573</v>
+      </c>
+      <c r="U169" s="4" t="n">
+        <v>0.01111327481156573</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>KLO</t>
+          <t>vadim123</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>0.01166556890935342</v>
+        <v>0.01105159159833482</v>
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" s="2" t="n"/>
@@ -5061,7 +5424,9 @@
       <c r="R170" s="2" t="n"/>
       <c r="S170" s="2" t="n"/>
       <c r="T170" s="2" t="n"/>
-      <c r="U170" s="2" t="n"/>
+      <c r="U170" s="3" t="n">
+        <v>0.01105159159833482</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5073,20 +5438,23 @@
         <v>170</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.01160057976116039</v>
+        <v>0.01099002293162563</v>
+      </c>
+      <c r="U171" s="4" t="n">
+        <v>0.01099002293162563</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>mrsMarivanna</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>0.01153571174855424</v>
+        <v>0.01092856902494612</v>
       </c>
       <c r="D172" s="2" t="n"/>
       <c r="E172" s="2" t="n"/>
@@ -5105,32 +5473,37 @@
       <c r="R172" s="2" t="n"/>
       <c r="S172" s="2" t="n"/>
       <c r="T172" s="2" t="n"/>
-      <c r="U172" s="2" t="n"/>
+      <c r="U172" s="3" t="n">
+        <v>0.01092856902494612</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>МВика</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>172</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.01147096509816941</v>
+        <v>0.0108672300930026</v>
+      </c>
+      <c r="U173" s="4" t="n">
+        <v>0.0108672300930026</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>vadim123</t>
+          <t>mrsMarivanna</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>0.01140634003791721</v>
+        <v>0.01080600635171104</v>
       </c>
       <c r="D174" s="2" t="n"/>
       <c r="E174" s="2" t="n"/>
@@ -5149,32 +5522,37 @@
       <c r="R174" s="2" t="n"/>
       <c r="S174" s="2" t="n"/>
       <c r="T174" s="2" t="n"/>
-      <c r="U174" s="2" t="n"/>
+      <c r="U174" s="3" t="n">
+        <v>0.01080600635171104</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>174</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.01134183679699774</v>
+        <v>0.01074489801820839</v>
+      </c>
+      <c r="U175" s="4" t="n">
+        <v>0.01074489801820839</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>МВика</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>0.01127745560591221</v>
+        <v>0.0106839053108642</v>
       </c>
       <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="n"/>
@@ -5193,32 +5571,37 @@
       <c r="R176" s="2" t="n"/>
       <c r="S176" s="2" t="n"/>
       <c r="T176" s="2" t="n"/>
-      <c r="U176" s="2" t="n"/>
+      <c r="U176" s="3" t="n">
+        <v>0.0106839053108642</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Отец Дмитрий</t>
+          <t>Эди не доехал</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>176</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.01121319669647521</v>
+        <v>0.01062302844929231</v>
+      </c>
+      <c r="U177" s="4" t="n">
+        <v>0.01062302844929231</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Мистер Захаров</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>0.01114906030182726</v>
+        <v>0.01056226765436267</v>
       </c>
       <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="n"/>
@@ -5237,32 +5620,37 @@
       <c r="R178" s="2" t="n"/>
       <c r="S178" s="2" t="n"/>
       <c r="T178" s="2" t="n"/>
-      <c r="U178" s="2" t="n"/>
+      <c r="U178" s="3" t="n">
+        <v>0.01056226765436267</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Отец Дмитрий</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>178</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.0110850466564475</v>
+        <v>0.01050162314821342</v>
+      </c>
+      <c r="U179" s="4" t="n">
+        <v>0.01050162314821342</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Ivanjmj</t>
+          <t>dobrotova</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>0.01102115599616654</v>
+        <v>0.01044109515426304</v>
       </c>
       <c r="D180" s="2" t="n"/>
       <c r="E180" s="2" t="n"/>
@@ -5281,7 +5669,9 @@
       <c r="R180" s="2" t="n"/>
       <c r="S180" s="2" t="n"/>
       <c r="T180" s="2" t="n"/>
-      <c r="U180" s="2" t="n"/>
+      <c r="U180" s="3" t="n">
+        <v>0.01044109515426304</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5293,20 +5683,23 @@
         <v>180</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.0109573885581795</v>
+        <v>0.01038068389722268</v>
+      </c>
+      <c r="U181" s="4" t="n">
+        <v>0.01038068389722268</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>dobrotova</t>
+          <t>ЭтоМойНик</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>0.01089374458105922</v>
+        <v>0.01032038960310873</v>
       </c>
       <c r="D182" s="2" t="n"/>
       <c r="E182" s="2" t="n"/>
@@ -5325,32 +5718,37 @@
       <c r="R182" s="2" t="n"/>
       <c r="S182" s="2" t="n"/>
       <c r="T182" s="2" t="n"/>
-      <c r="U182" s="2" t="n"/>
+      <c r="U182" s="3" t="n">
+        <v>0.01032038960310873</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>whitecurly_rr</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>182</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.01083022430476964</v>
+        <v>0.01026021249925545</v>
+      </c>
+      <c r="U183" s="4" t="n">
+        <v>0.01026021249925545</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>NEVERLUCKY</t>
+          <t>balamut</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>0.01076682797067939</v>
+        <v>0.01020015281432784</v>
       </c>
       <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="n"/>
@@ -5369,32 +5767,37 @@
       <c r="R184" s="2" t="n"/>
       <c r="S184" s="2" t="n"/>
       <c r="T184" s="2" t="n"/>
-      <c r="U184" s="2" t="n"/>
+      <c r="U184" s="3" t="n">
+        <v>0.01020015281432784</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Nastyareshonova</t>
+          <t>Коленвал</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>184</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.01070355582157552</v>
+        <v>0.01014021077833471</v>
+      </c>
+      <c r="U185" s="4" t="n">
+        <v>0.01014021077833471</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ЭтоМойНик</t>
+          <t>Мистер Захаров</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
         <v>185</v>
       </c>
       <c r="C186" s="3" t="n">
-        <v>0.01064040810167748</v>
+        <v>0.01008038662264182</v>
       </c>
       <c r="D186" s="2" t="n"/>
       <c r="E186" s="2" t="n"/>
@@ -5413,32 +5816,37 @@
       <c r="R186" s="2" t="n"/>
       <c r="S186" s="2" t="n"/>
       <c r="T186" s="2" t="n"/>
-      <c r="U186" s="2" t="n"/>
+      <c r="U186" s="3" t="n">
+        <v>0.01008038662264182</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>balamut</t>
+          <t>Ilia M</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>186</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.01057738505665123</v>
+        <v>0.01002068057998537</v>
+      </c>
+      <c r="U187" s="4" t="n">
+        <v>0.01002068057998537</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>whitecurly_rr</t>
+          <t>NEVERLUCKY</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="C188" s="3" t="n">
-        <v>0.01051448693362359</v>
+        <v>0.009961092884485509</v>
       </c>
       <c r="D188" s="2" t="n"/>
       <c r="E188" s="2" t="n"/>
@@ -5457,32 +5865,37 @@
       <c r="R188" s="2" t="n"/>
       <c r="S188" s="2" t="n"/>
       <c r="T188" s="2" t="n"/>
-      <c r="U188" s="2" t="n"/>
+      <c r="U188" s="3" t="n">
+        <v>0.009961092884485509</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ilia M</t>
+          <t>Nastyareshonova</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>188</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.0104517139811968</v>
+        <v>0.009901623771660121</v>
+      </c>
+      <c r="U189" s="4" t="n">
+        <v>0.009901623771660121</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Ivanjmj</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="C190" s="3" t="n">
-        <v>0.01038906644946319</v>
+        <v>0.009842273478438815</v>
       </c>
       <c r="D190" s="2" t="n"/>
       <c r="E190" s="2" t="n"/>
@@ -5501,32 +5914,37 @@
       <c r="R190" s="2" t="n"/>
       <c r="S190" s="2" t="n"/>
       <c r="T190" s="2" t="n"/>
-      <c r="U190" s="2" t="n"/>
+      <c r="U190" s="3" t="n">
+        <v>0.009842273478438815</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>VVP</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>190</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>0.01032654459002022</v>
+        <v>0.009783042243177055</v>
+      </c>
+      <c r="U191" s="4" t="n">
+        <v>0.009783042243177055</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>JuZa</t>
+          <t>Даша 12 см</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
         <v>191</v>
       </c>
       <c r="C192" s="3" t="n">
-        <v>0.01026414865598557</v>
+        <v>0.009723930305670541</v>
       </c>
       <c r="D192" s="2" t="n"/>
       <c r="E192" s="2" t="n"/>
@@ -5545,32 +5963,37 @@
       <c r="R192" s="2" t="n"/>
       <c r="S192" s="2" t="n"/>
       <c r="T192" s="2" t="n"/>
-      <c r="U192" s="2" t="n"/>
+      <c r="U192" s="3" t="n">
+        <v>0.009723930305670541</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Zack</t>
+          <t>JuZa</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>192</v>
       </c>
       <c r="C193" s="4" t="n">
-        <v>0.01020187890201252</v>
+        <v>0.009664937907169753</v>
+      </c>
+      <c r="U193" s="4" t="n">
+        <v>0.009664937907169753</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Ruslan1</t>
+          <t>Kerbi</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="C194" s="3" t="n">
-        <v>0.01013973558430556</v>
+        <v>0.00960606529039474</v>
       </c>
       <c r="D194" s="2" t="n"/>
       <c r="E194" s="2" t="n"/>
@@ -5589,32 +6012,37 @@
       <c r="R194" s="2" t="n"/>
       <c r="S194" s="2" t="n"/>
       <c r="T194" s="2" t="n"/>
-      <c r="U194" s="2" t="n"/>
+      <c r="U194" s="3" t="n">
+        <v>0.00960606529039474</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Alisa Prekrati</t>
+          <t>Artemon</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>194</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>0.01007771896063619</v>
+        <v>0.009547312699550078</v>
+      </c>
+      <c r="U195" s="4" t="n">
+        <v>0.009547312699550078</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Даша 12 см</t>
+          <t>Alisa Prekrati</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="C196" s="3" t="n">
-        <v>0.01001582929035898</v>
+        <v>0.009488680380340087</v>
       </c>
       <c r="D196" s="2" t="n"/>
       <c r="E196" s="2" t="n"/>
@@ -5633,32 +6061,37 @@
       <c r="R196" s="2" t="n"/>
       <c r="S196" s="2" t="n"/>
       <c r="T196" s="2" t="n"/>
-      <c r="U196" s="2" t="n"/>
+      <c r="U196" s="3" t="n">
+        <v>0.009488680380340087</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>Zack</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>196</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>0.009954066834427793</v>
+        <v>0.009430168579984227</v>
+      </c>
+      <c r="U197" s="4" t="n">
+        <v>0.009430168579984227</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Коленвал</t>
+          <t>vad1m09473</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="C198" s="3" t="n">
-        <v>0.009892431855412345</v>
+        <v>0.009371777547232748</v>
       </c>
       <c r="D198" s="2" t="n"/>
       <c r="E198" s="2" t="n"/>
@@ -5677,32 +6110,37 @@
       <c r="R198" s="2" t="n"/>
       <c r="S198" s="2" t="n"/>
       <c r="T198" s="2" t="n"/>
-      <c r="U198" s="2" t="n"/>
+      <c r="U198" s="3" t="n">
+        <v>0.009371777547232748</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Гела</t>
+          <t>maxim_galeev</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>198</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>0.009830924617514912</v>
+        <v>0.009313507532382546</v>
+      </c>
+      <c r="U199" s="4" t="n">
+        <v>0.009313507532382546</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>FireSnail</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="C200" s="3" t="n">
-        <v>0.009769545386587331</v>
+        <v>0.00925535878729326</v>
       </c>
       <c r="D200" s="2" t="n"/>
       <c r="E200" s="2" t="n"/>
@@ -5721,32 +6159,37 @@
       <c r="R200" s="2" t="n"/>
       <c r="S200" s="2" t="n"/>
       <c r="T200" s="2" t="n"/>
-      <c r="U200" s="2" t="n"/>
+      <c r="U200" s="3" t="n">
+        <v>0.00925535878729326</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>FireSnail</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>200</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.009708294430148243</v>
+        <v>0.009197331565403599</v>
+      </c>
+      <c r="U201" s="4" t="n">
+        <v>0.009197331565403599</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Kerbi</t>
+          <t>VVP</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
         <v>201</v>
       </c>
       <c r="C202" s="3" t="n">
-        <v>0.009647172017400571</v>
+        <v>0.009139426121747909</v>
       </c>
       <c r="D202" s="2" t="n"/>
       <c r="E202" s="2" t="n"/>
@@ -5765,7 +6208,9 @@
       <c r="R202" s="2" t="n"/>
       <c r="S202" s="2" t="n"/>
       <c r="T202" s="2" t="n"/>
-      <c r="U202" s="2" t="n"/>
+      <c r="U202" s="3" t="n">
+        <v>0.009139426121747909</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5777,20 +6222,23 @@
         <v>202</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.00958617841924928</v>
+        <v>0.009081642712973003</v>
+      </c>
+      <c r="U203" s="4" t="n">
+        <v>0.009081642712973003</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>vad1m09473</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
         <v>203</v>
       </c>
       <c r="C204" s="3" t="n">
-        <v>0.009525313908319373</v>
+        <v>0.009023981597355197</v>
       </c>
       <c r="D204" s="2" t="n"/>
       <c r="E204" s="2" t="n"/>
@@ -5809,32 +6257,37 @@
       <c r="R204" s="2" t="n"/>
       <c r="S204" s="2" t="n"/>
       <c r="T204" s="2" t="n"/>
-      <c r="U204" s="2" t="n"/>
+      <c r="U204" s="3" t="n">
+        <v>0.009023981597355197</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Artemon</t>
+          <t>Ruslan1</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>204</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.009464578758974194</v>
+        <v>0.008966443034817657</v>
+      </c>
+      <c r="U205" s="4" t="n">
+        <v>0.008966443034817657</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>maxim_galeev</t>
+          <t>lubashley</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
         <v>205</v>
       </c>
       <c r="C206" s="3" t="n">
-        <v>0.00940397324733395</v>
+        <v>0.008909027286947951</v>
       </c>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="2" t="n"/>
@@ -5853,32 +6306,37 @@
       <c r="R206" s="2" t="n"/>
       <c r="S206" s="2" t="n"/>
       <c r="T206" s="2" t="n"/>
-      <c r="U206" s="2" t="n"/>
+      <c r="U206" s="3" t="n">
+        <v>0.008909027286947951</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>206</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.009343497651294568</v>
+        <v>0.008851734617015907</v>
+      </c>
+      <c r="U207" s="4" t="n">
+        <v>0.008851734617015907</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>lubashley</t>
+          <t>Cocacola</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
         <v>207</v>
       </c>
       <c r="C208" s="3" t="n">
-        <v>0.009283152250546801</v>
+        <v>0.008794565289991707</v>
       </c>
       <c r="D208" s="2" t="n"/>
       <c r="E208" s="2" t="n"/>
@@ -5897,32 +6355,37 @@
       <c r="R208" s="2" t="n"/>
       <c r="S208" s="2" t="n"/>
       <c r="T208" s="2" t="n"/>
-      <c r="U208" s="2" t="n"/>
+      <c r="U208" s="3" t="n">
+        <v>0.008794565289991707</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>208</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>0.009222937326595623</v>
+        <v>0.008737519572564275</v>
+      </c>
+      <c r="U209" s="4" t="n">
+        <v>0.008737519572564275</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>Гела</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="C210" s="3" t="n">
-        <v>0.009162853162779934</v>
+        <v>0.008680597733159939</v>
       </c>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="2" t="n"/>
@@ -5941,32 +6404,37 @@
       <c r="R210" s="2" t="n"/>
       <c r="S210" s="2" t="n"/>
       <c r="T210" s="2" t="n"/>
-      <c r="U210" s="2" t="n"/>
+      <c r="U210" s="3" t="n">
+        <v>0.008680597733159939</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>210</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.009102900044292568</v>
+        <v>0.008623800041961381</v>
+      </c>
+      <c r="U211" s="4" t="n">
+        <v>0.008623800041961381</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Halo</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="C212" s="3" t="n">
-        <v>0.009043078258200582</v>
+        <v>0.008567126770926867</v>
       </c>
       <c r="D212" s="2" t="n"/>
       <c r="E212" s="2" t="n"/>
@@ -5985,32 +6453,37 @@
       <c r="R212" s="2" t="n"/>
       <c r="S212" s="2" t="n"/>
       <c r="T212" s="2" t="n"/>
-      <c r="U212" s="2" t="n"/>
+      <c r="U212" s="3" t="n">
+        <v>0.008567126770926867</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Фуфа</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>212</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>0.008983388093465891</v>
+        <v>0.008510578193809792</v>
+      </c>
+      <c r="U213" s="4" t="n">
+        <v>0.008510578193809792</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Cocacola</t>
+          <t>Катюха</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="C214" s="3" t="n">
-        <v>0.008923829840966195</v>
+        <v>0.008454154586178502</v>
       </c>
       <c r="D214" s="2" t="n"/>
       <c r="E214" s="2" t="n"/>
@@ -6029,32 +6502,37 @@
       <c r="R214" s="2" t="n"/>
       <c r="S214" s="2" t="n"/>
       <c r="T214" s="2" t="n"/>
-      <c r="U214" s="2" t="n"/>
+      <c r="U214" s="3" t="n">
+        <v>0.008454154586178502</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>NumberCat</t>
+          <t>Halo</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>214</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.008864403793516251</v>
+        <v>0.008397856225436448</v>
+      </c>
+      <c r="U215" s="4" t="n">
+        <v>0.008397856225436448</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>kciNik</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="C216" s="3" t="n">
-        <v>0.008805110245889458</v>
+        <v>0.008341683390842644</v>
       </c>
       <c r="D216" s="2" t="n"/>
       <c r="E216" s="2" t="n"/>
@@ -6073,32 +6551,37 @@
       <c r="R216" s="2" t="n"/>
       <c r="S216" s="2" t="n"/>
       <c r="T216" s="2" t="n"/>
-      <c r="U216" s="2" t="n"/>
+      <c r="U216" s="3" t="n">
+        <v>0.008341683390842644</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>kciNik</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>216</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.008745949494839795</v>
+        <v>0.008285636363532438</v>
+      </c>
+      <c r="U217" s="4" t="n">
+        <v>0.008285636363532438</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Север</t>
+          <t>Yrs</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="C218" s="3" t="n">
-        <v>0.008686921839124107</v>
+        <v>0.008229715426538628</v>
       </c>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="2" t="n"/>
@@ -6117,32 +6600,37 @@
       <c r="R218" s="2" t="n"/>
       <c r="S218" s="2" t="n"/>
       <c r="T218" s="2" t="n"/>
-      <c r="U218" s="2" t="n"/>
+      <c r="U218" s="3" t="n">
+        <v>0.008229715426538628</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>yungplague</t>
+          <t>NumberCat</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>218</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.00862802757952473</v>
+        <v>0.008173920864812901</v>
+      </c>
+      <c r="U219" s="4" t="n">
+        <v>0.008173920864812901</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Фуфа</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
         <v>219</v>
       </c>
       <c r="C220" s="3" t="n">
-        <v>0.008569267018872478</v>
+        <v>0.00811825296524761</v>
       </c>
       <c r="D220" s="2" t="n"/>
       <c r="E220" s="2" t="n"/>
@@ -6161,32 +6649,37 @@
       <c r="R220" s="2" t="n"/>
       <c r="S220" s="2" t="n"/>
       <c r="T220" s="2" t="n"/>
-      <c r="U220" s="2" t="n"/>
+      <c r="U220" s="3" t="n">
+        <v>0.00811825296524761</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Yrs</t>
+          <t>egorzubkovv</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>220</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.008510640462070007</v>
+        <v>0.008062712016697901</v>
+      </c>
+      <c r="U221" s="4" t="n">
+        <v>0.008062712016697901</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Катюха</t>
+          <t>yungplague</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="C222" s="3" t="n">
-        <v>0.00845214821611555</v>
+        <v>0.008007298310004204</v>
       </c>
       <c r="D222" s="2" t="n"/>
       <c r="E222" s="2" t="n"/>
@@ -6205,32 +6698,37 @@
       <c r="R222" s="2" t="n"/>
       <c r="S222" s="2" t="n"/>
       <c r="T222" s="2" t="n"/>
-      <c r="U222" s="2" t="n"/>
+      <c r="U222" s="3" t="n">
+        <v>0.008007298310004204</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>egorzubkovv</t>
+          <t>Север</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>222</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>0.008393790590127029</v>
+        <v>0.00795201213801508</v>
+      </c>
+      <c r="U223" s="4" t="n">
+        <v>0.00795201213801508</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>chinaonetown</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
         <v>223</v>
       </c>
       <c r="C224" s="3" t="n">
-        <v>0.008335567895366556</v>
+        <v>0.007896853795610422</v>
       </c>
       <c r="D224" s="2" t="n"/>
       <c r="E224" s="2" t="n"/>
@@ -6249,32 +6747,37 @@
       <c r="R224" s="2" t="n"/>
       <c r="S224" s="2" t="n"/>
       <c r="T224" s="2" t="n"/>
-      <c r="U224" s="2" t="n"/>
+      <c r="U224" s="3" t="n">
+        <v>0.007896853795610422</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>chinaonetown</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>224</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.008277480445265344</v>
+        <v>0.007841823579725063</v>
+      </c>
+      <c r="U225" s="4" t="n">
+        <v>0.007841823579725063</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>Borsalino</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
         <v>225</v>
       </c>
       <c r="C226" s="3" t="n">
-        <v>0.008219528555449017</v>
+        <v>0.007786921789372753</v>
       </c>
       <c r="D226" s="2" t="n"/>
       <c r="E226" s="2" t="n"/>
@@ -6293,32 +6796,37 @@
       <c r="R226" s="2" t="n"/>
       <c r="S226" s="2" t="n"/>
       <c r="T226" s="2" t="n"/>
-      <c r="U226" s="2" t="n"/>
+      <c r="U226" s="3" t="n">
+        <v>0.007786921789372753</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Retik</t>
+          <t>toronto970</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>226</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.008161712543763328</v>
+        <v>0.007732148725670521</v>
+      </c>
+      <c r="U227" s="4" t="n">
+        <v>0.007732148725670521</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Borsalino</t>
+          <t>Retik</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
         <v>227</v>
       </c>
       <c r="C228" s="3" t="n">
-        <v>0.008104032730300323</v>
+        <v>0.007677504691863463</v>
       </c>
       <c r="D228" s="2" t="n"/>
       <c r="E228" s="2" t="n"/>
@@ -6337,32 +6845,37 @@
       <c r="R228" s="2" t="n"/>
       <c r="S228" s="2" t="n"/>
       <c r="T228" s="2" t="n"/>
-      <c r="U228" s="2" t="n"/>
+      <c r="U228" s="3" t="n">
+        <v>0.007677504691863463</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>moodellas</t>
+          <t>puppet</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>228</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.008046489437424911</v>
+        <v>0.007622989993349915</v>
+      </c>
+      <c r="U229" s="4" t="n">
+        <v>0.007622989993349915</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>toronto970</t>
+          <t>moodellas</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="C230" s="3" t="n">
-        <v>0.007989082989801903</v>
+        <v>0.007568604937707067</v>
       </c>
       <c r="D230" s="2" t="n"/>
       <c r="E230" s="2" t="n"/>
@@ -6381,32 +6894,37 @@
       <c r="R230" s="2" t="n"/>
       <c r="S230" s="2" t="n"/>
       <c r="T230" s="2" t="n"/>
-      <c r="U230" s="2" t="n"/>
+      <c r="U230" s="3" t="n">
+        <v>0.007568604937707067</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Альфред</t>
+          <t>MYDAK</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>230</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.00793181371442348</v>
+        <v>0.00751434983471698</v>
+      </c>
+      <c r="U231" s="4" t="n">
+        <v>0.00751434983471698</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>MYDAK</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
         <v>231</v>
       </c>
       <c r="C232" s="3" t="n">
-        <v>0.007874681940637132</v>
+        <v>0.007460224996393073</v>
       </c>
       <c r="D232" s="2" t="n"/>
       <c r="E232" s="2" t="n"/>
@@ -6425,32 +6943,37 @@
       <c r="R232" s="2" t="n"/>
       <c r="S232" s="2" t="n"/>
       <c r="T232" s="2" t="n"/>
-      <c r="U232" s="2" t="n"/>
+      <c r="U232" s="3" t="n">
+        <v>0.007460224996393073</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Killreal</t>
+          <t>Хэнк Муди</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>232</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>0.007817688000174088</v>
+        <v>0.007406230737007031</v>
+      </c>
+      <c r="U233" s="4" t="n">
+        <v>0.007406230737007031</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Пётр 1</t>
+          <t>Кристина П</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
         <v>233</v>
       </c>
       <c r="C234" s="3" t="n">
-        <v>0.007760832227178184</v>
+        <v>0.007352367373116175</v>
       </c>
       <c r="D234" s="2" t="n"/>
       <c r="E234" s="2" t="n"/>
@@ -6469,32 +6992,37 @@
       <c r="R234" s="2" t="n"/>
       <c r="S234" s="2" t="n"/>
       <c r="T234" s="2" t="n"/>
-      <c r="U234" s="2" t="n"/>
+      <c r="U234" s="3" t="n">
+        <v>0.007352367373116175</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>puppet</t>
+          <t>Император</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>234</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.007704114958235272</v>
+        <v>0.007298635223591311</v>
+      </c>
+      <c r="U235" s="4" t="n">
+        <v>0.007298635223591311</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Кристина П</t>
+          <t>steyk</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
         <v>235</v>
       </c>
       <c r="C236" s="3" t="n">
-        <v>0.007647536532403097</v>
+        <v>0.007245034609645039</v>
       </c>
       <c r="D236" s="2" t="n"/>
       <c r="E236" s="2" t="n"/>
@@ -6513,32 +7041,37 @@
       <c r="R236" s="2" t="n"/>
       <c r="S236" s="2" t="n"/>
       <c r="T236" s="2" t="n"/>
-      <c r="U236" s="2" t="n"/>
+      <c r="U236" s="3" t="n">
+        <v>0.007245034609645039</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>steyk</t>
+          <t>Aronio</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>236</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.007591097291241708</v>
+        <v>0.007191565854860565</v>
+      </c>
+      <c r="U237" s="4" t="n">
+        <v>0.007191565854860565</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Vikki</t>
+          <t>over9000mmr</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="C238" s="3" t="n">
-        <v>0.007534797578844386</v>
+        <v>0.007138229285220997</v>
       </c>
       <c r="D238" s="2" t="n"/>
       <c r="E238" s="2" t="n"/>
@@ -6557,32 +7090,37 @@
       <c r="R238" s="2" t="n"/>
       <c r="S238" s="2" t="n"/>
       <c r="T238" s="2" t="n"/>
-      <c r="U238" s="2" t="n"/>
+      <c r="U238" s="3" t="n">
+        <v>0.007138229285220997</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Полинат</t>
+          <t>Альфред</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>238</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.007478637741869118</v>
+        <v>0.007085025229139165</v>
+      </c>
+      <c r="U239" s="4" t="n">
+        <v>0.007085025229139165</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Адольф</t>
+          <t>Kasatik</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="C240" s="3" t="n">
-        <v>0.00742261812957061</v>
+        <v>0.007031954017487946</v>
       </c>
       <c r="D240" s="2" t="n"/>
       <c r="E240" s="2" t="n"/>
@@ -6601,32 +7139,37 @@
       <c r="R240" s="2" t="n"/>
       <c r="S240" s="2" t="n"/>
       <c r="T240" s="2" t="n"/>
-      <c r="U240" s="2" t="n"/>
+      <c r="U240" s="3" t="n">
+        <v>0.007031954017487946</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Сантьяго</t>
+          <t>Наталья</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>240</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.00736673909383288</v>
+        <v>0.006979015983631149</v>
+      </c>
+      <c r="U241" s="4" t="n">
+        <v>0.006979015983631149</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Император</t>
+          <t>Vii</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="C242" s="3" t="n">
-        <v>0.007311000989202399</v>
+        <v>0.006926211463454904</v>
       </c>
       <c r="D242" s="2" t="n"/>
       <c r="E242" s="2" t="n"/>
@@ -6645,32 +7188,37 @@
       <c r="R242" s="2" t="n"/>
       <c r="S242" s="2" t="n"/>
       <c r="T242" s="2" t="n"/>
-      <c r="U242" s="2" t="n"/>
+      <c r="U242" s="3" t="n">
+        <v>0.006926211463454904</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Наталья</t>
+          <t>Killreal</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>242</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.007255404172921849</v>
+        <v>0.006873540795399646</v>
+      </c>
+      <c r="U243" s="4" t="n">
+        <v>0.006873540795399646</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Aronio</t>
+          <t>Пётр 1</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="C244" s="3" t="n">
-        <v>0.007199949004964467</v>
+        <v>0.006821004320492653</v>
       </c>
       <c r="D244" s="2" t="n"/>
       <c r="E244" s="2" t="n"/>
@@ -6689,32 +7237,37 @@
       <c r="R244" s="2" t="n"/>
       <c r="S244" s="2" t="n"/>
       <c r="T244" s="2" t="n"/>
-      <c r="U244" s="2" t="n"/>
+      <c r="U244" s="3" t="n">
+        <v>0.006821004320492653</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Хэнк Муди</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>244</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.007144635848069002</v>
+        <v>0.00676860238238116</v>
+      </c>
+      <c r="U245" s="4" t="n">
+        <v>0.00676860238238116</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Luckymodjo</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="C246" s="3" t="n">
-        <v>0.007089465067775321</v>
+        <v>0.006716335327366093</v>
       </c>
       <c r="D246" s="2" t="n"/>
       <c r="E246" s="2" t="n"/>
@@ -6733,32 +7286,37 @@
       <c r="R246" s="2" t="n"/>
       <c r="S246" s="2" t="n"/>
       <c r="T246" s="2" t="n"/>
-      <c r="U246" s="2" t="n"/>
+      <c r="U246" s="3" t="n">
+        <v>0.006716335327366093</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>over9000mmr</t>
+          <t>Полинат</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>246</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.007034437032460627</v>
+        <v>0.006664203504436384</v>
+      </c>
+      <c r="U247" s="4" t="n">
+        <v>0.006664203504436384</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Kasatik</t>
+          <t>Сантьяго</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="C248" s="3" t="n">
-        <v>0.006979552113376382</v>
+        <v>0.00661220726530394</v>
       </c>
       <c r="D248" s="2" t="n"/>
       <c r="E248" s="2" t="n"/>
@@ -6777,32 +7335,37 @@
       <c r="R248" s="2" t="n"/>
       <c r="S248" s="2" t="n"/>
       <c r="T248" s="2" t="n"/>
-      <c r="U248" s="2" t="n"/>
+      <c r="U248" s="3" t="n">
+        <v>0.00661220726530394</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Vii</t>
+          <t>Vikki</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>248</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.006924810684685855</v>
+        <v>0.00656034696443923</v>
+      </c>
+      <c r="U249" s="4" t="n">
+        <v>0.00656034696443923</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Luckymodjo</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="C250" s="3" t="n">
-        <v>0.006870213123502398</v>
+        <v>0.006508622959107536</v>
       </c>
       <c r="D250" s="2" t="n"/>
       <c r="E250" s="2" t="n"/>
@@ -6821,32 +7384,37 @@
       <c r="R250" s="2" t="n"/>
       <c r="S250" s="2" t="n"/>
       <c r="T250" s="2" t="n"/>
-      <c r="U250" s="2" t="n"/>
+      <c r="U250" s="3" t="n">
+        <v>0.006508622959107536</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Bagira</t>
+          <t>Errchi</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>250</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>0.006815759809928422</v>
+        <v>0.006457035609405874</v>
+      </c>
+      <c r="U251" s="4" t="n">
+        <v>0.006457035609405874</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>Адольф</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="C252" s="3" t="n">
-        <v>0.006761451127095078</v>
+        <v>0.006405585278300601</v>
       </c>
       <c r="D252" s="2" t="n"/>
       <c r="E252" s="2" t="n"/>
@@ -6865,32 +7433,37 @@
       <c r="R252" s="2" t="n"/>
       <c r="S252" s="2" t="n"/>
       <c r="T252" s="2" t="n"/>
-      <c r="U252" s="2" t="n"/>
+      <c r="U252" s="3" t="n">
+        <v>0.006405585278300601</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Groove</t>
+          <t>Bagira</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>252</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>0.006707287461202708</v>
+        <v>0.006354272331665724</v>
+      </c>
+      <c r="U253" s="4" t="n">
+        <v>0.006354272331665724</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Errchi</t>
+          <t>Gambling Addiction</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="C254" s="3" t="n">
-        <v>0.006653269201562039</v>
+        <v>0.006303097138321932</v>
       </c>
       <c r="D254" s="2" t="n"/>
       <c r="E254" s="2" t="n"/>
@@ -6909,19 +7482,24 @@
       <c r="R254" s="2" t="n"/>
       <c r="S254" s="2" t="n"/>
       <c r="T254" s="2" t="n"/>
-      <c r="U254" s="2" t="n"/>
+      <c r="U254" s="3" t="n">
+        <v>0.006303097138321932</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>рачули</t>
+          <t>STG</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>254</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>0.006599396740636156</v>
+        <v>0.00625206007007636</v>
+      </c>
+      <c r="U255" s="4" t="n">
+        <v>0.00625206007007636</v>
       </c>
     </row>
     <row r="256">
@@ -6934,7 +7512,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="3" t="n">
-        <v>0.00654567047408329</v>
+        <v>0.006201161501763116</v>
       </c>
       <c r="D256" s="2" t="n"/>
       <c r="E256" s="2" t="n"/>
@@ -6953,32 +7531,37 @@
       <c r="R256" s="2" t="n"/>
       <c r="S256" s="2" t="n"/>
       <c r="T256" s="2" t="n"/>
-      <c r="U256" s="2" t="n"/>
+      <c r="U256" s="3" t="n">
+        <v>0.006201161501763116</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STG</t>
+          <t>Groove</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>256</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>0.006492090800800381</v>
+        <v>0.006150401811284572</v>
+      </c>
+      <c r="U257" s="4" t="n">
+        <v>0.006150401811284572</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>mmrrll</t>
+          <t>витя доезд</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="C258" s="3" t="n">
-        <v>0.006438658122967537</v>
+        <v>0.006099781379653457</v>
       </c>
       <c r="D258" s="2" t="n"/>
       <c r="E258" s="2" t="n"/>
@@ -6997,19 +7580,24 @@
       <c r="R258" s="2" t="n"/>
       <c r="S258" s="2" t="n"/>
       <c r="T258" s="2" t="n"/>
-      <c r="U258" s="2" t="n"/>
+      <c r="U258" s="3" t="n">
+        <v>0.006099781379653457</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>viktorHQC</t>
+          <t>рачули</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>258</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>0.006385372846093296</v>
+        <v>0.006049300591035755</v>
+      </c>
+      <c r="U259" s="4" t="n">
+        <v>0.006049300591035755</v>
       </c>
     </row>
     <row r="260">
@@ -7022,7 +7610,7 @@
         <v>259</v>
       </c>
       <c r="C260" s="3" t="n">
-        <v>0.006332235379060808</v>
+        <v>0.005998959832794451</v>
       </c>
       <c r="D260" s="2" t="n"/>
       <c r="E260" s="2" t="n"/>
@@ -7041,19 +7629,24 @@
       <c r="R260" s="2" t="n"/>
       <c r="S260" s="2" t="n"/>
       <c r="T260" s="2" t="n"/>
-      <c r="U260" s="2" t="n"/>
+      <c r="U260" s="3" t="n">
+        <v>0.005998959832794451</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>mmrrll</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>260</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.00627924613417489</v>
+        <v>0.005948759495534106</v>
+      </c>
+      <c r="U261" s="4" t="n">
+        <v>0.005948759495534106</v>
       </c>
     </row>
     <row r="262">
@@ -7066,7 +7659,7 @@
         <v>261</v>
       </c>
       <c r="C262" s="3" t="n">
-        <v>0.00622640552721002</v>
+        <v>0.005898699973146336</v>
       </c>
       <c r="D262" s="2" t="n"/>
       <c r="E262" s="2" t="n"/>
@@ -7085,32 +7678,37 @@
       <c r="R262" s="2" t="n"/>
       <c r="S262" s="2" t="n"/>
       <c r="T262" s="2" t="n"/>
-      <c r="U262" s="2" t="n"/>
+      <c r="U262" s="3" t="n">
+        <v>0.005898699973146336</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>витя доезд</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>262</v>
       </c>
       <c r="C263" s="4" t="n">
-        <v>0.006173713977459284</v>
+        <v>0.005848781662856164</v>
+      </c>
+      <c r="U263" s="4" t="n">
+        <v>0.005848781662856164</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>xairullah</t>
+          <t>viktorHQC</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
         <v>263</v>
       </c>
       <c r="C264" s="3" t="n">
-        <v>0.006121171907784274</v>
+        <v>0.005799004965269312</v>
       </c>
       <c r="D264" s="2" t="n"/>
       <c r="E264" s="2" t="n"/>
@@ -7129,32 +7727,37 @@
       <c r="R264" s="2" t="n"/>
       <c r="S264" s="2" t="n"/>
       <c r="T264" s="2" t="n"/>
-      <c r="U264" s="2" t="n"/>
+      <c r="U264" s="3" t="n">
+        <v>0.005799004965269312</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>aisel</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>264</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.006068779744666001</v>
+        <v>0.005749370284420421</v>
+      </c>
+      <c r="U265" s="4" t="n">
+        <v>0.005749370284420421</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Gambling Addiction</t>
+          <t>xairullah</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
         <v>265</v>
       </c>
       <c r="C266" s="3" t="n">
-        <v>0.006016537918256824</v>
+        <v>0.005699878027822254</v>
       </c>
       <c r="D266" s="2" t="n"/>
       <c r="E266" s="2" t="n"/>
@@ -7173,19 +7776,24 @@
       <c r="R266" s="2" t="n"/>
       <c r="S266" s="2" t="n"/>
       <c r="T266" s="2" t="n"/>
-      <c r="U266" s="2" t="n"/>
+      <c r="U266" s="3" t="n">
+        <v>0.005699878027822254</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Danil123</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>266</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.005964446862433432</v>
+        <v>0.005650528606515883</v>
+      </c>
+      <c r="U267" s="4" t="n">
+        <v>0.005650528606515883</v>
       </c>
     </row>
     <row r="268">
@@ -7198,7 +7806,7 @@
         <v>267</v>
       </c>
       <c r="C268" s="3" t="n">
-        <v>0.005912507014850893</v>
+        <v>0.005601322435121898</v>
       </c>
       <c r="D268" s="2" t="n"/>
       <c r="E268" s="2" t="n"/>
@@ -7217,7 +7825,9 @@
       <c r="R268" s="2" t="n"/>
       <c r="S268" s="2" t="n"/>
       <c r="T268" s="2" t="n"/>
-      <c r="U268" s="2" t="n"/>
+      <c r="U268" s="3" t="n">
+        <v>0.005601322435121898</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7229,20 +7839,23 @@
         <v>268</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>0.00586071881699782</v>
+        <v>0.005552259931892672</v>
+      </c>
+      <c r="U269" s="4" t="n">
+        <v>0.005552259931892672</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Danil123</t>
+          <t>aisel</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
         <v>269</v>
       </c>
       <c r="C270" s="3" t="n">
-        <v>0.005809082714252661</v>
+        <v>0.005503341518765678</v>
       </c>
       <c r="D270" s="2" t="n"/>
       <c r="E270" s="2" t="n"/>
@@ -7261,32 +7874,37 @@
       <c r="R270" s="2" t="n"/>
       <c r="S270" s="2" t="n"/>
       <c r="T270" s="2" t="n"/>
-      <c r="U270" s="2" t="n"/>
+      <c r="U270" s="3" t="n">
+        <v>0.005503341518765678</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Alkyds</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>270</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>0.005757599155941166</v>
+        <v>0.005454567621417946</v>
+      </c>
+      <c r="U271" s="4" t="n">
+        <v>0.005454567621417946</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Эдгар</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
         <v>271</v>
       </c>
       <c r="C272" s="3" t="n">
-        <v>0.005706268595395025</v>
+        <v>0.005405938669321602</v>
       </c>
       <c r="D272" s="2" t="n"/>
       <c r="E272" s="2" t="n"/>
@@ -7305,32 +7923,37 @@
       <c r="R272" s="2" t="n"/>
       <c r="S272" s="2" t="n"/>
       <c r="T272" s="2" t="n"/>
-      <c r="U272" s="2" t="n"/>
+      <c r="U272" s="3" t="n">
+        <v>0.005405938669321602</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>Bad Beat Bunny</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>272</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>0.005655091490011765</v>
+        <v>0.005357455095800619</v>
+      </c>
+      <c r="U273" s="4" t="n">
+        <v>0.005357455095800619</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>dpolyaa</t>
+          <t>Alkyds</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="C274" s="3" t="n">
-        <v>0.005604068301315882</v>
+        <v>0.005309117338088731</v>
       </c>
       <c r="D274" s="2" t="n"/>
       <c r="E274" s="2" t="n"/>
@@ -7349,32 +7972,37 @@
       <c r="R274" s="2" t="n"/>
       <c r="S274" s="2" t="n"/>
       <c r="T274" s="2" t="n"/>
-      <c r="U274" s="2" t="n"/>
+      <c r="U274" s="3" t="n">
+        <v>0.005309117338088731</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Эдгар</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>274</v>
       </c>
       <c r="C275" s="4" t="n">
-        <v>0.005553199495021284</v>
+        <v>0.005260925837388584</v>
+      </c>
+      <c r="U275" s="4" t="n">
+        <v>0.005260925837388584</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>onedrakeo</t>
+          <t>Голиаф</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="C276" s="3" t="n">
-        <v>0.005502485541095054</v>
+        <v>0.005212881038932157</v>
       </c>
       <c r="D276" s="2" t="n"/>
       <c r="E276" s="2" t="n"/>
@@ -7393,32 +8021,37 @@
       <c r="R276" s="2" t="n"/>
       <c r="S276" s="2" t="n"/>
       <c r="T276" s="2" t="n"/>
-      <c r="U276" s="2" t="n"/>
+      <c r="U276" s="3" t="n">
+        <v>0.005212881038932157</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Голиаф</t>
+          <t>fe1k</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>276</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.005451926913822587</v>
+        <v>0.00516498339204245</v>
+      </c>
+      <c r="U277" s="4" t="n">
+        <v>0.00516498339204245</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="C278" s="3" t="n">
-        <v>0.005401524091874127</v>
+        <v>0.005117233350196542</v>
       </c>
       <c r="D278" s="2" t="n"/>
       <c r="E278" s="2" t="n"/>
@@ -7437,32 +8070,37 @@
       <c r="R278" s="2" t="n"/>
       <c r="S278" s="2" t="n"/>
       <c r="T278" s="2" t="n"/>
-      <c r="U278" s="2" t="n"/>
+      <c r="U278" s="3" t="n">
+        <v>0.005117233350196542</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Bad Beat Bunny</t>
+          <t>dpolyaa</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>278</v>
       </c>
       <c r="C279" s="4" t="n">
-        <v>0.005351277558372758</v>
+        <v>0.005069631371089981</v>
+      </c>
+      <c r="U279" s="4" t="n">
+        <v>0.005069631371089981</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>eff1002</t>
+          <t>onedrakeo</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="C280" s="3" t="n">
-        <v>0.005301187800963865</v>
+        <v>0.005022177916702609</v>
       </c>
       <c r="D280" s="2" t="n"/>
       <c r="E280" s="2" t="n"/>
@@ -7481,32 +8119,37 @@
       <c r="R280" s="2" t="n"/>
       <c r="S280" s="2" t="n"/>
       <c r="T280" s="2" t="n"/>
-      <c r="U280" s="2" t="n"/>
+      <c r="U280" s="3" t="n">
+        <v>0.005022177916702609</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>fe1k</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>280</v>
       </c>
       <c r="C281" s="4" t="n">
-        <v>0.005251255311886133</v>
+        <v>0.00497487345336581</v>
+      </c>
+      <c r="U281" s="4" t="n">
+        <v>0.00497487345336581</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>eff1002</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="C282" s="3" t="n">
-        <v>0.005201480588044113</v>
+        <v>0.004927718451831265</v>
       </c>
       <c r="D282" s="2" t="n"/>
       <c r="E282" s="2" t="n"/>
@@ -7525,32 +8168,37 @@
       <c r="R282" s="2" t="n"/>
       <c r="S282" s="2" t="n"/>
       <c r="T282" s="2" t="n"/>
-      <c r="U282" s="2" t="n"/>
+      <c r="U282" s="3" t="n">
+        <v>0.004927718451831265</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Pasha2796</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>282</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.005151864131082406</v>
+        <v>0.004880713387341227</v>
+      </c>
+      <c r="U283" s="4" t="n">
+        <v>0.004880713387341227</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>xiolloix</t>
+          <t>Pasha2796</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="C284" s="3" t="n">
-        <v>0.0051024064474615</v>
+        <v>0.004833858739700369</v>
       </c>
       <c r="D284" s="2" t="n"/>
       <c r="E284" s="2" t="n"/>
@@ -7569,32 +8217,37 @@
       <c r="R284" s="2" t="n"/>
       <c r="S284" s="2" t="n"/>
       <c r="T284" s="2" t="n"/>
-      <c r="U284" s="2" t="n"/>
+      <c r="U284" s="3" t="n">
+        <v>0.004833858739700369</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Akatones</t>
+          <t>Kiselka</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>284</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.005053108048535327</v>
+        <v>0.004787154993349257</v>
+      </c>
+      <c r="U285" s="4" t="n">
+        <v>0.004787154993349257</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Kiselka</t>
+          <t>avdoda</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="C286" s="3" t="n">
-        <v>0.005003969450630576</v>
+        <v>0.004740602637439494</v>
       </c>
       <c r="D286" s="2" t="n"/>
       <c r="E286" s="2" t="n"/>
@@ -7613,32 +8266,37 @@
       <c r="R286" s="2" t="n"/>
       <c r="S286" s="2" t="n"/>
       <c r="T286" s="2" t="n"/>
-      <c r="U286" s="2" t="n"/>
+      <c r="U286" s="3" t="n">
+        <v>0.004740602637439494</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Olga Sheil</t>
+          <t>Akatones</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>286</v>
       </c>
       <c r="C287" s="4" t="n">
-        <v>0.004954991175127818</v>
+        <v>0.004694202165910565</v>
+      </c>
+      <c r="U287" s="4" t="n">
+        <v>0.004694202165910565</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>журналист</t>
+          <t>xiolloix</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="C288" s="3" t="n">
-        <v>0.00490617374854449</v>
+        <v>0.004647954077568465</v>
       </c>
       <c r="D288" s="2" t="n"/>
       <c r="E288" s="2" t="n"/>
@@ -7657,32 +8315,37 @@
       <c r="R288" s="2" t="n"/>
       <c r="S288" s="2" t="n"/>
       <c r="T288" s="2" t="n"/>
-      <c r="U288" s="2" t="n"/>
+      <c r="U288" s="3" t="n">
+        <v>0.004647954077568465</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ginger</t>
+          <t>ivolodya</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>288</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.004857517702619808</v>
+        <v>0.004601858876166134</v>
+      </c>
+      <c r="U289" s="4" t="n">
+        <v>0.004601858876166134</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>журналист</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
         <v>289</v>
       </c>
       <c r="C290" s="3" t="n">
-        <v>0.004809023574401657</v>
+        <v>0.00455591707048578</v>
       </c>
       <c r="D290" s="2" t="n"/>
       <c r="E290" s="2" t="n"/>
@@ -7701,7 +8364,9 @@
       <c r="R290" s="2" t="n"/>
       <c r="S290" s="2" t="n"/>
       <c r="T290" s="2" t="n"/>
-      <c r="U290" s="2" t="n"/>
+      <c r="U290" s="3" t="n">
+        <v>0.00455591707048578</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7713,20 +8378,23 @@
         <v>290</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.00476069190633551</v>
+        <v>0.004510129174423115</v>
+      </c>
+      <c r="U291" s="4" t="n">
+        <v>0.004510129174423115</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>ivolodya</t>
+          <t>Olga Sheil</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
         <v>291</v>
       </c>
       <c r="C292" s="3" t="n">
-        <v>0.00471252324635546</v>
+        <v>0.004464495707073594</v>
       </c>
       <c r="D292" s="2" t="n"/>
       <c r="E292" s="2" t="n"/>
@@ -7745,32 +8413,37 @@
       <c r="R292" s="2" t="n"/>
       <c r="S292" s="2" t="n"/>
       <c r="T292" s="2" t="n"/>
-      <c r="U292" s="2" t="n"/>
+      <c r="U292" s="3" t="n">
+        <v>0.004464495707073594</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>avdoda</t>
+          <t>call_me_zanavo</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>292</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.004664518147977402</v>
+        <v>0.004419017192820697</v>
+      </c>
+      <c r="U293" s="4" t="n">
+        <v>0.004419017192820697</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Anastasia</t>
+          <t>Ginger</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
         <v>293</v>
       </c>
       <c r="C294" s="3" t="n">
-        <v>0.004616677170394459</v>
+        <v>0.00437369416142633</v>
       </c>
       <c r="D294" s="2" t="n"/>
       <c r="E294" s="2" t="n"/>
@@ -7789,32 +8462,37 @@
       <c r="R294" s="2" t="n"/>
       <c r="S294" s="2" t="n"/>
       <c r="T294" s="2" t="n"/>
-      <c r="U294" s="2" t="n"/>
+      <c r="U294" s="3" t="n">
+        <v>0.00437369416142633</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>call_me_zanavo</t>
+          <t>Сэм</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>294</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.004569000878574692</v>
+        <v>0.004328527148123392</v>
+      </c>
+      <c r="U295" s="4" t="n">
+        <v>0.004328527148123392</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Сэм</t>
+          <t>ArtemDavidyan</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
         <v>295</v>
       </c>
       <c r="C296" s="3" t="n">
-        <v>0.004521489843361193</v>
+        <v>0.004283516693710604</v>
       </c>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="2" t="n"/>
@@ -7833,32 +8511,37 @@
       <c r="R296" s="2" t="n"/>
       <c r="S296" s="2" t="n"/>
       <c r="T296" s="2" t="n"/>
-      <c r="U296" s="2" t="n"/>
+      <c r="U296" s="3" t="n">
+        <v>0.004283516693710604</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>avveev</t>
+          <t>Anastasia</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>296</v>
       </c>
       <c r="C297" s="4" t="n">
-        <v>0.004474144641574622</v>
+        <v>0.004238663344649641</v>
+      </c>
+      <c r="U297" s="4" t="n">
+        <v>0.004238663344649641</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>ArtemDavidyan</t>
+          <t>Kapukatya</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
         <v>297</v>
       </c>
       <c r="C298" s="3" t="n">
-        <v>0.004426965856118258</v>
+        <v>0.004193967653164665</v>
       </c>
       <c r="D298" s="2" t="n"/>
       <c r="E298" s="2" t="n"/>
@@ -7877,32 +8560,37 @@
       <c r="R298" s="2" t="n"/>
       <c r="S298" s="2" t="n"/>
       <c r="T298" s="2" t="n"/>
-      <c r="U298" s="2" t="n"/>
+      <c r="U298" s="3" t="n">
+        <v>0.004193967653164665</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>avveev</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>298</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.004379954076085668</v>
+        <v>0.004149430177344318</v>
+      </c>
+      <c r="U299" s="4" t="n">
+        <v>0.004149430177344318</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Kapukatya</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
         <v>299</v>
       </c>
       <c r="C300" s="3" t="n">
-        <v>0.00433310989687105</v>
+        <v>0.004105051481246257</v>
       </c>
       <c r="D300" s="2" t="n"/>
       <c r="E300" s="2" t="n"/>
@@ -7921,32 +8609,37 @@
       <c r="R300" s="2" t="n"/>
       <c r="S300" s="2" t="n"/>
       <c r="T300" s="2" t="n"/>
-      <c r="U300" s="2" t="n"/>
+      <c r="U300" s="3" t="n">
+        <v>0.004105051481246257</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>Nell</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>300</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.004286433920282352</v>
+        <v>0.004060832135004334</v>
+      </c>
+      <c r="U301" s="4" t="n">
+        <v>0.004060832135004334</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Тихий Лис</t>
+          <t>Mar_u_shka</t>
         </is>
       </c>
       <c r="B302" s="2" t="n">
         <v>301</v>
       </c>
       <c r="C302" s="3" t="n">
-        <v>0.004239926754657268</v>
+        <v>0.004016772714938464</v>
       </c>
       <c r="D302" s="2" t="n"/>
       <c r="E302" s="2" t="n"/>
@@ -7965,32 +8658,37 @@
       <c r="R302" s="2" t="n"/>
       <c r="S302" s="2" t="n"/>
       <c r="T302" s="2" t="n"/>
-      <c r="U302" s="2" t="n"/>
+      <c r="U302" s="3" t="n">
+        <v>0.004016772714938464</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Тихий Лис</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>302</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.004193589014982168</v>
+        <v>0.003972873803667317</v>
+      </c>
+      <c r="U303" s="4" t="n">
+        <v>0.003972873803667317</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Nell</t>
+          <t>repe_kate</t>
         </is>
       </c>
       <c r="B304" s="2" t="n">
         <v>303</v>
       </c>
       <c r="C304" s="3" t="n">
-        <v>0.004147421323014103</v>
+        <v>0.003929135990223887</v>
       </c>
       <c r="D304" s="2" t="n"/>
       <c r="E304" s="2" t="n"/>
@@ -8009,32 +8707,37 @@
       <c r="R304" s="2" t="n"/>
       <c r="S304" s="2" t="n"/>
       <c r="T304" s="2" t="n"/>
-      <c r="U304" s="2" t="n"/>
+      <c r="U304" s="3" t="n">
+        <v>0.003929135990223887</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Nemo</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B305" t="n">
         <v>304</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.004101424307405965</v>
+        <v>0.003885559870174073</v>
+      </c>
+      <c r="U305" s="4" t="n">
+        <v>0.003885559870174073</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>Nikoshka</t>
         </is>
       </c>
       <c r="B306" s="2" t="n">
         <v>305</v>
       </c>
       <c r="C306" s="3" t="n">
-        <v>0.004055598603834903</v>
+        <v>0.003842146045738329</v>
       </c>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="2" t="n"/>
@@ -8053,7 +8756,9 @@
       <c r="R306" s="2" t="n"/>
       <c r="S306" s="2" t="n"/>
       <c r="T306" s="2" t="n"/>
-      <c r="U306" s="2" t="n"/>
+      <c r="U306" s="3" t="n">
+        <v>0.003842146045738329</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -8065,20 +8770,23 @@
         <v>306</v>
       </c>
       <c r="C307" s="4" t="n">
-        <v>0.004009944855134108</v>
+        <v>0.003798895125916523</v>
+      </c>
+      <c r="U307" s="4" t="n">
+        <v>0.003798895125916523</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Nikoshka</t>
+          <t>Тома</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
         <v>307</v>
       </c>
       <c r="C308" s="3" t="n">
-        <v>0.003964463711428108</v>
+        <v>0.003755807726616102</v>
       </c>
       <c r="D308" s="2" t="n"/>
       <c r="E308" s="2" t="n"/>
@@ -8097,32 +8805,37 @@
       <c r="R308" s="2" t="n"/>
       <c r="S308" s="2" t="n"/>
       <c r="T308" s="2" t="n"/>
-      <c r="U308" s="2" t="n"/>
+      <c r="U308" s="3" t="n">
+        <v>0.003755807726616102</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Blitz</t>
+          <t>Nemo</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>308</v>
       </c>
       <c r="C309" s="4" t="n">
-        <v>0.003919155830271646</v>
+        <v>0.003712884470783665</v>
+      </c>
+      <c r="U309" s="4" t="n">
+        <v>0.003712884470783665</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Nastya123</t>
+          <t>Blitz</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
         <v>309</v>
       </c>
       <c r="C310" s="3" t="n">
-        <v>0.003874021876792305</v>
+        <v>0.003670125988540078</v>
       </c>
       <c r="D310" s="2" t="n"/>
       <c r="E310" s="2" t="n"/>
@@ -8141,32 +8854,37 @@
       <c r="R310" s="2" t="n"/>
       <c r="S310" s="2" t="n"/>
       <c r="T310" s="2" t="n"/>
-      <c r="U310" s="2" t="n"/>
+      <c r="U310" s="3" t="n">
+        <v>0.003670125988540078</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Тома</t>
+          <t>Nastya123</t>
         </is>
       </c>
       <c r="B311" t="n">
         <v>310</v>
       </c>
       <c r="C311" s="4" t="n">
-        <v>0.003829062523836988</v>
+        <v>0.003627532917319251</v>
+      </c>
+      <c r="U311" s="4" t="n">
+        <v>0.003627532917319251</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
         <v>311</v>
       </c>
       <c r="C312" s="3" t="n">
-        <v>0.0037842784521224</v>
+        <v>0.003585105902010695</v>
       </c>
       <c r="D312" s="2" t="n"/>
       <c r="E312" s="2" t="n"/>
@@ -8185,32 +8903,37 @@
       <c r="R312" s="2" t="n"/>
       <c r="S312" s="2" t="n"/>
       <c r="T312" s="2" t="n"/>
-      <c r="U312" s="2" t="n"/>
+      <c r="U312" s="3" t="n">
+        <v>0.003585105902010695</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Tanyashl</t>
+          <t>Аня</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>312</v>
       </c>
       <c r="C313" s="4" t="n">
-        <v>0.003739670350389668</v>
+        <v>0.003542845595106001</v>
+      </c>
+      <c r="U313" s="4" t="n">
+        <v>0.003542845595106001</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>Tanyashl</t>
         </is>
       </c>
       <c r="B314" s="2" t="n">
         <v>313</v>
       </c>
       <c r="C314" s="3" t="n">
-        <v>0.003695238915563251</v>
+        <v>0.003500752656849395</v>
       </c>
       <c r="D314" s="2" t="n"/>
       <c r="E314" s="2" t="n"/>
@@ -8229,32 +8952,37 @@
       <c r="R314" s="2" t="n"/>
       <c r="S314" s="2" t="n"/>
       <c r="T314" s="2" t="n"/>
-      <c r="U314" s="2" t="n"/>
+      <c r="U314" s="3" t="n">
+        <v>0.003500752656849395</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Svetab</t>
+          <t>Darksoul</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>314</v>
       </c>
       <c r="C315" s="4" t="n">
-        <v>0.003650984852914278</v>
+        <v>0.003458827755392474</v>
+      </c>
+      <c r="U315" s="4" t="n">
+        <v>0.003458827755392474</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Darksoul</t>
+          <t>klavson</t>
         </is>
       </c>
       <c r="B316" s="2" t="n">
         <v>315</v>
       </c>
       <c r="C316" s="3" t="n">
-        <v>0.003606908876228511</v>
+        <v>0.003417071566953326</v>
       </c>
       <c r="D316" s="2" t="n"/>
       <c r="E316" s="2" t="n"/>
@@ -8273,32 +9001,37 @@
       <c r="R316" s="2" t="n"/>
       <c r="S316" s="2" t="n"/>
       <c r="T316" s="2" t="n"/>
-      <c r="U316" s="2" t="n"/>
+      <c r="U316" s="3" t="n">
+        <v>0.003417071566953326</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>klavson</t>
+          <t>CozImDrunk</t>
         </is>
       </c>
       <c r="B317" t="n">
         <v>316</v>
       </c>
       <c r="C317" s="4" t="n">
-        <v>0.003563011707979049</v>
+        <v>0.003375484775980151</v>
+      </c>
+      <c r="U317" s="4" t="n">
+        <v>0.003375484775980151</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>Аня</t>
+          <t>mflameee</t>
         </is>
       </c>
       <c r="B318" s="2" t="n">
         <v>317</v>
       </c>
       <c r="C318" s="3" t="n">
-        <v>0.003519294079504002</v>
+        <v>0.003334068075319581</v>
       </c>
       <c r="D318" s="2" t="n"/>
       <c r="E318" s="2" t="n"/>
@@ -8317,32 +9050,37 @@
       <c r="R318" s="2" t="n"/>
       <c r="S318" s="2" t="n"/>
       <c r="T318" s="2" t="n"/>
-      <c r="U318" s="2" t="n"/>
+      <c r="U318" s="3" t="n">
+        <v>0.003334068075319581</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>avomerfe</t>
+          <t>Svetab</t>
         </is>
       </c>
       <c r="B319" t="n">
         <v>318</v>
       </c>
       <c r="C319" s="4" t="n">
-        <v>0.00347575673118928</v>
+        <v>0.003292822166389844</v>
+      </c>
+      <c r="U319" s="4" t="n">
+        <v>0.003292822166389844</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CozImDrunk</t>
+          <t>avomerfe</t>
         </is>
       </c>
       <c r="B320" s="2" t="n">
         <v>319</v>
       </c>
       <c r="C320" s="3" t="n">
-        <v>0.003432400412656706</v>
+        <v>0.003251747759358985</v>
       </c>
       <c r="D320" s="2" t="n"/>
       <c r="E320" s="2" t="n"/>
@@ -8361,7 +9099,9 @@
       <c r="R320" s="2" t="n"/>
       <c r="S320" s="2" t="n"/>
       <c r="T320" s="2" t="n"/>
-      <c r="U320" s="2" t="n"/>
+      <c r="U320" s="3" t="n">
+        <v>0.003251747759358985</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -8373,7 +9113,10 @@
         <v>320</v>
       </c>
       <c r="C321" s="4" t="n">
-        <v>0.003389225882957652</v>
+        <v>0.003210845573328302</v>
+      </c>
+      <c r="U321" s="4" t="n">
+        <v>0.003210845573328302</v>
       </c>
     </row>
     <row r="322">
@@ -8386,7 +9129,7 @@
         <v>321</v>
       </c>
       <c r="C322" s="3" t="n">
-        <v>0.003346233910772406</v>
+        <v>0.003170116336521226</v>
       </c>
       <c r="D322" s="2" t="n"/>
       <c r="E322" s="2" t="n"/>
@@ -8405,32 +9148,37 @@
       <c r="R322" s="2" t="n"/>
       <c r="S322" s="2" t="n"/>
       <c r="T322" s="2" t="n"/>
-      <c r="U322" s="2" t="n"/>
+      <c r="U322" s="3" t="n">
+        <v>0.003170116336521226</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ollyapgk</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="B323" t="n">
         <v>322</v>
       </c>
       <c r="C323" s="4" t="n">
-        <v>0.003303425274615485</v>
+        <v>0.003129560786477828</v>
+      </c>
+      <c r="U323" s="4" t="n">
+        <v>0.003129560786477828</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>Tim19</t>
+          <t>ollyapgk</t>
         </is>
       </c>
       <c r="B324" s="2" t="n">
         <v>323</v>
       </c>
       <c r="C324" s="3" t="n">
-        <v>0.003260800763047147</v>
+        <v>0.003089179670255192</v>
       </c>
       <c r="D324" s="2" t="n"/>
       <c r="E324" s="2" t="n"/>
@@ -8449,19 +9197,24 @@
       <c r="R324" s="2" t="n"/>
       <c r="S324" s="2" t="n"/>
       <c r="T324" s="2" t="n"/>
-      <c r="U324" s="2" t="n"/>
+      <c r="U324" s="3" t="n">
+        <v>0.003089179670255192</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Tim19</t>
         </is>
       </c>
       <c r="B325" t="n">
         <v>324</v>
       </c>
       <c r="C325" s="4" t="n">
-        <v>0.003218361174891299</v>
+        <v>0.003048973744633862</v>
+      </c>
+      <c r="U325" s="4" t="n">
+        <v>0.003048973744633862</v>
       </c>
     </row>
     <row r="326">
@@ -8474,7 +9227,7 @@
         <v>325</v>
       </c>
       <c r="C326" s="3" t="n">
-        <v>0.003176107319460112</v>
+        <v>0.003008943776330632</v>
       </c>
       <c r="D326" s="2" t="n"/>
       <c r="E326" s="2" t="n"/>
@@ -8493,32 +9246,37 @@
       <c r="R326" s="2" t="n"/>
       <c r="S326" s="2" t="n"/>
       <c r="T326" s="2" t="n"/>
-      <c r="U326" s="2" t="n"/>
+      <c r="U326" s="3" t="n">
+        <v>0.003008943776330632</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>okiyumi</t>
+          <t>FizMatXimik</t>
         </is>
       </c>
       <c r="B327" t="n">
         <v>326</v>
       </c>
       <c r="C327" s="4" t="n">
-        <v>0.003134040016785549</v>
+        <v>0.002969090542217889</v>
+      </c>
+      <c r="U327" s="4" t="n">
+        <v>0.002969090542217889</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>stil9ger</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B328" s="2" t="n">
         <v>327</v>
       </c>
       <c r="C328" s="3" t="n">
-        <v>0.00309216009785814</v>
+        <v>0.002929414829549816</v>
       </c>
       <c r="D328" s="2" t="n"/>
       <c r="E328" s="2" t="n"/>
@@ -8537,32 +9295,37 @@
       <c r="R328" s="2" t="n"/>
       <c r="S328" s="2" t="n"/>
       <c r="T328" s="2" t="n"/>
-      <c r="U328" s="2" t="n"/>
+      <c r="U328" s="3" t="n">
+        <v>0.002929414829549816</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>Алина П.</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>328</v>
       </c>
       <c r="C329" s="4" t="n">
-        <v>0.003050468404873246</v>
+        <v>0.002889917436195706</v>
+      </c>
+      <c r="U329" s="4" t="n">
+        <v>0.002889917436195706</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Алина П.</t>
+          <t>Руслан Ж.</t>
         </is>
       </c>
       <c r="B330" s="2" t="n">
         <v>329</v>
       </c>
       <c r="C330" s="3" t="n">
-        <v>0.003008965791485157</v>
+        <v>0.002850599170880675</v>
       </c>
       <c r="D330" s="2" t="n"/>
       <c r="E330" s="2" t="n"/>
@@ -8581,19 +9344,24 @@
       <c r="R330" s="2" t="n"/>
       <c r="S330" s="2" t="n"/>
       <c r="T330" s="2" t="n"/>
-      <c r="U330" s="2" t="n"/>
+      <c r="U330" s="3" t="n">
+        <v>0.002850599170880675</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Руслан Ж.</t>
+          <t>Luter</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>330</v>
       </c>
       <c r="C331" s="4" t="n">
-        <v>0.002967653123069327</v>
+        <v>0.002811460853434099</v>
+      </c>
+      <c r="U331" s="4" t="n">
+        <v>0.002811460853434099</v>
       </c>
     </row>
     <row r="332">
@@ -8606,7 +9374,7 @@
         <v>331</v>
       </c>
       <c r="C332" s="3" t="n">
-        <v>0.002926531276993083</v>
+        <v>0.002772503315046079</v>
       </c>
       <c r="D332" s="2" t="n"/>
       <c r="E332" s="2" t="n"/>
@@ -8625,32 +9393,37 @@
       <c r="R332" s="2" t="n"/>
       <c r="S332" s="2" t="n"/>
       <c r="T332" s="2" t="n"/>
-      <c r="U332" s="2" t="n"/>
+      <c r="U332" s="3" t="n">
+        <v>0.002772503315046079</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Nika</t>
+          <t>chilly</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>332</v>
       </c>
       <c r="C333" s="4" t="n">
-        <v>0.002885601142895178</v>
+        <v>0.002733727398532274</v>
+      </c>
+      <c r="U333" s="4" t="n">
+        <v>0.002733727398532274</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>6igfi$Hf4n</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B334" s="2" t="n">
         <v>333</v>
       </c>
       <c r="C334" s="3" t="n">
-        <v>0.002844863622974541</v>
+        <v>0.002695133958607461</v>
       </c>
       <c r="D334" s="2" t="n"/>
       <c r="E334" s="2" t="n"/>
@@ -8669,32 +9442,37 @@
       <c r="R334" s="2" t="n"/>
       <c r="S334" s="2" t="n"/>
       <c r="T334" s="2" t="n"/>
-      <c r="U334" s="2" t="n"/>
+      <c r="U334" s="3" t="n">
+        <v>0.002695133958607461</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>FizMatXimik</t>
+          <t>Степан</t>
         </is>
       </c>
       <c r="B335" t="n">
         <v>334</v>
       </c>
       <c r="C335" s="4" t="n">
-        <v>0.002804319632288649</v>
+        <v>0.002656723862168195</v>
+      </c>
+      <c r="U335" s="4" t="n">
+        <v>0.002656723862168195</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>ywmoxd</t>
+          <t>okiyumi</t>
         </is>
       </c>
       <c r="B336" s="2" t="n">
         <v>335</v>
       </c>
       <c r="C336" s="3" t="n">
-        <v>0.002763970099061898</v>
+        <v>0.002618497988584956</v>
       </c>
       <c r="D336" s="2" t="n"/>
       <c r="E336" s="2" t="n"/>
@@ -8713,32 +9491,37 @@
       <c r="R336" s="2" t="n"/>
       <c r="S336" s="2" t="n"/>
       <c r="T336" s="2" t="n"/>
-      <c r="U336" s="2" t="n"/>
+      <c r="U336" s="3" t="n">
+        <v>0.002618497988584956</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>LPZ18</t>
+          <t>ywmoxd</t>
         </is>
       </c>
       <c r="B337" t="n">
         <v>336</v>
       </c>
       <c r="C337" s="4" t="n">
-        <v>0.002723815965004438</v>
+        <v>0.002580457230004205</v>
+      </c>
+      <c r="U337" s="4" t="n">
+        <v>0.002580457230004205</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>chilly</t>
+          <t>damashniy</t>
         </is>
       </c>
       <c r="B338" s="2" t="n">
         <v>337</v>
       </c>
       <c r="C338" s="3" t="n">
-        <v>0.002683858185641922</v>
+        <v>0.002542602491660768</v>
       </c>
       <c r="D338" s="2" t="n"/>
       <c r="E338" s="2" t="n"/>
@@ -8757,32 +9540,37 @@
       <c r="R338" s="2" t="n"/>
       <c r="S338" s="2" t="n"/>
       <c r="T338" s="2" t="n"/>
-      <c r="U338" s="2" t="n"/>
+      <c r="U338" s="3" t="n">
+        <v>0.002542602491660768</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Степан</t>
+          <t>pavel</t>
         </is>
       </c>
       <c r="B339" t="n">
         <v>338</v>
       </c>
       <c r="C339" s="4" t="n">
-        <v>0.002644097730656651</v>
+        <v>0.002504934692201038</v>
+      </c>
+      <c r="U339" s="4" t="n">
+        <v>0.002504934692201038</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>damashniy</t>
+          <t>6igfi$Hf4n</t>
         </is>
       </c>
       <c r="B340" s="2" t="n">
         <v>339</v>
       </c>
       <c r="C340" s="3" t="n">
-        <v>0.002604535584240636</v>
+        <v>0.002467454764017444</v>
       </c>
       <c r="D340" s="2" t="n"/>
       <c r="E340" s="2" t="n"/>
@@ -8801,32 +9589,37 @@
       <c r="R340" s="2" t="n"/>
       <c r="S340" s="2" t="n"/>
       <c r="T340" s="2" t="n"/>
-      <c r="U340" s="2" t="n"/>
+      <c r="U340" s="3" t="n">
+        <v>0.002467454764017444</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Loosars</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B341" t="n">
         <v>340</v>
       </c>
       <c r="C341" s="4" t="n">
-        <v>0.002565172745461107</v>
+        <v>0.002430163653594733</v>
+      </c>
+      <c r="U341" s="4" t="n">
+        <v>0.002430163653594733</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Luter</t>
+          <t>SPiRiT</t>
         </is>
       </c>
       <c r="B342" s="2" t="n">
         <v>341</v>
       </c>
       <c r="C342" s="3" t="n">
-        <v>0.002526010228639046</v>
+        <v>0.00239306232186857</v>
       </c>
       <c r="D342" s="2" t="n"/>
       <c r="E342" s="2" t="n"/>
@@ -8845,32 +9638,37 @@
       <c r="R342" s="2" t="n"/>
       <c r="S342" s="2" t="n"/>
       <c r="T342" s="2" t="n"/>
-      <c r="U342" s="2" t="n"/>
+      <c r="U342" s="3" t="n">
+        <v>0.00239306232186857</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>igor forehand</t>
+          <t>stil9ger</t>
         </is>
       </c>
       <c r="B343" t="n">
         <v>342</v>
       </c>
       <c r="C343" s="4" t="n">
-        <v>0.002487049063741341</v>
+        <v>0.002356151744597061</v>
+      </c>
+      <c r="U343" s="4" t="n">
+        <v>0.002356151744597061</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>pavel</t>
+          <t>Loosars</t>
         </is>
       </c>
       <c r="B344" s="2" t="n">
         <v>343</v>
       </c>
       <c r="C344" s="3" t="n">
-        <v>0.002448290296787213</v>
+        <v>0.002319432912745781</v>
       </c>
       <c r="D344" s="2" t="n"/>
       <c r="E344" s="2" t="n"/>
@@ -8889,32 +9687,37 @@
       <c r="R344" s="2" t="n"/>
       <c r="S344" s="2" t="n"/>
       <c r="T344" s="2" t="n"/>
-      <c r="U344" s="2" t="n"/>
+      <c r="U344" s="3" t="n">
+        <v>0.002319432912745781</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Nika</t>
         </is>
       </c>
       <c r="B345" t="n">
         <v>344</v>
       </c>
       <c r="C345" s="4" t="n">
-        <v>0.002409734990269561</v>
+        <v>0.002282906832886952</v>
+      </c>
+      <c r="U345" s="4" t="n">
+        <v>0.002282906832886952</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>SPiRiT</t>
+          <t>igor forehand</t>
         </is>
       </c>
       <c r="B346" s="2" t="n">
         <v>345</v>
       </c>
       <c r="C346" s="3" t="n">
-        <v>0.002371384223591968</v>
+        <v>0.002246574527613444</v>
       </c>
       <c r="D346" s="2" t="n"/>
       <c r="E346" s="2" t="n"/>
@@ -8933,32 +9736,37 @@
       <c r="R346" s="2" t="n"/>
       <c r="S346" s="2" t="n"/>
       <c r="T346" s="2" t="n"/>
-      <c r="U346" s="2" t="n"/>
+      <c r="U346" s="3" t="n">
+        <v>0.002246574527613444</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>Dreemur</t>
         </is>
       </c>
       <c r="B347" t="n">
         <v>346</v>
       </c>
       <c r="C347" s="4" t="n">
-        <v>0.002333239093522113</v>
+        <v>0.002210437035968318</v>
+      </c>
+      <c r="U347" s="4" t="n">
+        <v>0.002210437035968318</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Dreemur</t>
+          <t>lifechampagne</t>
         </is>
       </c>
       <c r="B348" s="2" t="n">
         <v>347</v>
       </c>
       <c r="C348" s="3" t="n">
-        <v>0.002295300714662377</v>
+        <v>0.002174495413890673</v>
       </c>
       <c r="D348" s="2" t="n"/>
       <c r="E348" s="2" t="n"/>
@@ -8977,32 +9785,37 @@
       <c r="R348" s="2" t="n"/>
       <c r="S348" s="2" t="n"/>
       <c r="T348" s="2" t="n"/>
-      <c r="U348" s="2" t="n"/>
+      <c r="U348" s="3" t="n">
+        <v>0.002174495413890673</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>lifechampagne</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B349" t="n">
         <v>348</v>
       </c>
       <c r="C349" s="4" t="n">
-        <v>0.002257570219938507</v>
+        <v>0.002138750734678586</v>
+      </c>
+      <c r="U349" s="4" t="n">
+        <v>0.002138750734678586</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Virt Ceo</t>
+          <t>LPZ18</t>
         </is>
       </c>
       <c r="B350" s="2" t="n">
         <v>349</v>
       </c>
       <c r="C350" s="3" t="n">
-        <v>0.002220048761107239</v>
+        <v>0.002103204089470016</v>
       </c>
       <c r="D350" s="2" t="n"/>
       <c r="E350" s="2" t="n"/>
@@ -9021,32 +9834,37 @@
       <c r="R350" s="2" t="n"/>
       <c r="S350" s="2" t="n"/>
       <c r="T350" s="2" t="n"/>
-      <c r="U350" s="2" t="n"/>
+      <c r="U350" s="3" t="n">
+        <v>0.002103204089470016</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>FireSnail636</t>
         </is>
       </c>
       <c r="B351" t="n">
         <v>350</v>
       </c>
       <c r="C351" s="4" t="n">
-        <v>0.002182737509283816</v>
+        <v>0.002067856587742562</v>
+      </c>
+      <c r="U351" s="4" t="n">
+        <v>0.002067856587742562</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>FireSnail636</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B352" s="2" t="n">
         <v>351</v>
       </c>
       <c r="C352" s="3" t="n">
-        <v>0.002145637655490447</v>
+        <v>0.002032709357833055</v>
       </c>
       <c r="D352" s="2" t="n"/>
       <c r="E352" s="2" t="n"/>
@@ -9065,7 +9883,9 @@
       <c r="R352" s="2" t="n"/>
       <c r="S352" s="2" t="n"/>
       <c r="T352" s="2" t="n"/>
-      <c r="U352" s="2" t="n"/>
+      <c r="U352" s="3" t="n">
+        <v>0.002032709357833055</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -9077,20 +9897,23 @@
         <v>352</v>
       </c>
       <c r="C353" s="4" t="n">
-        <v>0.002108750411226753</v>
+        <v>0.001997763547477977</v>
+      </c>
+      <c r="U353" s="4" t="n">
+        <v>0.001997763547477977</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>Volodnika</t>
         </is>
       </c>
       <c r="B354" s="2" t="n">
         <v>353</v>
       </c>
       <c r="C354" s="3" t="n">
-        <v>0.002072077009063379</v>
+        <v>0.001963020324375833</v>
       </c>
       <c r="D354" s="2" t="n"/>
       <c r="E354" s="2" t="n"/>
@@ -9109,32 +9932,37 @@
       <c r="R354" s="2" t="n"/>
       <c r="S354" s="2" t="n"/>
       <c r="T354" s="2" t="n"/>
-      <c r="U354" s="2" t="n"/>
+      <c r="U354" s="3" t="n">
+        <v>0.001963020324375833</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Volodnika</t>
+          <t>Virt Ceo</t>
         </is>
       </c>
       <c r="B355" t="n">
         <v>354</v>
       </c>
       <c r="C355" s="4" t="n">
-        <v>0.00203561870325997</v>
+        <v>0.001928480876772603</v>
+      </c>
+      <c r="U355" s="4" t="n">
+        <v>0.001928480876772603</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B356" s="2" t="n">
         <v>355</v>
       </c>
       <c r="C356" s="3" t="n">
-        <v>0.001999376770408828</v>
+        <v>0.001894146414071521</v>
       </c>
       <c r="D356" s="2" t="n"/>
       <c r="E356" s="2" t="n"/>
@@ -9153,32 +9981,37 @@
       <c r="R356" s="2" t="n"/>
       <c r="S356" s="2" t="n"/>
       <c r="T356" s="2" t="n"/>
-      <c r="U356" s="2" t="n"/>
+      <c r="U356" s="3" t="n">
+        <v>0.001894146414071521</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Natasha_fsb</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B357" t="n">
         <v>356</v>
       </c>
       <c r="C357" s="4" t="n">
-        <v>0.001963352510105631</v>
+        <v>0.001860018167468492</v>
+      </c>
+      <c r="U357" s="4" t="n">
+        <v>0.001860018167468492</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CICADA</t>
+          <t>kornaakov</t>
         </is>
       </c>
       <c r="B358" s="2" t="n">
         <v>357</v>
       </c>
       <c r="C358" s="3" t="n">
-        <v>0.001927547245648699</v>
+        <v>0.001826097390614556</v>
       </c>
       <c r="D358" s="2" t="n"/>
       <c r="E358" s="2" t="n"/>
@@ -9197,32 +10030,37 @@
       <c r="R358" s="2" t="n"/>
       <c r="S358" s="2" t="n"/>
       <c r="T358" s="2" t="n"/>
-      <c r="U358" s="2" t="n"/>
+      <c r="U358" s="3" t="n">
+        <v>0.001826097390614556</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>averagemorningstarenjoyer</t>
+          <t>CICADA</t>
         </is>
       </c>
       <c r="B359" t="n">
         <v>358</v>
       </c>
       <c r="C359" s="4" t="n">
-        <v>0.001891962324768384</v>
+        <v>0.00179238536030689</v>
+      </c>
+      <c r="U359" s="4" t="n">
+        <v>0.00179238536030689</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>averagemorningstarenjoyer</t>
         </is>
       </c>
       <c r="B360" s="2" t="n">
         <v>359</v>
       </c>
       <c r="C360" s="3" t="n">
-        <v>0.001856599120388282</v>
+        <v>0.001758883377209951</v>
       </c>
       <c r="D360" s="2" t="n"/>
       <c r="E360" s="2" t="n"/>
@@ -9241,32 +10079,37 @@
       <c r="R360" s="2" t="n"/>
       <c r="S360" s="2" t="n"/>
       <c r="T360" s="2" t="n"/>
-      <c r="U360" s="2" t="n"/>
+      <c r="U360" s="3" t="n">
+        <v>0.001758883377209951</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>Natasha_fsb</t>
         </is>
       </c>
       <c r="B361" t="n">
         <v>360</v>
       </c>
       <c r="C361" s="4" t="n">
-        <v>0.001821459031420055</v>
+        <v>0.001725592766608473</v>
+      </c>
+      <c r="U361" s="4" t="n">
+        <v>0.001725592766608473</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>ira_karpova</t>
+          <t>t1m</t>
         </is>
       </c>
       <c r="B362" s="2" t="n">
         <v>361</v>
       </c>
       <c r="C362" s="3" t="n">
-        <v>0.001786543483593825</v>
+        <v>0.00169251487919415</v>
       </c>
       <c r="D362" s="2" t="n"/>
       <c r="E362" s="2" t="n"/>
@@ -9285,32 +10128,37 @@
       <c r="R362" s="2" t="n"/>
       <c r="S362" s="2" t="n"/>
       <c r="T362" s="2" t="n"/>
-      <c r="U362" s="2" t="n"/>
+      <c r="U362" s="3" t="n">
+        <v>0.00169251487919415</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>kornaakov</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B363" t="n">
         <v>362</v>
       </c>
       <c r="C363" s="4" t="n">
-        <v>0.00175185393032619</v>
+        <v>0.00165965109188797</v>
+      </c>
+      <c r="U363" s="4" t="n">
+        <v>0.00165965109188797</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>t1m</t>
+          <t>ira_karpova</t>
         </is>
       </c>
       <c r="B364" s="2" t="n">
         <v>363</v>
       </c>
       <c r="C364" s="3" t="n">
-        <v>0.001717391853628083</v>
+        <v>0.001627002808700289</v>
       </c>
       <c r="D364" s="2" t="n"/>
       <c r="E364" s="2" t="n"/>
@@ -9329,32 +10177,37 @@
       <c r="R364" s="2" t="n"/>
       <c r="S364" s="2" t="n"/>
       <c r="T364" s="2" t="n"/>
-      <c r="U364" s="2" t="n"/>
+      <c r="U364" s="3" t="n">
+        <v>0.001627002808700289</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Марат</t>
+          <t>Kety</t>
         </is>
       </c>
       <c r="B365" t="n">
         <v>364</v>
       </c>
       <c r="C365" s="4" t="n">
-        <v>0.001683158765054875</v>
+        <v>0.001594571461630935</v>
+      </c>
+      <c r="U365" s="4" t="n">
+        <v>0.001594571461630935</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>nevsskii</t>
+          <t>Марат</t>
         </is>
       </c>
       <c r="B366" s="2" t="n">
         <v>365</v>
       </c>
       <c r="C366" s="3" t="n">
-        <v>0.001649156206701268</v>
+        <v>0.001562358511611728</v>
       </c>
       <c r="D366" s="2" t="n"/>
       <c r="E366" s="2" t="n"/>
@@ -9373,32 +10226,37 @@
       <c r="R366" s="2" t="n"/>
       <c r="S366" s="2" t="n"/>
       <c r="T366" s="2" t="n"/>
-      <c r="U366" s="2" t="n"/>
+      <c r="U366" s="3" t="n">
+        <v>0.001562358511611728</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>msbxmx</t>
         </is>
       </c>
       <c r="B367" t="n">
         <v>366</v>
       </c>
       <c r="C367" s="4" t="n">
-        <v>0.001615385752243729</v>
+        <v>0.001530365449494059</v>
+      </c>
+      <c r="U367" s="4" t="n">
+        <v>0.001530365449494059</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>Kety</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B368" s="2" t="n">
         <v>367</v>
       </c>
       <c r="C368" s="3" t="n">
-        <v>0.001581849008033435</v>
+        <v>0.001498593797084307</v>
       </c>
       <c r="D368" s="2" t="n"/>
       <c r="E368" s="2" t="n"/>
@@ -9417,32 +10275,37 @@
       <c r="R368" s="2" t="n"/>
       <c r="S368" s="2" t="n"/>
       <c r="T368" s="2" t="n"/>
-      <c r="U368" s="2" t="n"/>
+      <c r="U368" s="3" t="n">
+        <v>0.001498593797084307</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Павлуша</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B369" t="n">
         <v>368</v>
       </c>
       <c r="C369" s="4" t="n">
-        <v>0.001548547614242918</v>
+        <v>0.001467045108230133</v>
+      </c>
+      <c r="U369" s="4" t="n">
+        <v>0.001467045108230133</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>гофер</t>
+          <t>Павлуша</t>
         </is>
       </c>
       <c r="B370" s="2" t="n">
         <v>369</v>
       </c>
       <c r="C370" s="3" t="n">
-        <v>0.001515483246069844</v>
+        <v>0.001435720969960905</v>
       </c>
       <c r="D370" s="2" t="n"/>
       <c r="E370" s="2" t="n"/>
@@ -9461,32 +10324,37 @@
       <c r="R370" s="2" t="n"/>
       <c r="S370" s="2" t="n"/>
       <c r="T370" s="2" t="n"/>
-      <c r="U370" s="2" t="n"/>
+      <c r="U370" s="3" t="n">
+        <v>0.001435720969960905</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="B371" t="n">
         <v>370</v>
       </c>
       <c r="C371" s="4" t="n">
-        <v>0.001482657615001653</v>
+        <v>0.001404623003685776</v>
+      </c>
+      <c r="U371" s="4" t="n">
+        <v>0.001404623003685776</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>nevsskii</t>
         </is>
       </c>
       <c r="B372" s="2" t="n">
         <v>371</v>
       </c>
       <c r="C372" s="3" t="n">
-        <v>0.001450072470145049</v>
+        <v>0.001373752866453204</v>
       </c>
       <c r="D372" s="2" t="n"/>
       <c r="E372" s="2" t="n"/>
@@ -9505,32 +10373,37 @@
       <c r="R372" s="2" t="n"/>
       <c r="S372" s="2" t="n"/>
       <c r="T372" s="2" t="n"/>
-      <c r="U372" s="2" t="n"/>
+      <c r="U372" s="3" t="n">
+        <v>0.001373752866453204</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ksellym</t>
+          <t>гофер</t>
         </is>
       </c>
       <c r="B373" t="n">
         <v>372</v>
       </c>
       <c r="C373" s="4" t="n">
-        <v>0.001417729599624718</v>
+        <v>0.001343112252276049</v>
+      </c>
+      <c r="U373" s="4" t="n">
+        <v>0.001343112252276049</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>ksellym</t>
         </is>
       </c>
       <c r="B374" s="2" t="n">
         <v>373</v>
       </c>
       <c r="C374" s="3" t="n">
-        <v>0.001385630832055937</v>
+        <v>0.001312702893526678</v>
       </c>
       <c r="D374" s="2" t="n"/>
       <c r="E374" s="2" t="n"/>
@@ -9549,19 +10422,24 @@
       <c r="R374" s="2" t="n"/>
       <c r="S374" s="2" t="n"/>
       <c r="T374" s="2" t="n"/>
-      <c r="U374" s="2" t="n"/>
+      <c r="U374" s="3" t="n">
+        <v>0.001312702893526678</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>msbxmx</t>
+          <t>SuD</t>
         </is>
       </c>
       <c r="B375" t="n">
         <v>374</v>
       </c>
       <c r="C375" s="4" t="n">
-        <v>0.001353778038096205</v>
+        <v>0.001282526562406931</v>
+      </c>
+      <c r="U375" s="4" t="n">
+        <v>0.001282526562406931</v>
       </c>
     </row>
     <row r="376">
@@ -9574,7 +10452,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="3" t="n">
-        <v>0.001322173132081403</v>
+        <v>0.001252585072498172</v>
       </c>
       <c r="D376" s="2" t="n"/>
       <c r="E376" s="2" t="n"/>
@@ -9593,32 +10471,37 @@
       <c r="R376" s="2" t="n"/>
       <c r="S376" s="2" t="n"/>
       <c r="T376" s="2" t="n"/>
-      <c r="U376" s="2" t="n"/>
+      <c r="U376" s="3" t="n">
+        <v>0.001252585072498172</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>SuD</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B377" t="n">
         <v>376</v>
       </c>
       <c r="C377" s="4" t="n">
-        <v>0.001290818073752528</v>
+        <v>0.001222880280397132</v>
+      </c>
+      <c r="U377" s="4" t="n">
+        <v>0.001222880280397132</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>arteminil</t>
+          <t>Ksu666</t>
         </is>
       </c>
       <c r="B378" s="2" t="n">
         <v>377</v>
       </c>
       <c r="C378" s="3" t="n">
-        <v>0.001259714870079524</v>
+        <v>0.00119341408744376</v>
       </c>
       <c r="D378" s="2" t="n"/>
       <c r="E378" s="2" t="n"/>
@@ -9637,19 +10520,24 @@
       <c r="R378" s="2" t="n"/>
       <c r="S378" s="2" t="n"/>
       <c r="T378" s="2" t="n"/>
-      <c r="U378" s="2" t="n"/>
+      <c r="U378" s="3" t="n">
+        <v>0.00119341408744376</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Ksu666</t>
+          <t>cloudromeo</t>
         </is>
       </c>
       <c r="B379" t="n">
         <v>378</v>
       </c>
       <c r="C379" s="4" t="n">
-        <v>0.001228865577189364</v>
+        <v>0.001164188441547818</v>
+      </c>
+      <c r="U379" s="4" t="n">
+        <v>0.001164188441547818</v>
       </c>
     </row>
     <row r="380">
@@ -9662,7 +10550,7 @@
         <v>379</v>
       </c>
       <c r="C380" s="3" t="n">
-        <v>0.00119827230240616</v>
+        <v>0.001135205339121625</v>
       </c>
       <c r="D380" s="2" t="n"/>
       <c r="E380" s="2" t="n"/>
@@ -9681,32 +10569,37 @@
       <c r="R380" s="2" t="n"/>
       <c r="S380" s="2" t="n"/>
       <c r="T380" s="2" t="n"/>
-      <c r="U380" s="2" t="n"/>
+      <c r="U380" s="3" t="n">
+        <v>0.001135205339121625</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Sendre</t>
+          <t>Палёвка</t>
         </is>
       </c>
       <c r="B381" t="n">
         <v>380</v>
       </c>
       <c r="C381" s="4" t="n">
-        <v>0.001167937206411821</v>
+        <v>0.001106466827126988</v>
+      </c>
+      <c r="U381" s="4" t="n">
+        <v>0.001106466827126988</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>cloudromeo</t>
+          <t>Sendre</t>
         </is>
       </c>
       <c r="B382" s="2" t="n">
         <v>381</v>
       </c>
       <c r="C382" s="3" t="n">
-        <v>0.001137862505536571</v>
+        <v>0.001077975005245173</v>
       </c>
       <c r="D382" s="2" t="n"/>
       <c r="E382" s="2" t="n"/>
@@ -9725,7 +10618,9 @@
       <c r="R382" s="2" t="n"/>
       <c r="S382" s="2" t="n"/>
       <c r="T382" s="2" t="n"/>
-      <c r="U382" s="2" t="n"/>
+      <c r="U382" s="3" t="n">
+        <v>0.001077975005245173</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -9737,20 +10632,23 @@
         <v>382</v>
       </c>
       <c r="C383" s="4" t="n">
-        <v>0.001108050474189531</v>
+        <v>0.001049732028179556</v>
+      </c>
+      <c r="U383" s="4" t="n">
+        <v>0.001049732028179556</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>frlvmaria</t>
+          <t>arteminil</t>
         </is>
       </c>
       <c r="B384" s="2" t="n">
         <v>383</v>
       </c>
       <c r="C384" s="3" t="n">
-        <v>0.001078503447440591</v>
+        <v>0.001021740108101613</v>
       </c>
       <c r="D384" s="2" t="n"/>
       <c r="E384" s="2" t="n"/>
@@ -9769,32 +10667,37 @@
       <c r="R384" s="2" t="n"/>
       <c r="S384" s="2" t="n"/>
       <c r="T384" s="2" t="n"/>
-      <c r="U384" s="2" t="n"/>
+      <c r="U384" s="3" t="n">
+        <v>0.001021740108101613</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Палёвка</t>
+          <t>Гонзалес</t>
         </is>
       </c>
       <c r="B385" t="n">
         <v>384</v>
       </c>
       <c r="C385" s="4" t="n">
-        <v>0.001049223823765879</v>
+        <v>0.000994001517251885</v>
+      </c>
+      <c r="U385" s="4" t="n">
+        <v>0.000994001517251885</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Гонзалес</t>
+          <t>frlvmaria</t>
         </is>
       </c>
       <c r="B386" s="2" t="n">
         <v>385</v>
       </c>
       <c r="C386" s="3" t="n">
-        <v>0.001020214067970416</v>
+        <v>0.0009665185907088152</v>
       </c>
       <c r="D386" s="2" t="n"/>
       <c r="E386" s="2" t="n"/>
@@ -9813,7 +10716,9 @@
       <c r="R386" s="2" t="n"/>
       <c r="S386" s="2" t="n"/>
       <c r="T386" s="2" t="n"/>
-      <c r="U386" s="2" t="n"/>
+      <c r="U386" s="3" t="n">
+        <v>0.0009665185907088152</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9825,20 +10730,23 @@
         <v>386</v>
       </c>
       <c r="C387" s="4" t="n">
-        <v>0.000991476714302935</v>
+        <v>0.0009392937293396224</v>
+      </c>
+      <c r="U387" s="4" t="n">
+        <v>0.0009392937293396224</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>lanz8</t>
+          <t>etovadikk</t>
         </is>
       </c>
       <c r="B388" s="2" t="n">
         <v>387</v>
       </c>
       <c r="C388" s="3" t="n">
-        <v>0.000963014369779409</v>
+        <v>0.0009123294029489138</v>
       </c>
       <c r="D388" s="2" t="n"/>
       <c r="E388" s="2" t="n"/>
@@ -9857,7 +10765,9 @@
       <c r="R388" s="2" t="n"/>
       <c r="S388" s="2" t="n"/>
       <c r="T388" s="2" t="n"/>
-      <c r="U388" s="2" t="n"/>
+      <c r="U388" s="3" t="n">
+        <v>0.0009123294029489138</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9869,20 +10779,23 @@
         <v>388</v>
       </c>
       <c r="C389" s="4" t="n">
-        <v>0.0009348297177336398</v>
+        <v>0.0008856281536423956</v>
+      </c>
+      <c r="U389" s="4" t="n">
+        <v>0.0008856281536423956</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>Malinskaya</t>
+          <t>DmitriiM0</t>
         </is>
       </c>
       <c r="B390" s="2" t="n">
         <v>389</v>
       </c>
       <c r="C390" s="3" t="n">
-        <v>0.0009069255216152311</v>
+        <v>0.0008591925994249558</v>
       </c>
       <c r="D390" s="2" t="n"/>
       <c r="E390" s="2" t="n"/>
@@ -9901,32 +10814,37 @@
       <c r="R390" s="2" t="n"/>
       <c r="S390" s="2" t="n"/>
       <c r="T390" s="2" t="n"/>
-      <c r="U390" s="2" t="n"/>
+      <c r="U390" s="3" t="n">
+        <v>0.0008591925994249558</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>etovadikk</t>
+          <t>lanz8</t>
         </is>
       </c>
       <c r="B391" t="n">
         <v>390</v>
       </c>
       <c r="C391" s="4" t="n">
-        <v>0.0008793046290575784</v>
+        <v>0.000833025438054548</v>
+      </c>
+      <c r="U391" s="4" t="n">
+        <v>0.000833025438054548</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>Malinskaya</t>
         </is>
       </c>
       <c r="B392" s="2" t="n">
         <v>391</v>
       </c>
       <c r="C392" s="3" t="n">
-        <v>0.0008519699762410528</v>
+        <v>0.0008071294511757342</v>
       </c>
       <c r="D392" s="2" t="n"/>
       <c r="E392" s="2" t="n"/>
@@ -9945,19 +10863,24 @@
       <c r="R392" s="2" t="n"/>
       <c r="S392" s="2" t="n"/>
       <c r="T392" s="2" t="n"/>
-      <c r="U392" s="2" t="n"/>
+      <c r="U392" s="3" t="n">
+        <v>0.0008071294511757342</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>DmitriiM0</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B393" t="n">
         <v>392</v>
       </c>
       <c r="C393" s="4" t="n">
-        <v>0.0008249245925795195</v>
+        <v>0.000781507508759545</v>
+      </c>
+      <c r="U393" s="4" t="n">
+        <v>0.000781507508759545</v>
       </c>
     </row>
     <row r="394">
@@ -9970,7 +10893,7 @@
         <v>393</v>
       </c>
       <c r="C394" s="3" t="n">
-        <v>0.000798171605761662</v>
+        <v>0.0007561625738794693</v>
       </c>
       <c r="D394" s="2" t="n"/>
       <c r="E394" s="2" t="n"/>
@@ -9989,32 +10912,37 @@
       <c r="R394" s="2" t="n"/>
       <c r="S394" s="2" t="n"/>
       <c r="T394" s="2" t="n"/>
-      <c r="U394" s="2" t="n"/>
+      <c r="U394" s="3" t="n">
+        <v>0.0007561625738794693</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>M1kayt</t>
         </is>
       </c>
       <c r="B395" t="n">
         <v>394</v>
       </c>
       <c r="C395" s="4" t="n">
-        <v>0.0007717142471824106</v>
+        <v>0.0007310977078570205</v>
+      </c>
+      <c r="U395" s="4" t="n">
+        <v>0.0007310977078570205</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>M1kayt</t>
+          <t>ns_sh</t>
         </is>
       </c>
       <c r="B396" s="2" t="n">
         <v>395</v>
       </c>
       <c r="C396" s="3" t="n">
-        <v>0.000745555857804179</v>
+        <v>0.0007063160758144854</v>
       </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="2" t="n"/>
@@ -10033,32 +10961,37 @@
       <c r="R396" s="2" t="n"/>
       <c r="S396" s="2" t="n"/>
       <c r="T396" s="2" t="n"/>
-      <c r="U396" s="2" t="n"/>
+      <c r="U396" s="3" t="n">
+        <v>0.0007063160758144854</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>като</t>
+          <t>Khizir.V</t>
         </is>
       </c>
       <c r="B397" t="n">
         <v>396</v>
       </c>
       <c r="C397" s="4" t="n">
-        <v>0.0007196998944926457</v>
+        <v>0.0006818209526772433</v>
+      </c>
+      <c r="U397" s="4" t="n">
+        <v>0.0006818209526772433</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>kirp4712</t>
+          <t>moz1lo_jr</t>
         </is>
       </c>
       <c r="B398" s="2" t="n">
         <v>397</v>
       </c>
       <c r="C398" s="3" t="n">
-        <v>0.0006941499368776605</v>
+        <v>0.000657615729673573</v>
       </c>
       <c r="D398" s="2" t="n"/>
       <c r="E398" s="2" t="n"/>
@@ -10077,19 +11010,24 @@
       <c r="R398" s="2" t="n"/>
       <c r="S398" s="2" t="n"/>
       <c r="T398" s="2" t="n"/>
-      <c r="U398" s="2" t="n"/>
+      <c r="U398" s="3" t="n">
+        <v>0.000657615729673573</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Sokrat_Ab</t>
+          <t>poysty</t>
         </is>
       </c>
       <c r="B399" t="n">
         <v>398</v>
       </c>
       <c r="C399" s="4" t="n">
-        <v>0.0006689096947965947</v>
+        <v>0.0006337039213862477</v>
+      </c>
+      <c r="U399" s="4" t="n">
+        <v>0.0006337039213862477</v>
       </c>
     </row>
     <row r="400">
@@ -10102,7 +11040,7 @@
         <v>399</v>
       </c>
       <c r="C400" s="3" t="n">
-        <v>0.0006439830163853008</v>
+        <v>0.0006100891734176534</v>
       </c>
       <c r="D400" s="2" t="n"/>
       <c r="E400" s="2" t="n"/>
@@ -10121,32 +11059,37 @@
       <c r="R400" s="2" t="n"/>
       <c r="S400" s="2" t="n"/>
       <c r="T400" s="2" t="n"/>
-      <c r="U400" s="2" t="n"/>
+      <c r="U400" s="3" t="n">
+        <v>0.0006100891734176534</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>kosty_mlg</t>
+          <t>Nikolay</t>
         </is>
       </c>
       <c r="B401" t="n">
         <v>400</v>
       </c>
       <c r="C401" s="4" t="n">
-        <v>0.0006193738968909773</v>
+        <v>0.0005867752707388206</v>
+      </c>
+      <c r="U401" s="4" t="n">
+        <v>0.0005867752707388206</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>kavun_prime</t>
+          <t>glava9</t>
         </is>
       </c>
       <c r="B402" s="2" t="n">
         <v>401</v>
       </c>
       <c r="C402" s="3" t="n">
-        <v>0.0005950864882919388</v>
+        <v>0.0005637661468028893</v>
       </c>
       <c r="D402" s="2" t="n"/>
       <c r="E402" s="2" t="n"/>
@@ -10165,32 +11108,37 @@
       <c r="R402" s="2" t="n"/>
       <c r="S402" s="2" t="n"/>
       <c r="T402" s="2" t="n"/>
-      <c r="U402" s="2" t="n"/>
+      <c r="U402" s="3" t="n">
+        <v>0.0005637661468028893</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>inteuis</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="B403" t="n">
         <v>402</v>
       </c>
       <c r="C403" s="4" t="n">
-        <v>0.0005711251098218365</v>
+        <v>0.0005410658935154241</v>
+      </c>
+      <c r="U403" s="4" t="n">
+        <v>0.0005410658935154241</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>ns_sh</t>
+          <t>inteuis</t>
         </is>
       </c>
       <c r="B404" s="2" t="n">
         <v>403</v>
       </c>
       <c r="C404" s="3" t="n">
-        <v>0.0005474942595107085</v>
+        <v>0.0005186787721680398</v>
       </c>
       <c r="D404" s="2" t="n"/>
       <c r="E404" s="2" t="n"/>
@@ -10209,33 +11157,30 @@
       <c r="R404" s="2" t="n"/>
       <c r="S404" s="2" t="n"/>
       <c r="T404" s="2" t="n"/>
-      <c r="U404" s="2" t="n"/>
+      <c r="U404" s="3" t="n">
+        <v>0.0005186787721680398</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Riteral</t>
+          <t>Марк</t>
         </is>
       </c>
       <c r="B405" t="n">
         <v>404</v>
       </c>
-      <c r="C405" s="4" t="n">
-        <v>0.0005241986268727709</v>
-      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>nik_zverev</t>
+          <t>veronesss</t>
         </is>
       </c>
       <c r="B406" s="2" t="n">
         <v>405</v>
       </c>
-      <c r="C406" s="3" t="n">
-        <v>0.0005012431068917635</v>
-      </c>
+      <c r="C406" s="2" t="n"/>
       <c r="D406" s="2" t="n"/>
       <c r="E406" s="2" t="n"/>
       <c r="F406" s="2" t="n"/>
@@ -10258,7 +11203,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>poysty</t>
+          <t>Акоп</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -10268,7 +11213,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>nik_zverev</t>
         </is>
       </c>
       <c r="B408" s="2" t="n">
@@ -10297,7 +11242,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Khizir.V</t>
+          <t>skr_anton</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -10307,7 +11252,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Me1man77</t>
+          <t>kosty_mlg</t>
         </is>
       </c>
       <c r="B410" s="2" t="n">
@@ -10336,7 +11281,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Broski</t>
+          <t>Me1man77</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -10346,7 +11291,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Акоп</t>
+          <t>denisyoung04</t>
         </is>
       </c>
       <c r="B412" s="2" t="n">
@@ -10375,7 +11320,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>denisyoung04</t>
+          <t>Chumba656</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -10385,7 +11330,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>Zubrilliant</t>
+          <t>kirp4712</t>
         </is>
       </c>
       <c r="B414" s="2" t="n">
@@ -10414,7 +11359,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>skr_anton</t>
+          <t>Broski</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -10424,7 +11369,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>svyatophor</t>
+          <t>Zubrilliant</t>
         </is>
       </c>
       <c r="B416" s="2" t="n">
@@ -10453,7 +11398,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>veronesss</t>
+          <t>Sokrat_Ab</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -10492,7 +11437,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>JhonyCash</t>
+          <t>roman_1_2_3</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10502,7 +11447,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>roman_1_2_3</t>
+          <t>Pedal9l</t>
         </is>
       </c>
       <c r="B420" s="2" t="n">
@@ -10541,7 +11486,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>Марк</t>
+          <t>JhonyCash</t>
         </is>
       </c>
       <c r="B422" s="2" t="n">
@@ -10570,7 +11515,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>WHATSWRONGib</t>
+          <t>Riteral</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -10580,7 +11525,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>glava9</t>
+          <t>WHATSWRONGib</t>
         </is>
       </c>
       <c r="B424" s="2" t="n">
@@ -10609,7 +11554,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Chumba656</t>
+          <t>Donny</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -10619,7 +11564,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>Михаил Ю</t>
+          <t>@lidiasol07</t>
         </is>
       </c>
       <c r="B426" s="2" t="n">
@@ -10648,7 +11593,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Asakura_Russell</t>
+          <t>set</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -10658,7 +11603,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Donny</t>
+          <t>deps</t>
         </is>
       </c>
       <c r="B428" s="2" t="n">
@@ -10687,7 +11632,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>като</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -10697,7 +11642,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Лудоман</t>
+          <t>Михаил Ю</t>
         </is>
       </c>
       <c r="B430" s="2" t="n">
@@ -10726,7 +11671,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>@lidiasol07</t>
+          <t>Aleksa</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -10736,7 +11681,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>Aleksa</t>
+          <t>Cucumberrr</t>
         </is>
       </c>
       <c r="B432" s="2" t="n">
@@ -10765,7 +11710,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>moz1lo_jr</t>
+          <t>kavun_prime</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -10775,7 +11720,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>Cucumberrr</t>
+          <t>Лудоман</t>
         </is>
       </c>
       <c r="B434" s="2" t="n">
@@ -10804,7 +11749,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Pedal9l</t>
+          <t>ЧЕРЕМША</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -10814,7 +11759,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>ЧЕРЕМША</t>
+          <t>dnaskila</t>
         </is>
       </c>
       <c r="B436" s="2" t="n">
@@ -10843,7 +11788,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>deps</t>
+          <t>svyatophor</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -10853,7 +11798,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>dnaskila</t>
+          <t>Asakura_Russell</t>
         </is>
       </c>
       <c r="B438" s="2" t="n">

--- a/data/playoff_odds.xlsx
+++ b/data/playoff_odds.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U438"/>
+  <dimension ref="A1:U437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -601,29 +601,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.71</v>
+        <v>0.006</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.203</v>
+        <v>0.04</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.053</v>
+        <v>0.16</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.022</v>
+        <v>0.212</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.008</v>
+        <v>0.286</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.001</v>
-      </c>
+        <v>0.296</v>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -647,93 +643,57 @@
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.024</v>
-      </c>
       <c r="J3" s="4" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Yars</t>
+          <t>Антуан Гризманн</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8457500000000001</v>
+        <v>0.84235</v>
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="3" t="n">
-        <v>0.00595</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.01445</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.06034999999999999</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.10965</v>
-      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
       <c r="M4" s="3" t="n">
-        <v>0.1241</v>
+        <v>0.00085</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.119</v>
+        <v>0.01105</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.12835</v>
+        <v>0.0731</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.10115</v>
+        <v>0.3485</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.07479999999999999</v>
+        <v>0.1785</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0459</v>
+        <v>0.1054</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.02295</v>
+        <v>0.0697</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.0119</v>
+        <v>0.03655</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="5">
@@ -746,112 +706,84 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.8245</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.00085</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.00595</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.0102</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0.03825</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.0595</v>
+        <v>0.8083499999999999</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.0799</v>
+        <v>0.0017</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.12495</v>
+        <v>0.01105</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.13175</v>
+        <v>0.1054</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0.11815</v>
+        <v>0.18615</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.1139</v>
+        <v>0.16405</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.07905</v>
+        <v>0.15215</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.04505</v>
+        <v>0.11475</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.0136</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Антуан Гризманн</t>
+          <t>Yars</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.8168500000000001</v>
+        <v>0.8040999999999999</v>
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n">
-        <v>0.00085</v>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="3" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.01275</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.02465</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0.04845</v>
-      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
       <c r="N6" s="3" t="n">
-        <v>0.08754999999999999</v>
+        <v>0.0017</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.0935</v>
+        <v>0.007649999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.12835</v>
+        <v>0.11645</v>
       </c>
       <c r="Q6" s="3" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.14535</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>0.1258</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>0.12155</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0.0799</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0.0527</v>
-      </c>
       <c r="U6" s="3" t="n">
-        <v>0.0357</v>
+        <v>0.07565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>gara_077</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -861,99 +793,59 @@
         <v>0.55</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.003850000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0242</v>
+        <v>0.0231</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.05885000000000001</v>
+        <v>0.1166</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.08855</v>
+        <v>0.1529</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.12375</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.09625</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.08745000000000001</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0.04125</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.01815</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0.00055</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>gara_077</t>
+          <t>Cordell</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.55</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.00055</v>
+        <v>0.3223</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.01925</v>
+        <v>0.1815</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.05335000000000001</v>
+        <v>0.03245</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.06325000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.09295000000000002</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0.09350000000000001</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.06985000000000001</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.03135</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0.01595</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.00495</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.00055</v>
-      </c>
+        <v>0.00275</v>
+      </c>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -963,172 +855,111 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cordell</t>
+          <t>Great Teacher Onizuka</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.00055</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.003850000000000001</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.0143</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.05060000000000001</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0.06050000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1122</v>
+        <v>0.002</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.09405000000000001</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.138</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.0539</v>
+        <v>0.098</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.02475</v>
+        <v>0.068</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0143</v>
+        <v>0.0044</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.00605</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0.00055</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Great Teacher Onizuka</t>
+          <t>FISHer</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.3732</v>
+        <v>0.4</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="3" t="n">
-        <v>0.0004</v>
-      </c>
+      <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="3" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.03240000000000001</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="R10" s="3" t="n">
         <v>0.0012</v>
       </c>
-      <c r="L10" s="3" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0.0144</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>0.03920000000000001</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.0444</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.0576</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0.0216</v>
-      </c>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FISHer</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3556</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0.005600000000000001</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.0116</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0.0164</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0.0264</v>
+        <v>0.38885</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.0356</v>
+        <v>0.0121</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.052</v>
+        <v>0.03025</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.0644</v>
+        <v>0.04785</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.068</v>
+        <v>0.07260000000000001</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.04680000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.0264</v>
+        <v>0.13805</v>
       </c>
     </row>
     <row r="12">
@@ -1144,45 +975,31 @@
         <v>0.25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.093</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0285</v>
+        <v>0.11425</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.0565</v>
+        <v>0.0265</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.047</v>
+        <v>0.0105</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.041</v>
+        <v>0.005</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.0105</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.00475</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N12" s="3" t="n">
         <v>0.00075</v>
       </c>
-      <c r="O12" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="n"/>
@@ -1191,7 +1008,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>by_twentyseven</t>
+          <t>lavr</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1201,43 +1018,28 @@
         <v>0.25</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.003</v>
+        <v>0.00425</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0255</v>
+        <v>0.01875</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.0485</v>
+        <v>0.06425</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.0485</v>
+        <v>0.0605</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.04575</v>
+        <v>0.05425</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.03425</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Иван Царевич</t>
+          <t>nk_telller</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1247,48 +1049,32 @@
         <v>0.25</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.01875</v>
+        <v>0.014</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.03625</v>
+        <v>0.0515</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.04375</v>
+        <v>0.0515</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.03825</v>
+        <v>0.06175</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.04125</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.03675</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.0105</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0.00425</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.0005</v>
-      </c>
+        <v>0.06825000000000001</v>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="3" t="n">
-        <v>0.00025</v>
-      </c>
+      <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="n"/>
@@ -1296,7 +1082,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lavr</t>
+          <t>Иван Царевич</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1305,190 +1091,109 @@
       <c r="C15" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.00225</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0.0295</v>
-      </c>
       <c r="K15" s="4" t="n">
-        <v>0.04825</v>
+        <v>0.24225</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.046</v>
+        <v>0.0065</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.03525</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>0.02325</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="Q15" s="4" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="R15" s="4" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="S15" s="4" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="T15" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <v>0.00025</v>
+        <v>0.00125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Похороное бюро «улыбка»</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.2495</v>
+        <v>0.25</v>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
       <c r="K16" s="3" t="n">
-        <v>0.022</v>
+        <v>0.00625</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.035</v>
+        <v>0.13975</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.04025</v>
+        <v>0.0645</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.04375</v>
+        <v>0.028</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.0105</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.0245</v>
+        <v>0.00075</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0.01175</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>0.00175</v>
-      </c>
+        <v>0.00025</v>
+      </c>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
       <c r="U16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KidPoker</t>
+          <t>by_twentyseven</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.24625</v>
-      </c>
-      <c r="E17" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K17" s="4" t="n">
         <v>0.00025</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="I17" s="4" t="n">
+      <c r="L17" s="4" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.08575000000000001</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0.05975</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>0.00075</v>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.01775</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>0.03775</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0.02825</v>
-      </c>
       <c r="R17" s="4" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>0.00275</v>
+        <v>0.00075</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Gur4an</t>
+          <t>balamuto4ka</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1836</v>
+        <v>0.22925</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1501,41 +1206,41 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="3" t="n">
-        <v>0.0012</v>
+        <v>0.00025</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.00275</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.02275</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0.0168</v>
+        <v>0.034</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0.0216</v>
+        <v>0.048</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.0356</v>
+        <v>0.04425</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0.0492</v>
+        <v>0.04275</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0.0504</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>balamuto4ka</t>
+          <t>Демон</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.11175</v>
+        <v>0.2235</v>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
@@ -1545,48 +1250,42 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
-      <c r="L19" s="6" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0.00125</v>
-      </c>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
       <c r="O19" s="6" t="n">
         <v>0.00225</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.0045</v>
+        <v>0.02075</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.008</v>
+        <v>0.03875</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>0.013</v>
+        <v>0.04475</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0.02175</v>
+        <v>0.0465</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>0.03025</v>
+        <v>0.04175</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.03025</v>
+        <v>0.02875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>nk_telller</t>
+          <t>sashaRXY</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.10475</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1597,76 +1296,70 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="Q20" s="3" t="n">
         <v>0.00225</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0.0045</v>
-      </c>
       <c r="R20" s="3" t="n">
-        <v>0.0145</v>
+        <v>0.00475</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.01625</v>
+        <v>0.01125</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0.02875</v>
+        <v>0.02625</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.0335</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Бэндер</t>
+          <t>danalanaaa</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.095</v>
+        <v>0.05725</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00025</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.001</v>
+        <v>0.00125</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.004</v>
+        <v>0.0015</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.02</v>
+        <v>0.0065</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.028</v>
+        <v>0.017</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.041</v>
+        <v>0.03075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>mary_muse7</t>
+          <t>Похороное бюро «улыбка»</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.07875</v>
+        <v>0.02137586867996688</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
@@ -1679,73 +1372,51 @@
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
-      <c r="O22" s="3" t="n">
-        <v>0.00075</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>0.00375</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>0.00725</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>0.01075</v>
-      </c>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>0.02375</v>
+        <v>0.00534396716999172</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0.03075</v>
+        <v>0.01603190150997516</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Noize MC</t>
+          <t>Комар</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.05610000000000001</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>0.00055</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>0.00055</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>0.00165</v>
+        <v>0.02129883856895583</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.0011</v>
+        <v>0.003042691224136548</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.01155</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>0.011</v>
+        <v>0.003042691224136548</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.01521345612068274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>dzhemus</t>
+          <t>Gur4an</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.05225</v>
+        <v>0.02122190120948913</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1757,73 +1428,46 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0.00025</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>0.00175</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>0.00325</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0.00725</v>
-      </c>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>0.01625</v>
+        <v>0.01061095060474456</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.023</v>
+        <v>0.01061095060474456</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julia_2499</t>
+          <t>Чека-чека</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>0.00055</v>
-      </c>
-      <c r="Q25" s="4" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0.00495</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>0.00605</v>
+        <v>0.02114505671351814</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.01595</v>
+        <v>0.02114505671351814</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sashaRXY</t>
+          <t>artyomkalina</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.02110070273650771</v>
+        <v>0.02106830519340059</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
@@ -1837,65 +1481,42 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
-      <c r="P26" s="3" t="n">
-        <v>0.0007033567578835906</v>
-      </c>
+      <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
-      <c r="R26" s="3" t="n">
-        <v>0.002110070273650772</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>0.002110070273650772</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>0.005275175684126929</v>
-      </c>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
       <c r="U26" s="3" t="n">
-        <v>0.01090202974719565</v>
+        <v>0.02106830519340059</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nolekri</t>
+          <t>Maza</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.02094798390867965</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>0.0005661617272616122</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0.0005661617272616122</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>0.001698485181784837</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>0.003963132090831285</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>0.006793940727139346</v>
+        <v>0.02099164676190304</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.007360102454400958</v>
+        <v>0.02099164676190304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Демон</t>
+          <t>Noize MC</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.0208717632741894</v>
+        <v>0.02091508153220335</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
@@ -1910,56 +1531,41 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="3" t="n">
-        <v>0.001605520251860723</v>
-      </c>
+      <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
-      <c r="S28" s="3" t="n">
-        <v>0.001605520251860723</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>0.004013800629651808</v>
-      </c>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
       <c r="U28" s="3" t="n">
-        <v>0.01364692214081615</v>
+        <v>0.02091508153220335</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Сан Саныч</t>
+          <t>Moпс</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.02079563530922068</v>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>0.00109450712153793</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>0.00109450712153793</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>0.0109450712153793</v>
+        <v>0.0208386096178932</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.007661549850765513</v>
+        <v>0.0208386096178932</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>artyomkalina</t>
+          <t>лучший игрок</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.02071960012671645</v>
+        <v>0.02076223113298061</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
@@ -1977,46 +1583,38 @@
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="3" t="n">
-        <v>0.005919885750490416</v>
-      </c>
+      <c r="T30" s="2" t="n"/>
       <c r="U30" s="3" t="n">
-        <v>0.01479971437622604</v>
+        <v>0.02076223113298061</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sl1dbygad</t>
+          <t>Бэндер</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02064365784003364</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>0.00516091446000841</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>0.00516091446000841</v>
+        <v>0.02068594619189248</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.01032182892001682</v>
+        <v>0.02068594619189248</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Moпс</t>
+          <t>cheremsha</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.02056780856294565</v>
+        <v>0.0206097549094772</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
@@ -2034,40 +1632,38 @@
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
-      <c r="T32" s="3" t="n">
-        <v>0.005141952140736412</v>
-      </c>
+      <c r="T32" s="2" t="n"/>
       <c r="U32" s="3" t="n">
-        <v>0.01542585642220924</v>
+        <v>0.0206097549094772</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kuromi</t>
+          <t>FreSko</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02049205240964496</v>
+        <v>0.02053365740100719</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.02049205240964496</v>
+        <v>0.02053365740100719</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Lancelot</t>
+          <t>KidPoker</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.02041638949474567</v>
+        <v>0.02045765378218156</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
@@ -2084,45 +1680,39 @@
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
-      <c r="S34" s="3" t="n">
-        <v>0.02041638949474567</v>
-      </c>
+      <c r="S34" s="2" t="n"/>
       <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="n"/>
+      <c r="U34" s="3" t="n">
+        <v>0.02045765378218156</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>G_rant_999</t>
+          <t>Julia_2499</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.02034081993328614</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>0.006780273311095381</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>0.006780273311095381</v>
+        <v>0.02038174416912871</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.006780273311095381</v>
+        <v>0.02038174416912871</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>gvrdkn</t>
+          <t>lethalpresence</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.02026534384073158</v>
+        <v>0.02030592867840906</v>
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
@@ -2142,36 +1732,36 @@
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n"/>
       <c r="U36" s="3" t="n">
-        <v>0.02026534384073158</v>
+        <v>0.02030592867840906</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sfv</t>
+          <t>emilian_s</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.02018996133297668</v>
+        <v>0.02023020742701762</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>0.02018996133297668</v>
+        <v>0.02023020742701762</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>STrelOK</t>
+          <t>ЛЕНИН</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.02011467252634834</v>
+        <v>0.02015458053238683</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
@@ -2191,36 +1781,36 @@
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n"/>
       <c r="U38" s="3" t="n">
-        <v>0.02011467252634834</v>
+        <v>0.02015458053238683</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ЛЕНИН</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>38</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.0200394775376083</v>
+        <v>0.02007904811238918</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>0.0200394775376083</v>
+        <v>0.02007904811238918</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>emilian_s</t>
+          <t>jieb</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.01996437648395592</v>
+        <v>0.02000361028534005</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -2240,36 +1830,36 @@
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n"/>
       <c r="U40" s="3" t="n">
-        <v>0.01996437648395592</v>
+        <v>0.02000361028534005</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>z9</t>
+          <t>G_rant_999</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>40</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.01988936948303086</v>
+        <v>0.01992826717000043</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.01988936948303086</v>
+        <v>0.01992826717000043</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Лось</t>
+          <t>long_2203</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.01981445665291585</v>
+        <v>0.01985301888557976</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -2289,36 +1879,36 @@
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n"/>
       <c r="U42" s="3" t="n">
-        <v>0.01981445665291585</v>
+        <v>0.01985301888557976</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Комар</t>
+          <t>dolMy</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>42</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.01973963811213955</v>
+        <v>0.01977786555173874</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>0.01973963811213955</v>
+        <v>0.01977786555173874</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>long_2203</t>
+          <t>Kanti</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.01966491397967927</v>
+        <v>0.0197028072885922</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -2338,36 +1928,36 @@
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n"/>
       <c r="U44" s="3" t="n">
-        <v>0.01966491397967927</v>
+        <v>0.0197028072885922</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>дисциплина</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>44</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.01959028437496386</v>
+        <v>0.01962784421671196</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>0.01959028437496386</v>
+        <v>0.01962784421671196</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>wasapmaaan</t>
+          <t>sfv</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.01951574941787655</v>
+        <v>0.01955297645712975</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
@@ -2387,36 +1977,36 @@
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
       <c r="U46" s="3" t="n">
-        <v>0.01951574941787655</v>
+        <v>0.01955297645712975</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>лучший игрок</t>
+          <t>Горыныч</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.01944130922875786</v>
+        <v>0.01947820413134016</v>
       </c>
       <c r="U47" s="4" t="n">
-        <v>0.01944130922875786</v>
+        <v>0.01947820413134016</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Yanchik_250</t>
+          <t>Лось</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.01936696392840852</v>
+        <v>0.01940352736130354</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
@@ -2436,36 +2026,36 @@
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="n"/>
       <c r="U48" s="3" t="n">
-        <v>0.01936696392840852</v>
+        <v>0.01940352736130354</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deroz</t>
+          <t>Сан Саныч</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>48</v>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.01929271363809237</v>
+        <v>0.01932894626944905</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>0.01929271363809237</v>
+        <v>0.01932894626944905</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>dolMy</t>
+          <t>Абеляр</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.01921855847953937</v>
+        <v>0.01925446097867761</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
@@ -2485,36 +2075,36 @@
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="2" t="n"/>
       <c r="U50" s="3" t="n">
-        <v>0.01921855847953937</v>
+        <v>0.01925446097867761</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Shuricspinoza</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>50</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.01914449857494856</v>
+        <v>0.019180071612365</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>0.01914449857494856</v>
+        <v>0.019180071612365</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>jieb</t>
+          <t>gvrdkn</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.01907053404699111</v>
+        <v>0.01910577829436487</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
@@ -2534,36 +2124,36 @@
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="n"/>
       <c r="U52" s="3" t="n">
-        <v>0.01907053404699111</v>
+        <v>0.01910577829436487</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Чека-чека</t>
+          <t>MAKKSMIR</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>52</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.01899666501881334</v>
+        <v>0.01903158114901187</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>0.01899666501881334</v>
+        <v>0.01903158114901187</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Koff1ek</t>
+          <t>Dima!</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.01892289161403983</v>
+        <v>0.01895748030112476</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
@@ -2583,23 +2173,23 @@
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="2" t="n"/>
       <c r="U54" s="3" t="n">
-        <v>0.01892289161403983</v>
+        <v>0.01895748030112476</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>дисциплина</t>
+          <t>kuromi</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>54</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.01884921395677648</v>
+        <v>0.01888347587600954</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>0.01884921395677648</v>
+        <v>0.01888347587600954</v>
       </c>
     </row>
     <row r="56">
@@ -2612,7 +2202,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.0187756321716137</v>
+        <v>0.01880956799946265</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
@@ -2632,36 +2222,36 @@
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="2" t="n"/>
       <c r="U56" s="3" t="n">
-        <v>0.0187756321716137</v>
+        <v>0.01880956799946265</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>swapblet</t>
+          <t>STrelOK</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>56</v>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.01870214638362949</v>
+        <v>0.0187357567977742</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>0.01870214638362949</v>
+        <v>0.0187357567977742</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Maza</t>
+          <t>1С</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.01862875671839271</v>
+        <v>0.01866204239773115</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
@@ -2681,36 +2271,36 @@
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="2" t="n"/>
       <c r="U58" s="3" t="n">
-        <v>0.01862875671839271</v>
+        <v>0.01866204239773115</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Chesters</t>
+          <t>mary_muse7</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>58</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.01855546330196625</v>
+        <v>0.01858842492662062</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>0.01855546330196625</v>
+        <v>0.01858842492662062</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Shuricspinoza</t>
+          <t>Драйв</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.01848226626091028</v>
+        <v>0.01851490451223319</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
@@ -2730,36 +2320,36 @@
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="2" t="n"/>
       <c r="U60" s="3" t="n">
-        <v>0.01848226626091028</v>
+        <v>0.01851490451223319</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dunkaeva</t>
+          <t>Yanchik_250</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>60</v>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.01840916572228557</v>
+        <v>0.01844148128286618</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>0.01840916572228557</v>
+        <v>0.01844148128286618</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Chinaski</t>
+          <t>dzhemus</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.01833616181365673</v>
+        <v>0.01836815536732706</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
@@ -2779,36 +2369,36 @@
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="2" t="n"/>
       <c r="U62" s="3" t="n">
-        <v>0.01833616181365673</v>
+        <v>0.01836815536732706</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vovaa_25</t>
+          <t>Николай К</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>62</v>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.01826325466309562</v>
+        <v>0.01829492689493681</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>0.01826325466309562</v>
+        <v>0.01829492689493681</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FreSko</t>
+          <t>Chesters</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.01819044439918466</v>
+        <v>0.01822179599553337</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
@@ -2828,36 +2418,36 @@
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="2" t="n"/>
       <c r="U64" s="3" t="n">
-        <v>0.01819044439918466</v>
+        <v>0.01822179599553337</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>danalanaaa</t>
+          <t>Ruslan1</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>64</v>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.01811773115102029</v>
+        <v>0.01814876279947506</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>0.01811773115102029</v>
+        <v>0.01814876279947506</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>HellGnomik</t>
+          <t>Nolekri</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.01804511504821634</v>
+        <v>0.01807582743764408</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
@@ -2877,36 +2467,36 @@
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="2" t="n"/>
       <c r="U66" s="3" t="n">
-        <v>0.01804511504821634</v>
+        <v>0.01807582743764408</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dima!</t>
+          <t>Лабуба</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.01797259622090755</v>
+        <v>0.01800299004145003</v>
       </c>
       <c r="U67" s="4" t="n">
-        <v>0.01797259622090755</v>
+        <v>0.01800299004145003</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Jeereky</t>
+          <t>dunkaeva</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.01790017479975304</v>
+        <v>0.01793025074283347</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
@@ -2926,36 +2516,36 @@
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="2" t="n"/>
       <c r="U68" s="3" t="n">
-        <v>0.01790017479975304</v>
+        <v>0.01793025074283347</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bad_teacher</t>
+          <t>sl1dbygad</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>68</v>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.01782785091593984</v>
+        <v>0.01785760967426946</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>0.01782785091593984</v>
+        <v>0.01785760967426946</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>cheremsha</t>
+          <t>Ромчик</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.01775562470118647</v>
+        <v>0.01778506696877127</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
@@ -2975,36 +2565,36 @@
       <c r="S70" s="2" t="n"/>
       <c r="T70" s="2" t="n"/>
       <c r="U70" s="3" t="n">
-        <v>0.01775562470118647</v>
+        <v>0.01778506696877127</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lethalpresence</t>
+          <t>Mozilo</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>70</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.01768349628774654</v>
+        <v>0.01771262275989393</v>
       </c>
       <c r="U71" s="4" t="n">
-        <v>0.01768349628774654</v>
+        <v>0.01771262275989393</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Leomane</t>
+          <t>serpav_04</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.01761146580841236</v>
+        <v>0.01764027718173799</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
@@ -3024,36 +2614,36 @@
       <c r="S72" s="2" t="n"/>
       <c r="T72" s="2" t="n"/>
       <c r="U72" s="3" t="n">
-        <v>0.01761146580841236</v>
+        <v>0.01764027718173799</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Руслан</t>
+          <t>z9</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>72</v>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.01753953339651862</v>
+        <v>0.01756803036895321</v>
       </c>
       <c r="U73" s="4" t="n">
-        <v>0.01753953339651862</v>
+        <v>0.01756803036895321</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>duy27</t>
+          <t>FireSnail</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.0174676991859461</v>
+        <v>0.01749588245674234</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
@@ -3073,36 +2663,36 @@
       <c r="S74" s="2" t="n"/>
       <c r="T74" s="2" t="n"/>
       <c r="U74" s="3" t="n">
-        <v>0.0174676991859461</v>
+        <v>0.01749588245674234</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kanti</t>
+          <t>lubashley</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>74</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>0.01739596331112538</v>
+        <v>0.01742383358086487</v>
       </c>
       <c r="U75" s="4" t="n">
-        <v>0.01739596331112538</v>
+        <v>0.01742383358086487</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ustayonmymind</t>
+          <t>wasapmaaan</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.01732432590704068</v>
+        <v>0.01735188387764095</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
@@ -3122,36 +2712,36 @@
       <c r="S76" s="2" t="n"/>
       <c r="T76" s="2" t="n"/>
       <c r="U76" s="3" t="n">
-        <v>0.01732432590704068</v>
+        <v>0.01735188387764095</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ромчик</t>
+          <t>Deroz</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>76</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>0.01725278710923357</v>
+        <v>0.01728003348395515</v>
       </c>
       <c r="U77" s="4" t="n">
-        <v>0.01725278710923357</v>
+        <v>0.01728003348395515</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Добросердечный</t>
+          <t>Bushido</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0.01718134705380692</v>
+        <v>0.01720828253726047</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n"/>
@@ -3171,36 +2761,36 @@
       <c r="S78" s="2" t="n"/>
       <c r="T78" s="2" t="n"/>
       <c r="U78" s="3" t="n">
-        <v>0.01718134705380692</v>
+        <v>0.01720828253726047</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Горыныч</t>
+          <t>HellGnomik</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>78</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>0.01711000587742869</v>
+        <v>0.0171366311755822</v>
       </c>
       <c r="U79" s="4" t="n">
-        <v>0.01711000587742869</v>
+        <v>0.0171366311755822</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GodЗИЛLa</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.01703876371733593</v>
+        <v>0.01706507953752196</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n"/>
@@ -3220,36 +2810,36 @@
       <c r="S80" s="2" t="n"/>
       <c r="T80" s="2" t="n"/>
       <c r="U80" s="3" t="n">
-        <v>0.01703876371733593</v>
+        <v>0.01706507953752196</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OlgaaGeorgieva</t>
+          <t>No1z11</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>0.01696762071133869</v>
+        <v>0.01699362776226168</v>
       </c>
       <c r="U81" s="4" t="n">
-        <v>0.01696762071133869</v>
+        <v>0.01699362776226168</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Абеляр</t>
+          <t>bad_teacher</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.01689657699782405</v>
+        <v>0.01692227598956769</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="n"/>
@@ -3269,36 +2859,36 @@
       <c r="S82" s="2" t="n"/>
       <c r="T82" s="2" t="n"/>
       <c r="U82" s="3" t="n">
-        <v>0.01689657699782405</v>
+        <v>0.01692227598956769</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TryFraiz</t>
+          <t>Serg</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>82</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0.01682563271576013</v>
+        <v>0.01685102435979482</v>
       </c>
       <c r="U83" s="4" t="n">
-        <v>0.01682563271576013</v>
+        <v>0.01685102435979482</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Николай К</t>
+          <t>Chinaski</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0.01675478800470018</v>
+        <v>0.01677987301389054</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n"/>
@@ -3318,36 +2908,36 @@
       <c r="S84" s="2" t="n"/>
       <c r="T84" s="2" t="n"/>
       <c r="U84" s="3" t="n">
-        <v>0.01675478800470018</v>
+        <v>0.01677987301389054</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MAKKSMIR</t>
+          <t>Пупупу</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>84</v>
       </c>
       <c r="C85" s="4" t="n">
-        <v>0.01668404300478672</v>
+        <v>0.0167088220933991</v>
       </c>
       <c r="U85" s="4" t="n">
-        <v>0.01668404300478672</v>
+        <v>0.0167088220933991</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Rik_dds</t>
+          <t>Jeereky</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.01661339785675565</v>
+        <v>0.01663787174046583</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n"/>
@@ -3367,36 +2957,36 @@
       <c r="S86" s="2" t="n"/>
       <c r="T86" s="2" t="n"/>
       <c r="U86" s="3" t="n">
-        <v>0.01661339785675565</v>
+        <v>0.01663787174046583</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Пиковая Дама</t>
+          <t>Пассажир</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>86</v>
       </c>
       <c r="C87" s="4" t="n">
-        <v>0.0165428527019405</v>
+        <v>0.01656702209784135</v>
       </c>
       <c r="U87" s="4" t="n">
-        <v>0.0165428527019405</v>
+        <v>0.01656702209784135</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Bushido</t>
+          <t>OwTlion</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.01647240768227664</v>
+        <v>0.01649627330888588</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n"/>
@@ -3416,36 +3006,36 @@
       <c r="S88" s="2" t="n"/>
       <c r="T88" s="2" t="n"/>
       <c r="U88" s="3" t="n">
-        <v>0.01647240768227664</v>
+        <v>0.01649627330888588</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Татьяна Юрьевна Р.</t>
+          <t>Dio</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>88</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>0.01640206294030556</v>
+        <v>0.01642562551757363</v>
       </c>
       <c r="U89" s="4" t="n">
-        <v>0.01640206294030556</v>
+        <v>0.01642562551757363</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Кубус</t>
+          <t>terzzzzzzzzz</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0.01633181861917923</v>
+        <v>0.01635507886849715</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n"/>
@@ -3465,36 +3055,36 @@
       <c r="S90" s="2" t="n"/>
       <c r="T90" s="2" t="n"/>
       <c r="U90" s="3" t="n">
-        <v>0.01633181861917923</v>
+        <v>0.01635507886849715</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Chimedaschool1</t>
+          <t>Dim</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>0.01626167486266444</v>
+        <v>0.01628463350687181</v>
       </c>
       <c r="U91" s="4" t="n">
-        <v>0.01626167486266444</v>
+        <v>0.01628463350687181</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Лабуба</t>
+          <t>Татьяна Юрьевна Р.</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.01619163181514721</v>
+        <v>0.01621428957854024</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="n"/>
@@ -3514,36 +3104,36 @@
       <c r="S92" s="2" t="n"/>
       <c r="T92" s="2" t="n"/>
       <c r="U92" s="3" t="n">
-        <v>0.01619163181514721</v>
+        <v>0.01621428957854024</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Hotmandog</t>
+          <t>AlexBluff</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>92</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>0.01612168962163728</v>
+        <v>0.01614404722997689</v>
       </c>
       <c r="U93" s="4" t="n">
-        <v>0.01612168962163728</v>
+        <v>0.01614404722997689</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Чучел</t>
+          <t>Кинзу</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.01605184842777259</v>
+        <v>0.01607390660829261</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
@@ -3563,36 +3153,36 @@
       <c r="S94" s="2" t="n"/>
       <c r="T94" s="2" t="n"/>
       <c r="U94" s="3" t="n">
-        <v>0.01605184842777259</v>
+        <v>0.01607390660829261</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Holmes</t>
+          <t>Chimedaschool1</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>94</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>0.01598210837982381</v>
+        <v>0.01600386786123924</v>
       </c>
       <c r="U95" s="4" t="n">
-        <v>0.01598210837982381</v>
+        <v>0.01600386786123924</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Billie</t>
+          <t>Hotmandog</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.01591246962469899</v>
+        <v>0.01593393113721429</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n"/>
@@ -3612,36 +3202,36 @@
       <c r="S96" s="2" t="n"/>
       <c r="T96" s="2" t="n"/>
       <c r="U96" s="3" t="n">
-        <v>0.01591246962469899</v>
+        <v>0.01593393113721429</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>srgzorge</t>
+          <t>Xxx</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>96</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>0.01584293230994815</v>
+        <v>0.01586409658526572</v>
       </c>
       <c r="U97" s="4" t="n">
-        <v>0.01584293230994815</v>
+        <v>0.01586409658526572</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Викусик</t>
+          <t>kapayaki</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>0.01577349658376801</v>
+        <v>0.01579436435509656</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n"/>
@@ -3661,36 +3251,36 @@
       <c r="S98" s="2" t="n"/>
       <c r="T98" s="2" t="n"/>
       <c r="U98" s="3" t="n">
-        <v>0.01577349658376801</v>
+        <v>0.01579436435509656</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Константин 1</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>98</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>0.01570416259500667</v>
+        <v>0.01572473459706988</v>
       </c>
       <c r="U99" s="4" t="n">
-        <v>0.01570416259500667</v>
+        <v>0.01572473459706988</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>willy &lt;/3</t>
+          <t>Плейбой в карты</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.01563493049316845</v>
+        <v>0.01565520746221358</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n"/>
@@ -3710,36 +3300,36 @@
       <c r="S100" s="2" t="n"/>
       <c r="T100" s="2" t="n"/>
       <c r="U100" s="3" t="n">
-        <v>0.01563493049316845</v>
+        <v>0.01565520746221358</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Пассажир</t>
+          <t>Пиковая Дама</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>100</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>0.01556580042841874</v>
+        <v>0.01558578310222528</v>
       </c>
       <c r="U101" s="4" t="n">
-        <v>0.01556580042841874</v>
+        <v>0.01558578310222528</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Dim</t>
+          <t>vovaa_25</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
         <v>101</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0.01549677255158882</v>
+        <v>0.01551646166947733</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="n"/>
@@ -3759,36 +3349,36 @@
       <c r="S102" s="2" t="n"/>
       <c r="T102" s="2" t="n"/>
       <c r="U102" s="3" t="n">
-        <v>0.01549677255158882</v>
+        <v>0.01551646166947733</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dance_with_vlad</t>
+          <t>OlgaaGeorgieva</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>102</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>0.01542784701418083</v>
+        <v>0.01544724331702181</v>
       </c>
       <c r="U103" s="4" t="n">
-        <v>0.01542784701418083</v>
+        <v>0.01544724331702181</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Пупупу</t>
+          <t>Lawyer</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.01535902396837277</v>
+        <v>0.01537812819859561</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="n"/>
@@ -3808,36 +3398,36 @@
       <c r="S104" s="2" t="n"/>
       <c r="T104" s="2" t="n"/>
       <c r="U104" s="3" t="n">
-        <v>0.01535902396837277</v>
+        <v>0.01537812819859561</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Dio</t>
+          <t>avveev</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>104</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>0.01529030356702354</v>
+        <v>0.01530911646862553</v>
       </c>
       <c r="U105" s="4" t="n">
-        <v>0.01529030356702354</v>
+        <v>0.01530911646862553</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>OwTlion</t>
+          <t>БОЛЬШОЙ МИХА</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.01522168596367801</v>
+        <v>0.01524020828223347</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n"/>
@@ -3857,36 +3447,36 @@
       <c r="S106" s="2" t="n"/>
       <c r="T106" s="2" t="n"/>
       <c r="U106" s="3" t="n">
-        <v>0.01522168596367801</v>
+        <v>0.01524020828223347</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Manhattan</t>
+          <t>ПокерНЕок</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>106</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>0.01515317131257217</v>
+        <v>0.01517140379524165</v>
       </c>
       <c r="U107" s="4" t="n">
-        <v>0.01515317131257217</v>
+        <v>0.01517140379524165</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Kichatov</t>
+          <t>Настя дай стек</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0.01508475976863835</v>
+        <v>0.01510270316417793</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n"/>
@@ -3906,36 +3496,36 @@
       <c r="S108" s="2" t="n"/>
       <c r="T108" s="2" t="n"/>
       <c r="U108" s="3" t="n">
-        <v>0.01508475976863835</v>
+        <v>0.01510270316417793</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>E_ishutkin</t>
+          <t>turkoid</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>108</v>
       </c>
       <c r="C109" s="4" t="n">
-        <v>0.01501645148751045</v>
+        <v>0.01503410654628109</v>
       </c>
       <c r="U109" s="4" t="n">
-        <v>0.01501645148751045</v>
+        <v>0.01503410654628109</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>AlexBluff</t>
+          <t>Alina_97</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0.0149482466255293</v>
+        <v>0.01496561409950629</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n"/>
@@ -3955,36 +3545,36 @@
       <c r="S110" s="2" t="n"/>
       <c r="T110" s="2" t="n"/>
       <c r="U110" s="3" t="n">
-        <v>0.0149482466255293</v>
+        <v>0.01496561409950629</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kapayaki</t>
+          <t>sssx_xsss</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>110</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>0.01488014533974794</v>
+        <v>0.01489722598253048</v>
       </c>
       <c r="U111" s="4" t="n">
-        <v>0.01488014533974794</v>
+        <v>0.01489722598253048</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Плейбой в карты</t>
+          <t>Koff1ek</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.01481214778793714</v>
+        <v>0.01482894235475796</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n"/>
@@ -4004,36 +3594,36 @@
       <c r="S112" s="2" t="n"/>
       <c r="T112" s="2" t="n"/>
       <c r="U112" s="3" t="n">
-        <v>0.01481214778793714</v>
+        <v>0.01482894235475796</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>112</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>0.01474425412859081</v>
+        <v>0.01476076337632589</v>
       </c>
       <c r="U113" s="4" t="n">
-        <v>0.01474425412859081</v>
+        <v>0.01476076337632589</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Кальян</t>
+          <t>Obscur</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0.0146764645209316</v>
+        <v>0.01469268920811</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" s="2" t="n"/>
@@ -4053,36 +3643,36 @@
       <c r="S114" s="2" t="n"/>
       <c r="T114" s="2" t="n"/>
       <c r="U114" s="3" t="n">
-        <v>0.0146764645209316</v>
+        <v>0.01469268920811</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bogdanov</t>
+          <t>John Fisher</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>114</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>0.01460877912491645</v>
+        <v>0.0146247200117302</v>
       </c>
       <c r="U115" s="4" t="n">
-        <v>0.01460877912491645</v>
+        <v>0.0146247200117302</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Mozilo</t>
+          <t>Руслан</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
         <v>115</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0.01454119810124228</v>
+        <v>0.01455685594955643</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="n"/>
@@ -4102,36 +3692,36 @@
       <c r="S116" s="2" t="n"/>
       <c r="T116" s="2" t="n"/>
       <c r="U116" s="3" t="n">
-        <v>0.01454119810124228</v>
+        <v>0.01455685594955643</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Lawyer</t>
+          <t>Legi</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>116</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>0.01447372161135172</v>
+        <v>0.01448909718471439</v>
       </c>
       <c r="U117" s="4" t="n">
-        <v>0.01447372161135172</v>
+        <v>0.01448909718471439</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Legi</t>
+          <t>szrvi</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.01440634981743885</v>
+        <v>0.01442144388109147</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="n"/>
@@ -4151,36 +3741,36 @@
       <c r="S118" s="2" t="n"/>
       <c r="T118" s="2" t="n"/>
       <c r="U118" s="3" t="n">
-        <v>0.01440634981743885</v>
+        <v>0.01442144388109147</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ПокерНЕок</t>
+          <t>Сокол</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>118</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>0.01433908288245512</v>
+        <v>0.0143538962033427</v>
       </c>
       <c r="U119" s="4" t="n">
-        <v>0.01433908288245512</v>
+        <v>0.0143538962033427</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Ташкент</t>
+          <t>dance_with_vlad</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>119</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0.0142719209701152</v>
+        <v>0.01428645431689673</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="n"/>
@@ -4200,36 +3790,36 @@
       <c r="S120" s="2" t="n"/>
       <c r="T120" s="2" t="n"/>
       <c r="U120" s="3" t="n">
-        <v>0.0142719209701152</v>
+        <v>0.01428645431689673</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Лука</t>
+          <t>bogdanov</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>120</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>0.01420486424490297</v>
+        <v>0.01421911838796193</v>
       </c>
       <c r="U121" s="4" t="n">
-        <v>0.01420486424490297</v>
+        <v>0.01421911838796193</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Катальня</t>
+          <t>prostachoker</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>0.0141379128720776</v>
+        <v>0.01415188858353255</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="n"/>
@@ -4249,36 +3839,36 @@
       <c r="S122" s="2" t="n"/>
       <c r="T122" s="2" t="n"/>
       <c r="U122" s="3" t="n">
-        <v>0.0141379128720776</v>
+        <v>0.01415188858353255</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Milana_Xam</t>
+          <t>Rabie</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>122</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0.01407106701767961</v>
+        <v>0.01408476507139487</v>
       </c>
       <c r="U123" s="4" t="n">
-        <v>0.01407106701767961</v>
+        <v>0.01408476507139487</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Настя дай стек</t>
+          <t>nesmotri_v_shelll1</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
         <v>123</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0.01400432684853707</v>
+        <v>0.01401774802013355</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="n"/>
@@ -4298,36 +3888,36 @@
       <c r="S124" s="2" t="n"/>
       <c r="T124" s="2" t="n"/>
       <c r="U124" s="3" t="n">
-        <v>0.01400432684853707</v>
+        <v>0.01401774802013355</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Кинзу</t>
+          <t>Викусик</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>124</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>0.01393769253227185</v>
+        <v>0.01395083759913796</v>
       </c>
       <c r="U125" s="4" t="n">
-        <v>0.01393769253227185</v>
+        <v>0.01395083759913796</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Константин 1</t>
+          <t>duy27</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0.01387116423730594</v>
+        <v>0.01388403397860859</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
@@ -4347,36 +3937,36 @@
       <c r="S126" s="2" t="n"/>
       <c r="T126" s="2" t="n"/>
       <c r="U126" s="3" t="n">
-        <v>0.01387116423730594</v>
+        <v>0.01388403397860859</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>serpav_04</t>
+          <t>katevertu</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>126</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>0.01380474213286778</v>
+        <v>0.01381733732956354</v>
       </c>
       <c r="U127" s="4" t="n">
-        <v>0.01380474213286778</v>
+        <v>0.01381733732956354</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>sssx_xsss</t>
+          <t>Rik_dds</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0.01373842638899882</v>
+        <v>0.0137507478238451</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" s="2" t="n"/>
@@ -4396,36 +3986,36 @@
       <c r="S128" s="2" t="n"/>
       <c r="T128" s="2" t="n"/>
       <c r="U128" s="3" t="n">
-        <v>0.01373842638899882</v>
+        <v>0.0137507478238451</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>szrvi</t>
+          <t>maria_merlot</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>128</v>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.01367221717655996</v>
+        <v>0.0136842656341264</v>
       </c>
       <c r="U129" s="4" t="n">
-        <v>0.01367221717655996</v>
+        <v>0.0136842656341264</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Лина</t>
+          <t>Добросердечный</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.01360611466723817</v>
+        <v>0.01361789093391812</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" s="2" t="n"/>
@@ -4445,36 +4035,36 @@
       <c r="S130" s="2" t="n"/>
       <c r="T130" s="2" t="n"/>
       <c r="U130" s="3" t="n">
-        <v>0.01360611466723817</v>
+        <v>0.01361789093391812</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Xxx</t>
+          <t>E_ishutkin</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>130</v>
       </c>
       <c r="C131" s="4" t="n">
-        <v>0.0135401190335532</v>
+        <v>0.01355162389757525</v>
       </c>
       <c r="U131" s="4" t="n">
-        <v>0.0135401190335532</v>
+        <v>0.01355162389757525</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>terzzzzzzzzz</t>
+          <t>В азарт не входим</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.01347423044886434</v>
+        <v>0.01348546470030403</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="n"/>
@@ -4494,36 +4084,36 @@
       <c r="S132" s="2" t="n"/>
       <c r="T132" s="2" t="n"/>
       <c r="U132" s="3" t="n">
-        <v>0.01347423044886434</v>
+        <v>0.01348546470030403</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ajolana</t>
+          <t>GodЗИЛLa</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>132</v>
       </c>
       <c r="C133" s="4" t="n">
-        <v>0.01340844908737719</v>
+        <v>0.01341941351816883</v>
       </c>
       <c r="U133" s="4" t="n">
-        <v>0.01340844908737719</v>
+        <v>0.01341941351816883</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>No1z11</t>
+          <t>call_me_zanavo</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0.01334277512415062</v>
+        <v>0.01335347052809921</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" s="2" t="n"/>
@@ -4543,36 +4133,36 @@
       <c r="S134" s="2" t="n"/>
       <c r="T134" s="2" t="n"/>
       <c r="U134" s="3" t="n">
-        <v>0.01334277512415062</v>
+        <v>0.01335347052809921</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Qrexi</t>
+          <t>ustayonmymind</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>134</v>
       </c>
       <c r="C135" s="4" t="n">
-        <v>0.01327720873510376</v>
+        <v>0.01328763590789702</v>
       </c>
       <c r="U135" s="4" t="n">
-        <v>0.01327720873510376</v>
+        <v>0.01328763590789702</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ddv</t>
+          <t>TryFraiz</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>0.01321175009702302</v>
+        <v>0.01322190983624362</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" s="2" t="n"/>
@@ -4592,36 +4182,36 @@
       <c r="S136" s="2" t="n"/>
       <c r="T136" s="2" t="n"/>
       <c r="U136" s="3" t="n">
-        <v>0.01321175009702302</v>
+        <v>0.01322190983624362</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Davit</t>
+          <t>Staryii</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>136</v>
       </c>
       <c r="C137" s="4" t="n">
-        <v>0.0131463993875693</v>
+        <v>0.01315629249270711</v>
       </c>
       <c r="U137" s="4" t="n">
-        <v>0.0131463993875693</v>
+        <v>0.01315629249270711</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Бутербродский</t>
+          <t>Leomane</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>0.0130811567852852</v>
+        <v>0.01309078405774972</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="n"/>
@@ -4641,36 +4231,36 @@
       <c r="S138" s="2" t="n"/>
       <c r="T138" s="2" t="n"/>
       <c r="U138" s="3" t="n">
-        <v>0.0130811567852852</v>
+        <v>0.01309078405774972</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Анна Мария Гансалез</t>
+          <t>Никитос</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>138</v>
       </c>
       <c r="C139" s="4" t="n">
-        <v>0.01301602246960231</v>
+        <v>0.01302538471273523</v>
       </c>
       <c r="U139" s="4" t="n">
-        <v>0.01301602246960231</v>
+        <v>0.01302538471273523</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Kepeeshman</t>
+          <t>kirienish</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>0.01295099662084867</v>
+        <v>0.01296009463993653</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="n"/>
@@ -4690,36 +4280,36 @@
       <c r="S140" s="2" t="n"/>
       <c r="T140" s="2" t="n"/>
       <c r="U140" s="3" t="n">
-        <v>0.01295099662084867</v>
+        <v>0.01296009463993653</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Фиш</t>
+          <t>STG</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>140</v>
       </c>
       <c r="C141" s="4" t="n">
-        <v>0.01288607942025618</v>
+        <v>0.01289491402254322</v>
       </c>
       <c r="U141" s="4" t="n">
-        <v>0.01288607942025618</v>
+        <v>0.01289491402254322</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Студент</t>
+          <t>ksuhony</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="C142" s="3" t="n">
-        <v>0.01282127104996827</v>
+        <v>0.01282984304466935</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" s="2" t="n"/>
@@ -4739,36 +4329,36 @@
       <c r="S142" s="2" t="n"/>
       <c r="T142" s="2" t="n"/>
       <c r="U142" s="3" t="n">
-        <v>0.01282127104996827</v>
+        <v>0.01282984304466935</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1С</t>
+          <t>Yrs</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>142</v>
       </c>
       <c r="C143" s="4" t="n">
-        <v>0.01275657169304748</v>
+        <v>0.01276488189136117</v>
       </c>
       <c r="U143" s="4" t="n">
-        <v>0.01275657169304748</v>
+        <v>0.01276488189136117</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>sasha12039</t>
+          <t>clayzid</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>0.01269198153348327</v>
+        <v>0.01270003074860506</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" s="2" t="n"/>
@@ -4788,23 +4378,23 @@
       <c r="S144" s="2" t="n"/>
       <c r="T144" s="2" t="n"/>
       <c r="U144" s="3" t="n">
-        <v>0.01269198153348327</v>
+        <v>0.01270003074860506</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Margaery_ZHU</t>
+          <t>Retbin</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>144</v>
       </c>
       <c r="C145" s="4" t="n">
-        <v>0.01262750075619988</v>
+        <v>0.01263528980333552</v>
       </c>
       <c r="U145" s="4" t="n">
-        <v>0.01262750075619988</v>
+        <v>0.01263528980333552</v>
       </c>
     </row>
     <row r="146">
@@ -4817,7 +4407,7 @@
         <v>145</v>
       </c>
       <c r="C146" s="3" t="n">
-        <v>0.01256312954706418</v>
+        <v>0.01257065924344323</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="n"/>
@@ -4837,36 +4427,36 @@
       <c r="S146" s="2" t="n"/>
       <c r="T146" s="2" t="n"/>
       <c r="U146" s="3" t="n">
-        <v>0.01256312954706418</v>
+        <v>0.01257065924344323</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Лудоданя</t>
+          <t>VVP</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>146</v>
       </c>
       <c r="C147" s="4" t="n">
-        <v>0.01249886809289382</v>
+        <v>0.01250613925778325</v>
       </c>
       <c r="U147" s="4" t="n">
-        <v>0.01249886809289382</v>
+        <v>0.01250613925778325</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Лиза</t>
+          <t>sasha12039</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>0.01243471658146532</v>
+        <v>0.01244173003618328</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" s="2" t="n"/>
@@ -4886,36 +4476,36 @@
       <c r="S148" s="2" t="n"/>
       <c r="T148" s="2" t="n"/>
       <c r="U148" s="3" t="n">
-        <v>0.01243471658146532</v>
+        <v>0.01244173003618328</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>maria_merlot</t>
+          <t>mflameee</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>148</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>0.01237067520152228</v>
+        <v>0.01237743176945206</v>
       </c>
       <c r="U149" s="4" t="n">
-        <v>0.01237067520152228</v>
+        <v>0.01237743176945206</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Serg</t>
+          <t>Qrexi</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="C150" s="3" t="n">
-        <v>0.0123067441427837</v>
+        <v>0.01231324464938783</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" s="2" t="n"/>
@@ -4935,36 +4525,36 @@
       <c r="S150" s="2" t="n"/>
       <c r="T150" s="2" t="n"/>
       <c r="U150" s="3" t="n">
-        <v>0.0123067441427837</v>
+        <v>0.01231324464938783</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Бандэрос</t>
+          <t>Лудоданя</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>150</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>0.01224292359595247</v>
+        <v>0.01224916886878693</v>
       </c>
       <c r="U151" s="4" t="n">
-        <v>0.01224292359595247</v>
+        <v>0.01224916886878693</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Dupont</t>
+          <t>Bad Beat Bunny</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>0.01217921375272387</v>
+        <v>0.01218520462145245</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" s="2" t="n"/>
@@ -4984,36 +4574,36 @@
       <c r="S152" s="2" t="n"/>
       <c r="T152" s="2" t="n"/>
       <c r="U152" s="3" t="n">
-        <v>0.01217921375272387</v>
+        <v>0.01218520462145245</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Отец Дмитрий</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>152</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>0.01211561480579419</v>
+        <v>0.01212135210220308</v>
       </c>
       <c r="U153" s="4" t="n">
-        <v>0.01211561480579419</v>
+        <v>0.01212135210220308</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Катала</t>
+          <t>chilly</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>0.01205212694886949</v>
+        <v>0.01205761150688195</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" s="2" t="n"/>
@@ -5033,36 +4623,36 @@
       <c r="S154" s="2" t="n"/>
       <c r="T154" s="2" t="n"/>
       <c r="U154" s="3" t="n">
-        <v>0.01205212694886949</v>
+        <v>0.01205761150688195</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>prostachoker</t>
+          <t>Laches1</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>154</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>0.01198875037667445</v>
+        <v>0.0119939830323657</v>
       </c>
       <c r="U155" s="4" t="n">
-        <v>0.01198875037667445</v>
+        <v>0.0119939830323657</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>𝓼𝓸𝓾𝓵</t>
+          <t>rusya6996</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>0.01192548528496134</v>
+        <v>0.01193046687657354</v>
       </c>
       <c r="D156" s="2" t="n"/>
       <c r="E156" s="2" t="n"/>
@@ -5082,36 +4672,36 @@
       <c r="S156" s="2" t="n"/>
       <c r="T156" s="2" t="n"/>
       <c r="U156" s="3" t="n">
-        <v>0.01192548528496134</v>
+        <v>0.01193046687657354</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>katevertu</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>156</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>0.01186233187051906</v>
+        <v>0.01186706323847654</v>
       </c>
       <c r="U157" s="4" t="n">
-        <v>0.01186233187051906</v>
+        <v>0.01186706323847654</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Котяра</t>
+          <t>lifechampagne</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>0.01179929033118235</v>
+        <v>0.01180377231810695</v>
       </c>
       <c r="D158" s="2" t="n"/>
       <c r="E158" s="2" t="n"/>
@@ -5131,36 +4721,36 @@
       <c r="S158" s="2" t="n"/>
       <c r="T158" s="2" t="n"/>
       <c r="U158" s="3" t="n">
-        <v>0.01179929033118235</v>
+        <v>0.01180377231810695</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KLO</t>
+          <t>kornaakov</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>158</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>0.01173636086584106</v>
+        <v>0.01174059431656766</v>
       </c>
       <c r="U159" s="4" t="n">
-        <v>0.01173636086584106</v>
+        <v>0.01174059431656766</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>БОЛЬШОЙ МИХА</t>
+          <t>Davit</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>0.01167354367444961</v>
+        <v>0.01167752943604182</v>
       </c>
       <c r="D160" s="2" t="n"/>
       <c r="E160" s="2" t="n"/>
@@ -5180,36 +4770,36 @@
       <c r="S160" s="2" t="n"/>
       <c r="T160" s="2" t="n"/>
       <c r="U160" s="3" t="n">
-        <v>0.01167354367444961</v>
+        <v>0.01167752943604182</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>mrCelviano</t>
+          <t>ksellym</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>160</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>0.01161083895803644</v>
+        <v>0.0116145778798025</v>
       </c>
       <c r="U161" s="4" t="n">
-        <v>0.01161083895803644</v>
+        <v>0.0116145778798025</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>nesmotri_v_shelll1</t>
+          <t>гофер</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="C162" s="3" t="n">
-        <v>0.01154824691871376</v>
+        <v>0.01155173985222257</v>
       </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="n"/>
@@ -5229,36 +4819,36 @@
       <c r="S162" s="2" t="n"/>
       <c r="T162" s="2" t="n"/>
       <c r="U162" s="3" t="n">
-        <v>0.01154824691871376</v>
+        <v>0.01155173985222257</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rusya6996</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>162</v>
       </c>
       <c r="C163" s="4" t="n">
-        <v>0.01148576775968724</v>
+        <v>0.01148901555878458</v>
       </c>
       <c r="U163" s="4" t="n">
-        <v>0.01148576775968724</v>
+        <v>0.01148901555878458</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Вега</t>
+          <t>pеtr32</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>0.01142340168526594</v>
+        <v>0.01142640520609094</v>
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" s="2" t="n"/>
@@ -5278,36 +4868,36 @@
       <c r="S164" s="2" t="n"/>
       <c r="T164" s="2" t="n"/>
       <c r="U164" s="3" t="n">
-        <v>0.01142340168526594</v>
+        <v>0.01142640520609094</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Стич</t>
+          <t>DmitriiM0</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>164</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>0.01136114890087235</v>
+        <v>0.01136390900187401</v>
       </c>
       <c r="U165" s="4" t="n">
-        <v>0.01136114890087235</v>
+        <v>0.01136390900187401</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Yandi</t>
+          <t>Гонзалес</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>0.01129900961305248</v>
+        <v>0.01130152715500657</v>
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" s="2" t="n"/>
@@ -5327,36 +4917,36 @@
       <c r="S166" s="2" t="n"/>
       <c r="T166" s="2" t="n"/>
       <c r="U166" s="3" t="n">
-        <v>0.01129900961305248</v>
+        <v>0.01130152715500657</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Retbin</t>
+          <t>etovadikk</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>166</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>0.01123698402948621</v>
+        <v>0.01123925987551216</v>
       </c>
       <c r="U167" s="4" t="n">
-        <v>0.01123698402948621</v>
+        <v>0.01123925987551216</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Драйв</t>
+          <t>Стич</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>0.01117507235899765</v>
+        <v>0.01117710737457578</v>
       </c>
       <c r="D168" s="2" t="n"/>
       <c r="E168" s="2" t="n"/>
@@ -5376,36 +4966,36 @@
       <c r="S168" s="2" t="n"/>
       <c r="T168" s="2" t="n"/>
       <c r="U168" s="3" t="n">
-        <v>0.01117507235899765</v>
+        <v>0.01117710737457578</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Black Crystal</t>
+          <t>Nastya123</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>168</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>0.01111327481156573</v>
+        <v>0.0111150698645546</v>
       </c>
       <c r="U169" s="4" t="n">
-        <v>0.01111327481156573</v>
+        <v>0.0111150698645546</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>vadim123</t>
+          <t>okiyumi</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>0.01105159159833482</v>
+        <v>0.01105314755898884</v>
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" s="2" t="n"/>
@@ -5425,36 +5015,36 @@
       <c r="S170" s="2" t="n"/>
       <c r="T170" s="2" t="n"/>
       <c r="U170" s="3" t="n">
-        <v>0.01105159159833482</v>
+        <v>0.01105314755898884</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Bereza</t>
+          <t>NumberCat</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>170</v>
       </c>
       <c r="C171" s="4" t="n">
-        <v>0.01099002293162563</v>
+        <v>0.0109913406726128</v>
       </c>
       <c r="U171" s="4" t="n">
-        <v>0.01099002293162563</v>
+        <v>0.0109913406726128</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Сокол</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>0.01092856902494612</v>
+        <v>0.01092964942136605</v>
       </c>
       <c r="D172" s="2" t="n"/>
       <c r="E172" s="2" t="n"/>
@@ -5474,36 +5064,36 @@
       <c r="S172" s="2" t="n"/>
       <c r="T172" s="2" t="n"/>
       <c r="U172" s="3" t="n">
-        <v>0.01092856902494612</v>
+        <v>0.01092964942136605</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>МВика</t>
+          <t>stil9ger</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>172</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>0.0108672300930026</v>
+        <v>0.01086807402240472</v>
       </c>
       <c r="U173" s="4" t="n">
-        <v>0.0108672300930026</v>
+        <v>0.01086807402240472</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>mrsMarivanna</t>
+          <t>yungplague</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>0.01080600635171104</v>
+        <v>0.01080661469411297</v>
       </c>
       <c r="D174" s="2" t="n"/>
       <c r="E174" s="2" t="n"/>
@@ -5523,36 +5113,36 @@
       <c r="S174" s="2" t="n"/>
       <c r="T174" s="2" t="n"/>
       <c r="U174" s="3" t="n">
-        <v>0.01080600635171104</v>
+        <v>0.01080661469411297</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Obscur</t>
+          <t>ajolana</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>174</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>0.01074489801820839</v>
+        <v>0.01074527165611461</v>
       </c>
       <c r="U175" s="4" t="n">
-        <v>0.01074489801820839</v>
+        <v>0.01074527165611461</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ksuhony</t>
+          <t>Gambling Addiction</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>0.0106839053108642</v>
+        <v>0.0106840451292849</v>
       </c>
       <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="n"/>
@@ -5572,36 +5162,36 @@
       <c r="S176" s="2" t="n"/>
       <c r="T176" s="2" t="n"/>
       <c r="U176" s="3" t="n">
-        <v>0.0106839053108642</v>
+        <v>0.0106840451292849</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Эди не доехал</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>176</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.01062302844929231</v>
+        <v>0.01062293533576244</v>
       </c>
       <c r="U177" s="4" t="n">
-        <v>0.01062302844929231</v>
+        <v>0.01062293533576244</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Alina_97</t>
+          <t>Катюха</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>0.01056226765436267</v>
+        <v>0.01056194249896128</v>
       </c>
       <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="n"/>
@@ -5621,36 +5211,36 @@
       <c r="S178" s="2" t="n"/>
       <c r="T178" s="2" t="n"/>
       <c r="U178" s="3" t="n">
-        <v>0.01056226765436267</v>
+        <v>0.01056194249896128</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Отец Дмитрий</t>
+          <t>springbulk</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>178</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.01050162314821342</v>
+        <v>0.01050106684358317</v>
       </c>
       <c r="U179" s="4" t="n">
-        <v>0.01050162314821342</v>
+        <v>0.01050106684358317</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>dobrotova</t>
+          <t>Cocacola</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>0.01044109515426304</v>
+        <v>0.01044030859562997</v>
       </c>
       <c r="D180" s="2" t="n"/>
       <c r="E180" s="2" t="n"/>
@@ -5670,36 +5260,36 @@
       <c r="S180" s="2" t="n"/>
       <c r="T180" s="2" t="n"/>
       <c r="U180" s="3" t="n">
-        <v>0.01044109515426304</v>
+        <v>0.01044030859562997</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>bron</t>
+          <t>Davydovpussy</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>180</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>0.01038068389722268</v>
+        <v>0.01037966798241626</v>
       </c>
       <c r="U181" s="4" t="n">
-        <v>0.01038068389722268</v>
+        <v>0.01037966798241626</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ЭтоМойНик</t>
+          <t>Фиш</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>0.01032038960310873</v>
+        <v>0.01031914523258206</v>
       </c>
       <c r="D182" s="2" t="n"/>
       <c r="E182" s="2" t="n"/>
@@ -5719,36 +5309,36 @@
       <c r="S182" s="2" t="n"/>
       <c r="T182" s="2" t="n"/>
       <c r="U182" s="3" t="n">
-        <v>0.01032038960310873</v>
+        <v>0.01031914523258206</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>whitecurly_rr</t>
+          <t>elli</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>182</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>0.01026021249925545</v>
+        <v>0.01025874057610578</v>
       </c>
       <c r="U183" s="4" t="n">
-        <v>0.01026021249925545</v>
+        <v>0.01025874057610578</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>balamut</t>
+          <t>Fara</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>0.01020015281432784</v>
+        <v>0.01019845424431736</v>
       </c>
       <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="n"/>
@@ -5768,36 +5358,36 @@
       <c r="S184" s="2" t="n"/>
       <c r="T184" s="2" t="n"/>
       <c r="U184" s="3" t="n">
-        <v>0.01020015281432784</v>
+        <v>0.01019845424431736</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Коленвал</t>
+          <t>He3hAy</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>184</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.01014021077833471</v>
+        <v>0.01013828646991149</v>
       </c>
       <c r="U185" s="4" t="n">
-        <v>0.01014021077833471</v>
+        <v>0.01013828646991149</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Мистер Захаров</t>
+          <t>twewefe</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
         <v>185</v>
       </c>
       <c r="C186" s="3" t="n">
-        <v>0.01008038662264182</v>
+        <v>0.01007823748696115</v>
       </c>
       <c r="D186" s="2" t="n"/>
       <c r="E186" s="2" t="n"/>
@@ -5817,36 +5407,36 @@
       <c r="S186" s="2" t="n"/>
       <c r="T186" s="2" t="n"/>
       <c r="U186" s="3" t="n">
-        <v>0.01008038662264182</v>
+        <v>0.01007823748696115</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ilia M</t>
+          <t>Al</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>186</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>0.01002068057998537</v>
+        <v>0.01001830753093124</v>
       </c>
       <c r="U187" s="4" t="n">
-        <v>0.01002068057998537</v>
+        <v>0.01001830753093124</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>NEVERLUCKY</t>
+          <t>Катальня</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="C188" s="3" t="n">
-        <v>0.009961092884485509</v>
+        <v>0.009958496838692404</v>
       </c>
       <c r="D188" s="2" t="n"/>
       <c r="E188" s="2" t="n"/>
@@ -5866,36 +5456,36 @@
       <c r="S188" s="2" t="n"/>
       <c r="T188" s="2" t="n"/>
       <c r="U188" s="3" t="n">
-        <v>0.009961092884485509</v>
+        <v>0.009958496838692404</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Nastyareshonova</t>
+          <t>DanilaOdinokov</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>188</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>0.009901623771660121</v>
+        <v>0.009898805648535139</v>
       </c>
       <c r="U189" s="4" t="n">
-        <v>0.009901623771660121</v>
+        <v>0.009898805648535139</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Ivanjmj</t>
+          <t>repe_kate</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="C190" s="3" t="n">
-        <v>0.009842273478438815</v>
+        <v>0.009839234200183981</v>
       </c>
       <c r="D190" s="2" t="n"/>
       <c r="E190" s="2" t="n"/>
@@ -5915,36 +5505,36 @@
       <c r="S190" s="2" t="n"/>
       <c r="T190" s="2" t="n"/>
       <c r="U190" s="3" t="n">
-        <v>0.009842273478438815</v>
+        <v>0.009839234200183981</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Son_Ton</t>
+          <t>Аннэтт</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>190</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>0.009783042243177055</v>
+        <v>0.009779782734811962</v>
       </c>
       <c r="U191" s="4" t="n">
-        <v>0.009783042243177055</v>
+        <v>0.009779782734811962</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Даша 12 см</t>
+          <t>katerina_boc</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
         <v>191</v>
       </c>
       <c r="C192" s="3" t="n">
-        <v>0.009723930305670541</v>
+        <v>0.009720451495055266</v>
       </c>
       <c r="D192" s="2" t="n"/>
       <c r="E192" s="2" t="n"/>
@@ -5964,36 +5554,36 @@
       <c r="S192" s="2" t="n"/>
       <c r="T192" s="2" t="n"/>
       <c r="U192" s="3" t="n">
-        <v>0.009723930305670541</v>
+        <v>0.009720451495055266</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>JuZa</t>
+          <t>DARI</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>192</v>
       </c>
       <c r="C193" s="4" t="n">
-        <v>0.009664937907169753</v>
+        <v>0.009661240725028077</v>
       </c>
       <c r="U193" s="4" t="n">
-        <v>0.009664937907169753</v>
+        <v>0.009661240725028077</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Kerbi</t>
+          <t>Son_Ton</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="C194" s="3" t="n">
-        <v>0.00960606529039474</v>
+        <v>0.009602150670337636</v>
       </c>
       <c r="D194" s="2" t="n"/>
       <c r="E194" s="2" t="n"/>
@@ -6013,36 +5603,36 @@
       <c r="S194" s="2" t="n"/>
       <c r="T194" s="2" t="n"/>
       <c r="U194" s="3" t="n">
-        <v>0.00960606529039474</v>
+        <v>0.009602150670337636</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Artemon</t>
+          <t>Loosars</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>194</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>0.009547312699550078</v>
+        <v>0.009543181578099543</v>
       </c>
       <c r="U195" s="4" t="n">
-        <v>0.009547312699550078</v>
+        <v>0.009543181578099543</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Alisa Prekrati</t>
+          <t>alinaadmv</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="C196" s="3" t="n">
-        <v>0.009488680380340087</v>
+        <v>0.009484333696953244</v>
       </c>
       <c r="D196" s="2" t="n"/>
       <c r="E196" s="2" t="n"/>
@@ -6062,36 +5652,36 @@
       <c r="S196" s="2" t="n"/>
       <c r="T196" s="2" t="n"/>
       <c r="U196" s="3" t="n">
-        <v>0.009488680380340087</v>
+        <v>0.009484333696953244</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Zack</t>
+          <t>Кальян</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>196</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>0.009430168579984227</v>
+        <v>0.009425607277077761</v>
       </c>
       <c r="U197" s="4" t="n">
-        <v>0.009430168579984227</v>
+        <v>0.009425607277077761</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>vad1m09473</t>
+          <t>Schwepp1S</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="C198" s="3" t="n">
-        <v>0.009371777547232748</v>
+        <v>0.009367002570207649</v>
       </c>
       <c r="D198" s="2" t="n"/>
       <c r="E198" s="2" t="n"/>
@@ -6111,36 +5701,36 @@
       <c r="S198" s="2" t="n"/>
       <c r="T198" s="2" t="n"/>
       <c r="U198" s="3" t="n">
-        <v>0.009371777547232748</v>
+        <v>0.009367002570207649</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>maxim_galeev</t>
+          <t>frida_hk</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>198</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>0.009313507532382546</v>
+        <v>0.009308519829649175</v>
       </c>
       <c r="U199" s="4" t="n">
-        <v>0.009313507532382546</v>
+        <v>0.009308519829649175</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Аннэтт</t>
+          <t>nsa</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="C200" s="3" t="n">
-        <v>0.00925535878729326</v>
+        <v>0.00925015931029676</v>
       </c>
       <c r="D200" s="2" t="n"/>
       <c r="E200" s="2" t="n"/>
@@ -6160,36 +5750,36 @@
       <c r="S200" s="2" t="n"/>
       <c r="T200" s="2" t="n"/>
       <c r="U200" s="3" t="n">
-        <v>0.00925535878729326</v>
+        <v>0.00925015931029676</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FireSnail</t>
+          <t>Tim19</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>200</v>
       </c>
       <c r="C201" s="4" t="n">
-        <v>0.009197331565403599</v>
+        <v>0.00919192126864962</v>
       </c>
       <c r="U201" s="4" t="n">
-        <v>0.009197331565403599</v>
+        <v>0.00919192126864962</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>VVP</t>
+          <t>Mar_u_shka</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
         <v>201</v>
       </c>
       <c r="C202" s="3" t="n">
-        <v>0.009139426121747909</v>
+        <v>0.009133805962828692</v>
       </c>
       <c r="D202" s="2" t="n"/>
       <c r="E202" s="2" t="n"/>
@@ -6209,36 +5799,36 @@
       <c r="S202" s="2" t="n"/>
       <c r="T202" s="2" t="n"/>
       <c r="U202" s="3" t="n">
-        <v>0.009139426121747909</v>
+        <v>0.009133805962828692</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>springbulk</t>
+          <t>edimerfi</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>202</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>0.009081642712973003</v>
+        <v>0.009075813652593792</v>
       </c>
       <c r="U203" s="4" t="n">
-        <v>0.009081642712973003</v>
+        <v>0.009075813652593792</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Ryumon_Hozukimaruu</t>
+          <t>Адольф</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
         <v>203</v>
       </c>
       <c r="C204" s="3" t="n">
-        <v>0.009023981597355197</v>
+        <v>0.009017944599361028</v>
       </c>
       <c r="D204" s="2" t="n"/>
       <c r="E204" s="2" t="n"/>
@@ -6258,36 +5848,36 @@
       <c r="S204" s="2" t="n"/>
       <c r="T204" s="2" t="n"/>
       <c r="U204" s="3" t="n">
-        <v>0.009023981597355197</v>
+        <v>0.009017944599361028</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ruslan1</t>
+          <t>srgzorge</t>
         </is>
       </c>
       <c r="B205" t="n">
         <v>204</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>0.008966443034817657</v>
+        <v>0.008960199066220483</v>
       </c>
       <c r="U205" s="4" t="n">
-        <v>0.008966443034817657</v>
+        <v>0.008960199066220483</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>lubashley</t>
+          <t>avomerfe</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
         <v>205</v>
       </c>
       <c r="C206" s="3" t="n">
-        <v>0.008909027286947951</v>
+        <v>0.008902577317954154</v>
       </c>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="2" t="n"/>
@@ -6307,36 +5897,36 @@
       <c r="S206" s="2" t="n"/>
       <c r="T206" s="2" t="n"/>
       <c r="U206" s="3" t="n">
-        <v>0.008909027286947951</v>
+        <v>0.008902577317954154</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Gluckspilz8</t>
+          <t>juliezh</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>206</v>
       </c>
       <c r="C207" s="4" t="n">
-        <v>0.008851734617015907</v>
+        <v>0.008845079621054162</v>
       </c>
       <c r="U207" s="4" t="n">
-        <v>0.008851734617015907</v>
+        <v>0.008845079621054162</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Cocacola</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
         <v>207</v>
       </c>
       <c r="C208" s="3" t="n">
-        <v>0.008794565289991707</v>
+        <v>0.00878770624374124</v>
       </c>
       <c r="D208" s="2" t="n"/>
       <c r="E208" s="2" t="n"/>
@@ -6356,36 +5946,36 @@
       <c r="S208" s="2" t="n"/>
       <c r="T208" s="2" t="n"/>
       <c r="U208" s="3" t="n">
-        <v>0.008794565289991707</v>
+        <v>0.00878770624374124</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>rus210385</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>208</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>0.008737519572564275</v>
+        <v>0.008730457455983515</v>
       </c>
       <c r="U209" s="4" t="n">
-        <v>0.008737519572564275</v>
+        <v>0.008730457455983515</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Гела</t>
+          <t>Ryumon_Hozukimaruu</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="C210" s="3" t="n">
-        <v>0.008680597733159939</v>
+        <v>0.008673333529515537</v>
       </c>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="2" t="n"/>
@@ -6405,36 +5995,36 @@
       <c r="S210" s="2" t="n"/>
       <c r="T210" s="2" t="n"/>
       <c r="U210" s="3" t="n">
-        <v>0.008680597733159939</v>
+        <v>0.008673333529515537</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Катала</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>210</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>0.008623800041961381</v>
+        <v>0.00861633473785766</v>
       </c>
       <c r="U211" s="4" t="n">
-        <v>0.008623800041961381</v>
+        <v>0.00861633473785766</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Rabie</t>
+          <t>Коленвал</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
         <v>211</v>
       </c>
       <c r="C212" s="3" t="n">
-        <v>0.008567126770926867</v>
+        <v>0.008559461356335658</v>
       </c>
       <c r="D212" s="2" t="n"/>
       <c r="E212" s="2" t="n"/>
@@ -6454,36 +6044,36 @@
       <c r="S212" s="2" t="n"/>
       <c r="T212" s="2" t="n"/>
       <c r="U212" s="3" t="n">
-        <v>0.008567126770926867</v>
+        <v>0.008559461356335658</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Фуфа</t>
+          <t>Чучел</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>212</v>
       </c>
       <c r="C213" s="4" t="n">
-        <v>0.008510578193809792</v>
+        <v>0.008502713662100692</v>
       </c>
       <c r="U213" s="4" t="n">
-        <v>0.008510578193809792</v>
+        <v>0.008502713662100692</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Катюха</t>
+          <t>msbxmx</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
         <v>213</v>
       </c>
       <c r="C214" s="3" t="n">
-        <v>0.008454154586178502</v>
+        <v>0.008446091934149571</v>
       </c>
       <c r="D214" s="2" t="n"/>
       <c r="E214" s="2" t="n"/>
@@ -6503,36 +6093,36 @@
       <c r="S214" s="2" t="n"/>
       <c r="T214" s="2" t="n"/>
       <c r="U214" s="3" t="n">
-        <v>0.008454154586178502</v>
+        <v>0.008446091934149571</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Halo</t>
+          <t>xairullah</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>214</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>0.008397856225436448</v>
+        <v>0.008389596453345312</v>
       </c>
       <c r="U215" s="4" t="n">
-        <v>0.008397856225436448</v>
+        <v>0.008389596453345312</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>kciNik</t>
+          <t>Kasatik</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
         <v>215</v>
       </c>
       <c r="C216" s="3" t="n">
-        <v>0.008341683390842644</v>
+        <v>0.008333227502438059</v>
       </c>
       <c r="D216" s="2" t="n"/>
       <c r="E216" s="2" t="n"/>
@@ -6552,36 +6142,36 @@
       <c r="S216" s="2" t="n"/>
       <c r="T216" s="2" t="n"/>
       <c r="U216" s="3" t="n">
-        <v>0.008341683390842644</v>
+        <v>0.008333227502438059</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Davydovpussy</t>
+          <t>Luckymodjo</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>216</v>
       </c>
       <c r="C217" s="4" t="n">
-        <v>0.008285636363532438</v>
+        <v>0.008276985366086299</v>
       </c>
       <c r="U217" s="4" t="n">
-        <v>0.008285636363532438</v>
+        <v>0.008276985366086299</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Yrs</t>
+          <t>dobrotova</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="C218" s="3" t="n">
-        <v>0.008229715426538628</v>
+        <v>0.008220870330878418</v>
       </c>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="2" t="n"/>
@@ -6601,36 +6191,36 @@
       <c r="S218" s="2" t="n"/>
       <c r="T218" s="2" t="n"/>
       <c r="U218" s="3" t="n">
-        <v>0.008229715426538628</v>
+        <v>0.008220870330878418</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NumberCat</t>
+          <t>SuD</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>218</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>0.008173920864812901</v>
+        <v>0.008164882685354632</v>
       </c>
       <c r="U219" s="4" t="n">
-        <v>0.008173920864812901</v>
+        <v>0.008164882685354632</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>kirienish</t>
+          <t>Вега</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
         <v>219</v>
       </c>
       <c r="C220" s="3" t="n">
-        <v>0.00811825296524761</v>
+        <v>0.008109022720029217</v>
       </c>
       <c r="D220" s="2" t="n"/>
       <c r="E220" s="2" t="n"/>
@@ -6650,36 +6240,36 @@
       <c r="S220" s="2" t="n"/>
       <c r="T220" s="2" t="n"/>
       <c r="U220" s="3" t="n">
-        <v>0.00811825296524761</v>
+        <v>0.008109022720029217</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>egorzubkovv</t>
+          <t>Errchi</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>220</v>
       </c>
       <c r="C221" s="4" t="n">
-        <v>0.008062712016697901</v>
+        <v>0.008053290727413134</v>
       </c>
       <c r="U221" s="4" t="n">
-        <v>0.008062712016697901</v>
+        <v>0.008053290727413134</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>yungplague</t>
+          <t>KLO</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
         <v>221</v>
       </c>
       <c r="C222" s="3" t="n">
-        <v>0.008007298310004204</v>
+        <v>0.007997687002037009</v>
       </c>
       <c r="D222" s="2" t="n"/>
       <c r="E222" s="2" t="n"/>
@@ -6699,36 +6289,36 @@
       <c r="S222" s="2" t="n"/>
       <c r="T222" s="2" t="n"/>
       <c r="U222" s="3" t="n">
-        <v>0.008007298310004204</v>
+        <v>0.007997687002037009</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Север</t>
+          <t>klavson</t>
         </is>
       </c>
       <c r="B223" t="n">
         <v>222</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>0.00795201213801508</v>
+        <v>0.007942211840474469</v>
       </c>
       <c r="U223" s="4" t="n">
-        <v>0.00795201213801508</v>
+        <v>0.007942211840474469</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Staryii</t>
+          <t>Billie</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
         <v>223</v>
       </c>
       <c r="C224" s="3" t="n">
-        <v>0.007896853795610422</v>
+        <v>0.007886865541365893</v>
       </c>
       <c r="D224" s="2" t="n"/>
       <c r="E224" s="2" t="n"/>
@@ -6748,36 +6338,36 @@
       <c r="S224" s="2" t="n"/>
       <c r="T224" s="2" t="n"/>
       <c r="U224" s="3" t="n">
-        <v>0.007896853795610422</v>
+        <v>0.007886865541365893</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>chinaonetown</t>
+          <t>рачули</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>224</v>
       </c>
       <c r="C225" s="4" t="n">
-        <v>0.007841823579725063</v>
+        <v>0.007831648405442501</v>
       </c>
       <c r="U225" s="4" t="n">
-        <v>0.007841823579725063</v>
+        <v>0.007831648405442501</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Borsalino</t>
+          <t>Мистер Захаров</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
         <v>225</v>
       </c>
       <c r="C226" s="3" t="n">
-        <v>0.007786921789372753</v>
+        <v>0.007776560735550888</v>
       </c>
       <c r="D226" s="2" t="n"/>
       <c r="E226" s="2" t="n"/>
@@ -6797,36 +6387,36 @@
       <c r="S226" s="2" t="n"/>
       <c r="T226" s="2" t="n"/>
       <c r="U226" s="3" t="n">
-        <v>0.007786921789372753</v>
+        <v>0.007776560735550888</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>toronto970</t>
+          <t>Retik</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>226</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>0.007732148725670521</v>
+        <v>0.007721602836677928</v>
       </c>
       <c r="U227" s="4" t="n">
-        <v>0.007732148725670521</v>
+        <v>0.007721602836677928</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Retik</t>
+          <t>imt360_ATDK</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
         <v>227</v>
       </c>
       <c r="C228" s="3" t="n">
-        <v>0.007677504691863463</v>
+        <v>0.007666775015976112</v>
       </c>
       <c r="D228" s="2" t="n"/>
       <c r="E228" s="2" t="n"/>
@@ -6846,36 +6436,36 @@
       <c r="S228" s="2" t="n"/>
       <c r="T228" s="2" t="n"/>
       <c r="U228" s="3" t="n">
-        <v>0.007677504691863463</v>
+        <v>0.007666775015976112</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>puppet</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>228</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>0.007622989993349915</v>
+        <v>0.00761207758278929</v>
       </c>
       <c r="U229" s="4" t="n">
-        <v>0.007622989993349915</v>
+        <v>0.00761207758278929</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>moodellas</t>
+          <t>Эдгар</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="C230" s="3" t="n">
-        <v>0.007568604937707067</v>
+        <v>0.007557510848678857</v>
       </c>
       <c r="D230" s="2" t="n"/>
       <c r="E230" s="2" t="n"/>
@@ -6895,36 +6485,36 @@
       <c r="S230" s="2" t="n"/>
       <c r="T230" s="2" t="n"/>
       <c r="U230" s="3" t="n">
-        <v>0.007568604937707067</v>
+        <v>0.007557510848678857</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MYDAK</t>
+          <t>Голиаф</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>230</v>
       </c>
       <c r="C231" s="4" t="n">
-        <v>0.00751434983471698</v>
+        <v>0.007503075127450379</v>
       </c>
       <c r="U231" s="4" t="n">
-        <v>0.00751434983471698</v>
+        <v>0.007503075127450379</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>bogdansskii</t>
+          <t>6igfi$Hf4n</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
         <v>231</v>
       </c>
       <c r="C232" s="3" t="n">
-        <v>0.007460224996393073</v>
+        <v>0.007448770735180657</v>
       </c>
       <c r="D232" s="2" t="n"/>
       <c r="E232" s="2" t="n"/>
@@ -6944,36 +6534,36 @@
       <c r="S232" s="2" t="n"/>
       <c r="T232" s="2" t="n"/>
       <c r="U232" s="3" t="n">
-        <v>0.007460224996393073</v>
+        <v>0.007448770735180657</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Хэнк Муди</t>
+          <t>Кристина П</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>232</v>
       </c>
       <c r="C233" s="4" t="n">
-        <v>0.007406230737007031</v>
+        <v>0.007394597990245258</v>
       </c>
       <c r="U233" s="4" t="n">
-        <v>0.007406230737007031</v>
+        <v>0.007394597990245258</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Кристина П</t>
+          <t>Danil123</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
         <v>233</v>
       </c>
       <c r="C234" s="3" t="n">
-        <v>0.007352367373116175</v>
+        <v>0.007340557213346524</v>
       </c>
       <c r="D234" s="2" t="n"/>
       <c r="E234" s="2" t="n"/>
@@ -6993,7 +6583,7 @@
       <c r="S234" s="2" t="n"/>
       <c r="T234" s="2" t="n"/>
       <c r="U234" s="3" t="n">
-        <v>0.007352367373116175</v>
+        <v>0.007340557213346524</v>
       </c>
     </row>
     <row r="235">
@@ -7006,23 +6596,23 @@
         <v>234</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>0.007298635223591311</v>
+        <v>0.007286648727542034</v>
       </c>
       <c r="U235" s="4" t="n">
-        <v>0.007298635223591311</v>
+        <v>0.007286648727542034</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>steyk</t>
+          <t>mmrrll</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
         <v>235</v>
       </c>
       <c r="C236" s="3" t="n">
-        <v>0.007245034609645039</v>
+        <v>0.007232872858273601</v>
       </c>
       <c r="D236" s="2" t="n"/>
       <c r="E236" s="2" t="n"/>
@@ -7042,36 +6632,36 @@
       <c r="S236" s="2" t="n"/>
       <c r="T236" s="2" t="n"/>
       <c r="U236" s="3" t="n">
-        <v>0.007245034609645039</v>
+        <v>0.007232872858273601</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Aronio</t>
+          <t>Sendre</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>236</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>0.007191565854860565</v>
+        <v>0.007179229933396717</v>
       </c>
       <c r="U237" s="4" t="n">
-        <v>0.007191565854860565</v>
+        <v>0.007179229933396717</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>over9000mmr</t>
+          <t>Bagira</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="C238" s="3" t="n">
-        <v>0.007138229285220997</v>
+        <v>0.007125720283210552</v>
       </c>
       <c r="D238" s="2" t="n"/>
       <c r="E238" s="2" t="n"/>
@@ -7091,36 +6681,36 @@
       <c r="S238" s="2" t="n"/>
       <c r="T238" s="2" t="n"/>
       <c r="U238" s="3" t="n">
-        <v>0.007138229285220997</v>
+        <v>0.007125720283210552</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Альфред</t>
+          <t>toronto970</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>238</v>
       </c>
       <c r="C239" s="4" t="n">
-        <v>0.007085025229139165</v>
+        <v>0.007072344240488459</v>
       </c>
       <c r="U239" s="4" t="n">
-        <v>0.007085025229139165</v>
+        <v>0.007072344240488459</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Kasatik</t>
+          <t>Сантьяго</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
         <v>239</v>
       </c>
       <c r="C240" s="3" t="n">
-        <v>0.007031954017487946</v>
+        <v>0.007019102140509021</v>
       </c>
       <c r="D240" s="2" t="n"/>
       <c r="E240" s="2" t="n"/>
@@ -7140,36 +6730,36 @@
       <c r="S240" s="2" t="n"/>
       <c r="T240" s="2" t="n"/>
       <c r="U240" s="3" t="n">
-        <v>0.007031954017487946</v>
+        <v>0.007019102140509021</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Наталья</t>
+          <t>Kapukatya</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>240</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>0.006979015983631149</v>
+        <v>0.006965994321087638</v>
       </c>
       <c r="U241" s="4" t="n">
-        <v>0.006979015983631149</v>
+        <v>0.006965994321087638</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Vii</t>
+          <t>CICADA</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
         <v>241</v>
       </c>
       <c r="C242" s="3" t="n">
-        <v>0.006926211463454904</v>
+        <v>0.006913021122608682</v>
       </c>
       <c r="D242" s="2" t="n"/>
       <c r="E242" s="2" t="n"/>
@@ -7189,36 +6779,36 @@
       <c r="S242" s="2" t="n"/>
       <c r="T242" s="2" t="n"/>
       <c r="U242" s="3" t="n">
-        <v>0.006926211463454904</v>
+        <v>0.006913021122608682</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Killreal</t>
+          <t>Tanyashl</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>242</v>
       </c>
       <c r="C243" s="4" t="n">
-        <v>0.006873540795399646</v>
+        <v>0.006860182888058225</v>
       </c>
       <c r="U243" s="4" t="n">
-        <v>0.006873540795399646</v>
+        <v>0.006860182888058225</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Пётр 1</t>
+          <t>Лиза</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
         <v>243</v>
       </c>
       <c r="C244" s="3" t="n">
-        <v>0.006821004320492653</v>
+        <v>0.006807479963057353</v>
       </c>
       <c r="D244" s="2" t="n"/>
       <c r="E244" s="2" t="n"/>
@@ -7238,36 +6828,36 @@
       <c r="S244" s="2" t="n"/>
       <c r="T244" s="2" t="n"/>
       <c r="U244" s="3" t="n">
-        <v>0.006821004320492653</v>
+        <v>0.006807479963057353</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Al</t>
+          <t>Nemo</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>244</v>
       </c>
       <c r="C245" s="4" t="n">
-        <v>0.00676860238238116</v>
+        <v>0.006754912695896077</v>
       </c>
       <c r="U245" s="4" t="n">
-        <v>0.00676860238238116</v>
+        <v>0.006754912695896077</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>frlvmaria</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
         <v>245</v>
       </c>
       <c r="C246" s="3" t="n">
-        <v>0.006716335327366093</v>
+        <v>0.006702481437567855</v>
       </c>
       <c r="D246" s="2" t="n"/>
       <c r="E246" s="2" t="n"/>
@@ -7287,36 +6877,36 @@
       <c r="S246" s="2" t="n"/>
       <c r="T246" s="2" t="n"/>
       <c r="U246" s="3" t="n">
-        <v>0.006716335327366093</v>
+        <v>0.006702481437567855</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Полинат</t>
+          <t>viktorHQC</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>246</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>0.006664203504436384</v>
+        <v>0.006650186541804761</v>
       </c>
       <c r="U247" s="4" t="n">
-        <v>0.006664203504436384</v>
+        <v>0.006650186541804761</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Сантьяго</t>
+          <t>balamut</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
         <v>247</v>
       </c>
       <c r="C248" s="3" t="n">
-        <v>0.00661220726530394</v>
+        <v>0.006598028365113277</v>
       </c>
       <c r="D248" s="2" t="n"/>
       <c r="E248" s="2" t="n"/>
@@ -7336,36 +6926,36 @@
       <c r="S248" s="2" t="n"/>
       <c r="T248" s="2" t="n"/>
       <c r="U248" s="3" t="n">
-        <v>0.00661220726530394</v>
+        <v>0.006598028365113277</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Vikki</t>
+          <t>Ginger</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>248</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>0.00656034696443923</v>
+        <v>0.006546007266810748</v>
       </c>
       <c r="U249" s="4" t="n">
-        <v>0.00656034696443923</v>
+        <v>0.006546007266810748</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Luckymodjo</t>
+          <t>Natasha_fsb</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
         <v>249</v>
       </c>
       <c r="C250" s="3" t="n">
-        <v>0.006508622959107536</v>
+        <v>0.006494123609062521</v>
       </c>
       <c r="D250" s="2" t="n"/>
       <c r="E250" s="2" t="n"/>
@@ -7385,36 +6975,36 @@
       <c r="S250" s="2" t="n"/>
       <c r="T250" s="2" t="n"/>
       <c r="U250" s="3" t="n">
-        <v>0.006508622959107536</v>
+        <v>0.006494123609062521</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Errchi</t>
+          <t>pavel</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>250</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>0.006457035609405874</v>
+        <v>0.006442377756919762</v>
       </c>
       <c r="U251" s="4" t="n">
-        <v>0.006457035609405874</v>
+        <v>0.006442377756919762</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Адольф</t>
+          <t>aisel</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
         <v>251</v>
       </c>
       <c r="C252" s="3" t="n">
-        <v>0.006405585278300601</v>
+        <v>0.006390770078357992</v>
       </c>
       <c r="D252" s="2" t="n"/>
       <c r="E252" s="2" t="n"/>
@@ -7434,36 +7024,36 @@
       <c r="S252" s="2" t="n"/>
       <c r="T252" s="2" t="n"/>
       <c r="U252" s="3" t="n">
-        <v>0.006405585278300601</v>
+        <v>0.006390770078357992</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Bagira</t>
+          <t>LPZ18</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>252</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>0.006354272331665724</v>
+        <v>0.006339300944316337</v>
       </c>
       <c r="U253" s="4" t="n">
-        <v>0.006354272331665724</v>
+        <v>0.006339300944316337</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Gambling Addiction</t>
+          <t>Svetab</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
         <v>253</v>
       </c>
       <c r="C254" s="3" t="n">
-        <v>0.006303097138321932</v>
+        <v>0.006287970728737521</v>
       </c>
       <c r="D254" s="2" t="n"/>
       <c r="E254" s="2" t="n"/>
@@ -7483,36 +7073,36 @@
       <c r="S254" s="2" t="n"/>
       <c r="T254" s="2" t="n"/>
       <c r="U254" s="3" t="n">
-        <v>0.006303097138321932</v>
+        <v>0.006287970728737521</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STG</t>
+          <t>Olga Sheil</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>254</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>0.00625206007007636</v>
+        <v>0.006236779808608627</v>
       </c>
       <c r="U255" s="4" t="n">
-        <v>0.00625206007007636</v>
+        <v>0.006236779808608627</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>DARI</t>
+          <t>nevsskii</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
         <v>255</v>
       </c>
       <c r="C256" s="3" t="n">
-        <v>0.006201161501763116</v>
+        <v>0.006185728564002628</v>
       </c>
       <c r="D256" s="2" t="n"/>
       <c r="E256" s="2" t="n"/>
@@ -7532,36 +7122,36 @@
       <c r="S256" s="2" t="n"/>
       <c r="T256" s="2" t="n"/>
       <c r="U256" s="3" t="n">
-        <v>0.006201161501763116</v>
+        <v>0.006185728564002628</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Groove</t>
+          <t>eff1002</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>256</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>0.006150401811284572</v>
+        <v>0.00613481737812072</v>
       </c>
       <c r="U257" s="4" t="n">
-        <v>0.006150401811284572</v>
+        <v>0.00613481737812072</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>витя доезд</t>
+          <t>Марат</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
         <v>257</v>
       </c>
       <c r="C258" s="3" t="n">
-        <v>0.006099781379653457</v>
+        <v>0.006084046637335466</v>
       </c>
       <c r="D258" s="2" t="n"/>
       <c r="E258" s="2" t="n"/>
@@ -7581,36 +7171,36 @@
       <c r="S258" s="2" t="n"/>
       <c r="T258" s="2" t="n"/>
       <c r="U258" s="3" t="n">
-        <v>0.006099781379653457</v>
+        <v>0.006084046637335466</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>рачули</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>258</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>0.006049300591035755</v>
+        <v>0.006033416731234783</v>
       </c>
       <c r="U259" s="4" t="n">
-        <v>0.006049300591035755</v>
+        <v>0.006033416731234783</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Госпожа</t>
+          <t>dpolyaa</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
         <v>259</v>
       </c>
       <c r="C260" s="3" t="n">
-        <v>0.005998959832794451</v>
+        <v>0.005982928052666803</v>
       </c>
       <c r="D260" s="2" t="n"/>
       <c r="E260" s="2" t="n"/>
@@ -7630,36 +7220,36 @@
       <c r="S260" s="2" t="n"/>
       <c r="T260" s="2" t="n"/>
       <c r="U260" s="3" t="n">
-        <v>0.005998959832794451</v>
+        <v>0.005982928052666803</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>mmrrll</t>
+          <t>Фуфа</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>260</v>
       </c>
       <c r="C261" s="4" t="n">
-        <v>0.005948759495534106</v>
+        <v>0.005932580997785574</v>
       </c>
       <c r="U261" s="4" t="n">
-        <v>0.005948759495534106</v>
+        <v>0.005932580997785574</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>nkuraevv</t>
+          <t>MYDAK</t>
         </is>
       </c>
       <c r="B262" s="2" t="n">
         <v>261</v>
       </c>
       <c r="C262" s="3" t="n">
-        <v>0.005898699973146336</v>
+        <v>0.005882375966097707</v>
       </c>
       <c r="D262" s="2" t="n"/>
       <c r="E262" s="2" t="n"/>
@@ -7679,36 +7269,36 @@
       <c r="S262" s="2" t="n"/>
       <c r="T262" s="2" t="n"/>
       <c r="U262" s="3" t="n">
-        <v>0.005898699973146336</v>
+        <v>0.005882375966097707</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>arteminil</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>262</v>
       </c>
       <c r="C263" s="4" t="n">
-        <v>0.005848781662856164</v>
+        <v>0.005832313360509925</v>
       </c>
       <c r="U263" s="4" t="n">
-        <v>0.005848781662856164</v>
+        <v>0.005832313360509925</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>viktorHQC</t>
+          <t>igor forehand</t>
         </is>
       </c>
       <c r="B264" s="2" t="n">
         <v>263</v>
       </c>
       <c r="C264" s="3" t="n">
-        <v>0.005799004965269312</v>
+        <v>0.005782393587377572</v>
       </c>
       <c r="D264" s="2" t="n"/>
       <c r="E264" s="2" t="n"/>
@@ -7728,36 +7318,36 @@
       <c r="S264" s="2" t="n"/>
       <c r="T264" s="2" t="n"/>
       <c r="U264" s="3" t="n">
-        <v>0.005799004965269312</v>
+        <v>0.005782393587377572</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Nika</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>264</v>
       </c>
       <c r="C265" s="4" t="n">
-        <v>0.005749370284420421</v>
+        <v>0.005732617056554087</v>
       </c>
       <c r="U265" s="4" t="n">
-        <v>0.005749370284420421</v>
+        <v>0.005732617056554087</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>xairullah</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B266" s="2" t="n">
         <v>265</v>
       </c>
       <c r="C266" s="3" t="n">
-        <v>0.005699878027822254</v>
+        <v>0.005682984181441482</v>
       </c>
       <c r="D266" s="2" t="n"/>
       <c r="E266" s="2" t="n"/>
@@ -7777,36 +7367,36 @@
       <c r="S266" s="2" t="n"/>
       <c r="T266" s="2" t="n"/>
       <c r="U266" s="3" t="n">
-        <v>0.005699878027822254</v>
+        <v>0.005682984181441482</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Danil123</t>
+          <t>Virt Ceo</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>266</v>
       </c>
       <c r="C267" s="4" t="n">
-        <v>0.005650528606515883</v>
+        <v>0.005633495379041854</v>
       </c>
       <c r="U267" s="4" t="n">
-        <v>0.005650528606515883</v>
+        <v>0.005633495379041854</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>В азарт не входим</t>
+          <t>Nastyareshonova</t>
         </is>
       </c>
       <c r="B268" s="2" t="n">
         <v>267</v>
       </c>
       <c r="C268" s="3" t="n">
-        <v>0.005601322435121898</v>
+        <v>0.005584151070009933</v>
       </c>
       <c r="D268" s="2" t="n"/>
       <c r="E268" s="2" t="n"/>
@@ -7826,36 +7416,36 @@
       <c r="S268" s="2" t="n"/>
       <c r="T268" s="2" t="n"/>
       <c r="U268" s="3" t="n">
-        <v>0.005601322435121898</v>
+        <v>0.005584151070009933</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>turkoid</t>
+          <t>bogdansskii</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>268</v>
       </c>
       <c r="C269" s="4" t="n">
-        <v>0.005552259931892672</v>
+        <v>0.005534951678706732</v>
       </c>
       <c r="U269" s="4" t="n">
-        <v>0.005552259931892672</v>
+        <v>0.005534951678706732</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>aisel</t>
+          <t>Dreemur</t>
         </is>
       </c>
       <c r="B270" s="2" t="n">
         <v>269</v>
       </c>
       <c r="C270" s="3" t="n">
-        <v>0.005503341518765678</v>
+        <v>0.00548589763325428</v>
       </c>
       <c r="D270" s="2" t="n"/>
       <c r="E270" s="2" t="n"/>
@@ -7875,36 +7465,36 @@
       <c r="S270" s="2" t="n"/>
       <c r="T270" s="2" t="n"/>
       <c r="U270" s="3" t="n">
-        <v>0.005503341518765678</v>
+        <v>0.00548589763325428</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>clayzid</t>
+          <t>Госпожа</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>270</v>
       </c>
       <c r="C271" s="4" t="n">
-        <v>0.005454567621417946</v>
+        <v>0.005436989365591512</v>
       </c>
       <c r="U271" s="4" t="n">
-        <v>0.005454567621417946</v>
+        <v>0.005436989365591512</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Эдгар</t>
+          <t>veronesss</t>
         </is>
       </c>
       <c r="B272" s="2" t="n">
         <v>271</v>
       </c>
       <c r="C272" s="3" t="n">
-        <v>0.005405938669321602</v>
+        <v>0.005388227311531335</v>
       </c>
       <c r="D272" s="2" t="n"/>
       <c r="E272" s="2" t="n"/>
@@ -7924,36 +7514,36 @@
       <c r="S272" s="2" t="n"/>
       <c r="T272" s="2" t="n"/>
       <c r="U272" s="3" t="n">
-        <v>0.005405938669321602</v>
+        <v>0.005388227311531335</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Bad Beat Bunny</t>
+          <t>журналист</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>272</v>
       </c>
       <c r="C273" s="4" t="n">
-        <v>0.005357455095800619</v>
+        <v>0.00533961191081887</v>
       </c>
       <c r="U273" s="4" t="n">
-        <v>0.005357455095800619</v>
+        <v>0.00533961191081887</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Alkyds</t>
+          <t>Павлуша</t>
         </is>
       </c>
       <c r="B274" s="2" t="n">
         <v>273</v>
       </c>
       <c r="C274" s="3" t="n">
-        <v>0.005309117338088731</v>
+        <v>0.005291143607190952</v>
       </c>
       <c r="D274" s="2" t="n"/>
       <c r="E274" s="2" t="n"/>
@@ -7973,36 +7563,36 @@
       <c r="S274" s="2" t="n"/>
       <c r="T274" s="2" t="n"/>
       <c r="U274" s="3" t="n">
-        <v>0.005309117338088731</v>
+        <v>0.005291143607190952</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Vitos2049</t>
+          <t>Killreal</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>274</v>
       </c>
       <c r="C275" s="4" t="n">
-        <v>0.005260925837388584</v>
+        <v>0.005242822848436881</v>
       </c>
       <c r="U275" s="4" t="n">
-        <v>0.005260925837388584</v>
+        <v>0.005242822848436881</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Голиаф</t>
+          <t>Groove</t>
         </is>
       </c>
       <c r="B276" s="2" t="n">
         <v>275</v>
       </c>
       <c r="C276" s="3" t="n">
-        <v>0.005212881038932157</v>
+        <v>0.005194650086460492</v>
       </c>
       <c r="D276" s="2" t="n"/>
       <c r="E276" s="2" t="n"/>
@@ -8022,36 +7612,36 @@
       <c r="S276" s="2" t="n"/>
       <c r="T276" s="2" t="n"/>
       <c r="U276" s="3" t="n">
-        <v>0.005212881038932157</v>
+        <v>0.005194650086460492</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>fe1k</t>
+          <t>ArtemDavidyan</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>276</v>
       </c>
       <c r="C277" s="4" t="n">
-        <v>0.00516498339204245</v>
+        <v>0.005146625777343546</v>
       </c>
       <c r="U277" s="4" t="n">
-        <v>0.00516498339204245</v>
+        <v>0.005146625777343546</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Комарик</t>
+          <t>Kepeeshman</t>
         </is>
       </c>
       <c r="B278" s="2" t="n">
         <v>277</v>
       </c>
       <c r="C278" s="3" t="n">
-        <v>0.005117233350196542</v>
+        <v>0.005098750381410511</v>
       </c>
       <c r="D278" s="2" t="n"/>
       <c r="E278" s="2" t="n"/>
@@ -8071,36 +7661,36 @@
       <c r="S278" s="2" t="n"/>
       <c r="T278" s="2" t="n"/>
       <c r="U278" s="3" t="n">
-        <v>0.005117233350196542</v>
+        <v>0.005098750381410511</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>dpolyaa</t>
+          <t>Альфред</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>278</v>
       </c>
       <c r="C279" s="4" t="n">
-        <v>0.005069631371089981</v>
+        <v>0.00505102436329475</v>
       </c>
       <c r="U279" s="4" t="n">
-        <v>0.005069631371089981</v>
+        <v>0.00505102436329475</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>onedrakeo</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="B280" s="2" t="n">
         <v>279</v>
       </c>
       <c r="C280" s="3" t="n">
-        <v>0.005022177916702609</v>
+        <v>0.005003448192006174</v>
       </c>
       <c r="D280" s="2" t="n"/>
       <c r="E280" s="2" t="n"/>
@@ -8120,36 +7710,36 @@
       <c r="S280" s="2" t="n"/>
       <c r="T280" s="2" t="n"/>
       <c r="U280" s="3" t="n">
-        <v>0.005022177916702609</v>
+        <v>0.005003448192006174</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>He3hAy</t>
+          <t>Nell</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>280</v>
       </c>
       <c r="C281" s="4" t="n">
-        <v>0.00497487345336581</v>
+        <v>0.004956022341000368</v>
       </c>
       <c r="U281" s="4" t="n">
-        <v>0.00497487345336581</v>
+        <v>0.004956022341000368</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>eff1002</t>
+          <t>Север</t>
         </is>
       </c>
       <c r="B282" s="2" t="n">
         <v>281</v>
       </c>
       <c r="C282" s="3" t="n">
-        <v>0.004927718451831265</v>
+        <v>0.004908747288249288</v>
       </c>
       <c r="D282" s="2" t="n"/>
       <c r="E282" s="2" t="n"/>
@@ -8169,36 +7759,36 @@
       <c r="S282" s="2" t="n"/>
       <c r="T282" s="2" t="n"/>
       <c r="U282" s="3" t="n">
-        <v>0.004927718451831265</v>
+        <v>0.004908747288249288</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Laches1</t>
+          <t>Артанис</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>282</v>
       </c>
       <c r="C283" s="4" t="n">
-        <v>0.004880713387341227</v>
+        <v>0.004861623516313513</v>
       </c>
       <c r="U283" s="4" t="n">
-        <v>0.004880713387341227</v>
+        <v>0.004861623516313513</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Pasha2796</t>
+          <t>Zack</t>
         </is>
       </c>
       <c r="B284" s="2" t="n">
         <v>283</v>
       </c>
       <c r="C284" s="3" t="n">
-        <v>0.004833858739700369</v>
+        <v>0.004814651512416153</v>
       </c>
       <c r="D284" s="2" t="n"/>
       <c r="E284" s="2" t="n"/>
@@ -8218,36 +7808,36 @@
       <c r="S284" s="2" t="n"/>
       <c r="T284" s="2" t="n"/>
       <c r="U284" s="3" t="n">
-        <v>0.004833858739700369</v>
+        <v>0.004814651512416153</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Kiselka</t>
+          <t>Pasha2796</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>284</v>
       </c>
       <c r="C285" s="4" t="n">
-        <v>0.004787154993349257</v>
+        <v>0.004767831768518397</v>
       </c>
       <c r="U285" s="4" t="n">
-        <v>0.004787154993349257</v>
+        <v>0.004767831768518397</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>avdoda</t>
+          <t>Alisa Prekrati</t>
         </is>
       </c>
       <c r="B286" s="2" t="n">
         <v>285</v>
       </c>
       <c r="C286" s="3" t="n">
-        <v>0.004740602637439494</v>
+        <v>0.004721164781396829</v>
       </c>
       <c r="D286" s="2" t="n"/>
       <c r="E286" s="2" t="n"/>
@@ -8267,36 +7857,36 @@
       <c r="S286" s="2" t="n"/>
       <c r="T286" s="2" t="n"/>
       <c r="U286" s="3" t="n">
-        <v>0.004740602637439494</v>
+        <v>0.004721164781396829</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Akatones</t>
+          <t>Black Crystal</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>286</v>
       </c>
       <c r="C287" s="4" t="n">
-        <v>0.004694202165910565</v>
+        <v>0.00467465105272249</v>
       </c>
       <c r="U287" s="4" t="n">
-        <v>0.004694202165910565</v>
+        <v>0.00467465105272249</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>xiolloix</t>
+          <t>puppet</t>
         </is>
       </c>
       <c r="B288" s="2" t="n">
         <v>287</v>
       </c>
       <c r="C288" s="3" t="n">
-        <v>0.004647954077568465</v>
+        <v>0.004628291089141786</v>
       </c>
       <c r="D288" s="2" t="n"/>
       <c r="E288" s="2" t="n"/>
@@ -8316,36 +7906,36 @@
       <c r="S288" s="2" t="n"/>
       <c r="T288" s="2" t="n"/>
       <c r="U288" s="3" t="n">
-        <v>0.004647954077568465</v>
+        <v>0.004628291089141786</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ivolodya</t>
+          <t>Kety</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>288</v>
       </c>
       <c r="C289" s="4" t="n">
-        <v>0.004601858876166134</v>
+        <v>0.004582085402359271</v>
       </c>
       <c r="U289" s="4" t="n">
-        <v>0.004601858876166134</v>
+        <v>0.004582085402359271</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>журналист</t>
+          <t>𝓼𝓸𝓾𝓵</t>
         </is>
       </c>
       <c r="B290" s="2" t="n">
         <v>289</v>
       </c>
       <c r="C290" s="3" t="n">
-        <v>0.00455591707048578</v>
+        <v>0.00453603450922238</v>
       </c>
       <c r="D290" s="2" t="n"/>
       <c r="E290" s="2" t="n"/>
@@ -8365,36 +7955,36 @@
       <c r="S290" s="2" t="n"/>
       <c r="T290" s="2" t="n"/>
       <c r="U290" s="3" t="n">
-        <v>0.00455591707048578</v>
+        <v>0.00453603450922238</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>elli</t>
+          <t>Сэм</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>290</v>
       </c>
       <c r="C291" s="4" t="n">
-        <v>0.004510129174423115</v>
+        <v>0.004490138931808152</v>
       </c>
       <c r="U291" s="4" t="n">
-        <v>0.004510129174423115</v>
+        <v>0.004490138931808152</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Olga Sheil</t>
+          <t>nkuraevv</t>
         </is>
       </c>
       <c r="B292" s="2" t="n">
         <v>291</v>
       </c>
       <c r="C292" s="3" t="n">
-        <v>0.004464495707073594</v>
+        <v>0.004444399197512031</v>
       </c>
       <c r="D292" s="2" t="n"/>
       <c r="E292" s="2" t="n"/>
@@ -8414,36 +8004,36 @@
       <c r="S292" s="2" t="n"/>
       <c r="T292" s="2" t="n"/>
       <c r="U292" s="3" t="n">
-        <v>0.004464495707073594</v>
+        <v>0.004444399197512031</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>call_me_zanavo</t>
+          <t>averagemorningstarenjoyer</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>292</v>
       </c>
       <c r="C293" s="4" t="n">
-        <v>0.004419017192820697</v>
+        <v>0.004398815839138773</v>
       </c>
       <c r="U293" s="4" t="n">
-        <v>0.004419017192820697</v>
+        <v>0.004398815839138773</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Ginger</t>
+          <t>Marina7</t>
         </is>
       </c>
       <c r="B294" s="2" t="n">
         <v>293</v>
       </c>
       <c r="C294" s="3" t="n">
-        <v>0.00437369416142633</v>
+        <v>0.004353389394995555</v>
       </c>
       <c r="D294" s="2" t="n"/>
       <c r="E294" s="2" t="n"/>
@@ -8463,36 +8053,36 @@
       <c r="S294" s="2" t="n"/>
       <c r="T294" s="2" t="n"/>
       <c r="U294" s="3" t="n">
-        <v>0.00437369416142633</v>
+        <v>0.004353389394995555</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Сэм</t>
+          <t>Гела</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>294</v>
       </c>
       <c r="C295" s="4" t="n">
-        <v>0.004328527148123392</v>
+        <v>0.004308120408987343</v>
       </c>
       <c r="U295" s="4" t="n">
-        <v>0.004328527148123392</v>
+        <v>0.004308120408987343</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>ArtemDavidyan</t>
+          <t>Dupont</t>
         </is>
       </c>
       <c r="B296" s="2" t="n">
         <v>295</v>
       </c>
       <c r="C296" s="3" t="n">
-        <v>0.004283516693710604</v>
+        <v>0.004263009430714586</v>
       </c>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="2" t="n"/>
@@ -8512,36 +8102,36 @@
       <c r="S296" s="2" t="n"/>
       <c r="T296" s="2" t="n"/>
       <c r="U296" s="3" t="n">
-        <v>0.004283516693710604</v>
+        <v>0.004263009430714586</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Anastasia</t>
+          <t>Анна Мария Гансалез</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>296</v>
       </c>
       <c r="C297" s="4" t="n">
-        <v>0.004238663344649641</v>
+        <v>0.004218057015573319</v>
       </c>
       <c r="U297" s="4" t="n">
-        <v>0.004238663344649641</v>
+        <v>0.004218057015573319</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Kapukatya</t>
+          <t>vad1m09473</t>
         </is>
       </c>
       <c r="B298" s="2" t="n">
         <v>297</v>
       </c>
       <c r="C298" s="3" t="n">
-        <v>0.004193967653164665</v>
+        <v>0.004173263724857739</v>
       </c>
       <c r="D298" s="2" t="n"/>
       <c r="E298" s="2" t="n"/>
@@ -8561,36 +8151,36 @@
       <c r="S298" s="2" t="n"/>
       <c r="T298" s="2" t="n"/>
       <c r="U298" s="3" t="n">
-        <v>0.004193967653164665</v>
+        <v>0.004173263724857739</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>avveev</t>
+          <t>ЭтоМойНик</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>298</v>
       </c>
       <c r="C299" s="4" t="n">
-        <v>0.004149430177344318</v>
+        <v>0.004128630125865345</v>
       </c>
       <c r="U299" s="4" t="n">
-        <v>0.004149430177344318</v>
+        <v>0.004128630125865345</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Vikki</t>
         </is>
       </c>
       <c r="B300" s="2" t="n">
         <v>299</v>
       </c>
       <c r="C300" s="3" t="n">
-        <v>0.004105051481246257</v>
+        <v>0.004084156792004731</v>
       </c>
       <c r="D300" s="2" t="n"/>
       <c r="E300" s="2" t="n"/>
@@ -8610,36 +8200,36 @@
       <c r="S300" s="2" t="n"/>
       <c r="T300" s="2" t="n"/>
       <c r="U300" s="3" t="n">
-        <v>0.004105051481246257</v>
+        <v>0.004084156792004731</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Nell</t>
+          <t>FireSnail636</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>300</v>
       </c>
       <c r="C301" s="4" t="n">
-        <v>0.004060832135004334</v>
+        <v>0.004039844302906086</v>
       </c>
       <c r="U301" s="4" t="n">
-        <v>0.004060832135004334</v>
+        <v>0.004039844302906086</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Mar_u_shka</t>
+          <t>Эди не доехал</t>
         </is>
       </c>
       <c r="B302" s="2" t="n">
         <v>301</v>
       </c>
       <c r="C302" s="3" t="n">
-        <v>0.004016772714938464</v>
+        <v>0.003995693244534528</v>
       </c>
       <c r="D302" s="2" t="n"/>
       <c r="E302" s="2" t="n"/>
@@ -8659,36 +8249,36 @@
       <c r="S302" s="2" t="n"/>
       <c r="T302" s="2" t="n"/>
       <c r="U302" s="3" t="n">
-        <v>0.004016772714938464</v>
+        <v>0.003995693244534528</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Тихий Лис</t>
+          <t>Malinskaya</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>302</v>
       </c>
       <c r="C303" s="4" t="n">
-        <v>0.003972873803667317</v>
+        <v>0.003951704209306351</v>
       </c>
       <c r="U303" s="4" t="n">
-        <v>0.003972873803667317</v>
+        <v>0.003951704209306351</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>repe_kate</t>
+          <t>SPiRiT</t>
         </is>
       </c>
       <c r="B304" s="2" t="n">
         <v>303</v>
       </c>
       <c r="C304" s="3" t="n">
-        <v>0.003929135990223887</v>
+        <v>0.00390787779620827</v>
       </c>
       <c r="D304" s="2" t="n"/>
       <c r="E304" s="2" t="n"/>
@@ -8708,36 +8298,36 @@
       <c r="S304" s="2" t="n"/>
       <c r="T304" s="2" t="n"/>
       <c r="U304" s="3" t="n">
-        <v>0.003929135990223887</v>
+        <v>0.00390787779620827</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>ollyapgk</t>
         </is>
       </c>
       <c r="B305" t="n">
         <v>304</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>0.003885559870174073</v>
+        <v>0.00386421461091978</v>
       </c>
       <c r="U305" s="4" t="n">
-        <v>0.003885559870174073</v>
+        <v>0.00386421461091978</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Nikoshka</t>
+          <t>Vii</t>
         </is>
       </c>
       <c r="B306" s="2" t="n">
         <v>305</v>
       </c>
       <c r="C306" s="3" t="n">
-        <v>0.003842146045738329</v>
+        <v>0.003820715265938733</v>
       </c>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="2" t="n"/>
@@ -8757,36 +8347,36 @@
       <c r="S306" s="2" t="n"/>
       <c r="T306" s="2" t="n"/>
       <c r="U306" s="3" t="n">
-        <v>0.003842146045738329</v>
+        <v>0.003820715265938733</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>John Fisher</t>
+          <t>notefa</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>306</v>
       </c>
       <c r="C307" s="4" t="n">
-        <v>0.003798895125916523</v>
+        <v>0.003777380380710229</v>
       </c>
       <c r="U307" s="4" t="n">
-        <v>0.003798895125916523</v>
+        <v>0.003777380380710229</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Тома</t>
+          <t>Anastasia</t>
         </is>
       </c>
       <c r="B308" s="2" t="n">
         <v>307</v>
       </c>
       <c r="C308" s="3" t="n">
-        <v>0.003755807726616102</v>
+        <v>0.003734210581758956</v>
       </c>
       <c r="D308" s="2" t="n"/>
       <c r="E308" s="2" t="n"/>
@@ -8806,36 +8396,36 @@
       <c r="S308" s="2" t="n"/>
       <c r="T308" s="2" t="n"/>
       <c r="U308" s="3" t="n">
-        <v>0.003755807726616102</v>
+        <v>0.003734210581758956</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Nemo</t>
+          <t>ira_karpova</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>308</v>
       </c>
       <c r="C309" s="4" t="n">
-        <v>0.003712884470783665</v>
+        <v>0.003691206502825077</v>
       </c>
       <c r="U309" s="4" t="n">
-        <v>0.003712884470783665</v>
+        <v>0.003691206502825077</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Blitz</t>
+          <t>Хэнк Муди</t>
         </is>
       </c>
       <c r="B310" s="2" t="n">
         <v>309</v>
       </c>
       <c r="C310" s="3" t="n">
-        <v>0.003670125988540078</v>
+        <v>0.003648368785003802</v>
       </c>
       <c r="D310" s="2" t="n"/>
       <c r="E310" s="2" t="n"/>
@@ -8855,36 +8445,36 @@
       <c r="S310" s="2" t="n"/>
       <c r="T310" s="2" t="n"/>
       <c r="U310" s="3" t="n">
-        <v>0.003670125988540078</v>
+        <v>0.003648368785003802</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Nastya123</t>
+          <t>vadim123</t>
         </is>
       </c>
       <c r="B311" t="n">
         <v>310</v>
       </c>
       <c r="C311" s="4" t="n">
-        <v>0.003627532917319251</v>
+        <v>0.003605698076888765</v>
       </c>
       <c r="U311" s="4" t="n">
-        <v>0.003627532917319251</v>
+        <v>0.003605698076888765</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Suruchik</t>
+          <t>kciNik</t>
         </is>
       </c>
       <c r="B312" s="2" t="n">
         <v>311</v>
       </c>
       <c r="C312" s="3" t="n">
-        <v>0.003585105902010695</v>
+        <v>0.00356319503471935</v>
       </c>
       <c r="D312" s="2" t="n"/>
       <c r="E312" s="2" t="n"/>
@@ -8904,36 +8494,36 @@
       <c r="S312" s="2" t="n"/>
       <c r="T312" s="2" t="n"/>
       <c r="U312" s="3" t="n">
-        <v>0.003585105902010695</v>
+        <v>0.00356319503471935</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Аня</t>
+          <t>витя доезд</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>312</v>
       </c>
       <c r="C313" s="4" t="n">
-        <v>0.003542845595106001</v>
+        <v>0.003520860322532098</v>
       </c>
       <c r="U313" s="4" t="n">
-        <v>0.003542845595106001</v>
+        <v>0.003520860322532098</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Tanyashl</t>
+          <t>damashniy</t>
         </is>
       </c>
       <c r="B314" s="2" t="n">
         <v>313</v>
       </c>
       <c r="C314" s="3" t="n">
-        <v>0.003500752656849395</v>
+        <v>0.003478694612316344</v>
       </c>
       <c r="D314" s="2" t="n"/>
       <c r="E314" s="2" t="n"/>
@@ -8953,36 +8543,36 @@
       <c r="S314" s="2" t="n"/>
       <c r="T314" s="2" t="n"/>
       <c r="U314" s="3" t="n">
-        <v>0.003500752656849395</v>
+        <v>0.003478694612316344</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Darksoul</t>
+          <t>chinaonetown</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>314</v>
       </c>
       <c r="C315" s="4" t="n">
-        <v>0.003458827755392474</v>
+        <v>0.003436698584174246</v>
       </c>
       <c r="U315" s="4" t="n">
-        <v>0.003458827755392474</v>
+        <v>0.003436698584174246</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>klavson</t>
+          <t>Darksoul</t>
         </is>
       </c>
       <c r="B316" s="2" t="n">
         <v>315</v>
       </c>
       <c r="C316" s="3" t="n">
-        <v>0.003417071566953326</v>
+        <v>0.003394872926485347</v>
       </c>
       <c r="D316" s="2" t="n"/>
       <c r="E316" s="2" t="n"/>
@@ -9002,36 +8592,36 @@
       <c r="S316" s="2" t="n"/>
       <c r="T316" s="2" t="n"/>
       <c r="U316" s="3" t="n">
-        <v>0.003417071566953326</v>
+        <v>0.003394872926485347</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CozImDrunk</t>
+          <t>Ivanjmj</t>
         </is>
       </c>
       <c r="B317" t="n">
         <v>316</v>
       </c>
       <c r="C317" s="4" t="n">
-        <v>0.003375484775980151</v>
+        <v>0.003353218336075858</v>
       </c>
       <c r="U317" s="4" t="n">
-        <v>0.003375484775980151</v>
+        <v>0.003353218336075858</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>mflameee</t>
+          <t>Halo</t>
         </is>
       </c>
       <c r="B318" s="2" t="n">
         <v>317</v>
       </c>
       <c r="C318" s="3" t="n">
-        <v>0.003334068075319581</v>
+        <v>0.003311735518392824</v>
       </c>
       <c r="D318" s="2" t="n"/>
       <c r="E318" s="2" t="n"/>
@@ -9051,36 +8641,36 @@
       <c r="S318" s="2" t="n"/>
       <c r="T318" s="2" t="n"/>
       <c r="U318" s="3" t="n">
-        <v>0.003334068075319581</v>
+        <v>0.003311735518392824</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Svetab</t>
+          <t>fe1k</t>
         </is>
       </c>
       <c r="B319" t="n">
         <v>318</v>
       </c>
       <c r="C319" s="4" t="n">
-        <v>0.003292822166389844</v>
+        <v>0.003270425187683358</v>
       </c>
       <c r="U319" s="4" t="n">
-        <v>0.003292822166389844</v>
+        <v>0.003270425187683358</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>avomerfe</t>
+          <t>Irina</t>
         </is>
       </c>
       <c r="B320" s="2" t="n">
         <v>319</v>
       </c>
       <c r="C320" s="3" t="n">
-        <v>0.003251747759358985</v>
+        <v>0.003229288067179145</v>
       </c>
       <c r="D320" s="2" t="n"/>
       <c r="E320" s="2" t="n"/>
@@ -9100,36 +8690,36 @@
       <c r="S320" s="2" t="n"/>
       <c r="T320" s="2" t="n"/>
       <c r="U320" s="3" t="n">
-        <v>0.003251747759358985</v>
+        <v>0.003229288067179145</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>juliezh</t>
+          <t>Тихий Лис</t>
         </is>
       </c>
       <c r="B321" t="n">
         <v>320</v>
       </c>
       <c r="C321" s="4" t="n">
-        <v>0.003210845573328302</v>
+        <v>0.003188324889286393</v>
       </c>
       <c r="U321" s="4" t="n">
-        <v>0.003210845573328302</v>
+        <v>0.003188324889286393</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Marina7</t>
+          <t>Margaery_ZHU</t>
         </is>
       </c>
       <c r="B322" s="2" t="n">
         <v>321</v>
       </c>
       <c r="C322" s="3" t="n">
-        <v>0.003170116336521226</v>
+        <v>0.003147536395781465</v>
       </c>
       <c r="D322" s="2" t="n"/>
       <c r="E322" s="2" t="n"/>
@@ -9149,36 +8739,36 @@
       <c r="S322" s="2" t="n"/>
       <c r="T322" s="2" t="n"/>
       <c r="U322" s="3" t="n">
-        <v>0.003170116336521226</v>
+        <v>0.003147536395781465</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Алина П.</t>
         </is>
       </c>
       <c r="B323" t="n">
         <v>322</v>
       </c>
       <c r="C323" s="4" t="n">
-        <v>0.003129560786477828</v>
+        <v>0.003106923338012397</v>
       </c>
       <c r="U323" s="4" t="n">
-        <v>0.003129560786477828</v>
+        <v>0.003106923338012397</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>ollyapgk</t>
+          <t>avdoda</t>
         </is>
       </c>
       <c r="B324" s="2" t="n">
         <v>323</v>
       </c>
       <c r="C324" s="3" t="n">
-        <v>0.003089179670255192</v>
+        <v>0.003066486477106545</v>
       </c>
       <c r="D324" s="2" t="n"/>
       <c r="E324" s="2" t="n"/>
@@ -9198,36 +8788,36 @@
       <c r="S324" s="2" t="n"/>
       <c r="T324" s="2" t="n"/>
       <c r="U324" s="3" t="n">
-        <v>0.003089179670255192</v>
+        <v>0.003066486477106545</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Tim19</t>
+          <t>Ksu666</t>
         </is>
       </c>
       <c r="B325" t="n">
         <v>324</v>
       </c>
       <c r="C325" s="4" t="n">
-        <v>0.003048973744633862</v>
+        <v>0.003026226584184573</v>
       </c>
       <c r="U325" s="4" t="n">
-        <v>0.003048973744633862</v>
+        <v>0.003026226584184573</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>notefa</t>
+          <t>FizMatXimik</t>
         </is>
       </c>
       <c r="B326" s="2" t="n">
         <v>325</v>
       </c>
       <c r="C326" s="3" t="n">
-        <v>0.003008943776330632</v>
+        <v>0.002986144440581083</v>
       </c>
       <c r="D326" s="2" t="n"/>
       <c r="E326" s="2" t="n"/>
@@ -9247,36 +8837,36 @@
       <c r="S326" s="2" t="n"/>
       <c r="T326" s="2" t="n"/>
       <c r="U326" s="3" t="n">
-        <v>0.003008943776330632</v>
+        <v>0.002986144440581083</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FizMatXimik</t>
+          <t>Пётр 1</t>
         </is>
       </c>
       <c r="B327" t="n">
         <v>326</v>
       </c>
       <c r="C327" s="4" t="n">
-        <v>0.002969090542217889</v>
+        <v>0.002946240838072094</v>
       </c>
       <c r="U327" s="4" t="n">
-        <v>0.002969090542217889</v>
+        <v>0.002946240838072094</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>katerina_boc</t>
+          <t>mrsMarivanna</t>
         </is>
       </c>
       <c r="B328" s="2" t="n">
         <v>327</v>
       </c>
       <c r="C328" s="3" t="n">
-        <v>0.002929414829549816</v>
+        <v>0.002906516579109713</v>
       </c>
       <c r="D328" s="2" t="n"/>
       <c r="E328" s="2" t="n"/>
@@ -9296,36 +8886,36 @@
       <c r="S328" s="2" t="n"/>
       <c r="T328" s="2" t="n"/>
       <c r="U328" s="3" t="n">
-        <v>0.002929414829549816</v>
+        <v>0.002906516579109713</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Алина П.</t>
+          <t>Aronio</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>328</v>
       </c>
       <c r="C329" s="4" t="n">
-        <v>0.002889917436195706</v>
+        <v>0.002866972477064221</v>
       </c>
       <c r="U329" s="4" t="n">
-        <v>0.002889917436195706</v>
+        <v>0.002866972477064221</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Руслан Ж.</t>
+          <t>onedrakeo</t>
         </is>
       </c>
       <c r="B330" s="2" t="n">
         <v>329</v>
       </c>
       <c r="C330" s="3" t="n">
-        <v>0.002850599170880675</v>
+        <v>0.002827609356473939</v>
       </c>
       <c r="D330" s="2" t="n"/>
       <c r="E330" s="2" t="n"/>
@@ -9345,36 +8935,36 @@
       <c r="S330" s="2" t="n"/>
       <c r="T330" s="2" t="n"/>
       <c r="U330" s="3" t="n">
-        <v>0.002850599170880675</v>
+        <v>0.002827609356473939</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Luter</t>
+          <t>Полинат</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>330</v>
       </c>
       <c r="C331" s="4" t="n">
-        <v>0.002811460853434099</v>
+        <v>0.002788428053303166</v>
       </c>
       <c r="U331" s="4" t="n">
-        <v>0.002811460853434099</v>
+        <v>0.002788428053303166</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Настя дай ребай блат</t>
+          <t>Руслан Ж.</t>
         </is>
       </c>
       <c r="B332" s="2" t="n">
         <v>331</v>
       </c>
       <c r="C332" s="3" t="n">
-        <v>0.002772503315046079</v>
+        <v>0.00274942941520854</v>
       </c>
       <c r="D332" s="2" t="n"/>
       <c r="E332" s="2" t="n"/>
@@ -9394,36 +8984,36 @@
       <c r="S332" s="2" t="n"/>
       <c r="T332" s="2" t="n"/>
       <c r="U332" s="3" t="n">
-        <v>0.002772503315046079</v>
+        <v>0.00274942941520854</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>chilly</t>
+          <t>Аня</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>332</v>
       </c>
       <c r="C333" s="4" t="n">
-        <v>0.002733727398532274</v>
+        <v>0.002710614301814154</v>
       </c>
       <c r="U333" s="4" t="n">
-        <v>0.002733727398532274</v>
+        <v>0.002710614301814154</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Тома</t>
         </is>
       </c>
       <c r="B334" s="2" t="n">
         <v>333</v>
       </c>
       <c r="C334" s="3" t="n">
-        <v>0.002695133958607461</v>
+        <v>0.00267198358499586</v>
       </c>
       <c r="D334" s="2" t="n"/>
       <c r="E334" s="2" t="n"/>
@@ -9443,36 +9033,36 @@
       <c r="S334" s="2" t="n"/>
       <c r="T334" s="2" t="n"/>
       <c r="U334" s="3" t="n">
-        <v>0.002695133958607461</v>
+        <v>0.00267198358499586</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Степан</t>
+          <t>Котяра</t>
         </is>
       </c>
       <c r="B335" t="n">
         <v>334</v>
       </c>
       <c r="C335" s="4" t="n">
-        <v>0.002656723862168195</v>
+        <v>0.002633538149175074</v>
       </c>
       <c r="U335" s="4" t="n">
-        <v>0.002656723862168195</v>
+        <v>0.002633538149175074</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>okiyumi</t>
+          <t>cloudromeo</t>
         </is>
       </c>
       <c r="B336" s="2" t="n">
         <v>335</v>
       </c>
       <c r="C336" s="3" t="n">
-        <v>0.002618497988584956</v>
+        <v>0.002595278891622576</v>
       </c>
       <c r="D336" s="2" t="n"/>
       <c r="E336" s="2" t="n"/>
@@ -9492,36 +9082,36 @@
       <c r="S336" s="2" t="n"/>
       <c r="T336" s="2" t="n"/>
       <c r="U336" s="3" t="n">
-        <v>0.002618497988584956</v>
+        <v>0.002595278891622576</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ywmoxd</t>
+          <t>Палёвка</t>
         </is>
       </c>
       <c r="B337" t="n">
         <v>336</v>
       </c>
       <c r="C337" s="4" t="n">
-        <v>0.002580457230004205</v>
+        <v>0.002557206722772695</v>
       </c>
       <c r="U337" s="4" t="n">
-        <v>0.002580457230004205</v>
+        <v>0.002557206722772695</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>damashniy</t>
+          <t>Степан</t>
         </is>
       </c>
       <c r="B338" s="2" t="n">
         <v>337</v>
       </c>
       <c r="C338" s="3" t="n">
-        <v>0.002542602491660768</v>
+        <v>0.002519322566548354</v>
       </c>
       <c r="D338" s="2" t="n"/>
       <c r="E338" s="2" t="n"/>
@@ -9541,36 +9131,36 @@
       <c r="S338" s="2" t="n"/>
       <c r="T338" s="2" t="n"/>
       <c r="U338" s="3" t="n">
-        <v>0.002542602491660768</v>
+        <v>0.002519322566548354</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>pavel</t>
+          <t>CozImDrunk</t>
         </is>
       </c>
       <c r="B339" t="n">
         <v>338</v>
       </c>
       <c r="C339" s="4" t="n">
-        <v>0.002504934692201038</v>
+        <v>0.00248162736069747</v>
       </c>
       <c r="U339" s="4" t="n">
-        <v>0.002504934692201038</v>
+        <v>0.00248162736069747</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>6igfi$Hf4n</t>
+          <t>JuZa</t>
         </is>
       </c>
       <c r="B340" s="2" t="n">
         <v>339</v>
       </c>
       <c r="C340" s="3" t="n">
-        <v>0.002467454764017444</v>
+        <v>0.002444122057141219</v>
       </c>
       <c r="D340" s="2" t="n"/>
       <c r="E340" s="2" t="n"/>
@@ -9590,36 +9180,36 @@
       <c r="S340" s="2" t="n"/>
       <c r="T340" s="2" t="n"/>
       <c r="U340" s="3" t="n">
-        <v>0.002467454764017444</v>
+        <v>0.002444122057141219</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>twewefe</t>
+          <t>Suruchik</t>
         </is>
       </c>
       <c r="B341" t="n">
         <v>340</v>
       </c>
       <c r="C341" s="4" t="n">
-        <v>0.002430163653594733</v>
+        <v>0.002406807622334701</v>
       </c>
       <c r="U341" s="4" t="n">
-        <v>0.002430163653594733</v>
+        <v>0.002406807622334701</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>SPiRiT</t>
+          <t>Комарик</t>
         </is>
       </c>
       <c r="B342" s="2" t="n">
         <v>341</v>
       </c>
       <c r="C342" s="3" t="n">
-        <v>0.00239306232186857</v>
+        <v>0.002369685037640595</v>
       </c>
       <c r="D342" s="2" t="n"/>
       <c r="E342" s="2" t="n"/>
@@ -9639,36 +9229,36 @@
       <c r="S342" s="2" t="n"/>
       <c r="T342" s="2" t="n"/>
       <c r="U342" s="3" t="n">
-        <v>0.00239306232186857</v>
+        <v>0.002369685037640595</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>stil9ger</t>
+          <t>Kiselka</t>
         </is>
       </c>
       <c r="B343" t="n">
         <v>342</v>
       </c>
       <c r="C343" s="4" t="n">
-        <v>0.002356151744597061</v>
+        <v>0.002332755299716394</v>
       </c>
       <c r="U343" s="4" t="n">
-        <v>0.002356151744597061</v>
+        <v>0.002332755299716394</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Loosars</t>
+          <t>lanz8</t>
         </is>
       </c>
       <c r="B344" s="2" t="n">
         <v>343</v>
       </c>
       <c r="C344" s="3" t="n">
-        <v>0.002319432912745781</v>
+        <v>0.002296019420915882</v>
       </c>
       <c r="D344" s="2" t="n"/>
       <c r="E344" s="2" t="n"/>
@@ -9688,36 +9278,36 @@
       <c r="S344" s="2" t="n"/>
       <c r="T344" s="2" t="n"/>
       <c r="U344" s="3" t="n">
-        <v>0.002319432912745781</v>
+        <v>0.002296019420915882</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Nika</t>
+          <t>Blitz</t>
         </is>
       </c>
       <c r="B345" t="n">
         <v>344</v>
       </c>
       <c r="C345" s="4" t="n">
-        <v>0.002282906832886952</v>
+        <v>0.00225947842970551</v>
       </c>
       <c r="U345" s="4" t="n">
-        <v>0.002282906832886952</v>
+        <v>0.00225947842970551</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>igor forehand</t>
+          <t>mrCelviano</t>
         </is>
       </c>
       <c r="B346" s="2" t="n">
         <v>345</v>
       </c>
       <c r="C346" s="3" t="n">
-        <v>0.002246574527613444</v>
+        <v>0.002223133371096409</v>
       </c>
       <c r="D346" s="2" t="n"/>
       <c r="E346" s="2" t="n"/>
@@ -9737,36 +9327,36 @@
       <c r="S346" s="2" t="n"/>
       <c r="T346" s="2" t="n"/>
       <c r="U346" s="3" t="n">
-        <v>0.002246574527613444</v>
+        <v>0.002223133371096409</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Dreemur</t>
+          <t>Borsalino</t>
         </is>
       </c>
       <c r="B347" t="n">
         <v>346</v>
       </c>
       <c r="C347" s="4" t="n">
-        <v>0.002210437035968318</v>
+        <v>0.002186985307092792</v>
       </c>
       <c r="U347" s="4" t="n">
-        <v>0.002210437035968318</v>
+        <v>0.002186985307092792</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>lifechampagne</t>
+          <t>ywmoxd</t>
         </is>
       </c>
       <c r="B348" s="2" t="n">
         <v>347</v>
       </c>
       <c r="C348" s="3" t="n">
-        <v>0.002174495413890673</v>
+        <v>0.002151035317157559</v>
       </c>
       <c r="D348" s="2" t="n"/>
       <c r="E348" s="2" t="n"/>
@@ -9786,36 +9376,36 @@
       <c r="S348" s="2" t="n"/>
       <c r="T348" s="2" t="n"/>
       <c r="U348" s="3" t="n">
-        <v>0.002174495413890673</v>
+        <v>0.002151035317157559</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Fara</t>
+          <t>Ташкент</t>
         </is>
       </c>
       <c r="B349" t="n">
         <v>348</v>
       </c>
       <c r="C349" s="4" t="n">
-        <v>0.002138750734678586</v>
+        <v>0.002115284498695961</v>
       </c>
       <c r="U349" s="4" t="n">
-        <v>0.002138750734678586</v>
+        <v>0.002115284498695961</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>LPZ18</t>
+          <t>millypoppins</t>
         </is>
       </c>
       <c r="B350" s="2" t="n">
         <v>349</v>
       </c>
       <c r="C350" s="3" t="n">
-        <v>0.002103204089470016</v>
+        <v>0.002079733967558229</v>
       </c>
       <c r="D350" s="2" t="n"/>
       <c r="E350" s="2" t="n"/>
@@ -9835,36 +9425,36 @@
       <c r="S350" s="2" t="n"/>
       <c r="T350" s="2" t="n"/>
       <c r="U350" s="3" t="n">
-        <v>0.002103204089470016</v>
+        <v>0.002079733967558229</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>FireSnail636</t>
+          <t>Yandi</t>
         </is>
       </c>
       <c r="B351" t="n">
         <v>350</v>
       </c>
       <c r="C351" s="4" t="n">
-        <v>0.002067856587742562</v>
+        <v>0.002044384858562144</v>
       </c>
       <c r="U351" s="4" t="n">
-        <v>0.002067856587742562</v>
+        <v>0.002044384858562144</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>frida_hk</t>
+          <t>Mitzy</t>
         </is>
       </c>
       <c r="B352" s="2" t="n">
         <v>351</v>
       </c>
       <c r="C352" s="3" t="n">
-        <v>0.002032709357833055</v>
+        <v>0.002009238326036576</v>
       </c>
       <c r="D352" s="2" t="n"/>
       <c r="E352" s="2" t="n"/>
@@ -9884,36 +9474,36 @@
       <c r="S352" s="2" t="n"/>
       <c r="T352" s="2" t="n"/>
       <c r="U352" s="3" t="n">
-        <v>0.002032709357833055</v>
+        <v>0.002009238326036576</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Артанис</t>
+          <t>willy &lt;/3</t>
         </is>
       </c>
       <c r="B353" t="n">
         <v>352</v>
       </c>
       <c r="C353" s="4" t="n">
-        <v>0.001997763547477977</v>
+        <v>0.00197429554438707</v>
       </c>
       <c r="U353" s="4" t="n">
-        <v>0.001997763547477977</v>
+        <v>0.00197429554438707</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Volodnika</t>
+          <t>Настя дай ребай блат</t>
         </is>
       </c>
       <c r="B354" s="2" t="n">
         <v>353</v>
       </c>
       <c r="C354" s="3" t="n">
-        <v>0.001963020324375833</v>
+        <v>0.001939557708684666</v>
       </c>
       <c r="D354" s="2" t="n"/>
       <c r="E354" s="2" t="n"/>
@@ -9933,36 +9523,36 @@
       <c r="S354" s="2" t="n"/>
       <c r="T354" s="2" t="n"/>
       <c r="U354" s="3" t="n">
-        <v>0.001963020324375833</v>
+        <v>0.001939557708684666</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Virt Ceo</t>
+          <t>Кубус</t>
         </is>
       </c>
       <c r="B355" t="n">
         <v>354</v>
       </c>
       <c r="C355" s="4" t="n">
-        <v>0.001928480876772603</v>
+        <v>0.001905026035279184</v>
       </c>
       <c r="U355" s="4" t="n">
-        <v>0.001928480876772603</v>
+        <v>0.001905026035279184</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Schwepp1S</t>
+          <t>moz1lo_jr</t>
         </is>
       </c>
       <c r="B356" s="2" t="n">
         <v>355</v>
       </c>
       <c r="C356" s="3" t="n">
-        <v>0.001894146414071521</v>
+        <v>0.001870701762438286</v>
       </c>
       <c r="D356" s="2" t="n"/>
       <c r="E356" s="2" t="n"/>
@@ -9982,36 +9572,36 @@
       <c r="S356" s="2" t="n"/>
       <c r="T356" s="2" t="n"/>
       <c r="U356" s="3" t="n">
-        <v>0.001894146414071521</v>
+        <v>0.001870701762438286</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>edimerfi</t>
+          <t>Ilia M</t>
         </is>
       </c>
       <c r="B357" t="n">
         <v>356</v>
       </c>
       <c r="C357" s="4" t="n">
-        <v>0.001860018167468492</v>
+        <v>0.00183658615101375</v>
       </c>
       <c r="U357" s="4" t="n">
-        <v>0.001860018167468492</v>
+        <v>0.00183658615101375</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>kornaakov</t>
+          <t>Manhattan</t>
         </is>
       </c>
       <c r="B358" s="2" t="n">
         <v>357</v>
       </c>
       <c r="C358" s="3" t="n">
-        <v>0.001826097390614556</v>
+        <v>0.001802680485136434</v>
       </c>
       <c r="D358" s="2" t="n"/>
       <c r="E358" s="2" t="n"/>
@@ -10031,36 +9621,36 @@
       <c r="S358" s="2" t="n"/>
       <c r="T358" s="2" t="n"/>
       <c r="U358" s="3" t="n">
-        <v>0.001826097390614556</v>
+        <v>0.001802680485136434</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>CICADA</t>
+          <t>xiolloix</t>
         </is>
       </c>
       <c r="B359" t="n">
         <v>358</v>
       </c>
       <c r="C359" s="4" t="n">
-        <v>0.00179238536030689</v>
+        <v>0.001768986072941568</v>
       </c>
       <c r="U359" s="4" t="n">
-        <v>0.00179238536030689</v>
+        <v>0.001768986072941568</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>averagemorningstarenjoyer</t>
+          <t>Alkyds</t>
         </is>
       </c>
       <c r="B360" s="2" t="n">
         <v>359</v>
       </c>
       <c r="C360" s="3" t="n">
-        <v>0.001758883377209951</v>
+        <v>0.001735504247326074</v>
       </c>
       <c r="D360" s="2" t="n"/>
       <c r="E360" s="2" t="n"/>
@@ -10080,36 +9670,36 @@
       <c r="S360" s="2" t="n"/>
       <c r="T360" s="2" t="n"/>
       <c r="U360" s="3" t="n">
-        <v>0.001758883377209951</v>
+        <v>0.001735504247326074</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Natasha_fsb</t>
+          <t>Cation</t>
         </is>
       </c>
       <c r="B361" t="n">
         <v>360</v>
       </c>
       <c r="C361" s="4" t="n">
-        <v>0.001725592766608473</v>
+        <v>0.001702236366739764</v>
       </c>
       <c r="U361" s="4" t="n">
-        <v>0.001725592766608473</v>
+        <v>0.001702236366739764</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>t1m</t>
+          <t>Kichatov</t>
         </is>
       </c>
       <c r="B362" s="2" t="n">
         <v>361</v>
       </c>
       <c r="C362" s="3" t="n">
-        <v>0.00169251487919415</v>
+        <v>0.001669183816012401</v>
       </c>
       <c r="D362" s="2" t="n"/>
       <c r="E362" s="2" t="n"/>
@@ -10129,36 +9719,36 @@
       <c r="S362" s="2" t="n"/>
       <c r="T362" s="2" t="n"/>
       <c r="U362" s="3" t="n">
-        <v>0.00169251487919415</v>
+        <v>0.001669183816012401</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>rus210385</t>
+          <t>JhonyCash</t>
         </is>
       </c>
       <c r="B363" t="n">
         <v>362</v>
       </c>
       <c r="C363" s="4" t="n">
-        <v>0.00165965109188797</v>
+        <v>0.001636348007218715</v>
       </c>
       <c r="U363" s="4" t="n">
-        <v>0.00165965109188797</v>
+        <v>0.001636348007218715</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>ira_karpova</t>
+          <t>Broski</t>
         </is>
       </c>
       <c r="B364" s="2" t="n">
         <v>363</v>
       </c>
       <c r="C364" s="3" t="n">
-        <v>0.001627002808700289</v>
+        <v>0.001603730380583669</v>
       </c>
       <c r="D364" s="2" t="n"/>
       <c r="E364" s="2" t="n"/>
@@ -10178,36 +9768,36 @@
       <c r="S364" s="2" t="n"/>
       <c r="T364" s="2" t="n"/>
       <c r="U364" s="3" t="n">
-        <v>0.001627002808700289</v>
+        <v>0.001603730380583669</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Kety</t>
+          <t>inteuis</t>
         </is>
       </c>
       <c r="B365" t="n">
         <v>364</v>
       </c>
       <c r="C365" s="4" t="n">
-        <v>0.001594571461630935</v>
+        <v>0.001571332405430404</v>
       </c>
       <c r="U365" s="4" t="n">
-        <v>0.001594571461630935</v>
+        <v>0.001571332405430404</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Марат</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="B366" s="2" t="n">
         <v>365</v>
       </c>
       <c r="C366" s="3" t="n">
-        <v>0.001562358511611728</v>
+        <v>0.001539155581173479</v>
       </c>
       <c r="D366" s="2" t="n"/>
       <c r="E366" s="2" t="n"/>
@@ -10227,36 +9817,36 @@
       <c r="S366" s="2" t="n"/>
       <c r="T366" s="2" t="n"/>
       <c r="U366" s="3" t="n">
-        <v>0.001562358511611728</v>
+        <v>0.001539155581173479</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>msbxmx</t>
+          <t>Nikolay</t>
         </is>
       </c>
       <c r="B367" t="n">
         <v>366</v>
       </c>
       <c r="C367" s="4" t="n">
-        <v>0.001530365449494059</v>
+        <v>0.001507201438360244</v>
       </c>
       <c r="U367" s="4" t="n">
-        <v>0.001530365449494059</v>
+        <v>0.001507201438360244</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>nsa</t>
+          <t>Donny</t>
         </is>
       </c>
       <c r="B368" s="2" t="n">
         <v>367</v>
       </c>
       <c r="C368" s="3" t="n">
-        <v>0.001498593797084307</v>
+        <v>0.001475471539763368</v>
       </c>
       <c r="D368" s="2" t="n"/>
       <c r="E368" s="2" t="n"/>
@@ -10276,36 +9866,36 @@
       <c r="S368" s="2" t="n"/>
       <c r="T368" s="2" t="n"/>
       <c r="U368" s="3" t="n">
-        <v>0.001498593797084307</v>
+        <v>0.001475471539763368</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>alinaadmv</t>
+          <t>deps</t>
         </is>
       </c>
       <c r="B369" t="n">
         <v>368</v>
       </c>
       <c r="C369" s="4" t="n">
-        <v>0.001467045108230133</v>
+        <v>0.001443967481527821</v>
       </c>
       <c r="U369" s="4" t="n">
-        <v>0.001467045108230133</v>
+        <v>0.001443967481527821</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>Павлуша</t>
+          <t>roman_1_2_3</t>
         </is>
       </c>
       <c r="B370" s="2" t="n">
         <v>369</v>
       </c>
       <c r="C370" s="3" t="n">
-        <v>0.001435720969960905</v>
+        <v>0.001412690894375822</v>
       </c>
       <c r="D370" s="2" t="n"/>
       <c r="E370" s="2" t="n"/>
@@ -10325,36 +9915,36 @@
       <c r="S370" s="2" t="n"/>
       <c r="T370" s="2" t="n"/>
       <c r="U370" s="3" t="n">
-        <v>0.001435720969960905</v>
+        <v>0.001412690894375822</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>nik_zverev</t>
         </is>
       </c>
       <c r="B371" t="n">
         <v>370</v>
       </c>
       <c r="C371" s="4" t="n">
-        <v>0.001404623003685776</v>
+        <v>0.001381643444873605</v>
       </c>
       <c r="U371" s="4" t="n">
-        <v>0.001404623003685776</v>
+        <v>0.001381643444873605</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>nevsskii</t>
+          <t>Михаил Ю</t>
         </is>
       </c>
       <c r="B372" s="2" t="n">
         <v>371</v>
       </c>
       <c r="C372" s="3" t="n">
-        <v>0.001373752866453204</v>
+        <v>0.001350826836764121</v>
       </c>
       <c r="D372" s="2" t="n"/>
       <c r="E372" s="2" t="n"/>
@@ -10374,36 +9964,36 @@
       <c r="S372" s="2" t="n"/>
       <c r="T372" s="2" t="n"/>
       <c r="U372" s="3" t="n">
-        <v>0.001373752866453204</v>
+        <v>0.001350826836764121</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>гофер</t>
+          <t>poysty</t>
         </is>
       </c>
       <c r="B373" t="n">
         <v>372</v>
       </c>
       <c r="C373" s="4" t="n">
-        <v>0.001343112252276049</v>
+        <v>0.00132024281237016</v>
       </c>
       <c r="U373" s="4" t="n">
-        <v>0.001343112252276049</v>
+        <v>0.00132024281237016</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>ksellym</t>
+          <t>skr_anton</t>
         </is>
       </c>
       <c r="B374" s="2" t="n">
         <v>373</v>
       </c>
       <c r="C374" s="3" t="n">
-        <v>0.001312702893526678</v>
+        <v>0.001289893154072757</v>
       </c>
       <c r="D374" s="2" t="n"/>
       <c r="E374" s="2" t="n"/>
@@ -10423,36 +10013,36 @@
       <c r="S374" s="2" t="n"/>
       <c r="T374" s="2" t="n"/>
       <c r="U374" s="3" t="n">
-        <v>0.001312702893526678</v>
+        <v>0.001289893154072757</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>SuD</t>
+          <t>@lidiasol07</t>
         </is>
       </c>
       <c r="B375" t="n">
         <v>374</v>
       </c>
       <c r="C375" s="4" t="n">
-        <v>0.001282526562406931</v>
+        <v>0.001259779685870144</v>
       </c>
       <c r="U375" s="4" t="n">
-        <v>0.001282526562406931</v>
+        <v>0.001259779685870144</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Aleksa</t>
         </is>
       </c>
       <c r="B376" s="2" t="n">
         <v>375</v>
       </c>
       <c r="C376" s="3" t="n">
-        <v>0.001252585072498172</v>
+        <v>0.001229904275022998</v>
       </c>
       <c r="D376" s="2" t="n"/>
       <c r="E376" s="2" t="n"/>
@@ -10472,36 +10062,36 @@
       <c r="S376" s="2" t="n"/>
       <c r="T376" s="2" t="n"/>
       <c r="U376" s="3" t="n">
-        <v>0.001252585072498172</v>
+        <v>0.001229904275022998</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>DanilaOdinokov</t>
+          <t>Sokrat_Ab</t>
         </is>
       </c>
       <c r="B377" t="n">
         <v>376</v>
       </c>
       <c r="C377" s="4" t="n">
-        <v>0.001222880280397132</v>
+        <v>0.001200268833792205</v>
       </c>
       <c r="U377" s="4" t="n">
-        <v>0.001222880280397132</v>
+        <v>0.001200268833792205</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Ksu666</t>
+          <t>Chumba656</t>
         </is>
       </c>
       <c r="B378" s="2" t="n">
         <v>377</v>
       </c>
       <c r="C378" s="3" t="n">
-        <v>0.00119341408744376</v>
+        <v>0.001170875321275956</v>
       </c>
       <c r="D378" s="2" t="n"/>
       <c r="E378" s="2" t="n"/>
@@ -10521,36 +10111,36 @@
       <c r="S378" s="2" t="n"/>
       <c r="T378" s="2" t="n"/>
       <c r="U378" s="3" t="n">
-        <v>0.00119341408744376</v>
+        <v>0.001170875321275956</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>cloudromeo</t>
+          <t>kirp4712</t>
         </is>
       </c>
       <c r="B379" t="n">
         <v>378</v>
       </c>
       <c r="C379" s="4" t="n">
-        <v>0.001164188441547818</v>
+        <v>0.001141725745353586</v>
       </c>
       <c r="U379" s="4" t="n">
-        <v>0.001164188441547818</v>
+        <v>0.001141725745353586</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>pеtr32</t>
+          <t>Danil</t>
         </is>
       </c>
       <c r="B380" s="2" t="n">
         <v>379</v>
       </c>
       <c r="C380" s="3" t="n">
-        <v>0.001135205339121625</v>
+        <v>0.001112822164744269</v>
       </c>
       <c r="D380" s="2" t="n"/>
       <c r="E380" s="2" t="n"/>
@@ -10570,36 +10160,36 @@
       <c r="S380" s="2" t="n"/>
       <c r="T380" s="2" t="n"/>
       <c r="U380" s="3" t="n">
-        <v>0.001135205339121625</v>
+        <v>0.001112822164744269</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Палёвка</t>
+          <t>dnaskila</t>
         </is>
       </c>
       <c r="B381" t="n">
         <v>380</v>
       </c>
       <c r="C381" s="4" t="n">
-        <v>0.001106466827126988</v>
+        <v>0.001084166691189442</v>
       </c>
       <c r="U381" s="4" t="n">
-        <v>0.001106466827126988</v>
+        <v>0.001084166691189442</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Sendre</t>
+          <t>Khizir.V</t>
         </is>
       </c>
       <c r="B382" s="2" t="n">
         <v>381</v>
       </c>
       <c r="C382" s="3" t="n">
-        <v>0.001077975005245173</v>
+        <v>0.001055761491768696</v>
       </c>
       <c r="D382" s="2" t="n"/>
       <c r="E382" s="2" t="n"/>
@@ -10619,36 +10209,36 @@
       <c r="S382" s="2" t="n"/>
       <c r="T382" s="2" t="n"/>
       <c r="U382" s="3" t="n">
-        <v>0.001077975005245173</v>
+        <v>0.001055761491768696</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>millypoppins</t>
+          <t>като</t>
         </is>
       </c>
       <c r="B383" t="n">
         <v>382</v>
       </c>
       <c r="C383" s="4" t="n">
-        <v>0.001049732028179556</v>
+        <v>0.001027608791359802</v>
       </c>
       <c r="U383" s="4" t="n">
-        <v>0.001049732028179556</v>
+        <v>0.001027608791359802</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>arteminil</t>
+          <t>Cucumberrr</t>
         </is>
       </c>
       <c r="B384" s="2" t="n">
         <v>383</v>
       </c>
       <c r="C384" s="3" t="n">
-        <v>0.001021740108101613</v>
+        <v>0.0009997108752546262</v>
       </c>
       <c r="D384" s="2" t="n"/>
       <c r="E384" s="2" t="n"/>
@@ -10668,36 +10258,36 @@
       <c r="S384" s="2" t="n"/>
       <c r="T384" s="2" t="n"/>
       <c r="U384" s="3" t="n">
-        <v>0.001021740108101613</v>
+        <v>0.0009997108752546262</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Гонзалес</t>
+          <t>WHATSWRONGib</t>
         </is>
       </c>
       <c r="B385" t="n">
         <v>384</v>
       </c>
       <c r="C385" s="4" t="n">
-        <v>0.000994001517251885</v>
+        <v>0.000972070091943861</v>
       </c>
       <c r="U385" s="4" t="n">
-        <v>0.000994001517251885</v>
+        <v>0.000972070091943861</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>frlvmaria</t>
+          <t>set</t>
         </is>
       </c>
       <c r="B386" s="2" t="n">
         <v>385</v>
       </c>
       <c r="C386" s="3" t="n">
-        <v>0.0009665185907088152</v>
+        <v>0.0009446888560848571</v>
       </c>
       <c r="D386" s="2" t="n"/>
       <c r="E386" s="2" t="n"/>
@@ -10717,36 +10307,36 @@
       <c r="S386" s="2" t="n"/>
       <c r="T386" s="2" t="n"/>
       <c r="U386" s="3" t="n">
-        <v>0.0009665185907088152</v>
+        <v>0.0009446888560848571</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>imt360_ATDK</t>
+          <t>Riteral</t>
         </is>
       </c>
       <c r="B387" t="n">
         <v>386</v>
       </c>
       <c r="C387" s="4" t="n">
-        <v>0.0009392937293396224</v>
+        <v>0.0009175696516683155</v>
       </c>
       <c r="U387" s="4" t="n">
-        <v>0.0009392937293396224</v>
+        <v>0.0009175696516683155</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>etovadikk</t>
+          <t>M1kayt</t>
         </is>
       </c>
       <c r="B388" s="2" t="n">
         <v>387</v>
       </c>
       <c r="C388" s="3" t="n">
-        <v>0.0009123294029489138</v>
+        <v>0.000890715035401319</v>
       </c>
       <c r="D388" s="2" t="n"/>
       <c r="E388" s="2" t="n"/>
@@ -10766,36 +10356,36 @@
       <c r="S388" s="2" t="n"/>
       <c r="T388" s="2" t="n"/>
       <c r="U388" s="3" t="n">
-        <v>0.0009123294029489138</v>
+        <v>0.000890715035401319</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Irina</t>
+          <t>Акоп</t>
         </is>
       </c>
       <c r="B389" t="n">
         <v>388</v>
       </c>
       <c r="C389" s="4" t="n">
-        <v>0.0008856281536423956</v>
+        <v>0.0008641276403260852</v>
       </c>
       <c r="U389" s="4" t="n">
-        <v>0.0008856281536423956</v>
+        <v>0.0008641276403260852</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>DmitriiM0</t>
+          <t>Zubrilliant</t>
         </is>
       </c>
       <c r="B390" s="2" t="n">
         <v>389</v>
       </c>
       <c r="C390" s="3" t="n">
-        <v>0.0008591925994249558</v>
+        <v>0.0008378101796959819</v>
       </c>
       <c r="D390" s="2" t="n"/>
       <c r="E390" s="2" t="n"/>
@@ -10815,36 +10405,36 @@
       <c r="S390" s="2" t="n"/>
       <c r="T390" s="2" t="n"/>
       <c r="U390" s="3" t="n">
-        <v>0.0008591925994249558</v>
+        <v>0.0008378101796959819</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>lanz8</t>
+          <t>Asakura_Russell</t>
         </is>
       </c>
       <c r="B391" t="n">
         <v>390</v>
       </c>
       <c r="C391" s="4" t="n">
-        <v>0.000833025438054548</v>
+        <v>0.0008117654511328151</v>
       </c>
       <c r="U391" s="4" t="n">
-        <v>0.000833025438054548</v>
+        <v>0.0008117654511328151</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>Malinskaya</t>
+          <t>glava9</t>
         </is>
       </c>
       <c r="B392" s="2" t="n">
         <v>391</v>
       </c>
       <c r="C392" s="3" t="n">
-        <v>0.0008071294511757342</v>
+        <v>0.0007859963410921902</v>
       </c>
       <c r="D392" s="2" t="n"/>
       <c r="E392" s="2" t="n"/>
@@ -10864,36 +10454,36 @@
       <c r="S392" s="2" t="n"/>
       <c r="T392" s="2" t="n"/>
       <c r="U392" s="3" t="n">
-        <v>0.0008071294511757342</v>
+        <v>0.0007859963410921902</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Никитос</t>
+          <t>ЧЕРЕМША</t>
         </is>
       </c>
       <c r="B393" t="n">
         <v>392</v>
       </c>
       <c r="C393" s="4" t="n">
-        <v>0.000781507508759545</v>
+        <v>0.0007605058296669332</v>
       </c>
       <c r="U393" s="4" t="n">
-        <v>0.000781507508759545</v>
+        <v>0.0007605058296669332</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>Mitzy</t>
+          <t>Volodnika</t>
         </is>
       </c>
       <c r="B394" s="2" t="n">
         <v>393</v>
       </c>
       <c r="C394" s="3" t="n">
-        <v>0.0007561625738794693</v>
+        <v>0.0007352969957622134</v>
       </c>
       <c r="D394" s="2" t="n"/>
       <c r="E394" s="2" t="n"/>
@@ -10913,36 +10503,36 @@
       <c r="S394" s="2" t="n"/>
       <c r="T394" s="2" t="n"/>
       <c r="U394" s="3" t="n">
-        <v>0.0007561625738794693</v>
+        <v>0.0007352969957622134</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>M1kayt</t>
+          <t>Лудоман</t>
         </is>
       </c>
       <c r="B395" t="n">
         <v>394</v>
       </c>
       <c r="C395" s="4" t="n">
-        <v>0.0007310977078570205</v>
+        <v>0.0007103730226801852</v>
       </c>
       <c r="U395" s="4" t="n">
-        <v>0.0007310977078570205</v>
+        <v>0.0007103730226801852</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>ns_sh</t>
+          <t>NEVERLUCKY</t>
         </is>
       </c>
       <c r="B396" s="2" t="n">
         <v>395</v>
       </c>
       <c r="C396" s="3" t="n">
-        <v>0.0007063160758144854</v>
+        <v>0.000685737204156785</v>
       </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="2" t="n"/>
@@ -10962,36 +10552,36 @@
       <c r="S396" s="2" t="n"/>
       <c r="T396" s="2" t="n"/>
       <c r="U396" s="3" t="n">
-        <v>0.0007063160758144854</v>
+        <v>0.000685737204156785</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Khizir.V</t>
+          <t>Me1man77</t>
         </is>
       </c>
       <c r="B397" t="n">
         <v>396</v>
       </c>
       <c r="C397" s="4" t="n">
-        <v>0.0006818209526772433</v>
+        <v>0.000661392950898869</v>
       </c>
       <c r="U397" s="4" t="n">
-        <v>0.0006818209526772433</v>
+        <v>0.000661392950898869</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>moz1lo_jr</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="B398" s="2" t="n">
         <v>397</v>
       </c>
       <c r="C398" s="3" t="n">
-        <v>0.000657615729673573</v>
+        <v>0.0006373437976763138</v>
       </c>
       <c r="D398" s="2" t="n"/>
       <c r="E398" s="2" t="n"/>
@@ -11011,36 +10601,36 @@
       <c r="S398" s="2" t="n"/>
       <c r="T398" s="2" t="n"/>
       <c r="U398" s="3" t="n">
-        <v>0.000657615729673573</v>
+        <v>0.0006373437976763138</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>poysty</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="B399" t="n">
         <v>398</v>
       </c>
       <c r="C399" s="4" t="n">
-        <v>0.0006337039213862477</v>
+        <v>0.000613593411031161</v>
       </c>
       <c r="U399" s="4" t="n">
-        <v>0.0006337039213862477</v>
+        <v>0.000613593411031161</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Danil</t>
+          <t>whitecurly_rr</t>
         </is>
       </c>
       <c r="B400" s="2" t="n">
         <v>399</v>
       </c>
       <c r="C400" s="3" t="n">
-        <v>0.0006100891734176534</v>
+        <v>0.0005901455976746036</v>
       </c>
       <c r="D400" s="2" t="n"/>
       <c r="E400" s="2" t="n"/>
@@ -11060,36 +10650,36 @@
       <c r="S400" s="2" t="n"/>
       <c r="T400" s="2" t="n"/>
       <c r="U400" s="3" t="n">
-        <v>0.0006100891734176534</v>
+        <v>0.0005901455976746036</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>Dark Horse</t>
         </is>
       </c>
       <c r="B401" t="n">
         <v>400</v>
       </c>
       <c r="C401" s="4" t="n">
-        <v>0.0005867752707388206</v>
+        <v>0.0005670043136527975</v>
       </c>
       <c r="U401" s="4" t="n">
-        <v>0.0005867752707388206</v>
+        <v>0.0005670043136527975</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>glava9</t>
+          <t>Студент</t>
         </is>
       </c>
       <c r="B402" s="2" t="n">
         <v>401</v>
       </c>
       <c r="C402" s="3" t="n">
-        <v>0.0005637661468028893</v>
+        <v>0.0005441736743744444</v>
       </c>
       <c r="D402" s="2" t="n"/>
       <c r="E402" s="2" t="n"/>
@@ -11109,37 +10699,35 @@
       <c r="S402" s="2" t="n"/>
       <c r="T402" s="2" t="n"/>
       <c r="U402" s="3" t="n">
-        <v>0.0005637661468028893</v>
+        <v>0.0005441736743744444</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Лука</t>
         </is>
       </c>
       <c r="B403" t="n">
         <v>402</v>
       </c>
       <c r="C403" s="4" t="n">
-        <v>0.0005410658935154241</v>
+        <v>0.0005216579656072174</v>
       </c>
       <c r="U403" s="4" t="n">
-        <v>0.0005410658935154241</v>
+        <v>0.0005216579656072174</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>inteuis</t>
+          <t>over9000mmr</t>
         </is>
       </c>
       <c r="B404" s="2" t="n">
         <v>403</v>
       </c>
-      <c r="C404" s="3" t="n">
-        <v>0.0005186787721680398</v>
-      </c>
+      <c r="C404" s="2" t="n"/>
       <c r="D404" s="2" t="n"/>
       <c r="E404" s="2" t="n"/>
       <c r="F404" s="2" t="n"/>
@@ -11157,14 +10745,12 @@
       <c r="R404" s="2" t="n"/>
       <c r="S404" s="2" t="n"/>
       <c r="T404" s="2" t="n"/>
-      <c r="U404" s="3" t="n">
-        <v>0.0005186787721680398</v>
-      </c>
+      <c r="U404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Марк</t>
+          <t>steyk</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -11174,7 +10760,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>veronesss</t>
+          <t>Milana_Xam</t>
         </is>
       </c>
       <c r="B406" s="2" t="n">
@@ -11203,7 +10789,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Акоп</t>
+          <t>svyatophor</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -11213,7 +10799,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>nik_zverev</t>
+          <t>ns_sh</t>
         </is>
       </c>
       <c r="B408" s="2" t="n">
@@ -11242,7 +10828,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>skr_anton</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -11252,7 +10838,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>kosty_mlg</t>
+          <t>egorzubkovv</t>
         </is>
       </c>
       <c r="B410" s="2" t="n">
@@ -11281,7 +10867,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Me1man77</t>
+          <t>kosty_mlg</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -11320,7 +10906,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Chumba656</t>
+          <t>Pedal9l</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -11330,7 +10916,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>kirp4712</t>
+          <t>ddv</t>
         </is>
       </c>
       <c r="B414" s="2" t="n">
@@ -11359,7 +10945,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Broski</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -11369,7 +10955,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>Zubrilliant</t>
+          <t>Наталья</t>
         </is>
       </c>
       <c r="B416" s="2" t="n">
@@ -11398,7 +10984,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Sokrat_Ab</t>
+          <t>Luter</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -11408,7 +10994,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Dark Horse</t>
+          <t>Kerbi</t>
         </is>
       </c>
       <c r="B418" s="2" t="n">
@@ -11437,7 +11023,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>roman_1_2_3</t>
+          <t>Даша 12 см</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -11447,7 +11033,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>Pedal9l</t>
+          <t>Bereza</t>
         </is>
       </c>
       <c r="B420" s="2" t="n">
@@ -11476,7 +11062,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cation</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -11486,7 +11072,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>JhonyCash</t>
+          <t>Марк</t>
         </is>
       </c>
       <c r="B422" s="2" t="n">
@@ -11515,7 +11101,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Riteral</t>
+          <t>МВика</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -11525,7 +11111,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>WHATSWRONGib</t>
+          <t>Лина</t>
         </is>
       </c>
       <c r="B424" s="2" t="n">
@@ -11554,7 +11140,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Donny</t>
+          <t>t1m</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -11564,7 +11150,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>@lidiasol07</t>
+          <t>maxim_galeev</t>
         </is>
       </c>
       <c r="B426" s="2" t="n">
@@ -11593,7 +11179,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>Artemon</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -11603,7 +11189,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>deps</t>
+          <t>Gluckspilz8</t>
         </is>
       </c>
       <c r="B428" s="2" t="n">
@@ -11632,7 +11218,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>като</t>
+          <t>Nikoshka</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -11642,7 +11228,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Михаил Ю</t>
+          <t>Бандэрос</t>
         </is>
       </c>
       <c r="B430" s="2" t="n">
@@ -11671,7 +11257,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Aleksa</t>
+          <t>kavun_prime</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -11681,7 +11267,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>Cucumberrr</t>
+          <t>Akatones</t>
         </is>
       </c>
       <c r="B432" s="2" t="n">
@@ -11710,7 +11296,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>kavun_prime</t>
+          <t>moodellas</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -11720,7 +11306,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>Лудоман</t>
+          <t>ivolodya</t>
         </is>
       </c>
       <c r="B434" s="2" t="n">
@@ -11749,7 +11335,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ЧЕРЕМША</t>
+          <t>bron</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -11759,7 +11345,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>dnaskila</t>
+          <t>Vitos2049</t>
         </is>
       </c>
       <c r="B436" s="2" t="n">
@@ -11788,44 +11374,15 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>svyatophor</t>
+          <t>Бутербродский</t>
         </is>
       </c>
       <c r="B437" t="n">
         <v>436</v>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" s="2" t="inlineStr">
-        <is>
-          <t>Asakura_Russell</t>
-        </is>
-      </c>
-      <c r="B438" s="2" t="n">
-        <v>437</v>
-      </c>
-      <c r="C438" s="2" t="n"/>
-      <c r="D438" s="2" t="n"/>
-      <c r="E438" s="2" t="n"/>
-      <c r="F438" s="2" t="n"/>
-      <c r="G438" s="2" t="n"/>
-      <c r="H438" s="2" t="n"/>
-      <c r="I438" s="2" t="n"/>
-      <c r="J438" s="2" t="n"/>
-      <c r="K438" s="2" t="n"/>
-      <c r="L438" s="2" t="n"/>
-      <c r="M438" s="2" t="n"/>
-      <c r="N438" s="2" t="n"/>
-      <c r="O438" s="2" t="n"/>
-      <c r="P438" s="2" t="n"/>
-      <c r="Q438" s="2" t="n"/>
-      <c r="R438" s="2" t="n"/>
-      <c r="S438" s="2" t="n"/>
-      <c r="T438" s="2" t="n"/>
-      <c r="U438" s="2" t="n"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C438">
+  <conditionalFormatting sqref="C2:C437">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11837,7 +11394,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:U438">
+  <conditionalFormatting sqref="D2:U437">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11849,7 +11406,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B438">
+  <conditionalFormatting sqref="B2:B437">
     <cfRule type="cellIs" priority="3" operator="lessThanOrEqual" dxfId="0">
       <formula>18</formula>
     </cfRule>
